--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-19 · 전주 2026-09-12</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-25 · 전주 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
+        <v>74000</v>
+      </c>
+      <c r="V3" t="n">
         <v>76000</v>
       </c>
-      <c r="V3" t="n">
-        <v>79400</v>
-      </c>
       <c r="W3" t="n">
-        <v>-4.3</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="4">
@@ -714,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
+        <v>70100</v>
+      </c>
+      <c r="V4" t="n">
         <v>71000</v>
       </c>
-      <c r="V4" t="n">
-        <v>72200</v>
-      </c>
       <c r="W4" t="n">
-        <v>-1.7</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="5">
@@ -753,46 +753,46 @@
         <v>25675</v>
       </c>
       <c r="G5" t="n">
-        <v>25864</v>
+        <v>25675</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>101666</v>
       </c>
       <c r="M5" t="n">
-        <v>102394.2</v>
+        <v>101666</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>111115</v>
       </c>
       <c r="P5" t="n">
-        <v>112935</v>
+        <v>111115</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>120413.3</v>
       </c>
       <c r="S5" t="n">
-        <v>121668</v>
+        <v>120413.3</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
+        <v>116200</v>
+      </c>
+      <c r="V5" t="n">
         <v>121600</v>
       </c>
-      <c r="V5" t="n">
-        <v>126600</v>
-      </c>
       <c r="W5" t="n">
-        <v>-3.9</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="6">
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>95900</v>
+      </c>
+      <c r="V6" t="n">
         <v>93600</v>
       </c>
-      <c r="V6" t="n">
-        <v>90700</v>
-      </c>
       <c r="W6" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -894,49 +894,49 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>780802</v>
+      </c>
+      <c r="G7" t="n">
         <v>781291</v>
       </c>
-      <c r="G7" t="n">
-        <v>783161</v>
-      </c>
       <c r="H7" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="L7" t="n">
+        <v>2651147.8</v>
+      </c>
+      <c r="M7" t="n">
         <v>2649256.6</v>
       </c>
-      <c r="M7" t="n">
-        <v>2652551.8</v>
-      </c>
       <c r="N7" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="O7" t="n">
+        <v>4018225.5</v>
+      </c>
+      <c r="P7" t="n">
         <v>3973945.3</v>
       </c>
-      <c r="P7" t="n">
-        <v>3954884.8</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="R7" t="n">
+        <v>4202122.2</v>
+      </c>
+      <c r="S7" t="n">
         <v>4105474.7</v>
       </c>
-      <c r="S7" t="n">
-        <v>4084823.7</v>
-      </c>
       <c r="T7" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
+        <v>1863000</v>
+      </c>
+      <c r="V7" t="n">
         <v>1849000</v>
       </c>
-      <c r="V7" t="n">
-        <v>1812000</v>
-      </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -966,49 +966,49 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2134</v>
+      </c>
+      <c r="G8" t="n">
         <v>2110</v>
       </c>
-      <c r="G8" t="n">
-        <v>2127</v>
-      </c>
       <c r="H8" t="n">
-        <v>-0.8</v>
+        <v>1.1</v>
       </c>
       <c r="L8" t="n">
+        <v>8658</v>
+      </c>
+      <c r="M8" t="n">
         <v>8672.4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8689.4</v>
       </c>
       <c r="N8" t="n">
         <v>-0.2</v>
       </c>
       <c r="O8" t="n">
+        <v>11338.9</v>
+      </c>
+      <c r="P8" t="n">
         <v>11284.6</v>
       </c>
-      <c r="P8" t="n">
-        <v>11276</v>
-      </c>
       <c r="Q8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="R8" t="n">
+        <v>13770.2</v>
+      </c>
+      <c r="S8" t="n">
         <v>13747.9</v>
       </c>
-      <c r="S8" t="n">
-        <v>13761.8</v>
-      </c>
       <c r="T8" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U8" t="n">
+        <v>122300</v>
+      </c>
+      <c r="V8" t="n">
         <v>125600</v>
       </c>
-      <c r="V8" t="n">
-        <v>134900</v>
-      </c>
       <c r="W8" t="n">
-        <v>-6.9</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="9">
@@ -1041,46 +1041,46 @@
         <v>399</v>
       </c>
       <c r="G9" t="n">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1663.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1649.4</v>
+        <v>1663.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>2255.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2253.9</v>
+        <v>2255.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>2616.9</v>
       </c>
       <c r="S9" t="n">
-        <v>2648.5</v>
+        <v>2616.9</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
+        <v>44700</v>
+      </c>
+      <c r="V9" t="n">
         <v>45150</v>
       </c>
-      <c r="V9" t="n">
-        <v>41450</v>
-      </c>
       <c r="W9" t="n">
-        <v>8.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -1146,13 +1146,13 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
+        <v>5590</v>
+      </c>
+      <c r="V10" t="n">
         <v>5580</v>
       </c>
-      <c r="V10" t="n">
-        <v>5800</v>
-      </c>
       <c r="W10" t="n">
-        <v>-3.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -1185,46 +1185,46 @@
         <v>216</v>
       </c>
       <c r="G11" t="n">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="H11" t="n">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>709</v>
       </c>
       <c r="M11" t="n">
-        <v>750</v>
+        <v>709</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>1068</v>
       </c>
       <c r="P11" t="n">
-        <v>1040</v>
+        <v>1068</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>1246</v>
       </c>
       <c r="S11" t="n">
-        <v>1300</v>
+        <v>1246</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
+        <v>13040</v>
+      </c>
+      <c r="V11" t="n">
         <v>13480</v>
       </c>
-      <c r="V11" t="n">
-        <v>14710</v>
-      </c>
       <c r="W11" t="n">
-        <v>-8.4</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="12">
@@ -1290,13 +1290,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
+        <v>9230</v>
+      </c>
+      <c r="V12" t="n">
         <v>9420</v>
       </c>
-      <c r="V12" t="n">
-        <v>9260</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="13">
@@ -1326,49 +1326,49 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>-12</v>
       </c>
       <c r="G13" t="n">
         <v>43</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-127.9</v>
       </c>
       <c r="L13" t="n">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="M13" t="n">
         <v>173</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-38.2</v>
       </c>
       <c r="O13" t="n">
-        <v>276</v>
+        <v>186</v>
       </c>
       <c r="P13" t="n">
         <v>276</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-32.6</v>
       </c>
       <c r="R13" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="S13" t="n">
         <v>292</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
+        <v>7840</v>
+      </c>
+      <c r="V13" t="n">
         <v>7890</v>
       </c>
-      <c r="V13" t="n">
-        <v>7970</v>
-      </c>
       <c r="W13" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="14">
@@ -1434,13 +1434,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
+        <v>1218000</v>
+      </c>
+      <c r="V14" t="n">
         <v>1296000</v>
       </c>
-      <c r="V14" t="n">
-        <v>1278000</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="15">
@@ -1470,49 +1470,49 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3131</v>
+      </c>
+      <c r="G15" t="n">
         <v>3721</v>
       </c>
-      <c r="G15" t="n">
-        <v>3575</v>
-      </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>-15.9</v>
       </c>
       <c r="L15" t="n">
+        <v>9909.1</v>
+      </c>
+      <c r="M15" t="n">
         <v>11090.7</v>
       </c>
-      <c r="M15" t="n">
-        <v>11003.5</v>
-      </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>-10.7</v>
       </c>
       <c r="O15" t="n">
+        <v>22587.2</v>
+      </c>
+      <c r="P15" t="n">
         <v>22452.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>22243.5</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="R15" t="n">
+        <v>26015.5</v>
+      </c>
+      <c r="S15" t="n">
         <v>25656.8</v>
       </c>
-      <c r="S15" t="n">
-        <v>25781.4</v>
-      </c>
       <c r="T15" t="n">
-        <v>-0.5</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
+        <v>31500</v>
+      </c>
+      <c r="V15" t="n">
         <v>29150</v>
       </c>
-      <c r="V15" t="n">
-        <v>28950</v>
-      </c>
       <c r="W15" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="16">
@@ -1542,49 +1542,49 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>258</v>
+      </c>
+      <c r="G16" t="n">
         <v>264</v>
       </c>
-      <c r="G16" t="n">
-        <v>268</v>
-      </c>
       <c r="H16" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>980.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>989.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1812.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1816.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2824.9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2826.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>180600</v>
+      </c>
+      <c r="V16" t="n">
+        <v>183300</v>
+      </c>
+      <c r="W16" t="n">
         <v>-1.5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>989.6</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1007.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1816.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1814.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2826.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2833.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>183300</v>
-      </c>
-      <c r="V16" t="n">
-        <v>185300</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-1.1</v>
       </c>
     </row>
     <row r="17">
@@ -1614,49 +1614,49 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1199</v>
+        <v>1160</v>
       </c>
       <c r="G17" t="n">
         <v>1199</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="L17" t="n">
-        <v>3680.5</v>
+        <v>3595.2</v>
       </c>
       <c r="M17" t="n">
         <v>3680.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>6744.2</v>
+        <v>6713.6</v>
       </c>
       <c r="P17" t="n">
         <v>6744.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R17" t="n">
-        <v>7811.8</v>
+        <v>7760.2</v>
       </c>
       <c r="S17" t="n">
         <v>7811.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="U17" t="n">
+        <v>32000</v>
+      </c>
+      <c r="V17" t="n">
         <v>35850</v>
       </c>
-      <c r="V17" t="n">
-        <v>33600</v>
-      </c>
       <c r="W17" t="n">
-        <v>6.7</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="18">
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
+        <v>391500</v>
+      </c>
+      <c r="V18" t="n">
         <v>392500</v>
       </c>
-      <c r="V18" t="n">
-        <v>414500</v>
-      </c>
       <c r="W18" t="n">
-        <v>-5.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="19">
@@ -1761,46 +1761,46 @@
         <v>859</v>
       </c>
       <c r="G19" t="n">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>2000.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2000.7</v>
+        <v>2000.6</v>
       </c>
       <c r="N19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>2249.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2256.2</v>
+        <v>2249.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>2422.6</v>
       </c>
       <c r="S19" t="n">
-        <v>2436.6</v>
+        <v>2422.6</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
+        <v>95800</v>
+      </c>
+      <c r="V19" t="n">
         <v>94600</v>
       </c>
-      <c r="V19" t="n">
-        <v>97600</v>
-      </c>
       <c r="W19" t="n">
-        <v>-3.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="20">
@@ -1833,46 +1833,46 @@
         <v>30088</v>
       </c>
       <c r="G20" t="n">
-        <v>30547</v>
+        <v>30088</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>113600.2</v>
       </c>
       <c r="M20" t="n">
-        <v>114487.2</v>
+        <v>113600.2</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>130563</v>
       </c>
       <c r="P20" t="n">
-        <v>132357</v>
+        <v>130563</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>140951.3</v>
       </c>
       <c r="S20" t="n">
-        <v>142401.3</v>
+        <v>140951.3</v>
       </c>
       <c r="T20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
+        <v>357000</v>
+      </c>
+      <c r="V20" t="n">
         <v>366500</v>
       </c>
-      <c r="V20" t="n">
-        <v>382500</v>
-      </c>
       <c r="W20" t="n">
-        <v>-4.2</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="21">
@@ -1938,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
+        <v>311500</v>
+      </c>
+      <c r="V21" t="n">
         <v>325500</v>
       </c>
-      <c r="V21" t="n">
-        <v>334000</v>
-      </c>
       <c r="W21" t="n">
-        <v>-2.5</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="22">
@@ -2010,13 +2010,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
+        <v>48550</v>
+      </c>
+      <c r="V22" t="n">
         <v>50400</v>
       </c>
-      <c r="V22" t="n">
-        <v>52200</v>
-      </c>
       <c r="W22" t="n">
-        <v>-3.4</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="23">
@@ -2046,49 +2046,49 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>1105736</v>
+      </c>
+      <c r="G23" t="n">
         <v>1113772</v>
       </c>
-      <c r="G23" t="n">
-        <v>1131257</v>
-      </c>
       <c r="H23" t="n">
-        <v>-1.5</v>
+        <v>-0.7</v>
       </c>
       <c r="L23" t="n">
+        <v>3876961.8</v>
+      </c>
+      <c r="M23" t="n">
         <v>3877835.9</v>
       </c>
-      <c r="M23" t="n">
-        <v>3912502.7</v>
-      </c>
       <c r="N23" t="n">
-        <v>-0.9</v>
+        <v>-0</v>
       </c>
       <c r="O23" t="n">
+        <v>5626926.8</v>
+      </c>
+      <c r="P23" t="n">
         <v>5547207.7</v>
       </c>
-      <c r="P23" t="n">
-        <v>5531305.9</v>
-      </c>
       <c r="Q23" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="R23" t="n">
+        <v>5747157.9</v>
+      </c>
+      <c r="S23" t="n">
         <v>5562056.8</v>
       </c>
-      <c r="S23" t="n">
-        <v>5516795.7</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
+        <v>286500</v>
+      </c>
+      <c r="V23" t="n">
         <v>260000</v>
       </c>
-      <c r="V23" t="n">
-        <v>259500</v>
-      </c>
       <c r="W23" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="24">
@@ -2121,34 +2121,46 @@
         <v>244</v>
       </c>
       <c r="G24" t="n">
-        <v>312</v>
+        <v>244</v>
       </c>
       <c r="H24" t="n">
-        <v>-21.8</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>807.5</v>
       </c>
       <c r="M24" t="n">
-        <v>932</v>
+        <v>807.5</v>
       </c>
       <c r="N24" t="n">
-        <v>-13.4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>836</v>
       </c>
+      <c r="P24" t="n">
+        <v>836</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
       <c r="R24" t="n">
         <v>1021</v>
       </c>
+      <c r="S24" t="n">
+        <v>1021</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
       <c r="U24" t="n">
+        <v>8470</v>
+      </c>
+      <c r="V24" t="n">
         <v>8670</v>
       </c>
-      <c r="V24" t="n">
-        <v>8240</v>
-      </c>
       <c r="W24" t="n">
-        <v>5.2</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="25">
@@ -2214,13 +2226,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
+        <v>35200</v>
+      </c>
+      <c r="V25" t="n">
         <v>35750</v>
       </c>
-      <c r="V25" t="n">
-        <v>38200</v>
-      </c>
       <c r="W25" t="n">
-        <v>-6.4</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="26">
@@ -2286,13 +2298,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
+        <v>123000</v>
+      </c>
+      <c r="V26" t="n">
         <v>122100</v>
       </c>
-      <c r="V26" t="n">
-        <v>128300</v>
-      </c>
       <c r="W26" t="n">
-        <v>-4.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="27">
@@ -2322,49 +2334,49 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="G27" t="n">
         <v>1204</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L27" t="n">
-        <v>4155.9</v>
+        <v>4127.9</v>
       </c>
       <c r="M27" t="n">
         <v>4155.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O27" t="n">
-        <v>5918.2</v>
+        <v>5925</v>
       </c>
       <c r="P27" t="n">
         <v>5918.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R27" t="n">
-        <v>6944.5</v>
+        <v>6966.9</v>
       </c>
       <c r="S27" t="n">
         <v>6944.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U27" t="n">
+        <v>34750</v>
+      </c>
+      <c r="V27" t="n">
         <v>37200</v>
       </c>
-      <c r="V27" t="n">
-        <v>38500</v>
-      </c>
       <c r="W27" t="n">
-        <v>-3.4</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="28">
@@ -2394,49 +2406,49 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G28" t="n">
         <v>1159</v>
       </c>
-      <c r="G28" t="n">
-        <v>1069</v>
-      </c>
       <c r="H28" t="n">
-        <v>8.4</v>
+        <v>13.7</v>
       </c>
       <c r="L28" t="n">
+        <v>4047.6</v>
+      </c>
+      <c r="M28" t="n">
         <v>3894.8</v>
       </c>
-      <c r="M28" t="n">
-        <v>3855.9</v>
-      </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
+        <v>14513.7</v>
+      </c>
+      <c r="P28" t="n">
         <v>14703.1</v>
       </c>
-      <c r="P28" t="n">
-        <v>14562.5</v>
-      </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>-1.3</v>
       </c>
       <c r="R28" t="n">
+        <v>25000.5</v>
+      </c>
+      <c r="S28" t="n">
         <v>25229.9</v>
       </c>
-      <c r="S28" t="n">
-        <v>24984.1</v>
-      </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>-0.9</v>
       </c>
       <c r="U28" t="n">
+        <v>521000</v>
+      </c>
+      <c r="V28" t="n">
         <v>542000</v>
       </c>
-      <c r="V28" t="n">
-        <v>545000</v>
-      </c>
       <c r="W28" t="n">
-        <v>-0.6</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="29">
@@ -2466,49 +2478,49 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="G29" t="n">
         <v>961</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L29" t="n">
-        <v>3494.6</v>
+        <v>3485.9</v>
       </c>
       <c r="M29" t="n">
         <v>3494.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O29" t="n">
-        <v>5281</v>
+        <v>5293</v>
       </c>
       <c r="P29" t="n">
         <v>5281</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R29" t="n">
-        <v>6436.2</v>
+        <v>6478.2</v>
       </c>
       <c r="S29" t="n">
         <v>6436.2</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U29" t="n">
+        <v>119200</v>
+      </c>
+      <c r="V29" t="n">
         <v>102400</v>
       </c>
-      <c r="V29" t="n">
-        <v>109900</v>
-      </c>
       <c r="W29" t="n">
-        <v>-6.8</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="30">
@@ -2574,13 +2586,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
+        <v>65100</v>
+      </c>
+      <c r="V30" t="n">
         <v>52200</v>
       </c>
-      <c r="V30" t="n">
-        <v>51100</v>
-      </c>
       <c r="W30" t="n">
-        <v>2.2</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="31">
@@ -2610,49 +2622,49 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>6051</v>
+      </c>
+      <c r="G31" t="n">
         <v>6022</v>
       </c>
-      <c r="G31" t="n">
-        <v>5972</v>
-      </c>
       <c r="H31" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L31" t="n">
+        <v>19607.2</v>
+      </c>
+      <c r="M31" t="n">
         <v>19535.4</v>
       </c>
-      <c r="M31" t="n">
-        <v>19468</v>
-      </c>
       <c r="N31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>37661.6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>37499.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>59601</v>
+      </c>
+      <c r="S31" t="n">
+        <v>59438.3</v>
+      </c>
+      <c r="T31" t="n">
         <v>0.3</v>
       </c>
-      <c r="O31" t="n">
-        <v>37499.6</v>
-      </c>
-      <c r="P31" t="n">
-        <v>37320.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>59438.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>58742.2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="U31" t="n">
+        <v>1501000</v>
+      </c>
+      <c r="V31" t="n">
         <v>1388000</v>
       </c>
-      <c r="V31" t="n">
-        <v>1400000</v>
-      </c>
       <c r="W31" t="n">
-        <v>-0.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="32">
@@ -2694,37 +2706,37 @@
         <v>61927.4</v>
       </c>
       <c r="M32" t="n">
-        <v>61584.5</v>
+        <v>61927.4</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>73808.2</v>
       </c>
       <c r="P32" t="n">
-        <v>73629.8</v>
+        <v>73808.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>84712.8</v>
       </c>
       <c r="S32" t="n">
-        <v>84285.2</v>
+        <v>84712.8</v>
       </c>
       <c r="T32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>335000</v>
+      </c>
+      <c r="V32" t="n">
         <v>340000</v>
       </c>
-      <c r="V32" t="n">
-        <v>365500</v>
-      </c>
       <c r="W32" t="n">
-        <v>-7</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="33">
@@ -2790,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
+        <v>207000</v>
+      </c>
+      <c r="V33" t="n">
         <v>208500</v>
       </c>
-      <c r="V33" t="n">
-        <v>204500</v>
-      </c>
       <c r="W33" t="n">
-        <v>2</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="34">
@@ -2862,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>1116000</v>
+      </c>
+      <c r="V34" t="n">
         <v>1132000</v>
       </c>
-      <c r="V34" t="n">
-        <v>1179000</v>
-      </c>
       <c r="W34" t="n">
-        <v>-4</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="35">
@@ -2901,46 +2913,46 @@
         <v>3463</v>
       </c>
       <c r="G35" t="n">
-        <v>3512</v>
+        <v>3463</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>13686.4</v>
       </c>
       <c r="M35" t="n">
-        <v>13813.9</v>
+        <v>13686.4</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>19754.7</v>
       </c>
       <c r="P35" t="n">
-        <v>19722.5</v>
+        <v>19754.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>23538.2</v>
       </c>
       <c r="S35" t="n">
-        <v>23460.8</v>
+        <v>23538.2</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
+        <v>20450</v>
+      </c>
+      <c r="V35" t="n">
         <v>21050</v>
       </c>
-      <c r="V35" t="n">
-        <v>21400</v>
-      </c>
       <c r="W35" t="n">
-        <v>-1.6</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="36">
@@ -2973,46 +2985,46 @@
         <v>223</v>
       </c>
       <c r="G36" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="H36" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>1560.5</v>
       </c>
       <c r="M36" t="n">
-        <v>1514.3</v>
+        <v>1560.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>1701</v>
       </c>
       <c r="P36" t="n">
-        <v>1717</v>
+        <v>1701</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>3059.2</v>
       </c>
       <c r="S36" t="n">
-        <v>3072</v>
+        <v>3059.2</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
+        <v>15050</v>
+      </c>
+      <c r="V36" t="n">
         <v>15500</v>
       </c>
-      <c r="V36" t="n">
-        <v>15770</v>
-      </c>
       <c r="W36" t="n">
-        <v>-1.7</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="37">
@@ -3042,49 +3054,49 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3112</v>
+        <v>3020</v>
       </c>
       <c r="G37" t="n">
         <v>3112</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L37" t="n">
-        <v>12757.3</v>
+        <v>12656.9</v>
       </c>
       <c r="M37" t="n">
         <v>12757.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="O37" t="n">
-        <v>14683.3</v>
+        <v>14594.1</v>
       </c>
       <c r="P37" t="n">
         <v>14683.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="R37" t="n">
-        <v>17479.8</v>
+        <v>17346.3</v>
       </c>
       <c r="S37" t="n">
         <v>17479.8</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="U37" t="n">
+        <v>536000</v>
+      </c>
+      <c r="V37" t="n">
         <v>531000</v>
       </c>
-      <c r="V37" t="n">
-        <v>543000</v>
-      </c>
       <c r="W37" t="n">
-        <v>-2.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -3117,46 +3129,46 @@
         <v>6036</v>
       </c>
       <c r="G38" t="n">
-        <v>6015</v>
+        <v>6036</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>16185.7</v>
       </c>
       <c r="M38" t="n">
-        <v>16138.8</v>
+        <v>16185.7</v>
       </c>
       <c r="N38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>10474.8</v>
       </c>
       <c r="P38" t="n">
-        <v>10364.8</v>
+        <v>10474.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>8921.9</v>
       </c>
       <c r="S38" t="n">
-        <v>8811.9</v>
+        <v>8921.9</v>
       </c>
       <c r="T38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
+        <v>20850</v>
+      </c>
+      <c r="V38" t="n">
         <v>20950</v>
       </c>
-      <c r="V38" t="n">
-        <v>20850</v>
-      </c>
       <c r="W38" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="39">
@@ -3198,37 +3210,37 @@
         <v>2195.2</v>
       </c>
       <c r="M39" t="n">
-        <v>2187.5</v>
+        <v>2195.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>2670.3</v>
       </c>
       <c r="P39" t="n">
-        <v>2666.6</v>
+        <v>2670.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>2989.7</v>
       </c>
       <c r="S39" t="n">
-        <v>2987</v>
+        <v>2989.7</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
+        <v>52500</v>
+      </c>
+      <c r="V39" t="n">
         <v>54700</v>
       </c>
-      <c r="V39" t="n">
-        <v>57400</v>
-      </c>
       <c r="W39" t="n">
-        <v>-4.7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="40">
@@ -3294,13 +3306,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
+        <v>17060</v>
+      </c>
+      <c r="V40" t="n">
         <v>16960</v>
       </c>
-      <c r="V40" t="n">
-        <v>16180</v>
-      </c>
       <c r="W40" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="41">
@@ -3333,46 +3345,46 @@
         <v>9593</v>
       </c>
       <c r="G41" t="n">
-        <v>9620</v>
+        <v>9593</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>37773</v>
       </c>
       <c r="M41" t="n">
-        <v>37881.4</v>
+        <v>37773</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>42321.6</v>
       </c>
       <c r="P41" t="n">
-        <v>42546.7</v>
+        <v>42321.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>46083.6</v>
       </c>
       <c r="S41" t="n">
-        <v>46080.3</v>
+        <v>46083.6</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
+        <v>369000</v>
+      </c>
+      <c r="V41" t="n">
         <v>380500</v>
       </c>
-      <c r="V41" t="n">
-        <v>415500</v>
-      </c>
       <c r="W41" t="n">
-        <v>-8.4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="42">
@@ -3405,46 +3417,46 @@
         <v>12383</v>
       </c>
       <c r="G42" t="n">
-        <v>12426</v>
+        <v>12383</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>46453.9</v>
       </c>
       <c r="M42" t="n">
-        <v>46495.8</v>
+        <v>46453.9</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>57056.4</v>
       </c>
       <c r="P42" t="n">
-        <v>57204.4</v>
+        <v>57056.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>63529.5</v>
       </c>
       <c r="S42" t="n">
-        <v>63569.3</v>
+        <v>63529.5</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
+        <v>1031000</v>
+      </c>
+      <c r="V42" t="n">
         <v>1092000</v>
       </c>
-      <c r="V42" t="n">
-        <v>1081000</v>
-      </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="43">
@@ -3477,46 +3489,46 @@
         <v>142</v>
       </c>
       <c r="G43" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>488</v>
       </c>
       <c r="M43" t="n">
-        <v>478.7</v>
+        <v>488</v>
       </c>
       <c r="N43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>701.5</v>
       </c>
       <c r="P43" t="n">
-        <v>661</v>
+        <v>701.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>831</v>
       </c>
       <c r="S43" t="n">
-        <v>733.7</v>
+        <v>831</v>
       </c>
       <c r="T43" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
+        <v>31050</v>
+      </c>
+      <c r="V43" t="n">
         <v>32300</v>
       </c>
-      <c r="V43" t="n">
-        <v>34300</v>
-      </c>
       <c r="W43" t="n">
-        <v>-5.8</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="44">
@@ -3549,46 +3561,46 @@
         <v>525</v>
       </c>
       <c r="G44" t="n">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>1805.2</v>
       </c>
       <c r="M44" t="n">
-        <v>1822.5</v>
+        <v>1805.2</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>2276.3</v>
       </c>
       <c r="P44" t="n">
-        <v>2257.2</v>
+        <v>2276.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>2956</v>
       </c>
       <c r="S44" t="n">
-        <v>2946</v>
+        <v>2956</v>
       </c>
       <c r="T44" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
+        <v>238000</v>
+      </c>
+      <c r="V44" t="n">
         <v>215000</v>
       </c>
-      <c r="V44" t="n">
-        <v>200000</v>
-      </c>
       <c r="W44" t="n">
-        <v>7.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="45">
@@ -3621,40 +3633,46 @@
         <v>340</v>
       </c>
       <c r="G45" t="n">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="H45" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>1180</v>
       </c>
       <c r="M45" t="n">
-        <v>990</v>
+        <v>1180</v>
       </c>
       <c r="N45" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>1570</v>
       </c>
       <c r="P45" t="n">
-        <v>1360</v>
+        <v>1570</v>
       </c>
       <c r="Q45" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>1770</v>
       </c>
+      <c r="S45" t="n">
+        <v>1770</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
       <c r="U45" t="n">
+        <v>2475</v>
+      </c>
+      <c r="V45" t="n">
         <v>2505</v>
       </c>
-      <c r="V45" t="n">
-        <v>2530</v>
-      </c>
       <c r="W45" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="46">
@@ -3693,40 +3711,40 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>19601.2</v>
+        <v>19596.6</v>
       </c>
       <c r="M46" t="n">
         <v>19601.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O46" t="n">
-        <v>20848.2</v>
+        <v>20873.8</v>
       </c>
       <c r="P46" t="n">
         <v>20848.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R46" t="n">
-        <v>22035.6</v>
+        <v>22118.1</v>
       </c>
       <c r="S46" t="n">
         <v>22035.6</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U46" t="n">
+        <v>87000</v>
+      </c>
+      <c r="V46" t="n">
         <v>89100</v>
       </c>
-      <c r="V46" t="n">
-        <v>90900</v>
-      </c>
       <c r="W46" t="n">
-        <v>-2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="47">
@@ -3759,46 +3777,46 @@
         <v>440</v>
       </c>
       <c r="G47" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>1832.2</v>
       </c>
       <c r="M47" t="n">
-        <v>1816.8</v>
+        <v>1832.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>1988.5</v>
       </c>
       <c r="P47" t="n">
-        <v>1989.4</v>
+        <v>1988.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>2195</v>
       </c>
       <c r="S47" t="n">
-        <v>2167.7</v>
+        <v>2195</v>
       </c>
       <c r="T47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
+        <v>20350</v>
+      </c>
+      <c r="V47" t="n">
         <v>21050</v>
       </c>
-      <c r="V47" t="n">
-        <v>21700</v>
-      </c>
       <c r="W47" t="n">
-        <v>-3</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="48">
@@ -3849,28 +3867,28 @@
         <v>10685.7</v>
       </c>
       <c r="P48" t="n">
-        <v>10686.6</v>
+        <v>10685.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>11870.6</v>
       </c>
       <c r="S48" t="n">
-        <v>11809.9</v>
+        <v>11870.6</v>
       </c>
       <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>221000</v>
+      </c>
+      <c r="V48" t="n">
+        <v>220000</v>
+      </c>
+      <c r="W48" t="n">
         <v>0.5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>220000</v>
-      </c>
-      <c r="V48" t="n">
-        <v>222500</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-1.1</v>
       </c>
     </row>
     <row r="49">
@@ -3936,13 +3954,13 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
+        <v>3245</v>
+      </c>
+      <c r="V49" t="n">
         <v>3450</v>
       </c>
-      <c r="V49" t="n">
-        <v>3520</v>
-      </c>
       <c r="W49" t="n">
-        <v>-2</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="50">
@@ -3975,46 +3993,46 @@
         <v>84</v>
       </c>
       <c r="G50" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H50" t="n">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>452.5</v>
       </c>
       <c r="M50" t="n">
-        <v>461.7</v>
+        <v>452.5</v>
       </c>
       <c r="N50" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>890.5</v>
       </c>
       <c r="P50" t="n">
-        <v>790.3</v>
+        <v>890.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>766</v>
       </c>
       <c r="S50" t="n">
-        <v>732</v>
+        <v>766</v>
       </c>
       <c r="T50" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
+        <v>26600</v>
+      </c>
+      <c r="V50" t="n">
         <v>26550</v>
       </c>
-      <c r="V50" t="n">
-        <v>28300</v>
-      </c>
       <c r="W50" t="n">
-        <v>-6.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
@@ -4044,49 +4062,49 @@
         </is>
       </c>
       <c r="F51" t="n">
+        <v>2479</v>
+      </c>
+      <c r="G51" t="n">
         <v>2496</v>
       </c>
-      <c r="G51" t="n">
-        <v>2490</v>
-      </c>
       <c r="H51" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="L51" t="n">
+        <v>9821.6</v>
+      </c>
+      <c r="M51" t="n">
         <v>9823.799999999999</v>
       </c>
-      <c r="M51" t="n">
-        <v>9821.4</v>
-      </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O51" t="n">
+        <v>11913.2</v>
+      </c>
+      <c r="P51" t="n">
         <v>11926.9</v>
       </c>
-      <c r="P51" t="n">
-        <v>11916.4</v>
-      </c>
       <c r="Q51" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="R51" t="n">
+        <v>13226.6</v>
+      </c>
+      <c r="S51" t="n">
         <v>13253.2</v>
       </c>
-      <c r="S51" t="n">
-        <v>13245.8</v>
-      </c>
       <c r="T51" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="U51" t="n">
+        <v>49600</v>
+      </c>
+      <c r="V51" t="n">
         <v>52100</v>
       </c>
-      <c r="V51" t="n">
-        <v>51000</v>
-      </c>
       <c r="W51" t="n">
-        <v>2.2</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="52">
@@ -4116,49 +4134,49 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>10206</v>
+        <v>9984</v>
       </c>
       <c r="G52" t="n">
         <v>10206</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="L52" t="n">
-        <v>38109</v>
+        <v>37961.1</v>
       </c>
       <c r="M52" t="n">
         <v>38109</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O52" t="n">
-        <v>44037.3</v>
+        <v>44118.2</v>
       </c>
       <c r="P52" t="n">
         <v>44037.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R52" t="n">
-        <v>47717.2</v>
+        <v>47921.2</v>
       </c>
       <c r="S52" t="n">
         <v>47717.2</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U52" t="n">
+        <v>368500</v>
+      </c>
+      <c r="V52" t="n">
         <v>353500</v>
       </c>
-      <c r="V52" t="n">
-        <v>367000</v>
-      </c>
       <c r="W52" t="n">
-        <v>-3.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="53">
@@ -4191,46 +4209,46 @@
         <v>1775</v>
       </c>
       <c r="G53" t="n">
-        <v>1768</v>
+        <v>1775</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>6772.1</v>
       </c>
       <c r="M53" t="n">
-        <v>6763</v>
+        <v>6772.1</v>
       </c>
       <c r="N53" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>6826.6</v>
       </c>
       <c r="P53" t="n">
-        <v>6810.9</v>
+        <v>6826.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>6990.1</v>
       </c>
       <c r="S53" t="n">
-        <v>6990.8</v>
+        <v>6990.1</v>
       </c>
       <c r="T53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>5610</v>
+      </c>
+      <c r="V53" t="n">
         <v>5770</v>
       </c>
-      <c r="V53" t="n">
-        <v>6030</v>
-      </c>
       <c r="W53" t="n">
-        <v>-4.3</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="54">
@@ -4296,13 +4314,13 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
+        <v>52900</v>
+      </c>
+      <c r="V54" t="n">
         <v>53200</v>
       </c>
-      <c r="V54" t="n">
-        <v>52700</v>
-      </c>
       <c r="W54" t="n">
-        <v>0.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="55">
@@ -4332,22 +4350,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="G55" t="n">
         <v>633</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="U55" t="n">
         <v>11730</v>
       </c>
       <c r="V55" t="n">
-        <v>12050</v>
+        <v>11730</v>
       </c>
       <c r="W55" t="n">
-        <v>-2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4395,31 +4413,31 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>12333.2</v>
+        <v>12363.7</v>
       </c>
       <c r="P56" t="n">
         <v>12333.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R56" t="n">
+        <v>13190.7</v>
+      </c>
+      <c r="S56" t="n">
         <v>13167.9</v>
       </c>
-      <c r="S56" t="n">
-        <v>13168.1</v>
-      </c>
       <c r="T56" t="n">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="U56" t="n">
+        <v>14630</v>
+      </c>
+      <c r="V56" t="n">
         <v>14190</v>
       </c>
-      <c r="V56" t="n">
-        <v>14890</v>
-      </c>
       <c r="W56" t="n">
-        <v>-4.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="57">
@@ -4485,13 +4503,13 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
+        <v>16050</v>
+      </c>
+      <c r="V57" t="n">
         <v>16640</v>
       </c>
-      <c r="V57" t="n">
-        <v>16790</v>
-      </c>
       <c r="W57" t="n">
-        <v>-0.9</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="58">
@@ -4521,49 +4539,49 @@
         </is>
       </c>
       <c r="F58" t="n">
+        <v>4931</v>
+      </c>
+      <c r="G58" t="n">
         <v>4922</v>
       </c>
-      <c r="G58" t="n">
-        <v>4928</v>
-      </c>
       <c r="H58" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L58" t="n">
+        <v>15332.9</v>
+      </c>
+      <c r="M58" t="n">
         <v>15314.2</v>
       </c>
-      <c r="M58" t="n">
-        <v>15328.5</v>
-      </c>
       <c r="N58" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="O58" t="n">
+        <v>16550.9</v>
+      </c>
+      <c r="P58" t="n">
         <v>16540.5</v>
       </c>
-      <c r="P58" t="n">
-        <v>16544.1</v>
-      </c>
       <c r="Q58" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="R58" t="n">
+        <v>17566.9</v>
+      </c>
+      <c r="S58" t="n">
         <v>17477</v>
       </c>
-      <c r="S58" t="n">
-        <v>17467</v>
-      </c>
       <c r="T58" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="U58" t="n">
+        <v>174500</v>
+      </c>
+      <c r="V58" t="n">
         <v>172800</v>
       </c>
-      <c r="V58" t="n">
-        <v>171800</v>
-      </c>
       <c r="W58" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -4629,13 +4647,13 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
+        <v>9550</v>
+      </c>
+      <c r="V59" t="n">
         <v>9670</v>
       </c>
-      <c r="V59" t="n">
-        <v>9930</v>
-      </c>
       <c r="W59" t="n">
-        <v>-2.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="60">
@@ -4668,46 +4686,46 @@
         <v>636</v>
       </c>
       <c r="G60" t="n">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.8</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>2130</v>
       </c>
       <c r="M60" t="n">
-        <v>2191.8</v>
+        <v>2130</v>
       </c>
       <c r="N60" t="n">
-        <v>-2.8</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>2075.8</v>
       </c>
       <c r="P60" t="n">
-        <v>2140.4</v>
+        <v>2075.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>2706.3</v>
       </c>
       <c r="S60" t="n">
-        <v>2715</v>
+        <v>2706.3</v>
       </c>
       <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>14380</v>
+      </c>
+      <c r="V60" t="n">
+        <v>14420</v>
+      </c>
+      <c r="W60" t="n">
         <v>-0.3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>14420</v>
-      </c>
-      <c r="V60" t="n">
-        <v>14800</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-2.6</v>
       </c>
     </row>
     <row r="61">
@@ -4737,49 +4755,49 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5547</v>
+        <v>5545</v>
       </c>
       <c r="G61" t="n">
         <v>5547</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L61" t="n">
-        <v>21970.3</v>
+        <v>21960.1</v>
       </c>
       <c r="M61" t="n">
         <v>21970.3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O61" t="n">
+        <v>25760.5</v>
+      </c>
+      <c r="P61" t="n">
         <v>25735.9</v>
       </c>
-      <c r="P61" t="n">
-        <v>25750.7</v>
-      </c>
       <c r="Q61" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="R61" t="n">
+        <v>30497</v>
+      </c>
+      <c r="S61" t="n">
         <v>30005.9</v>
       </c>
-      <c r="S61" t="n">
-        <v>30073.8</v>
-      </c>
       <c r="T61" t="n">
-        <v>-0.2</v>
+        <v>1.6</v>
       </c>
       <c r="U61" t="n">
+        <v>196000</v>
+      </c>
+      <c r="V61" t="n">
         <v>197500</v>
       </c>
-      <c r="V61" t="n">
-        <v>206500</v>
-      </c>
       <c r="W61" t="n">
-        <v>-4.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="62">
@@ -4809,49 +4827,49 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2660</v>
+        <v>2655</v>
       </c>
       <c r="G62" t="n">
         <v>2660</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L62" t="n">
-        <v>10366.6</v>
+        <v>10362.8</v>
       </c>
       <c r="M62" t="n">
         <v>10366.6</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O62" t="n">
-        <v>11835.5</v>
+        <v>11826.7</v>
       </c>
       <c r="P62" t="n">
         <v>11835.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R62" t="n">
-        <v>13471</v>
+        <v>13513.3</v>
       </c>
       <c r="S62" t="n">
         <v>13471</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U62" t="n">
+        <v>33800</v>
+      </c>
+      <c r="V62" t="n">
         <v>33600</v>
       </c>
-      <c r="V62" t="n">
-        <v>34500</v>
-      </c>
       <c r="W62" t="n">
-        <v>-2.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="63">
@@ -4917,13 +4935,13 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
+        <v>38900</v>
+      </c>
+      <c r="V63" t="n">
         <v>36600</v>
       </c>
-      <c r="V63" t="n">
-        <v>35000</v>
-      </c>
       <c r="W63" t="n">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="64">
@@ -4962,40 +4980,40 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
+        <v>1518.3</v>
+      </c>
+      <c r="M64" t="n">
         <v>1518.2</v>
       </c>
-      <c r="M64" t="n">
-        <v>1524.1</v>
-      </c>
       <c r="N64" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
+        <v>1675.8</v>
+      </c>
+      <c r="P64" t="n">
         <v>1674.3</v>
       </c>
-      <c r="P64" t="n">
-        <v>1670.9</v>
-      </c>
       <c r="Q64" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="R64" t="n">
+        <v>1685.5</v>
+      </c>
+      <c r="S64" t="n">
         <v>1683</v>
       </c>
-      <c r="S64" t="n">
-        <v>1678</v>
-      </c>
       <c r="T64" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="U64" t="n">
+        <v>37800</v>
+      </c>
+      <c r="V64" t="n">
         <v>38700</v>
       </c>
-      <c r="V64" t="n">
-        <v>39350</v>
-      </c>
       <c r="W64" t="n">
-        <v>-1.7</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="65">
@@ -5061,13 +5079,13 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>9560</v>
+      </c>
+      <c r="V65" t="n">
         <v>9110</v>
       </c>
-      <c r="V65" t="n">
-        <v>9010</v>
-      </c>
       <c r="W65" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="66">
@@ -5097,49 +5115,49 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="G66" t="n">
         <v>888</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L66" t="n">
+        <v>5227.9</v>
+      </c>
+      <c r="M66" t="n">
         <v>5227.6</v>
       </c>
-      <c r="M66" t="n">
-        <v>5227.7</v>
-      </c>
       <c r="N66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>5966.9</v>
+        <v>5901.3</v>
       </c>
       <c r="P66" t="n">
         <v>5966.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="R66" t="n">
-        <v>6073.5</v>
+        <v>6046.4</v>
       </c>
       <c r="S66" t="n">
         <v>6073.5</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="U66" t="n">
+        <v>213500</v>
+      </c>
+      <c r="V66" t="n">
         <v>209000</v>
       </c>
-      <c r="V66" t="n">
-        <v>205500</v>
-      </c>
       <c r="W66" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="67">
@@ -5205,13 +5223,13 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
+        <v>209500</v>
+      </c>
+      <c r="V67" t="n">
         <v>204500</v>
       </c>
-      <c r="V67" t="n">
-        <v>209000</v>
-      </c>
       <c r="W67" t="n">
-        <v>-2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="68">
@@ -5244,46 +5262,46 @@
         <v>85</v>
       </c>
       <c r="G68" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H68" t="n">
-        <v>-12.4</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>500.2</v>
       </c>
       <c r="M68" t="n">
-        <v>507.8</v>
+        <v>500.2</v>
       </c>
       <c r="N68" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>640.5</v>
       </c>
       <c r="P68" t="n">
-        <v>651.2</v>
+        <v>640.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>712.2</v>
       </c>
       <c r="S68" t="n">
-        <v>723.5</v>
+        <v>712.2</v>
       </c>
       <c r="T68" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
+        <v>30500</v>
+      </c>
+      <c r="V68" t="n">
         <v>30700</v>
       </c>
-      <c r="V68" t="n">
-        <v>33250</v>
-      </c>
       <c r="W68" t="n">
-        <v>-7.7</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="69">
@@ -5316,46 +5334,46 @@
         <v>48</v>
       </c>
       <c r="G69" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H69" t="n">
-        <v>-21.3</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>211</v>
       </c>
       <c r="M69" t="n">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="N69" t="n">
-        <v>-7.9</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>264</v>
       </c>
       <c r="P69" t="n">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="Q69" t="n">
-        <v>-10.8</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>320</v>
       </c>
       <c r="S69" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="T69" t="n">
-        <v>-8.6</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>9440</v>
+      </c>
+      <c r="V69" t="n">
         <v>9950</v>
       </c>
-      <c r="V69" t="n">
-        <v>11110</v>
-      </c>
       <c r="W69" t="n">
-        <v>-10.4</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="70">
@@ -5388,46 +5406,46 @@
         <v>397</v>
       </c>
       <c r="G70" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
+        <v>1878.2</v>
+      </c>
+      <c r="M70" t="n">
         <v>1878.6</v>
       </c>
-      <c r="M70" t="n">
-        <v>1880.7</v>
-      </c>
       <c r="N70" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="O70" t="n">
+        <v>2160.7</v>
+      </c>
+      <c r="P70" t="n">
         <v>2163.2</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2165.7</v>
       </c>
       <c r="Q70" t="n">
         <v>-0.1</v>
       </c>
       <c r="R70" t="n">
+        <v>2410.6</v>
+      </c>
+      <c r="S70" t="n">
         <v>2413.1</v>
       </c>
-      <c r="S70" t="n">
-        <v>2422.5</v>
-      </c>
       <c r="T70" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="U70" t="n">
+        <v>82800</v>
+      </c>
+      <c r="V70" t="n">
         <v>81600</v>
       </c>
-      <c r="V70" t="n">
-        <v>84000</v>
-      </c>
       <c r="W70" t="n">
-        <v>-2.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="71">
@@ -5457,49 +5475,49 @@
         </is>
       </c>
       <c r="F71" t="n">
+        <v>5715</v>
+      </c>
+      <c r="G71" t="n">
         <v>5682</v>
       </c>
-      <c r="G71" t="n">
-        <v>5701</v>
-      </c>
       <c r="H71" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="L71" t="n">
+        <v>22538.5</v>
+      </c>
+      <c r="M71" t="n">
         <v>22486.1</v>
       </c>
-      <c r="M71" t="n">
-        <v>22521.4</v>
-      </c>
       <c r="N71" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="O71" t="n">
+        <v>24962.3</v>
+      </c>
+      <c r="P71" t="n">
         <v>24957</v>
       </c>
-      <c r="P71" t="n">
-        <v>25152.4</v>
-      </c>
       <c r="Q71" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
+        <v>28431.9</v>
+      </c>
+      <c r="S71" t="n">
         <v>28407.4</v>
       </c>
-      <c r="S71" t="n">
-        <v>28582</v>
-      </c>
       <c r="T71" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="U71" t="n">
+        <v>80700</v>
+      </c>
+      <c r="V71" t="n">
         <v>83500</v>
       </c>
-      <c r="V71" t="n">
-        <v>85600</v>
-      </c>
       <c r="W71" t="n">
-        <v>-2.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="72">
@@ -5529,25 +5547,25 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1639</v>
+        <v>1651</v>
       </c>
       <c r="G72" t="n">
         <v>1639</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L72" t="n">
-        <v>8269.299999999999</v>
+        <v>8288.4</v>
       </c>
       <c r="M72" t="n">
         <v>8269.299999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O72" t="n">
-        <v>8120.3</v>
+        <v>8123.3</v>
       </c>
       <c r="P72" t="n">
         <v>8120.3</v>
@@ -5556,22 +5574,22 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>9066.200000000001</v>
+        <v>9084.200000000001</v>
       </c>
       <c r="S72" t="n">
         <v>9066.200000000001</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U72" t="n">
+        <v>17700</v>
+      </c>
+      <c r="V72" t="n">
         <v>19020</v>
       </c>
-      <c r="V72" t="n">
-        <v>19890</v>
-      </c>
       <c r="W72" t="n">
-        <v>-4.4</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="73">
@@ -5601,49 +5619,49 @@
         </is>
       </c>
       <c r="F73" t="n">
+        <v>3761</v>
+      </c>
+      <c r="G73" t="n">
         <v>3769</v>
       </c>
-      <c r="G73" t="n">
-        <v>3754</v>
-      </c>
       <c r="H73" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="L73" t="n">
+        <v>14749.1</v>
+      </c>
+      <c r="M73" t="n">
         <v>14729</v>
       </c>
-      <c r="M73" t="n">
-        <v>14652.1</v>
-      </c>
       <c r="N73" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O73" t="n">
+        <v>15595.9</v>
+      </c>
+      <c r="P73" t="n">
         <v>15589.4</v>
       </c>
-      <c r="P73" t="n">
-        <v>15480.2</v>
-      </c>
       <c r="Q73" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
+        <v>16432.3</v>
+      </c>
+      <c r="S73" t="n">
         <v>16455</v>
       </c>
-      <c r="S73" t="n">
-        <v>16311.2</v>
-      </c>
       <c r="T73" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="U73" t="n">
+        <v>55500</v>
+      </c>
+      <c r="V73" t="n">
         <v>57100</v>
       </c>
-      <c r="V73" t="n">
-        <v>57700</v>
-      </c>
       <c r="W73" t="n">
-        <v>-1</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="74">
@@ -5673,49 +5691,49 @@
         </is>
       </c>
       <c r="F74" t="n">
+        <v>837</v>
+      </c>
+      <c r="G74" t="n">
         <v>864</v>
       </c>
-      <c r="G74" t="n">
-        <v>872</v>
-      </c>
       <c r="H74" t="n">
-        <v>-0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="L74" t="n">
+        <v>3447.1</v>
+      </c>
+      <c r="M74" t="n">
         <v>3523.1</v>
       </c>
-      <c r="M74" t="n">
-        <v>3570.2</v>
-      </c>
       <c r="N74" t="n">
-        <v>-1.3</v>
+        <v>-2.2</v>
       </c>
       <c r="O74" t="n">
+        <v>5815.2</v>
+      </c>
+      <c r="P74" t="n">
         <v>5845.5</v>
       </c>
-      <c r="P74" t="n">
-        <v>5910.3</v>
-      </c>
       <c r="Q74" t="n">
-        <v>-1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="R74" t="n">
+        <v>7331</v>
+      </c>
+      <c r="S74" t="n">
         <v>7390.6</v>
       </c>
-      <c r="S74" t="n">
-        <v>7433.4</v>
-      </c>
       <c r="T74" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="U74" t="n">
+        <v>128400</v>
+      </c>
+      <c r="V74" t="n">
         <v>130200</v>
       </c>
-      <c r="V74" t="n">
-        <v>130500</v>
-      </c>
       <c r="W74" t="n">
-        <v>-0.2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="75">
@@ -5781,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
+        <v>21700</v>
+      </c>
+      <c r="V75" t="n">
         <v>21950</v>
       </c>
-      <c r="V75" t="n">
-        <v>22850</v>
-      </c>
       <c r="W75" t="n">
-        <v>-3.9</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="76">
@@ -5853,13 +5871,13 @@
         <v>0</v>
       </c>
       <c r="U76" t="n">
+        <v>100900</v>
+      </c>
+      <c r="V76" t="n">
         <v>99100</v>
       </c>
-      <c r="V76" t="n">
-        <v>96800</v>
-      </c>
       <c r="W76" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="77">
@@ -5916,13 +5934,13 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
+        <v>38850</v>
+      </c>
+      <c r="V77" t="n">
         <v>39950</v>
       </c>
-      <c r="V77" t="n">
-        <v>39900</v>
-      </c>
       <c r="W77" t="n">
-        <v>0.1</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="78">
@@ -5955,46 +5973,46 @@
         <v>2894</v>
       </c>
       <c r="G78" t="n">
-        <v>2899</v>
+        <v>2894</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>10808.2</v>
       </c>
       <c r="M78" t="n">
-        <v>10828.8</v>
+        <v>10808.2</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>13191.1</v>
       </c>
       <c r="P78" t="n">
-        <v>13178.4</v>
+        <v>13191.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>16463.6</v>
       </c>
       <c r="S78" t="n">
-        <v>16499.1</v>
+        <v>16463.6</v>
       </c>
       <c r="T78" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
+        <v>116700</v>
+      </c>
+      <c r="V78" t="n">
         <v>123500</v>
       </c>
-      <c r="V78" t="n">
-        <v>124100</v>
-      </c>
       <c r="W78" t="n">
-        <v>-0.5</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="79">
@@ -6060,13 +6078,13 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
+        <v>25700</v>
+      </c>
+      <c r="V79" t="n">
         <v>26100</v>
       </c>
-      <c r="V79" t="n">
-        <v>26850</v>
-      </c>
       <c r="W79" t="n">
-        <v>-2.8</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="80">
@@ -6132,13 +6150,13 @@
         <v>0</v>
       </c>
       <c r="U80" t="n">
+        <v>210500</v>
+      </c>
+      <c r="V80" t="n">
         <v>198700</v>
       </c>
-      <c r="V80" t="n">
-        <v>199500</v>
-      </c>
       <c r="W80" t="n">
-        <v>-0.4</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="81">
@@ -6171,46 +6189,46 @@
         <v>277</v>
       </c>
       <c r="G81" t="n">
-        <v>340</v>
+        <v>277</v>
       </c>
       <c r="H81" t="n">
-        <v>-18.5</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>2055.9</v>
       </c>
       <c r="M81" t="n">
-        <v>2153</v>
+        <v>2055.9</v>
       </c>
       <c r="N81" t="n">
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>2370.9</v>
       </c>
       <c r="P81" t="n">
-        <v>2383</v>
+        <v>2370.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>3217.6</v>
       </c>
       <c r="S81" t="n">
-        <v>3188.9</v>
+        <v>3217.6</v>
       </c>
       <c r="T81" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
+        <v>109500</v>
+      </c>
+      <c r="V81" t="n">
         <v>110500</v>
       </c>
-      <c r="V81" t="n">
-        <v>120000</v>
-      </c>
       <c r="W81" t="n">
-        <v>-7.9</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="82">
@@ -6276,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
+        <v>36600</v>
+      </c>
+      <c r="V82" t="n">
         <v>37000</v>
       </c>
-      <c r="V82" t="n">
-        <v>37100</v>
-      </c>
       <c r="W82" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="83">
@@ -6315,7 +6333,7 @@
         <v>5090</v>
       </c>
       <c r="G83" t="n">
-        <v>5089</v>
+        <v>5090</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -6324,37 +6342,37 @@
         <v>18569.9</v>
       </c>
       <c r="M83" t="n">
-        <v>18550.2</v>
+        <v>18569.9</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>22905.7</v>
       </c>
       <c r="P83" t="n">
-        <v>22666.6</v>
+        <v>22905.7</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>25840.6</v>
       </c>
       <c r="S83" t="n">
-        <v>25636.6</v>
+        <v>25840.6</v>
       </c>
       <c r="T83" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
+        <v>178100</v>
+      </c>
+      <c r="V83" t="n">
         <v>180100</v>
       </c>
-      <c r="V83" t="n">
-        <v>178200</v>
-      </c>
       <c r="W83" t="n">
-        <v>1.1</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="84">
@@ -6420,13 +6438,13 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
+        <v>107200</v>
+      </c>
+      <c r="V84" t="n">
         <v>110300</v>
       </c>
-      <c r="V84" t="n">
-        <v>111900</v>
-      </c>
       <c r="W84" t="n">
-        <v>-1.4</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="85">
@@ -6492,13 +6510,13 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
+        <v>49100</v>
+      </c>
+      <c r="V85" t="n">
         <v>52100</v>
       </c>
-      <c r="V85" t="n">
-        <v>52500</v>
-      </c>
       <c r="W85" t="n">
-        <v>-0.8</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="86">
@@ -6564,13 +6582,13 @@
         <v>0</v>
       </c>
       <c r="U86" t="n">
+        <v>6540</v>
+      </c>
+      <c r="V86" t="n">
         <v>7040</v>
       </c>
-      <c r="V86" t="n">
-        <v>7370</v>
-      </c>
       <c r="W86" t="n">
-        <v>-4.5</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="87">
@@ -6609,13 +6627,13 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
+        <v>10020</v>
+      </c>
+      <c r="V87" t="n">
         <v>10350</v>
       </c>
-      <c r="V87" t="n">
-        <v>10390</v>
-      </c>
       <c r="W87" t="n">
-        <v>-0.4</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="88">
@@ -6654,13 +6672,13 @@
         <v>0</v>
       </c>
       <c r="U88" t="n">
+        <v>13200</v>
+      </c>
+      <c r="V88" t="n">
         <v>11550</v>
       </c>
-      <c r="V88" t="n">
-        <v>10030</v>
-      </c>
       <c r="W88" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="89">
@@ -6726,13 +6744,13 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
+        <v>22300</v>
+      </c>
+      <c r="V89" t="n">
         <v>23700</v>
       </c>
-      <c r="V89" t="n">
-        <v>24800</v>
-      </c>
       <c r="W89" t="n">
-        <v>-4.4</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="90">
@@ -6762,49 +6780,49 @@
         </is>
       </c>
       <c r="F90" t="n">
+        <v>1071</v>
+      </c>
+      <c r="G90" t="n">
         <v>1064</v>
       </c>
-      <c r="G90" t="n">
-        <v>1065</v>
-      </c>
       <c r="H90" t="n">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L90" t="n">
+        <v>4489.9</v>
+      </c>
+      <c r="M90" t="n">
         <v>4489.8</v>
       </c>
-      <c r="M90" t="n">
-        <v>4486.9</v>
-      </c>
       <c r="N90" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
+        <v>6256.5</v>
+      </c>
+      <c r="P90" t="n">
         <v>6269.5</v>
       </c>
-      <c r="P90" t="n">
-        <v>6274.2</v>
-      </c>
       <c r="Q90" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="R90" t="n">
+        <v>8348.700000000001</v>
+      </c>
+      <c r="S90" t="n">
         <v>8384.6</v>
       </c>
-      <c r="S90" t="n">
-        <v>8410.299999999999</v>
-      </c>
       <c r="T90" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="U90" t="n">
+        <v>699000</v>
+      </c>
+      <c r="V90" t="n">
         <v>737000</v>
       </c>
-      <c r="V90" t="n">
-        <v>678000</v>
-      </c>
       <c r="W90" t="n">
-        <v>8.699999999999999</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="91">
@@ -6843,13 +6861,13 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
+        <v>8380</v>
+      </c>
+      <c r="V91" t="n">
         <v>8990</v>
       </c>
-      <c r="V91" t="n">
-        <v>9480</v>
-      </c>
       <c r="W91" t="n">
-        <v>-5.2</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="92">
@@ -6882,46 +6900,46 @@
         <v>601</v>
       </c>
       <c r="G92" t="n">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>2258.6</v>
       </c>
       <c r="M92" t="n">
-        <v>2273.1</v>
+        <v>2258.6</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>3761.1</v>
       </c>
       <c r="P92" t="n">
-        <v>3720.9</v>
+        <v>3761.1</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>4734.7</v>
       </c>
       <c r="S92" t="n">
-        <v>4694</v>
+        <v>4734.7</v>
       </c>
       <c r="T92" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
+        <v>48100</v>
+      </c>
+      <c r="V92" t="n">
         <v>51600</v>
       </c>
-      <c r="V92" t="n">
-        <v>50300</v>
-      </c>
       <c r="W92" t="n">
-        <v>2.6</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="93">
@@ -6987,13 +7005,13 @@
         <v>0</v>
       </c>
       <c r="U93" t="n">
+        <v>198000</v>
+      </c>
+      <c r="V93" t="n">
         <v>204000</v>
       </c>
-      <c r="V93" t="n">
-        <v>208500</v>
-      </c>
       <c r="W93" t="n">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="94">
@@ -7059,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="U94" t="n">
+        <v>49600</v>
+      </c>
+      <c r="V94" t="n">
         <v>49000</v>
       </c>
-      <c r="V94" t="n">
-        <v>49300</v>
-      </c>
       <c r="W94" t="n">
-        <v>-0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="95">
@@ -7098,46 +7116,46 @@
         <v>226</v>
       </c>
       <c r="G95" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="H95" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>951.5</v>
       </c>
       <c r="M95" t="n">
-        <v>922.3</v>
+        <v>951.5</v>
       </c>
       <c r="N95" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>1407</v>
       </c>
       <c r="P95" t="n">
-        <v>1380</v>
+        <v>1407</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>1717</v>
       </c>
       <c r="S95" t="n">
-        <v>1638.7</v>
+        <v>1717</v>
       </c>
       <c r="T95" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U95" t="n">
+        <v>62800</v>
+      </c>
+      <c r="V95" t="n">
         <v>55100</v>
       </c>
-      <c r="V95" t="n">
-        <v>48650</v>
-      </c>
       <c r="W95" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
@@ -7179,37 +7197,37 @@
         <v>4871.2</v>
       </c>
       <c r="M96" t="n">
-        <v>4845.6</v>
+        <v>4871.2</v>
       </c>
       <c r="N96" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>5671.9</v>
       </c>
       <c r="P96" t="n">
-        <v>5614.8</v>
+        <v>5671.9</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>6445.8</v>
       </c>
       <c r="S96" t="n">
-        <v>6373.3</v>
+        <v>6445.8</v>
       </c>
       <c r="T96" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
+        <v>142200</v>
+      </c>
+      <c r="V96" t="n">
         <v>142700</v>
       </c>
-      <c r="V96" t="n">
-        <v>140500</v>
-      </c>
       <c r="W96" t="n">
-        <v>1.6</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="97">
@@ -7248,40 +7266,40 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>340.8</v>
+        <v>337.8</v>
       </c>
       <c r="M97" t="n">
         <v>340.8</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="O97" t="n">
-        <v>487.2</v>
+        <v>483.2</v>
       </c>
       <c r="P97" t="n">
         <v>487.2</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="R97" t="n">
-        <v>642.8</v>
+        <v>629.2</v>
       </c>
       <c r="S97" t="n">
         <v>642.8</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="U97" t="n">
+        <v>17820</v>
+      </c>
+      <c r="V97" t="n">
         <v>17800</v>
       </c>
-      <c r="V97" t="n">
-        <v>17890</v>
-      </c>
       <c r="W97" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="98">
@@ -7347,13 +7365,13 @@
         <v>0</v>
       </c>
       <c r="U98" t="n">
+        <v>33850</v>
+      </c>
+      <c r="V98" t="n">
         <v>33900</v>
       </c>
-      <c r="V98" t="n">
-        <v>31550</v>
-      </c>
       <c r="W98" t="n">
-        <v>7.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="99">
@@ -7386,46 +7404,46 @@
         <v>3469</v>
       </c>
       <c r="G99" t="n">
-        <v>3477</v>
+        <v>3469</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>12077.8</v>
       </c>
       <c r="M99" t="n">
-        <v>12092.4</v>
+        <v>12077.8</v>
       </c>
       <c r="N99" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>13978.5</v>
       </c>
       <c r="P99" t="n">
-        <v>13996.2</v>
+        <v>13978.5</v>
       </c>
       <c r="Q99" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>15265.1</v>
       </c>
       <c r="S99" t="n">
-        <v>15284.4</v>
+        <v>15265.1</v>
       </c>
       <c r="T99" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
+        <v>176300</v>
+      </c>
+      <c r="V99" t="n">
         <v>175000</v>
       </c>
-      <c r="V99" t="n">
-        <v>179700</v>
-      </c>
       <c r="W99" t="n">
-        <v>-2.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="100">
@@ -7491,13 +7509,13 @@
         <v>0</v>
       </c>
       <c r="U100" t="n">
+        <v>15980</v>
+      </c>
+      <c r="V100" t="n">
         <v>16200</v>
       </c>
-      <c r="V100" t="n">
-        <v>16550</v>
-      </c>
       <c r="W100" t="n">
-        <v>-2.1</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="101">
@@ -7530,46 +7548,46 @@
         <v>69</v>
       </c>
       <c r="G101" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H101" t="n">
-        <v>-6.8</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>183.3</v>
       </c>
       <c r="M101" t="n">
-        <v>205</v>
+        <v>183.3</v>
       </c>
       <c r="N101" t="n">
-        <v>-10.6</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>354.3</v>
       </c>
       <c r="P101" t="n">
-        <v>426.5</v>
+        <v>354.3</v>
       </c>
       <c r="Q101" t="n">
-        <v>-16.9</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>407</v>
       </c>
       <c r="S101" t="n">
-        <v>554</v>
+        <v>407</v>
       </c>
       <c r="T101" t="n">
-        <v>-26.5</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
+        <v>78200</v>
+      </c>
+      <c r="V101" t="n">
         <v>78900</v>
       </c>
-      <c r="V101" t="n">
-        <v>70300</v>
-      </c>
       <c r="W101" t="n">
-        <v>12.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="102">
@@ -7602,46 +7620,46 @@
         <v>1111</v>
       </c>
       <c r="G102" t="n">
-        <v>1086</v>
+        <v>1111</v>
       </c>
       <c r="H102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>4287.8</v>
       </c>
       <c r="M102" t="n">
-        <v>4253.7</v>
+        <v>4287.8</v>
       </c>
       <c r="N102" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>3950.5</v>
       </c>
       <c r="P102" t="n">
-        <v>3853.9</v>
+        <v>3950.5</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>4212.5</v>
       </c>
       <c r="S102" t="n">
-        <v>4142.7</v>
+        <v>4212.5</v>
       </c>
       <c r="T102" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
+        <v>77500</v>
+      </c>
+      <c r="V102" t="n">
         <v>79700</v>
       </c>
-      <c r="V102" t="n">
-        <v>77500</v>
-      </c>
       <c r="W102" t="n">
-        <v>2.8</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="103">
@@ -7707,13 +7725,13 @@
         <v>0</v>
       </c>
       <c r="U103" t="n">
+        <v>301500</v>
+      </c>
+      <c r="V103" t="n">
         <v>307500</v>
       </c>
-      <c r="V103" t="n">
-        <v>323500</v>
-      </c>
       <c r="W103" t="n">
-        <v>-4.9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="104">
@@ -7752,13 +7770,13 @@
         <v>0</v>
       </c>
       <c r="U104" t="n">
+        <v>8910</v>
+      </c>
+      <c r="V104" t="n">
         <v>9030</v>
       </c>
-      <c r="V104" t="n">
-        <v>9220</v>
-      </c>
       <c r="W104" t="n">
-        <v>-2.1</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="105">
@@ -7788,49 +7806,49 @@
         </is>
       </c>
       <c r="F105" t="n">
+        <v>219</v>
+      </c>
+      <c r="G105" t="n">
         <v>217</v>
       </c>
-      <c r="G105" t="n">
-        <v>216</v>
-      </c>
       <c r="H105" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L105" t="n">
+        <v>781.6</v>
+      </c>
+      <c r="M105" t="n">
         <v>777.1</v>
       </c>
-      <c r="M105" t="n">
-        <v>774.5</v>
-      </c>
       <c r="N105" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="O105" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="P105" t="n">
         <v>708.4</v>
       </c>
-      <c r="P105" t="n">
-        <v>711.3</v>
-      </c>
       <c r="Q105" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>833.1</v>
       </c>
       <c r="S105" t="n">
-        <v>833.6</v>
+        <v>833.1</v>
       </c>
       <c r="T105" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
+        <v>43000</v>
+      </c>
+      <c r="V105" t="n">
         <v>43600</v>
       </c>
-      <c r="V105" t="n">
-        <v>43400</v>
-      </c>
       <c r="W105" t="n">
-        <v>0.5</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="106">
@@ -7863,46 +7881,46 @@
         <v>915</v>
       </c>
       <c r="G106" t="n">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>3664.9</v>
       </c>
       <c r="M106" t="n">
-        <v>3667.8</v>
+        <v>3664.9</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>3151.9</v>
       </c>
       <c r="P106" t="n">
-        <v>3096.4</v>
+        <v>3151.9</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>3115.8</v>
       </c>
       <c r="S106" t="n">
-        <v>3116.8</v>
+        <v>3115.8</v>
       </c>
       <c r="T106" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U106" t="n">
+        <v>519000</v>
+      </c>
+      <c r="V106" t="n">
         <v>505000</v>
       </c>
-      <c r="V106" t="n">
-        <v>464000</v>
-      </c>
       <c r="W106" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="107">
@@ -7935,19 +7953,19 @@
         <v>-1214</v>
       </c>
       <c r="M107" t="n">
-        <v>-1216</v>
+        <v>-1214</v>
       </c>
       <c r="N107" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>-771.5</v>
       </c>
       <c r="P107" t="n">
-        <v>-1287.7</v>
+        <v>-771.5</v>
       </c>
       <c r="Q107" t="n">
-        <v>40.1</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>522.5</v>
@@ -7959,13 +7977,13 @@
         <v>0</v>
       </c>
       <c r="U107" t="n">
+        <v>80700</v>
+      </c>
+      <c r="V107" t="n">
         <v>81900</v>
       </c>
-      <c r="V107" t="n">
-        <v>85200</v>
-      </c>
       <c r="W107" t="n">
-        <v>-3.9</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="108">
@@ -7995,49 +8013,49 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>550</v>
+        <v>474</v>
       </c>
       <c r="G108" t="n">
         <v>550</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>-13.8</v>
       </c>
       <c r="L108" t="n">
-        <v>2190.9</v>
+        <v>2070.6</v>
       </c>
       <c r="M108" t="n">
         <v>2190.9</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>-5.5</v>
       </c>
       <c r="O108" t="n">
-        <v>2843.4</v>
+        <v>2740.5</v>
       </c>
       <c r="P108" t="n">
         <v>2843.4</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="R108" t="n">
-        <v>3633.8</v>
+        <v>3549</v>
       </c>
       <c r="S108" t="n">
         <v>3633.8</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="U108" t="n">
+        <v>186800</v>
+      </c>
+      <c r="V108" t="n">
         <v>215000</v>
       </c>
-      <c r="V108" t="n">
-        <v>231000</v>
-      </c>
       <c r="W108" t="n">
-        <v>-6.9</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="109">
@@ -8103,13 +8121,13 @@
         <v>0</v>
       </c>
       <c r="U109" t="n">
+        <v>36800</v>
+      </c>
+      <c r="V109" t="n">
         <v>37900</v>
       </c>
-      <c r="V109" t="n">
-        <v>37850</v>
-      </c>
       <c r="W109" t="n">
-        <v>0.1</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="110">
@@ -8148,13 +8166,13 @@
         <v>0</v>
       </c>
       <c r="U110" t="n">
+        <v>10690</v>
+      </c>
+      <c r="V110" t="n">
         <v>10050</v>
       </c>
-      <c r="V110" t="n">
-        <v>8980</v>
-      </c>
       <c r="W110" t="n">
-        <v>11.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="111">
@@ -8220,13 +8238,13 @@
         <v>0</v>
       </c>
       <c r="U111" t="n">
+        <v>57300</v>
+      </c>
+      <c r="V111" t="n">
         <v>60700</v>
       </c>
-      <c r="V111" t="n">
-        <v>62300</v>
-      </c>
       <c r="W111" t="n">
-        <v>-2.6</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="112">
@@ -8268,7 +8286,7 @@
         <v>3458.2</v>
       </c>
       <c r="M112" t="n">
-        <v>3456.6</v>
+        <v>3458.2</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -8277,7 +8295,7 @@
         <v>4117</v>
       </c>
       <c r="P112" t="n">
-        <v>4115.3</v>
+        <v>4117</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -8286,19 +8304,19 @@
         <v>4677.1</v>
       </c>
       <c r="S112" t="n">
-        <v>4660.9</v>
+        <v>4677.1</v>
       </c>
       <c r="T112" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
+        <v>146700</v>
+      </c>
+      <c r="V112" t="n">
         <v>145500</v>
       </c>
-      <c r="V112" t="n">
-        <v>141300</v>
-      </c>
       <c r="W112" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="113">
@@ -8364,13 +8382,13 @@
         <v>0</v>
       </c>
       <c r="U113" t="n">
+        <v>34500</v>
+      </c>
+      <c r="V113" t="n">
         <v>35700</v>
       </c>
-      <c r="V113" t="n">
-        <v>36250</v>
-      </c>
       <c r="W113" t="n">
-        <v>-1.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="114">
@@ -8436,13 +8454,13 @@
         <v>0</v>
       </c>
       <c r="U114" t="n">
+        <v>64800</v>
+      </c>
+      <c r="V114" t="n">
         <v>64400</v>
       </c>
-      <c r="V114" t="n">
-        <v>66800</v>
-      </c>
       <c r="W114" t="n">
-        <v>-3.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="115">
@@ -8484,19 +8502,19 @@
         <v>367.6</v>
       </c>
       <c r="M115" t="n">
-        <v>366.4</v>
+        <v>367.6</v>
       </c>
       <c r="N115" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>567.1</v>
       </c>
       <c r="P115" t="n">
-        <v>564.1</v>
+        <v>567.1</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>907.2</v>
@@ -8508,13 +8526,13 @@
         <v>0</v>
       </c>
       <c r="U115" t="n">
+        <v>69700</v>
+      </c>
+      <c r="V115" t="n">
         <v>68600</v>
       </c>
-      <c r="V115" t="n">
-        <v>63400</v>
-      </c>
       <c r="W115" t="n">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="116">
@@ -8580,13 +8598,13 @@
         <v>0</v>
       </c>
       <c r="U116" t="n">
+        <v>58100</v>
+      </c>
+      <c r="V116" t="n">
         <v>59000</v>
       </c>
-      <c r="V116" t="n">
-        <v>58100</v>
-      </c>
       <c r="W116" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="117">
@@ -8616,49 +8634,49 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G117" t="n">
         <v>676</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L117" t="n">
+        <v>2570</v>
+      </c>
+      <c r="M117" t="n">
         <v>2568.9</v>
       </c>
-      <c r="M117" t="n">
-        <v>2567.3</v>
-      </c>
       <c r="N117" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
+        <v>3157.9</v>
+      </c>
+      <c r="P117" t="n">
         <v>3156.9</v>
       </c>
-      <c r="P117" t="n">
-        <v>3152.4</v>
-      </c>
       <c r="Q117" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
+        <v>3707.3</v>
+      </c>
+      <c r="S117" t="n">
         <v>3706.2</v>
       </c>
-      <c r="S117" t="n">
-        <v>3698.5</v>
-      </c>
       <c r="T117" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U117" t="n">
+        <v>270500</v>
+      </c>
+      <c r="V117" t="n">
         <v>274000</v>
       </c>
-      <c r="V117" t="n">
-        <v>270500</v>
-      </c>
       <c r="W117" t="n">
-        <v>1.3</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="118">
@@ -8727,10 +8745,10 @@
         <v>38900</v>
       </c>
       <c r="V118" t="n">
-        <v>40700</v>
+        <v>38900</v>
       </c>
       <c r="W118" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -8763,10 +8781,10 @@
         <v>1023</v>
       </c>
       <c r="G119" t="n">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
         <v>4116</v>
@@ -8781,10 +8799,10 @@
         <v>4713.2</v>
       </c>
       <c r="P119" t="n">
-        <v>4714.5</v>
+        <v>4713.2</v>
       </c>
       <c r="Q119" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>5334.9</v>
@@ -8796,13 +8814,13 @@
         <v>0</v>
       </c>
       <c r="U119" t="n">
+        <v>45500</v>
+      </c>
+      <c r="V119" t="n">
         <v>48250</v>
       </c>
-      <c r="V119" t="n">
-        <v>49750</v>
-      </c>
       <c r="W119" t="n">
-        <v>-3</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="120">
@@ -8868,13 +8886,13 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
+        <v>1373000</v>
+      </c>
+      <c r="V120" t="n">
         <v>1399000</v>
       </c>
-      <c r="V120" t="n">
-        <v>1415000</v>
-      </c>
       <c r="W120" t="n">
-        <v>-1.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="121">
@@ -8904,49 +8922,49 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="G121" t="n">
         <v>506</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="L121" t="n">
-        <v>1924.8</v>
+        <v>1912.4</v>
       </c>
       <c r="M121" t="n">
         <v>1924.8</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="O121" t="n">
-        <v>2548.9</v>
+        <v>2516.7</v>
       </c>
       <c r="P121" t="n">
         <v>2548.9</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="R121" t="n">
-        <v>3206.6</v>
+        <v>3169.4</v>
       </c>
       <c r="S121" t="n">
         <v>3206.6</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="U121" t="n">
+        <v>30750</v>
+      </c>
+      <c r="V121" t="n">
         <v>31450</v>
       </c>
-      <c r="V121" t="n">
-        <v>32050</v>
-      </c>
       <c r="W121" t="n">
-        <v>-1.9</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="122">
@@ -8976,49 +8994,49 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G122" t="n">
         <v>733</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L122" t="n">
-        <v>2717.2</v>
+        <v>2726.9</v>
       </c>
       <c r="M122" t="n">
         <v>2717.2</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O122" t="n">
-        <v>3382.9</v>
+        <v>3411</v>
       </c>
       <c r="P122" t="n">
         <v>3382.9</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R122" t="n">
-        <v>4073.6</v>
+        <v>4102.9</v>
       </c>
       <c r="S122" t="n">
         <v>4073.6</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U122" t="n">
+        <v>323500</v>
+      </c>
+      <c r="V122" t="n">
         <v>327000</v>
       </c>
-      <c r="V122" t="n">
-        <v>342000</v>
-      </c>
       <c r="W122" t="n">
-        <v>-4.4</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="123">
@@ -9060,10 +9078,10 @@
         <v>550.5</v>
       </c>
       <c r="M123" t="n">
-        <v>551.7</v>
+        <v>550.5</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>797.7</v>
@@ -9084,13 +9102,13 @@
         <v>0</v>
       </c>
       <c r="U123" t="n">
+        <v>58800</v>
+      </c>
+      <c r="V123" t="n">
         <v>61300</v>
       </c>
-      <c r="V123" t="n">
-        <v>48800</v>
-      </c>
       <c r="W123" t="n">
-        <v>25.6</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="124">
@@ -9156,13 +9174,13 @@
         <v>0</v>
       </c>
       <c r="U124" t="n">
+        <v>90800</v>
+      </c>
+      <c r="V124" t="n">
         <v>92700</v>
       </c>
-      <c r="V124" t="n">
-        <v>90000</v>
-      </c>
       <c r="W124" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="125">
@@ -9228,13 +9246,13 @@
         <v>0</v>
       </c>
       <c r="U125" t="n">
+        <v>57900</v>
+      </c>
+      <c r="V125" t="n">
         <v>59400</v>
       </c>
-      <c r="V125" t="n">
-        <v>61600</v>
-      </c>
       <c r="W125" t="n">
-        <v>-3.6</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="126">
@@ -9276,37 +9294,37 @@
         <v>1145</v>
       </c>
       <c r="M126" t="n">
-        <v>1143.9</v>
+        <v>1145</v>
       </c>
       <c r="N126" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>1368.3</v>
       </c>
       <c r="P126" t="n">
-        <v>1366.7</v>
+        <v>1368.3</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>1592.8</v>
       </c>
       <c r="S126" t="n">
-        <v>1595.4</v>
+        <v>1592.8</v>
       </c>
       <c r="T126" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
+        <v>127100</v>
+      </c>
+      <c r="V126" t="n">
         <v>132100</v>
       </c>
-      <c r="V126" t="n">
-        <v>125700</v>
-      </c>
       <c r="W126" t="n">
-        <v>5.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="127">
@@ -9372,13 +9390,13 @@
         <v>0</v>
       </c>
       <c r="U127" t="n">
+        <v>105500</v>
+      </c>
+      <c r="V127" t="n">
         <v>105300</v>
       </c>
-      <c r="V127" t="n">
-        <v>110300</v>
-      </c>
       <c r="W127" t="n">
-        <v>-4.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="128">
@@ -9444,13 +9462,13 @@
         <v>0</v>
       </c>
       <c r="U128" t="n">
+        <v>34600</v>
+      </c>
+      <c r="V128" t="n">
         <v>34750</v>
       </c>
-      <c r="V128" t="n">
-        <v>35200</v>
-      </c>
       <c r="W128" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="129">
@@ -9483,46 +9501,46 @@
         <v>205</v>
       </c>
       <c r="G129" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>732.2</v>
       </c>
       <c r="M129" t="n">
-        <v>732.5</v>
+        <v>732.2</v>
       </c>
       <c r="N129" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>867.7</v>
       </c>
       <c r="P129" t="n">
-        <v>868.4</v>
+        <v>867.7</v>
       </c>
       <c r="Q129" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>1000.4</v>
       </c>
       <c r="S129" t="n">
-        <v>1002</v>
+        <v>1000.4</v>
       </c>
       <c r="T129" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
+        <v>57700</v>
+      </c>
+      <c r="V129" t="n">
         <v>61700</v>
       </c>
-      <c r="V129" t="n">
-        <v>52800</v>
-      </c>
       <c r="W129" t="n">
-        <v>16.9</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="130">
@@ -9588,13 +9606,13 @@
         <v>0</v>
       </c>
       <c r="U130" t="n">
+        <v>20300</v>
+      </c>
+      <c r="V130" t="n">
         <v>21000</v>
       </c>
-      <c r="V130" t="n">
-        <v>21450</v>
-      </c>
       <c r="W130" t="n">
-        <v>-2.1</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="131">
@@ -9660,13 +9678,13 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
+        <v>198500</v>
+      </c>
+      <c r="V131" t="n">
         <v>204500</v>
       </c>
-      <c r="V131" t="n">
-        <v>212500</v>
-      </c>
       <c r="W131" t="n">
-        <v>-3.8</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="132">
@@ -9732,13 +9750,13 @@
         <v>0</v>
       </c>
       <c r="U132" t="n">
+        <v>713000</v>
+      </c>
+      <c r="V132" t="n">
         <v>727000</v>
       </c>
-      <c r="V132" t="n">
-        <v>747000</v>
-      </c>
       <c r="W132" t="n">
-        <v>-2.7</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="133">
@@ -9804,13 +9822,13 @@
         <v>0</v>
       </c>
       <c r="U133" t="n">
+        <v>130900</v>
+      </c>
+      <c r="V133" t="n">
         <v>140400</v>
       </c>
-      <c r="V133" t="n">
-        <v>142500</v>
-      </c>
       <c r="W133" t="n">
-        <v>-1.5</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="134">
@@ -9843,46 +9861,46 @@
         <v>1562</v>
       </c>
       <c r="G134" t="n">
-        <v>1578</v>
+        <v>1562</v>
       </c>
       <c r="H134" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
         <v>6397.1</v>
       </c>
       <c r="M134" t="n">
-        <v>6454.1</v>
+        <v>6397.1</v>
       </c>
       <c r="N134" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>6990.9</v>
       </c>
       <c r="P134" t="n">
-        <v>7063.9</v>
+        <v>6990.9</v>
       </c>
       <c r="Q134" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>7436.8</v>
       </c>
       <c r="S134" t="n">
-        <v>7555.4</v>
+        <v>7436.8</v>
       </c>
       <c r="T134" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
+        <v>110200</v>
+      </c>
+      <c r="V134" t="n">
         <v>112500</v>
       </c>
-      <c r="V134" t="n">
-        <v>119300</v>
-      </c>
       <c r="W134" t="n">
-        <v>-5.7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="135">
@@ -9915,46 +9933,46 @@
         <v>603</v>
       </c>
       <c r="G135" t="n">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="H135" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
         <v>2501.7</v>
       </c>
       <c r="M135" t="n">
-        <v>2485.5</v>
+        <v>2501.7</v>
       </c>
       <c r="N135" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>4527.8</v>
       </c>
       <c r="P135" t="n">
-        <v>4530.6</v>
+        <v>4527.8</v>
       </c>
       <c r="Q135" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>5763.9</v>
       </c>
       <c r="S135" t="n">
-        <v>5778.4</v>
+        <v>5763.9</v>
       </c>
       <c r="T135" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
+        <v>74400</v>
+      </c>
+      <c r="V135" t="n">
         <v>79900</v>
       </c>
-      <c r="V135" t="n">
-        <v>70900</v>
-      </c>
       <c r="W135" t="n">
-        <v>12.7</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="136">
@@ -9987,46 +10005,46 @@
         <v>-70</v>
       </c>
       <c r="G136" t="n">
-        <v>-97</v>
+        <v>-70</v>
       </c>
       <c r="H136" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>-161.5</v>
       </c>
       <c r="M136" t="n">
-        <v>-140</v>
+        <v>-161.5</v>
       </c>
       <c r="N136" t="n">
-        <v>-15.4</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>905.5</v>
       </c>
       <c r="P136" t="n">
-        <v>799</v>
+        <v>905.5</v>
       </c>
       <c r="Q136" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>1283.2</v>
       </c>
       <c r="S136" t="n">
-        <v>1281</v>
+        <v>1283.2</v>
       </c>
       <c r="T136" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
+        <v>6030</v>
+      </c>
+      <c r="V136" t="n">
         <v>5820</v>
       </c>
-      <c r="V136" t="n">
-        <v>5930</v>
-      </c>
       <c r="W136" t="n">
-        <v>-1.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="137">
@@ -10083,13 +10101,13 @@
         <v>0</v>
       </c>
       <c r="U137" t="n">
+        <v>435500</v>
+      </c>
+      <c r="V137" t="n">
         <v>434500</v>
       </c>
-      <c r="V137" t="n">
-        <v>436000</v>
-      </c>
       <c r="W137" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="138">
@@ -10119,49 +10137,49 @@
         </is>
       </c>
       <c r="F138" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G138" t="n">
         <v>1959</v>
       </c>
-      <c r="G138" t="n">
-        <v>1961</v>
-      </c>
       <c r="H138" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="L138" t="n">
+        <v>7667.3</v>
+      </c>
+      <c r="M138" t="n">
         <v>7659.4</v>
       </c>
-      <c r="M138" t="n">
-        <v>7666.7</v>
-      </c>
       <c r="N138" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="O138" t="n">
+        <v>10789.2</v>
+      </c>
+      <c r="P138" t="n">
         <v>10805.7</v>
       </c>
-      <c r="P138" t="n">
-        <v>10744.4</v>
-      </c>
       <c r="Q138" t="n">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="R138" t="n">
+        <v>13548.6</v>
+      </c>
+      <c r="S138" t="n">
         <v>13547.9</v>
       </c>
-      <c r="S138" t="n">
-        <v>13393</v>
-      </c>
       <c r="T138" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
+        <v>369000</v>
+      </c>
+      <c r="V138" t="n">
         <v>368000</v>
       </c>
-      <c r="V138" t="n">
-        <v>372000</v>
-      </c>
       <c r="W138" t="n">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="139">
@@ -10227,13 +10245,13 @@
         <v>0</v>
       </c>
       <c r="U139" t="n">
+        <v>125000</v>
+      </c>
+      <c r="V139" t="n">
         <v>127100</v>
       </c>
-      <c r="V139" t="n">
-        <v>142900</v>
-      </c>
       <c r="W139" t="n">
-        <v>-11.1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="140">
@@ -10263,49 +10281,49 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1462</v>
+        <v>1474</v>
       </c>
       <c r="G140" t="n">
         <v>1462</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L140" t="n">
-        <v>5213.7</v>
+        <v>5224.9</v>
       </c>
       <c r="M140" t="n">
         <v>5213.7</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O140" t="n">
-        <v>7038</v>
+        <v>7049.1</v>
       </c>
       <c r="P140" t="n">
         <v>7038</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R140" t="n">
-        <v>6523.9</v>
+        <v>6539.6</v>
       </c>
       <c r="S140" t="n">
         <v>6523.9</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U140" t="n">
+        <v>23500</v>
+      </c>
+      <c r="V140" t="n">
         <v>23550</v>
       </c>
-      <c r="V140" t="n">
-        <v>24850</v>
-      </c>
       <c r="W140" t="n">
-        <v>-5.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="141">
@@ -10335,7 +10353,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="G141" t="n">
         <v>3336</v>
@@ -10344,40 +10362,40 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
+        <v>11297.5</v>
+      </c>
+      <c r="M141" t="n">
         <v>11297.3</v>
       </c>
-      <c r="M141" t="n">
-        <v>11297.2</v>
-      </c>
       <c r="N141" t="n">
         <v>0</v>
       </c>
       <c r="O141" t="n">
+        <v>15690.3</v>
+      </c>
+      <c r="P141" t="n">
         <v>15675.3</v>
       </c>
-      <c r="P141" t="n">
-        <v>15675.4</v>
-      </c>
       <c r="Q141" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="R141" t="n">
+        <v>20451.1</v>
+      </c>
+      <c r="S141" t="n">
         <v>20398.8</v>
       </c>
-      <c r="S141" t="n">
-        <v>20398.5</v>
-      </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U141" t="n">
+        <v>2892000</v>
+      </c>
+      <c r="V141" t="n">
         <v>2888000</v>
       </c>
-      <c r="V141" t="n">
-        <v>2854000</v>
-      </c>
       <c r="W141" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="142">
@@ -10434,13 +10452,13 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
+        <v>35600</v>
+      </c>
+      <c r="V142" t="n">
         <v>35350</v>
       </c>
-      <c r="V142" t="n">
-        <v>37250</v>
-      </c>
       <c r="W142" t="n">
-        <v>-5.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="143">
@@ -10473,46 +10491,46 @@
         <v>254</v>
       </c>
       <c r="G143" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.8</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
+        <v>1136.7</v>
+      </c>
+      <c r="M143" t="n">
         <v>1118.2</v>
       </c>
-      <c r="M143" t="n">
-        <v>1115.3</v>
-      </c>
       <c r="N143" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="O143" t="n">
+        <v>1326.3</v>
+      </c>
+      <c r="P143" t="n">
         <v>1247.3</v>
       </c>
-      <c r="P143" t="n">
-        <v>1268.2</v>
-      </c>
       <c r="Q143" t="n">
-        <v>-1.6</v>
+        <v>6.3</v>
       </c>
       <c r="R143" t="n">
+        <v>1480.4</v>
+      </c>
+      <c r="S143" t="n">
         <v>1414.8</v>
       </c>
-      <c r="S143" t="n">
-        <v>1458.6</v>
-      </c>
       <c r="T143" t="n">
-        <v>-3</v>
+        <v>4.6</v>
       </c>
       <c r="U143" t="n">
+        <v>139000</v>
+      </c>
+      <c r="V143" t="n">
         <v>148000</v>
       </c>
-      <c r="V143" t="n">
-        <v>150600</v>
-      </c>
       <c r="W143" t="n">
-        <v>-1.7</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="144">
@@ -10545,46 +10563,46 @@
         <v>117</v>
       </c>
       <c r="G144" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H144" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>552.5</v>
       </c>
       <c r="M144" t="n">
-        <v>560</v>
+        <v>552.5</v>
       </c>
       <c r="N144" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>968.3</v>
       </c>
       <c r="P144" t="n">
-        <v>1003.5</v>
+        <v>968.3</v>
       </c>
       <c r="Q144" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>1149.5</v>
       </c>
       <c r="S144" t="n">
-        <v>1043</v>
+        <v>1149.5</v>
       </c>
       <c r="T144" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
+        <v>9870</v>
+      </c>
+      <c r="V144" t="n">
         <v>10040</v>
       </c>
-      <c r="V144" t="n">
-        <v>11330</v>
-      </c>
       <c r="W144" t="n">
-        <v>-11.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="145">
@@ -10650,13 +10668,13 @@
         <v>0</v>
       </c>
       <c r="U145" t="n">
+        <v>20000</v>
+      </c>
+      <c r="V145" t="n">
         <v>20550</v>
       </c>
-      <c r="V145" t="n">
-        <v>21350</v>
-      </c>
       <c r="W145" t="n">
-        <v>-3.7</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="146">
@@ -10689,46 +10707,46 @@
         <v>917</v>
       </c>
       <c r="G146" t="n">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="H146" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="L146" t="n">
         <v>3506.6</v>
       </c>
       <c r="M146" t="n">
-        <v>3470.2</v>
+        <v>3506.6</v>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>4671.7</v>
       </c>
       <c r="P146" t="n">
-        <v>4678.1</v>
+        <v>4671.7</v>
       </c>
       <c r="Q146" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>6034.1</v>
       </c>
       <c r="S146" t="n">
-        <v>6051.4</v>
+        <v>6034.1</v>
       </c>
       <c r="T146" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
+        <v>76200</v>
+      </c>
+      <c r="V146" t="n">
         <v>77900</v>
       </c>
-      <c r="V146" t="n">
-        <v>79400</v>
-      </c>
       <c r="W146" t="n">
-        <v>-1.9</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="147">
@@ -10761,46 +10779,46 @@
         <v>10123</v>
       </c>
       <c r="G147" t="n">
-        <v>10106</v>
+        <v>10123</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>40537.2</v>
       </c>
       <c r="M147" t="n">
-        <v>40491.8</v>
+        <v>40537.2</v>
       </c>
       <c r="N147" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>47419</v>
       </c>
       <c r="P147" t="n">
-        <v>47253.1</v>
+        <v>47419</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>55084</v>
       </c>
       <c r="S147" t="n">
-        <v>55163</v>
+        <v>55084</v>
       </c>
       <c r="T147" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
+        <v>444000</v>
+      </c>
+      <c r="V147" t="n">
         <v>462000</v>
       </c>
-      <c r="V147" t="n">
-        <v>479000</v>
-      </c>
       <c r="W147" t="n">
-        <v>-3.5</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="148">
@@ -10830,49 +10848,49 @@
         </is>
       </c>
       <c r="F148" t="n">
+        <v>1634</v>
+      </c>
+      <c r="G148" t="n">
         <v>1632</v>
       </c>
-      <c r="G148" t="n">
-        <v>1635</v>
-      </c>
       <c r="H148" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L148" t="n">
+        <v>2841.7</v>
+      </c>
+      <c r="M148" t="n">
         <v>2850</v>
-      </c>
-      <c r="M148" t="n">
-        <v>2859.5</v>
       </c>
       <c r="N148" t="n">
         <v>-0.3</v>
       </c>
       <c r="O148" t="n">
+        <v>4824.5</v>
+      </c>
+      <c r="P148" t="n">
         <v>4828.6</v>
       </c>
-      <c r="P148" t="n">
-        <v>4871.2</v>
-      </c>
       <c r="Q148" t="n">
-        <v>-0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="R148" t="n">
+        <v>5419.5</v>
+      </c>
+      <c r="S148" t="n">
         <v>5426.4</v>
-      </c>
-      <c r="S148" t="n">
-        <v>5432.4</v>
       </c>
       <c r="T148" t="n">
         <v>-0.1</v>
       </c>
       <c r="U148" t="n">
+        <v>157700</v>
+      </c>
+      <c r="V148" t="n">
         <v>166700</v>
       </c>
-      <c r="V148" t="n">
-        <v>173000</v>
-      </c>
       <c r="W148" t="n">
-        <v>-3.6</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="149">
@@ -10938,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
+        <v>119200</v>
+      </c>
+      <c r="V149" t="n">
         <v>103100</v>
       </c>
-      <c r="V149" t="n">
-        <v>100000</v>
-      </c>
       <c r="W149" t="n">
-        <v>3.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="150">
@@ -10974,49 +10992,49 @@
         </is>
       </c>
       <c r="F150" t="n">
+        <v>3081</v>
+      </c>
+      <c r="G150" t="n">
         <v>3039</v>
       </c>
-      <c r="G150" t="n">
-        <v>2906</v>
-      </c>
       <c r="H150" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="L150" t="n">
+        <v>8494.299999999999</v>
+      </c>
+      <c r="M150" t="n">
         <v>8408.200000000001</v>
       </c>
-      <c r="M150" t="n">
-        <v>8298.799999999999</v>
-      </c>
       <c r="N150" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O150" t="n">
+        <v>39952.1</v>
+      </c>
+      <c r="P150" t="n">
         <v>39847.6</v>
       </c>
-      <c r="P150" t="n">
-        <v>39816.5</v>
-      </c>
       <c r="Q150" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="R150" t="n">
+        <v>61044.8</v>
+      </c>
+      <c r="S150" t="n">
         <v>61289.5</v>
       </c>
-      <c r="S150" t="n">
-        <v>61264.2</v>
-      </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="U150" t="n">
+        <v>352000</v>
+      </c>
+      <c r="V150" t="n">
         <v>363500</v>
       </c>
-      <c r="V150" t="n">
-        <v>360000</v>
-      </c>
       <c r="W150" t="n">
-        <v>1</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="151">
@@ -11046,25 +11064,25 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="G151" t="n">
         <v>1274</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L151" t="n">
-        <v>5744.6</v>
+        <v>5759.8</v>
       </c>
       <c r="M151" t="n">
         <v>5744.6</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O151" t="n">
-        <v>5756.8</v>
+        <v>5759.6</v>
       </c>
       <c r="P151" t="n">
         <v>5756.8</v>
@@ -11073,22 +11091,22 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>6461.5</v>
+        <v>6468.6</v>
       </c>
       <c r="S151" t="n">
         <v>6461.5</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U151" t="n">
+        <v>81100</v>
+      </c>
+      <c r="V151" t="n">
         <v>86800</v>
       </c>
-      <c r="V151" t="n">
-        <v>85800</v>
-      </c>
       <c r="W151" t="n">
-        <v>1.2</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="152">
@@ -11121,46 +11139,46 @@
         <v>93</v>
       </c>
       <c r="G152" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.1</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
         <v>384.8</v>
       </c>
       <c r="M152" t="n">
-        <v>388.1</v>
+        <v>384.8</v>
       </c>
       <c r="N152" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>439.3</v>
       </c>
       <c r="P152" t="n">
-        <v>446.6</v>
+        <v>439.3</v>
       </c>
       <c r="Q152" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>492.6</v>
       </c>
       <c r="S152" t="n">
-        <v>513.1</v>
+        <v>492.6</v>
       </c>
       <c r="T152" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="U152" t="n">
+        <v>17000</v>
+      </c>
+      <c r="V152" t="n">
         <v>17140</v>
       </c>
-      <c r="V152" t="n">
-        <v>17850</v>
-      </c>
       <c r="W152" t="n">
-        <v>-4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="153">
@@ -11199,13 +11217,13 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
+        <v>43250</v>
+      </c>
+      <c r="V153" t="n">
         <v>40850</v>
       </c>
-      <c r="V153" t="n">
-        <v>40350</v>
-      </c>
       <c r="W153" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="154">
@@ -11244,13 +11262,13 @@
         <v>0</v>
       </c>
       <c r="U154" t="n">
+        <v>32600</v>
+      </c>
+      <c r="V154" t="n">
         <v>28900</v>
       </c>
-      <c r="V154" t="n">
-        <v>29500</v>
-      </c>
       <c r="W154" t="n">
-        <v>-2</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="155">
@@ -11316,13 +11334,13 @@
         <v>0</v>
       </c>
       <c r="U155" t="n">
+        <v>123100</v>
+      </c>
+      <c r="V155" t="n">
         <v>112100</v>
       </c>
-      <c r="V155" t="n">
-        <v>93800</v>
-      </c>
       <c r="W155" t="n">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -11388,13 +11406,13 @@
         <v>0</v>
       </c>
       <c r="U156" t="n">
+        <v>45550</v>
+      </c>
+      <c r="V156" t="n">
         <v>47100</v>
       </c>
-      <c r="V156" t="n">
-        <v>47300</v>
-      </c>
       <c r="W156" t="n">
-        <v>-0.4</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="157">
@@ -11427,46 +11445,46 @@
         <v>1072</v>
       </c>
       <c r="G157" t="n">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
         <v>4141.9</v>
       </c>
       <c r="M157" t="n">
-        <v>4149</v>
+        <v>4141.9</v>
       </c>
       <c r="N157" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>5245</v>
       </c>
       <c r="P157" t="n">
-        <v>5281.3</v>
+        <v>5245</v>
       </c>
       <c r="Q157" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>6557.7</v>
       </c>
       <c r="S157" t="n">
-        <v>6584.7</v>
+        <v>6557.7</v>
       </c>
       <c r="T157" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
+        <v>240000</v>
+      </c>
+      <c r="V157" t="n">
         <v>244000</v>
       </c>
-      <c r="V157" t="n">
-        <v>247000</v>
-      </c>
       <c r="W157" t="n">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="158">
@@ -11532,13 +11550,13 @@
         <v>0</v>
       </c>
       <c r="U158" t="n">
+        <v>9520</v>
+      </c>
+      <c r="V158" t="n">
         <v>10260</v>
       </c>
-      <c r="V158" t="n">
-        <v>10320</v>
-      </c>
       <c r="W158" t="n">
-        <v>-0.6</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="159">
@@ -11604,13 +11622,13 @@
         <v>0</v>
       </c>
       <c r="U159" t="n">
+        <v>31300</v>
+      </c>
+      <c r="V159" t="n">
         <v>31050</v>
       </c>
-      <c r="V159" t="n">
-        <v>31400</v>
-      </c>
       <c r="W159" t="n">
-        <v>-1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="160">
@@ -11643,46 +11661,46 @@
         <v>326</v>
       </c>
       <c r="G160" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H160" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
+        <v>1645.7</v>
+      </c>
+      <c r="M160" t="n">
         <v>1643.8</v>
-      </c>
-      <c r="M160" t="n">
-        <v>1642.4</v>
       </c>
       <c r="N160" t="n">
         <v>0.1</v>
       </c>
       <c r="O160" t="n">
+        <v>2217.9</v>
+      </c>
+      <c r="P160" t="n">
         <v>2220.6</v>
-      </c>
-      <c r="P160" t="n">
-        <v>2222.2</v>
       </c>
       <c r="Q160" t="n">
         <v>-0.1</v>
       </c>
       <c r="R160" t="n">
+        <v>2783.9</v>
+      </c>
+      <c r="S160" t="n">
         <v>2797.1</v>
       </c>
-      <c r="S160" t="n">
-        <v>2805.5</v>
-      </c>
       <c r="T160" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="U160" t="n">
+        <v>183100</v>
+      </c>
+      <c r="V160" t="n">
         <v>182100</v>
       </c>
-      <c r="V160" t="n">
-        <v>167600</v>
-      </c>
       <c r="W160" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="161">
@@ -11748,13 +11766,13 @@
         <v>0</v>
       </c>
       <c r="U161" t="n">
+        <v>17660</v>
+      </c>
+      <c r="V161" t="n">
         <v>18730</v>
       </c>
-      <c r="V161" t="n">
-        <v>17930</v>
-      </c>
       <c r="W161" t="n">
-        <v>4.5</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="162">
@@ -11820,13 +11838,13 @@
         <v>0</v>
       </c>
       <c r="U162" t="n">
+        <v>48100</v>
+      </c>
+      <c r="V162" t="n">
         <v>47350</v>
       </c>
-      <c r="V162" t="n">
-        <v>47200</v>
-      </c>
       <c r="W162" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="163">
@@ -11865,13 +11883,13 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
+        <v>30350</v>
+      </c>
+      <c r="V163" t="n">
         <v>29950</v>
       </c>
-      <c r="V163" t="n">
-        <v>32550</v>
-      </c>
       <c r="W163" t="n">
-        <v>-8</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-25 · 전주 2026-09-19</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-26 · 전주 2026-09-19</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -618,7 +618,7 @@
         <v>2081.7</v>
       </c>
       <c r="U3" t="n">
-        <v>15100</v>
+        <v>15110</v>
       </c>
     </row>
     <row r="4">
@@ -684,13 +684,13 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>74800</v>
+        <v>74400</v>
       </c>
       <c r="V4" t="n">
         <v>76000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.6</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="5">
@@ -756,13 +756,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>70500</v>
+        <v>70400</v>
       </c>
       <c r="V5" t="n">
         <v>71000</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="6">
@@ -804,7 +804,7 @@
         <v>31331</v>
       </c>
       <c r="U6" t="n">
-        <v>1433000</v>
+        <v>1415000</v>
       </c>
     </row>
     <row r="7">
@@ -846,7 +846,7 @@
         <v>6170</v>
       </c>
       <c r="U7" t="n">
-        <v>52300</v>
+        <v>51900</v>
       </c>
     </row>
     <row r="8">
@@ -954,13 +954,13 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>116300</v>
+        <v>117100</v>
       </c>
       <c r="V9" t="n">
         <v>121600</v>
       </c>
       <c r="W9" t="n">
-        <v>-4.4</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="10">
@@ -1026,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>92700</v>
+        <v>93700</v>
       </c>
       <c r="V10" t="n">
         <v>93600</v>
       </c>
       <c r="W10" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1098,13 +1098,13 @@
         <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1778000</v>
+        <v>1761000</v>
       </c>
       <c r="V11" t="n">
         <v>1849000</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.8</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="12">
@@ -1170,13 +1170,13 @@
         <v>0.2</v>
       </c>
       <c r="U12" t="n">
-        <v>125100</v>
+        <v>123200</v>
       </c>
       <c r="V12" t="n">
         <v>125600</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.4</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="13">
@@ -1218,7 +1218,7 @@
         <v>37044</v>
       </c>
       <c r="U13" t="n">
-        <v>650000</v>
+        <v>658000</v>
       </c>
     </row>
     <row r="14">
@@ -1260,7 +1260,7 @@
         <v>77944.8</v>
       </c>
       <c r="U14" t="n">
-        <v>132400</v>
+        <v>131500</v>
       </c>
     </row>
     <row r="15">
@@ -1302,7 +1302,7 @@
         <v>7010</v>
       </c>
       <c r="U15" t="n">
-        <v>130100</v>
+        <v>125600</v>
       </c>
     </row>
     <row r="16">
@@ -1344,7 +1344,7 @@
         <v>30875.4</v>
       </c>
       <c r="U16" t="n">
-        <v>134900</v>
+        <v>133300</v>
       </c>
     </row>
     <row r="17">
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>45850</v>
+        <v>44750</v>
       </c>
       <c r="V17" t="n">
         <v>45150</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="18">
@@ -1458,7 +1458,7 @@
         <v>3257.1</v>
       </c>
       <c r="U18" t="n">
-        <v>30350</v>
+        <v>29850</v>
       </c>
     </row>
     <row r="19">
@@ -1497,7 +1497,7 @@
         <v>15992.7</v>
       </c>
       <c r="U19" t="n">
-        <v>49000</v>
+        <v>48600</v>
       </c>
     </row>
     <row r="20">
@@ -1533,7 +1533,7 @@
         <v>2028</v>
       </c>
       <c r="U20" t="n">
-        <v>18330</v>
+        <v>18290</v>
       </c>
     </row>
     <row r="21">
@@ -1575,7 +1575,7 @@
         <v>6750</v>
       </c>
       <c r="U21" t="n">
-        <v>24050</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="22">
@@ -1641,13 +1641,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5690</v>
+        <v>5730</v>
       </c>
       <c r="V22" t="n">
         <v>5580</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -1689,7 +1689,7 @@
         <v>5566</v>
       </c>
       <c r="U23" t="n">
-        <v>476500</v>
+        <v>477500</v>
       </c>
     </row>
     <row r="24">
@@ -1755,13 +1755,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>12900</v>
+        <v>12950</v>
       </c>
       <c r="V24" t="n">
         <v>13480</v>
       </c>
       <c r="W24" t="n">
-        <v>-4.3</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="25">
@@ -1803,7 +1803,7 @@
         <v>3620</v>
       </c>
       <c r="U25" t="n">
-        <v>106400</v>
+        <v>107800</v>
       </c>
     </row>
     <row r="26">
@@ -1869,13 +1869,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>9220</v>
+        <v>9200</v>
       </c>
       <c r="V26" t="n">
         <v>9420</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="27">
@@ -2013,13 +2013,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1220000</v>
+        <v>1218000</v>
       </c>
       <c r="V28" t="n">
         <v>1296000</v>
       </c>
       <c r="W28" t="n">
-        <v>-5.9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="29">
@@ -2199,13 +2199,13 @@
         <v>-0.1</v>
       </c>
       <c r="U31" t="n">
-        <v>182000</v>
+        <v>182600</v>
       </c>
       <c r="V31" t="n">
         <v>183300</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="32">
@@ -2247,7 +2247,7 @@
         <v>1807.7</v>
       </c>
       <c r="U32" t="n">
-        <v>43700</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="33">
@@ -2313,13 +2313,13 @@
         <v>-0.7</v>
       </c>
       <c r="U33" t="n">
-        <v>30800</v>
+        <v>31000</v>
       </c>
       <c r="V33" t="n">
         <v>35850</v>
       </c>
       <c r="W33" t="n">
-        <v>-14.1</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="34">
@@ -2361,7 +2361,7 @@
         <v>9348.6</v>
       </c>
       <c r="U34" t="n">
-        <v>349000</v>
+        <v>343000</v>
       </c>
     </row>
     <row r="35">
@@ -2427,13 +2427,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>394000</v>
+        <v>394500</v>
       </c>
       <c r="V35" t="n">
         <v>392500</v>
       </c>
       <c r="W35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -2475,7 +2475,7 @@
         <v>5355</v>
       </c>
       <c r="U36" t="n">
-        <v>24450</v>
+        <v>24650</v>
       </c>
     </row>
     <row r="37">
@@ -2541,13 +2541,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>95700</v>
+        <v>96000</v>
       </c>
       <c r="V37" t="n">
         <v>94600</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
@@ -2613,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>354500</v>
+        <v>354000</v>
       </c>
       <c r="V38" t="n">
         <v>366500</v>
       </c>
       <c r="W38" t="n">
-        <v>-3.3</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="39">
@@ -2685,13 +2685,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>315500</v>
+        <v>313500</v>
       </c>
       <c r="V39" t="n">
         <v>325500</v>
       </c>
       <c r="W39" t="n">
-        <v>-3.1</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="40">
@@ -2730,7 +2730,7 @@
         <v>25469.6</v>
       </c>
       <c r="U40" t="n">
-        <v>187200</v>
+        <v>190300</v>
       </c>
     </row>
     <row r="41">
@@ -2796,13 +2796,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>50100</v>
+        <v>50300</v>
       </c>
       <c r="V41" t="n">
         <v>50400</v>
       </c>
       <c r="W41" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="42">
@@ -2868,13 +2868,13 @@
         <v>3.3</v>
       </c>
       <c r="U42" t="n">
-        <v>274500</v>
+        <v>270000</v>
       </c>
       <c r="V42" t="n">
         <v>260000</v>
       </c>
       <c r="W42" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="43">
@@ -2982,13 +2982,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>8390</v>
+        <v>8440</v>
       </c>
       <c r="V44" t="n">
         <v>8670</v>
       </c>
       <c r="W44" t="n">
-        <v>-3.2</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="45">
@@ -3054,13 +3054,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>35700</v>
+        <v>36000</v>
       </c>
       <c r="V45" t="n">
         <v>35750</v>
       </c>
       <c r="W45" t="n">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="46">
@@ -3102,7 +3102,7 @@
         <v>26635.8</v>
       </c>
       <c r="U46" t="n">
-        <v>314500</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="47">
@@ -3168,13 +3168,13 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>123200</v>
+        <v>122900</v>
       </c>
       <c r="V47" t="n">
         <v>122100</v>
       </c>
       <c r="W47" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="48">
@@ -3240,13 +3240,13 @@
         <v>0.3</v>
       </c>
       <c r="U48" t="n">
-        <v>35750</v>
+        <v>35350</v>
       </c>
       <c r="V48" t="n">
         <v>37200</v>
       </c>
       <c r="W48" t="n">
-        <v>-3.9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="49">
@@ -3312,13 +3312,13 @@
         <v>-0.9</v>
       </c>
       <c r="U49" t="n">
-        <v>531000</v>
+        <v>528000</v>
       </c>
       <c r="V49" t="n">
         <v>542000</v>
       </c>
       <c r="W49" t="n">
-        <v>-2</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="50">
@@ -3360,7 +3360,7 @@
         <v>2380.2</v>
       </c>
       <c r="U50" t="n">
-        <v>92600</v>
+        <v>91800</v>
       </c>
     </row>
     <row r="51">
@@ -3402,7 +3402,7 @@
         <v>27610.4</v>
       </c>
       <c r="U51" t="n">
-        <v>31700</v>
+        <v>31650</v>
       </c>
     </row>
     <row r="52">
@@ -3444,7 +3444,7 @@
         <v>4117.4</v>
       </c>
       <c r="U52" t="n">
-        <v>22950</v>
+        <v>23050</v>
       </c>
     </row>
     <row r="53">
@@ -3486,7 +3486,7 @@
         <v>8137</v>
       </c>
       <c r="U53" t="n">
-        <v>48950</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="54">
@@ -3552,13 +3552,13 @@
         <v>0.7</v>
       </c>
       <c r="U54" t="n">
-        <v>115300</v>
+        <v>112000</v>
       </c>
       <c r="V54" t="n">
         <v>102400</v>
       </c>
       <c r="W54" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="55">
@@ -3624,13 +3624,13 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>69300</v>
+        <v>69600</v>
       </c>
       <c r="V55" t="n">
         <v>52200</v>
       </c>
       <c r="W55" t="n">
-        <v>32.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="56">
@@ -3672,7 +3672,7 @@
         <v>2727.2</v>
       </c>
       <c r="U56" t="n">
-        <v>40200</v>
+        <v>40300</v>
       </c>
     </row>
     <row r="57">
@@ -3738,13 +3738,13 @@
         <v>0.3</v>
       </c>
       <c r="U57" t="n">
-        <v>1503000</v>
+        <v>1491000</v>
       </c>
       <c r="V57" t="n">
         <v>1388000</v>
       </c>
       <c r="W57" t="n">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="58">
@@ -3786,7 +3786,7 @@
         <v>536.8</v>
       </c>
       <c r="U58" t="n">
-        <v>40650</v>
+        <v>40400</v>
       </c>
     </row>
     <row r="59">
@@ -3900,7 +3900,7 @@
         <v>14592.8</v>
       </c>
       <c r="U60" t="n">
-        <v>32500</v>
+        <v>34250</v>
       </c>
     </row>
     <row r="61">
@@ -3942,7 +3942,7 @@
         <v>6588.9</v>
       </c>
       <c r="U61" t="n">
-        <v>226500</v>
+        <v>232000</v>
       </c>
     </row>
     <row r="62">
@@ -4008,13 +4008,13 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
       <c r="V62" t="n">
         <v>208500</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.2</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="63">
@@ -4080,13 +4080,13 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1105000</v>
+        <v>1094000</v>
       </c>
       <c r="V63" t="n">
         <v>1132000</v>
       </c>
       <c r="W63" t="n">
-        <v>-2.4</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="64">
@@ -4191,7 +4191,7 @@
         <v>59</v>
       </c>
       <c r="U65" t="n">
-        <v>17600</v>
+        <v>17260</v>
       </c>
     </row>
     <row r="66">
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>14980</v>
+        <v>14970</v>
       </c>
       <c r="V66" t="n">
         <v>15500</v>
@@ -4305,7 +4305,7 @@
         <v>28485.6</v>
       </c>
       <c r="U67" t="n">
-        <v>163300</v>
+        <v>164000</v>
       </c>
     </row>
     <row r="68">
@@ -4371,13 +4371,13 @@
         <v>-0.8</v>
       </c>
       <c r="U68" t="n">
-        <v>579000</v>
+        <v>574000</v>
       </c>
       <c r="V68" t="n">
         <v>531000</v>
       </c>
       <c r="W68" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="69">
@@ -4419,7 +4419,7 @@
         <v>3593.9</v>
       </c>
       <c r="U69" t="n">
-        <v>61700</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="70">
@@ -4485,13 +4485,13 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>21200</v>
+        <v>21350</v>
       </c>
       <c r="V70" t="n">
         <v>20950</v>
       </c>
       <c r="W70" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="71">
@@ -4557,13 +4557,13 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>54200</v>
+        <v>53500</v>
       </c>
       <c r="V71" t="n">
         <v>54700</v>
       </c>
       <c r="W71" t="n">
-        <v>-0.9</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="72">
@@ -4605,7 +4605,7 @@
         <v>4720.3</v>
       </c>
       <c r="U72" t="n">
-        <v>118600</v>
+        <v>117500</v>
       </c>
     </row>
     <row r="73">
@@ -4647,7 +4647,7 @@
         <v>2495</v>
       </c>
       <c r="U73" t="n">
-        <v>91200</v>
+        <v>90200</v>
       </c>
     </row>
     <row r="74">
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>17660</v>
+        <v>17700</v>
       </c>
       <c r="V74" t="n">
         <v>16960</v>
       </c>
       <c r="W74" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="75">
@@ -4785,13 +4785,13 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>374500</v>
+        <v>371500</v>
       </c>
       <c r="V75" t="n">
         <v>380500</v>
       </c>
       <c r="W75" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="76">
@@ -4857,13 +4857,13 @@
         <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>1043000</v>
+        <v>1034000</v>
       </c>
       <c r="V76" t="n">
         <v>1092000</v>
       </c>
       <c r="W76" t="n">
-        <v>-4.5</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="77">
@@ -4905,7 +4905,7 @@
         <v>2558.3</v>
       </c>
       <c r="U77" t="n">
-        <v>335500</v>
+        <v>332000</v>
       </c>
     </row>
     <row r="78">
@@ -4947,7 +4947,7 @@
         <v>2694</v>
       </c>
       <c r="U78" t="n">
-        <v>82300</v>
+        <v>82900</v>
       </c>
     </row>
     <row r="79">
@@ -5013,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>31200</v>
+        <v>31150</v>
       </c>
       <c r="V79" t="n">
         <v>32300</v>
       </c>
       <c r="W79" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="80">
@@ -5085,13 +5085,13 @@
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>235500</v>
+        <v>239500</v>
       </c>
       <c r="V80" t="n">
         <v>215000</v>
       </c>
       <c r="W80" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="81">
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>2570</v>
+        <v>2590</v>
       </c>
       <c r="V81" t="n">
         <v>2505</v>
       </c>
       <c r="W81" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="82">
@@ -5205,7 +5205,7 @@
         <v>133061.2</v>
       </c>
       <c r="U82" t="n">
-        <v>30700</v>
+        <v>30600</v>
       </c>
     </row>
     <row r="83">
@@ -5247,7 +5247,7 @@
         <v>21395.8</v>
       </c>
       <c r="U83" t="n">
-        <v>88400</v>
+        <v>88800</v>
       </c>
     </row>
     <row r="84">
@@ -5313,13 +5313,13 @@
         <v>0.4</v>
       </c>
       <c r="U84" t="n">
-        <v>87900</v>
+        <v>87700</v>
       </c>
       <c r="V84" t="n">
         <v>89100</v>
       </c>
       <c r="W84" t="n">
-        <v>-1.3</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="85">
@@ -5361,7 +5361,7 @@
         <v>2300</v>
       </c>
       <c r="U85" t="n">
-        <v>73900</v>
+        <v>73700</v>
       </c>
     </row>
     <row r="86">
@@ -5427,13 +5427,13 @@
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>20400</v>
+        <v>20450</v>
       </c>
       <c r="V86" t="n">
         <v>21050</v>
       </c>
       <c r="W86" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="87">
@@ -5499,13 +5499,13 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>219000</v>
+        <v>218000</v>
       </c>
       <c r="V87" t="n">
         <v>220000</v>
       </c>
       <c r="W87" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="88">
@@ -5571,13 +5571,13 @@
         <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>3320</v>
+        <v>3280</v>
       </c>
       <c r="V88" t="n">
         <v>3450</v>
       </c>
       <c r="W88" t="n">
-        <v>-3.8</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="89">
@@ -5619,7 +5619,7 @@
         <v>12775.5</v>
       </c>
       <c r="U89" t="n">
-        <v>99900</v>
+        <v>100700</v>
       </c>
     </row>
     <row r="90">
@@ -5661,7 +5661,7 @@
         <v>1161</v>
       </c>
       <c r="U90" t="n">
-        <v>20250</v>
+        <v>20150</v>
       </c>
     </row>
     <row r="91">
@@ -5727,13 +5727,13 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>27450</v>
+        <v>27650</v>
       </c>
       <c r="V91" t="n">
         <v>26550</v>
       </c>
       <c r="W91" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="92">
@@ -5775,7 +5775,7 @@
         <v>9380.1</v>
       </c>
       <c r="U92" t="n">
-        <v>101900</v>
+        <v>102200</v>
       </c>
     </row>
     <row r="93">
@@ -5817,7 +5817,7 @@
         <v>42377.2</v>
       </c>
       <c r="U93" t="n">
-        <v>20850</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="94">
@@ -5883,13 +5883,13 @@
         <v>-0.2</v>
       </c>
       <c r="U94" t="n">
-        <v>49750</v>
+        <v>49900</v>
       </c>
       <c r="V94" t="n">
         <v>52100</v>
       </c>
       <c r="W94" t="n">
-        <v>-4.5</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="95">
@@ -5955,13 +5955,13 @@
         <v>0.4</v>
       </c>
       <c r="U95" t="n">
-        <v>346500</v>
+        <v>345500</v>
       </c>
       <c r="V95" t="n">
         <v>353500</v>
       </c>
       <c r="W95" t="n">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="96">
@@ -6027,13 +6027,13 @@
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>5700</v>
+        <v>5690</v>
       </c>
       <c r="V96" t="n">
         <v>5770</v>
       </c>
       <c r="W96" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="97">
@@ -6075,7 +6075,7 @@
         <v>8603.299999999999</v>
       </c>
       <c r="U97" t="n">
-        <v>43100</v>
+        <v>43150</v>
       </c>
     </row>
     <row r="98">
@@ -6117,7 +6117,7 @@
         <v>3624.1</v>
       </c>
       <c r="U98" t="n">
-        <v>17770</v>
+        <v>17810</v>
       </c>
     </row>
     <row r="99">
@@ -6231,7 +6231,7 @@
         <v>1930.3</v>
       </c>
       <c r="U100" t="n">
-        <v>170700</v>
+        <v>166900</v>
       </c>
     </row>
     <row r="101">
@@ -6270,13 +6270,13 @@
         <v>-1.4</v>
       </c>
       <c r="U101" t="n">
-        <v>11790</v>
+        <v>11810</v>
       </c>
       <c r="V101" t="n">
         <v>11730</v>
       </c>
       <c r="W101" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="102">
@@ -6342,13 +6342,13 @@
         <v>0.2</v>
       </c>
       <c r="U102" t="n">
-        <v>14810</v>
+        <v>14780</v>
       </c>
       <c r="V102" t="n">
         <v>14190</v>
       </c>
       <c r="W102" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="103">
@@ -6390,7 +6390,7 @@
         <v>45800.4</v>
       </c>
       <c r="U103" t="n">
-        <v>290500</v>
+        <v>293000</v>
       </c>
     </row>
     <row r="104">
@@ -6456,13 +6456,13 @@
         <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>15950</v>
+        <v>16000</v>
       </c>
       <c r="V104" t="n">
         <v>16640</v>
       </c>
       <c r="W104" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="105">
@@ -6528,13 +6528,13 @@
         <v>0.5</v>
       </c>
       <c r="U105" t="n">
-        <v>175400</v>
+        <v>174600</v>
       </c>
       <c r="V105" t="n">
         <v>172800</v>
       </c>
       <c r="W105" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -6576,7 +6576,7 @@
         <v>20657.3</v>
       </c>
       <c r="U106" t="n">
-        <v>82000</v>
+        <v>81100</v>
       </c>
     </row>
     <row r="107">
@@ -6684,13 +6684,13 @@
         <v>0</v>
       </c>
       <c r="U108" t="n">
-        <v>9600</v>
+        <v>9670</v>
       </c>
       <c r="V108" t="n">
         <v>9670</v>
       </c>
       <c r="W108" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6732,7 +6732,7 @@
         <v>131827.2</v>
       </c>
       <c r="U109" t="n">
-        <v>573000</v>
+        <v>576000</v>
       </c>
     </row>
     <row r="110">
@@ -6798,13 +6798,13 @@
         <v>0</v>
       </c>
       <c r="U110" t="n">
-        <v>14390</v>
+        <v>14430</v>
       </c>
       <c r="V110" t="n">
         <v>14420</v>
       </c>
       <c r="W110" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="111">
@@ -6870,13 +6870,13 @@
         <v>1.6</v>
       </c>
       <c r="U111" t="n">
-        <v>199200</v>
+        <v>196300</v>
       </c>
       <c r="V111" t="n">
         <v>197500</v>
       </c>
       <c r="W111" t="n">
-        <v>0.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="112">
@@ -6942,13 +6942,13 @@
         <v>0.3</v>
       </c>
       <c r="U112" t="n">
-        <v>34300</v>
+        <v>33950</v>
       </c>
       <c r="V112" t="n">
         <v>33600</v>
       </c>
       <c r="W112" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -7158,13 +7158,13 @@
         <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>9390</v>
+        <v>9300</v>
       </c>
       <c r="V115" t="n">
         <v>9110</v>
       </c>
       <c r="W115" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="116">
@@ -7206,7 +7206,7 @@
         <v>24626</v>
       </c>
       <c r="U116" t="n">
-        <v>35300</v>
+        <v>35450</v>
       </c>
     </row>
     <row r="117">
@@ -7272,13 +7272,13 @@
         <v>-0.4</v>
       </c>
       <c r="U117" t="n">
-        <v>215000</v>
+        <v>213500</v>
       </c>
       <c r="V117" t="n">
         <v>209000</v>
       </c>
       <c r="W117" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="118">
@@ -7344,13 +7344,13 @@
         <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>210000</v>
+        <v>208000</v>
       </c>
       <c r="V118" t="n">
         <v>204500</v>
       </c>
       <c r="W118" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="119">
@@ -7392,7 +7392,7 @@
         <v>2373</v>
       </c>
       <c r="U119" t="n">
-        <v>472500</v>
+        <v>467500</v>
       </c>
     </row>
     <row r="120">
@@ -7506,7 +7506,7 @@
         <v>19670.8</v>
       </c>
       <c r="U121" t="n">
-        <v>255500</v>
+        <v>256500</v>
       </c>
     </row>
     <row r="122">
@@ -7572,13 +7572,13 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>9380</v>
+        <v>9430</v>
       </c>
       <c r="V122" t="n">
         <v>9950</v>
       </c>
       <c r="W122" t="n">
-        <v>-5.7</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="123">
@@ -7644,13 +7644,13 @@
         <v>-0.1</v>
       </c>
       <c r="U123" t="n">
-        <v>81400</v>
+        <v>82300</v>
       </c>
       <c r="V123" t="n">
         <v>81600</v>
       </c>
       <c r="W123" t="n">
-        <v>-0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="124">
@@ -7716,13 +7716,13 @@
         <v>0.1</v>
       </c>
       <c r="U124" t="n">
-        <v>80300</v>
+        <v>80500</v>
       </c>
       <c r="V124" t="n">
         <v>83500</v>
       </c>
       <c r="W124" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="125">
@@ -7764,7 +7764,7 @@
         <v>6843</v>
       </c>
       <c r="U125" t="n">
-        <v>239000</v>
+        <v>233000</v>
       </c>
     </row>
     <row r="126">
@@ -7803,7 +7803,7 @@
         <v>2273</v>
       </c>
       <c r="U126" t="n">
-        <v>25050</v>
+        <v>24700</v>
       </c>
     </row>
     <row r="127">
@@ -7869,13 +7869,13 @@
         <v>0.2</v>
       </c>
       <c r="U127" t="n">
-        <v>18740</v>
+        <v>18620</v>
       </c>
       <c r="V127" t="n">
         <v>19020</v>
       </c>
       <c r="W127" t="n">
-        <v>-1.5</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="128">
@@ -7941,13 +7941,13 @@
         <v>-0.1</v>
       </c>
       <c r="U128" t="n">
-        <v>57700</v>
+        <v>56900</v>
       </c>
       <c r="V128" t="n">
         <v>57100</v>
       </c>
       <c r="W128" t="n">
-        <v>1.1</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="129">
@@ -8013,13 +8013,13 @@
         <v>-0.8</v>
       </c>
       <c r="U129" t="n">
-        <v>130100</v>
+        <v>128600</v>
       </c>
       <c r="V129" t="n">
         <v>130200</v>
       </c>
       <c r="W129" t="n">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="130">
@@ -8085,13 +8085,13 @@
         <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>21800</v>
+        <v>21850</v>
       </c>
       <c r="V130" t="n">
         <v>21950</v>
       </c>
       <c r="W130" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="131">
@@ -8133,7 +8133,7 @@
         <v>2090.2</v>
       </c>
       <c r="U131" t="n">
-        <v>46300</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="132">
@@ -8175,7 +8175,7 @@
         <v>4861.5</v>
       </c>
       <c r="U132" t="n">
-        <v>289250</v>
+        <v>291500</v>
       </c>
     </row>
     <row r="133">
@@ -8217,7 +8217,7 @@
         <v>55616.1</v>
       </c>
       <c r="U133" t="n">
-        <v>259500</v>
+        <v>262000</v>
       </c>
     </row>
     <row r="134">
@@ -8259,7 +8259,7 @@
         <v>1507.4</v>
       </c>
       <c r="U134" t="n">
-        <v>127500</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="135">
@@ -8301,7 +8301,7 @@
         <v>87826.2</v>
       </c>
       <c r="U135" t="n">
-        <v>111100</v>
+        <v>110800</v>
       </c>
     </row>
     <row r="136">
@@ -8343,7 +8343,7 @@
         <v>3109.5</v>
       </c>
       <c r="U136" t="n">
-        <v>72100</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="137">
@@ -8409,13 +8409,13 @@
         <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>98700</v>
+        <v>96800</v>
       </c>
       <c r="V137" t="n">
         <v>99100</v>
       </c>
       <c r="W137" t="n">
-        <v>-0.4</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="138">
@@ -8472,13 +8472,13 @@
         <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>38850</v>
+        <v>39050</v>
       </c>
       <c r="V138" t="n">
         <v>39950</v>
       </c>
       <c r="W138" t="n">
-        <v>-2.8</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="139">
@@ -8520,7 +8520,7 @@
         <v>4380.8</v>
       </c>
       <c r="U139" t="n">
-        <v>203000</v>
+        <v>199900</v>
       </c>
     </row>
     <row r="140">
@@ -8586,13 +8586,13 @@
         <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>117000</v>
+        <v>116200</v>
       </c>
       <c r="V140" t="n">
         <v>123500</v>
       </c>
       <c r="W140" t="n">
-        <v>-5.3</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="141">
@@ -8634,7 +8634,7 @@
         <v>7375.3</v>
       </c>
       <c r="U141" t="n">
-        <v>70600</v>
+        <v>69700</v>
       </c>
     </row>
     <row r="142">
@@ -8676,7 +8676,7 @@
         <v>2073.8</v>
       </c>
       <c r="U142" t="n">
-        <v>275000</v>
+        <v>277500</v>
       </c>
     </row>
     <row r="143">
@@ -8742,13 +8742,13 @@
         <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>26150</v>
+        <v>27250</v>
       </c>
       <c r="V143" t="n">
         <v>26100</v>
       </c>
       <c r="W143" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="144">
@@ -8814,13 +8814,13 @@
         <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>215500</v>
+        <v>214500</v>
       </c>
       <c r="V144" t="n">
         <v>198700</v>
       </c>
       <c r="W144" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145">
@@ -8886,13 +8886,13 @@
         <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>113500</v>
+        <v>114500</v>
       </c>
       <c r="V145" t="n">
         <v>110500</v>
       </c>
       <c r="W145" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="146">
@@ -8958,13 +8958,13 @@
         <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>36450</v>
+        <v>37000</v>
       </c>
       <c r="V146" t="n">
         <v>37000</v>
       </c>
       <c r="W146" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -9006,7 +9006,7 @@
         <v>4756</v>
       </c>
       <c r="U147" t="n">
-        <v>45950</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="148">
@@ -9072,13 +9072,13 @@
         <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>178600</v>
+        <v>177900</v>
       </c>
       <c r="V148" t="n">
         <v>180100</v>
       </c>
       <c r="W148" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="149">
@@ -9120,7 +9120,7 @@
         <v>1060</v>
       </c>
       <c r="U149" t="n">
-        <v>16330</v>
+        <v>16360</v>
       </c>
     </row>
     <row r="150">
@@ -9234,7 +9234,7 @@
         <v>5553.6</v>
       </c>
       <c r="U151" t="n">
-        <v>92700</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="152">
@@ -9276,7 +9276,7 @@
         <v>33383.2</v>
       </c>
       <c r="U152" t="n">
-        <v>182300</v>
+        <v>181700</v>
       </c>
     </row>
     <row r="153">
@@ -9318,7 +9318,7 @@
         <v>4094</v>
       </c>
       <c r="U153" t="n">
-        <v>78700</v>
+        <v>78800</v>
       </c>
     </row>
     <row r="154">
@@ -9384,13 +9384,13 @@
         <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>48900</v>
+        <v>48950</v>
       </c>
       <c r="V154" t="n">
         <v>52100</v>
       </c>
       <c r="W154" t="n">
-        <v>-6.1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="155">
@@ -9456,13 +9456,13 @@
         <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>6900</v>
+        <v>6810</v>
       </c>
       <c r="V155" t="n">
         <v>7040</v>
       </c>
       <c r="W155" t="n">
-        <v>-2</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="156">
@@ -9501,13 +9501,13 @@
         <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>9970</v>
+        <v>9990</v>
       </c>
       <c r="V156" t="n">
         <v>10350</v>
       </c>
       <c r="W156" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="157">
@@ -9546,13 +9546,13 @@
         <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>13050</v>
+        <v>12700</v>
       </c>
       <c r="V157" t="n">
         <v>11550</v>
       </c>
       <c r="W157" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
@@ -9666,7 +9666,7 @@
         <v>36994</v>
       </c>
       <c r="U159" t="n">
-        <v>112000</v>
+        <v>114300</v>
       </c>
     </row>
     <row r="160">
@@ -9732,13 +9732,13 @@
         <v>-0.4</v>
       </c>
       <c r="U160" t="n">
-        <v>691000</v>
+        <v>690000</v>
       </c>
       <c r="V160" t="n">
         <v>737000</v>
       </c>
       <c r="W160" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="161">
@@ -9777,13 +9777,13 @@
         <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>8450</v>
+        <v>8470</v>
       </c>
       <c r="V161" t="n">
         <v>8990</v>
       </c>
       <c r="W161" t="n">
-        <v>-6</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="162">
@@ -9825,7 +9825,7 @@
         <v>6392</v>
       </c>
       <c r="U162" t="n">
-        <v>38250</v>
+        <v>38200</v>
       </c>
     </row>
     <row r="163">
@@ -9891,13 +9891,13 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>48000</v>
+        <v>47550</v>
       </c>
       <c r="V163" t="n">
         <v>51600</v>
       </c>
       <c r="W163" t="n">
-        <v>-7</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="164">
@@ -9939,7 +9939,7 @@
         <v>2224</v>
       </c>
       <c r="U164" t="n">
-        <v>60400</v>
+        <v>60100</v>
       </c>
     </row>
     <row r="165">
@@ -9981,7 +9981,7 @@
         <v>1800</v>
       </c>
       <c r="U165" t="n">
-        <v>155900</v>
+        <v>154100</v>
       </c>
     </row>
     <row r="166">
@@ -10047,13 +10047,13 @@
         <v>0</v>
       </c>
       <c r="U166" t="n">
-        <v>201000</v>
+        <v>198100</v>
       </c>
       <c r="V166" t="n">
         <v>204000</v>
       </c>
       <c r="W166" t="n">
-        <v>-1.5</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="167">
@@ -10137,7 +10137,7 @@
         <v>10708.8</v>
       </c>
       <c r="U168" t="n">
-        <v>5780</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="169">
@@ -10203,13 +10203,13 @@
         <v>0</v>
       </c>
       <c r="U169" t="n">
-        <v>49250</v>
+        <v>49550</v>
       </c>
       <c r="V169" t="n">
         <v>49000</v>
       </c>
       <c r="W169" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="170">
@@ -10275,13 +10275,13 @@
         <v>0</v>
       </c>
       <c r="U170" t="n">
-        <v>60600</v>
+        <v>59800</v>
       </c>
       <c r="V170" t="n">
         <v>55100</v>
       </c>
       <c r="W170" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="171">
@@ -10347,13 +10347,13 @@
         <v>0</v>
       </c>
       <c r="U171" t="n">
-        <v>142800</v>
+        <v>141900</v>
       </c>
       <c r="V171" t="n">
         <v>142700</v>
       </c>
       <c r="W171" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="172">
@@ -10386,7 +10386,7 @@
         <v>243</v>
       </c>
       <c r="U172" t="n">
-        <v>13960</v>
+        <v>13980</v>
       </c>
     </row>
     <row r="173">
@@ -10428,7 +10428,7 @@
         <v>1766.5</v>
       </c>
       <c r="U173" t="n">
-        <v>204000</v>
+        <v>203500</v>
       </c>
     </row>
     <row r="174">
@@ -10470,7 +10470,7 @@
         <v>1928.5</v>
       </c>
       <c r="U174" t="n">
-        <v>163400</v>
+        <v>161900</v>
       </c>
     </row>
     <row r="175">
@@ -10536,13 +10536,13 @@
         <v>-2.1</v>
       </c>
       <c r="U175" t="n">
-        <v>17860</v>
+        <v>17840</v>
       </c>
       <c r="V175" t="n">
         <v>17800</v>
       </c>
       <c r="W175" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="176">
@@ -10608,13 +10608,13 @@
         <v>0</v>
       </c>
       <c r="U176" t="n">
-        <v>34500</v>
+        <v>34100</v>
       </c>
       <c r="V176" t="n">
         <v>33900</v>
       </c>
       <c r="W176" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="177">
@@ -10656,7 +10656,7 @@
         <v>43017.9</v>
       </c>
       <c r="U177" t="n">
-        <v>157700</v>
+        <v>158900</v>
       </c>
     </row>
     <row r="178">
@@ -10722,13 +10722,13 @@
         <v>0</v>
       </c>
       <c r="U178" t="n">
-        <v>178600</v>
+        <v>178800</v>
       </c>
       <c r="V178" t="n">
         <v>175000</v>
       </c>
       <c r="W178" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="179">
@@ -10761,7 +10761,7 @@
         <v>156</v>
       </c>
       <c r="U179" t="n">
-        <v>29150</v>
+        <v>28850</v>
       </c>
     </row>
     <row r="180">
@@ -10827,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>15960</v>
+        <v>15950</v>
       </c>
       <c r="V180" t="n">
         <v>16200</v>
@@ -10899,13 +10899,13 @@
         <v>0</v>
       </c>
       <c r="U181" t="n">
-        <v>80000</v>
+        <v>80300</v>
       </c>
       <c r="V181" t="n">
         <v>78900</v>
       </c>
       <c r="W181" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="182">
@@ -10971,13 +10971,13 @@
         <v>0</v>
       </c>
       <c r="U182" t="n">
-        <v>78200</v>
+        <v>77900</v>
       </c>
       <c r="V182" t="n">
         <v>79700</v>
       </c>
       <c r="W182" t="n">
-        <v>-1.9</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="183">
@@ -11019,7 +11019,7 @@
         <v>98431.89999999999</v>
       </c>
       <c r="U183" t="n">
-        <v>174000</v>
+        <v>173800</v>
       </c>
     </row>
     <row r="184">
@@ -11085,13 +11085,13 @@
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>292000</v>
+        <v>283500</v>
       </c>
       <c r="V184" t="n">
         <v>307500</v>
       </c>
       <c r="W184" t="n">
-        <v>-5</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="185">
@@ -11133,7 +11133,7 @@
         <v>7986.8</v>
       </c>
       <c r="U185" t="n">
-        <v>71400</v>
+        <v>71100</v>
       </c>
     </row>
     <row r="186">
@@ -11175,7 +11175,7 @@
         <v>2642.8</v>
       </c>
       <c r="U186" t="n">
-        <v>50900</v>
+        <v>52800</v>
       </c>
     </row>
     <row r="187">
@@ -11262,7 +11262,7 @@
         <v>3361.8</v>
       </c>
       <c r="U188" t="n">
-        <v>55600</v>
+        <v>55700</v>
       </c>
     </row>
     <row r="189">
@@ -11328,13 +11328,13 @@
         <v>0</v>
       </c>
       <c r="U189" t="n">
-        <v>42600</v>
+        <v>42700</v>
       </c>
       <c r="V189" t="n">
         <v>43600</v>
       </c>
       <c r="W189" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="190">
@@ -11400,13 +11400,13 @@
         <v>0</v>
       </c>
       <c r="U190" t="n">
-        <v>505000</v>
+        <v>503000</v>
       </c>
       <c r="V190" t="n">
         <v>505000</v>
       </c>
       <c r="W190" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="191">
@@ -11448,7 +11448,7 @@
         <v>3054</v>
       </c>
       <c r="U191" t="n">
-        <v>287500</v>
+        <v>293000</v>
       </c>
     </row>
     <row r="192">
@@ -11490,7 +11490,7 @@
         <v>35646.6</v>
       </c>
       <c r="U192" t="n">
-        <v>130300</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="193">
@@ -11532,7 +11532,7 @@
         <v>11736.9</v>
       </c>
       <c r="U193" t="n">
-        <v>16410</v>
+        <v>16470</v>
       </c>
     </row>
     <row r="194">
@@ -11574,7 +11574,7 @@
         <v>7286.1</v>
       </c>
       <c r="U194" t="n">
-        <v>18810</v>
+        <v>18700</v>
       </c>
     </row>
     <row r="195">
@@ -11616,7 +11616,7 @@
         <v>6040.5</v>
       </c>
       <c r="U195" t="n">
-        <v>71900</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="196">
@@ -11658,7 +11658,7 @@
         <v>842.6</v>
       </c>
       <c r="U196" t="n">
-        <v>261500</v>
+        <v>263500</v>
       </c>
     </row>
     <row r="197">
@@ -11715,13 +11715,13 @@
         <v>0</v>
       </c>
       <c r="U197" t="n">
-        <v>80900</v>
+        <v>79400</v>
       </c>
       <c r="V197" t="n">
         <v>81900</v>
       </c>
       <c r="W197" t="n">
-        <v>-1.2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="198">
@@ -11787,13 +11787,13 @@
         <v>-2.3</v>
       </c>
       <c r="U198" t="n">
-        <v>188900</v>
+        <v>185700</v>
       </c>
       <c r="V198" t="n">
         <v>215000</v>
       </c>
       <c r="W198" t="n">
-        <v>-12.1</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="199">
@@ -11904,13 +11904,13 @@
         <v>0</v>
       </c>
       <c r="U200" t="n">
-        <v>10500</v>
+        <v>10400</v>
       </c>
       <c r="V200" t="n">
         <v>10050</v>
       </c>
       <c r="W200" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="201">
@@ -11976,13 +11976,13 @@
         <v>0</v>
       </c>
       <c r="U201" t="n">
-        <v>58400</v>
+        <v>59300</v>
       </c>
       <c r="V201" t="n">
         <v>60700</v>
       </c>
       <c r="W201" t="n">
-        <v>-3.8</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="202">
@@ -12048,13 +12048,13 @@
         <v>0</v>
       </c>
       <c r="U202" t="n">
-        <v>147800</v>
+        <v>148000</v>
       </c>
       <c r="V202" t="n">
         <v>145500</v>
       </c>
       <c r="W202" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="203">
@@ -12120,13 +12120,13 @@
         <v>0</v>
       </c>
       <c r="U203" t="n">
-        <v>34650</v>
+        <v>34750</v>
       </c>
       <c r="V203" t="n">
         <v>35700</v>
       </c>
       <c r="W203" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="204">
@@ -12210,7 +12210,7 @@
         <v>3491.5</v>
       </c>
       <c r="U205" t="n">
-        <v>36150</v>
+        <v>36300</v>
       </c>
     </row>
     <row r="206">
@@ -12276,13 +12276,13 @@
         <v>0</v>
       </c>
       <c r="U206" t="n">
-        <v>64800</v>
+        <v>65200</v>
       </c>
       <c r="V206" t="n">
         <v>64400</v>
       </c>
       <c r="W206" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="207">
@@ -12348,13 +12348,13 @@
         <v>0</v>
       </c>
       <c r="U207" t="n">
-        <v>68400</v>
+        <v>67200</v>
       </c>
       <c r="V207" t="n">
         <v>68600</v>
       </c>
       <c r="W207" t="n">
-        <v>-0.3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="208">
@@ -12420,13 +12420,13 @@
         <v>0</v>
       </c>
       <c r="U208" t="n">
-        <v>59000</v>
+        <v>58600</v>
       </c>
       <c r="V208" t="n">
         <v>59000</v>
       </c>
       <c r="W208" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="209">
@@ -12492,13 +12492,13 @@
         <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>272500</v>
+        <v>269500</v>
       </c>
       <c r="V209" t="n">
         <v>274000</v>
       </c>
       <c r="W209" t="n">
-        <v>-0.5</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="210">
@@ -12564,13 +12564,13 @@
         <v>0</v>
       </c>
       <c r="U210" t="n">
-        <v>39250</v>
+        <v>39150</v>
       </c>
       <c r="V210" t="n">
         <v>38900</v>
       </c>
       <c r="W210" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="211">
@@ -12612,7 +12612,7 @@
         <v>5785</v>
       </c>
       <c r="U211" t="n">
-        <v>254000</v>
+        <v>251000</v>
       </c>
     </row>
     <row r="212">
@@ -12678,13 +12678,13 @@
         <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>46450</v>
+        <v>46250</v>
       </c>
       <c r="V212" t="n">
         <v>48250</v>
       </c>
       <c r="W212" t="n">
-        <v>-3.7</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="213">
@@ -12750,13 +12750,13 @@
         <v>0</v>
       </c>
       <c r="U213" t="n">
-        <v>1388000</v>
+        <v>1390000</v>
       </c>
       <c r="V213" t="n">
         <v>1399000</v>
       </c>
       <c r="W213" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="214">
@@ -12822,13 +12822,13 @@
         <v>-1.2</v>
       </c>
       <c r="U214" t="n">
-        <v>31000</v>
+        <v>30850</v>
       </c>
       <c r="V214" t="n">
         <v>31450</v>
       </c>
       <c r="W214" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="215">
@@ -12894,13 +12894,13 @@
         <v>0.7</v>
       </c>
       <c r="U215" t="n">
-        <v>321000</v>
+        <v>319000</v>
       </c>
       <c r="V215" t="n">
         <v>327000</v>
       </c>
       <c r="W215" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="216">
@@ -12966,13 +12966,13 @@
         <v>0</v>
       </c>
       <c r="U216" t="n">
-        <v>57200</v>
+        <v>56400</v>
       </c>
       <c r="V216" t="n">
         <v>61300</v>
       </c>
       <c r="W216" t="n">
-        <v>-6.7</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="217">
@@ -13014,7 +13014,7 @@
         <v>5480.8</v>
       </c>
       <c r="U217" t="n">
-        <v>149300</v>
+        <v>145100</v>
       </c>
     </row>
     <row r="218">
@@ -13080,13 +13080,13 @@
         <v>0</v>
       </c>
       <c r="U218" t="n">
-        <v>93300</v>
+        <v>92800</v>
       </c>
       <c r="V218" t="n">
         <v>92700</v>
       </c>
       <c r="W218" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="219">
@@ -13128,7 +13128,7 @@
         <v>3478.3</v>
       </c>
       <c r="U219" t="n">
-        <v>126600</v>
+        <v>123700</v>
       </c>
     </row>
     <row r="220">
@@ -13194,13 +13194,13 @@
         <v>0</v>
       </c>
       <c r="U220" t="n">
-        <v>58100</v>
+        <v>58300</v>
       </c>
       <c r="V220" t="n">
         <v>59400</v>
       </c>
       <c r="W220" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="221">
@@ -13266,13 +13266,13 @@
         <v>0</v>
       </c>
       <c r="U221" t="n">
-        <v>126600</v>
+        <v>125000</v>
       </c>
       <c r="V221" t="n">
         <v>132100</v>
       </c>
       <c r="W221" t="n">
-        <v>-4.2</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="222">
@@ -13338,13 +13338,13 @@
         <v>0</v>
       </c>
       <c r="U222" t="n">
-        <v>107500</v>
+        <v>110500</v>
       </c>
       <c r="V222" t="n">
         <v>105300</v>
       </c>
       <c r="W222" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="223">
@@ -13410,13 +13410,13 @@
         <v>0</v>
       </c>
       <c r="U223" t="n">
-        <v>35150</v>
+        <v>35300</v>
       </c>
       <c r="V223" t="n">
         <v>34750</v>
       </c>
       <c r="W223" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="224">
@@ -13482,13 +13482,13 @@
         <v>0</v>
       </c>
       <c r="U224" t="n">
-        <v>62300</v>
+        <v>62100</v>
       </c>
       <c r="V224" t="n">
         <v>61700</v>
       </c>
       <c r="W224" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="225">
@@ -13602,7 +13602,7 @@
         <v>4611.6</v>
       </c>
       <c r="U226" t="n">
-        <v>38900</v>
+        <v>38700</v>
       </c>
     </row>
     <row r="227">
@@ -13668,13 +13668,13 @@
         <v>0</v>
       </c>
       <c r="U227" t="n">
-        <v>201000</v>
+        <v>200500</v>
       </c>
       <c r="V227" t="n">
         <v>204500</v>
       </c>
       <c r="W227" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="228">
@@ -13716,7 +13716,7 @@
         <v>2262.8</v>
       </c>
       <c r="U228" t="n">
-        <v>33500</v>
+        <v>33100</v>
       </c>
     </row>
     <row r="229">
@@ -13758,7 +13758,7 @@
         <v>132859.2</v>
       </c>
       <c r="U229" t="n">
-        <v>210500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="230">
@@ -13896,13 +13896,13 @@
         <v>0</v>
       </c>
       <c r="U231" t="n">
-        <v>129900</v>
+        <v>128400</v>
       </c>
       <c r="V231" t="n">
         <v>140400</v>
       </c>
       <c r="W231" t="n">
-        <v>-7.5</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="232">
@@ -13968,13 +13968,13 @@
         <v>0</v>
       </c>
       <c r="U232" t="n">
-        <v>111300</v>
+        <v>111600</v>
       </c>
       <c r="V232" t="n">
         <v>112500</v>
       </c>
       <c r="W232" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="233">
@@ -14040,13 +14040,13 @@
         <v>0</v>
       </c>
       <c r="U233" t="n">
-        <v>72800</v>
+        <v>72600</v>
       </c>
       <c r="V233" t="n">
         <v>79900</v>
       </c>
       <c r="W233" t="n">
-        <v>-8.9</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="234">
@@ -14112,13 +14112,13 @@
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>6020</v>
+        <v>5960</v>
       </c>
       <c r="V234" t="n">
         <v>5820</v>
       </c>
       <c r="W234" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="235">
@@ -14175,13 +14175,13 @@
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>426000</v>
+        <v>422500</v>
       </c>
       <c r="V235" t="n">
         <v>434500</v>
       </c>
       <c r="W235" t="n">
-        <v>-2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="236">
@@ -14247,13 +14247,13 @@
         <v>0</v>
       </c>
       <c r="U236" t="n">
-        <v>366000</v>
+        <v>367000</v>
       </c>
       <c r="V236" t="n">
         <v>368000</v>
       </c>
       <c r="W236" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="237">
@@ -14319,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="U237" t="n">
-        <v>126000</v>
+        <v>125900</v>
       </c>
       <c r="V237" t="n">
         <v>127100</v>
@@ -14367,7 +14367,7 @@
         <v>3671.2</v>
       </c>
       <c r="U238" t="n">
-        <v>133000</v>
+        <v>133500</v>
       </c>
     </row>
     <row r="239">
@@ -14409,7 +14409,7 @@
         <v>2230</v>
       </c>
       <c r="U239" t="n">
-        <v>51600</v>
+        <v>51700</v>
       </c>
     </row>
     <row r="240">
@@ -14523,7 +14523,7 @@
         <v>6487.3</v>
       </c>
       <c r="U241" t="n">
-        <v>313500</v>
+        <v>311000</v>
       </c>
     </row>
     <row r="242">
@@ -14589,13 +14589,13 @@
         <v>0.3</v>
       </c>
       <c r="U242" t="n">
-        <v>2787000</v>
+        <v>2784000</v>
       </c>
       <c r="V242" t="n">
         <v>2888000</v>
       </c>
       <c r="W242" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="243">
@@ -14637,7 +14637,7 @@
         <v>2979.5</v>
       </c>
       <c r="U243" t="n">
-        <v>165100</v>
+        <v>165900</v>
       </c>
     </row>
     <row r="244">
@@ -14679,7 +14679,7 @@
         <v>1723.5</v>
       </c>
       <c r="U244" t="n">
-        <v>16330</v>
+        <v>16280</v>
       </c>
     </row>
     <row r="245">
@@ -14736,13 +14736,13 @@
         <v>0</v>
       </c>
       <c r="U245" t="n">
-        <v>36350</v>
+        <v>36100</v>
       </c>
       <c r="V245" t="n">
         <v>35350</v>
       </c>
       <c r="W245" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="246">
@@ -14808,13 +14808,13 @@
         <v>4.6</v>
       </c>
       <c r="U246" t="n">
-        <v>145800</v>
+        <v>146200</v>
       </c>
       <c r="V246" t="n">
         <v>148000</v>
       </c>
       <c r="W246" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="247">
@@ -14856,7 +14856,7 @@
         <v>4543.1</v>
       </c>
       <c r="U247" t="n">
-        <v>378000</v>
+        <v>374500</v>
       </c>
     </row>
     <row r="248">
@@ -14898,7 +14898,7 @@
         <v>50413.7</v>
       </c>
       <c r="U248" t="n">
-        <v>36250</v>
+        <v>36200</v>
       </c>
     </row>
     <row r="249">
@@ -14964,13 +14964,13 @@
         <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>9870</v>
+        <v>9680</v>
       </c>
       <c r="V249" t="n">
         <v>10040</v>
       </c>
       <c r="W249" t="n">
-        <v>-1.7</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="250">
@@ -15012,7 +15012,7 @@
         <v>2609.8</v>
       </c>
       <c r="U250" t="n">
-        <v>142700</v>
+        <v>141000</v>
       </c>
     </row>
     <row r="251">
@@ -15078,13 +15078,13 @@
         <v>0</v>
       </c>
       <c r="U251" t="n">
-        <v>20350</v>
+        <v>20400</v>
       </c>
       <c r="V251" t="n">
         <v>20550</v>
       </c>
       <c r="W251" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="252">
@@ -15150,13 +15150,13 @@
         <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>76300</v>
+        <v>76000</v>
       </c>
       <c r="V252" t="n">
         <v>77900</v>
       </c>
       <c r="W252" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="253">
@@ -15222,13 +15222,13 @@
         <v>0</v>
       </c>
       <c r="U253" t="n">
-        <v>441250</v>
+        <v>439000</v>
       </c>
       <c r="V253" t="n">
         <v>462000</v>
       </c>
       <c r="W253" t="n">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="254">
@@ -15294,13 +15294,13 @@
         <v>-0.1</v>
       </c>
       <c r="U254" t="n">
-        <v>162500</v>
+        <v>161900</v>
       </c>
       <c r="V254" t="n">
         <v>166700</v>
       </c>
       <c r="W254" t="n">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="255">
@@ -15366,13 +15366,13 @@
         <v>0</v>
       </c>
       <c r="U255" t="n">
-        <v>123000</v>
+        <v>121700</v>
       </c>
       <c r="V255" t="n">
         <v>103100</v>
       </c>
       <c r="W255" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="256">
@@ -15414,7 +15414,7 @@
         <v>3590.6</v>
       </c>
       <c r="U256" t="n">
-        <v>373500</v>
+        <v>364500</v>
       </c>
     </row>
     <row r="257">
@@ -15456,7 +15456,7 @@
         <v>-130.5</v>
       </c>
       <c r="U257" t="n">
-        <v>18150</v>
+        <v>18280</v>
       </c>
     </row>
     <row r="258">
@@ -15522,13 +15522,13 @@
         <v>-0.4</v>
       </c>
       <c r="U258" t="n">
-        <v>360000</v>
+        <v>360500</v>
       </c>
       <c r="V258" t="n">
         <v>363500</v>
       </c>
       <c r="W258" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="259">
@@ -15666,13 +15666,13 @@
         <v>0</v>
       </c>
       <c r="U260" t="n">
-        <v>16960</v>
+        <v>17060</v>
       </c>
       <c r="V260" t="n">
         <v>17140</v>
       </c>
       <c r="W260" t="n">
-        <v>-1.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="261">
@@ -15714,7 +15714,7 @@
         <v>2468.7</v>
       </c>
       <c r="U261" t="n">
-        <v>41250</v>
+        <v>40900</v>
       </c>
     </row>
     <row r="262">
@@ -15756,7 +15756,7 @@
         <v>6274.3</v>
       </c>
       <c r="U262" t="n">
-        <v>69300</v>
+        <v>69100</v>
       </c>
     </row>
     <row r="263">
@@ -15795,13 +15795,13 @@
         <v>0</v>
       </c>
       <c r="U263" t="n">
-        <v>42700</v>
+        <v>41850</v>
       </c>
       <c r="V263" t="n">
         <v>40850</v>
       </c>
       <c r="W263" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="264">
@@ -15840,13 +15840,13 @@
         <v>0</v>
       </c>
       <c r="U264" t="n">
-        <v>31900</v>
+        <v>31450</v>
       </c>
       <c r="V264" t="n">
         <v>28900</v>
       </c>
       <c r="W264" t="n">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="265">
@@ -15888,7 +15888,7 @@
         <v>607606</v>
       </c>
       <c r="U265" t="n">
-        <v>1104000</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="266">
@@ -15921,7 +15921,7 @@
         <v>298</v>
       </c>
       <c r="U266" t="n">
-        <v>55800</v>
+        <v>55400</v>
       </c>
     </row>
     <row r="267">
@@ -15987,13 +15987,13 @@
         <v>0</v>
       </c>
       <c r="U267" t="n">
-        <v>123700</v>
+        <v>125900</v>
       </c>
       <c r="V267" t="n">
         <v>112100</v>
       </c>
       <c r="W267" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="268">
@@ -16107,7 +16107,7 @@
         <v>3103</v>
       </c>
       <c r="U269" t="n">
-        <v>82000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="270">
@@ -16173,13 +16173,13 @@
         <v>0</v>
       </c>
       <c r="U270" t="n">
-        <v>242000</v>
+        <v>242500</v>
       </c>
       <c r="V270" t="n">
         <v>244000</v>
       </c>
       <c r="W270" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="271">
@@ -16221,7 +16221,7 @@
         <v>1966.7</v>
       </c>
       <c r="U271" t="n">
-        <v>80700</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="272">
@@ -16320,13 +16320,13 @@
         <v>0</v>
       </c>
       <c r="U273" t="n">
-        <v>9470</v>
+        <v>9400</v>
       </c>
       <c r="V273" t="n">
         <v>10260</v>
       </c>
       <c r="W273" t="n">
-        <v>-7.7</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="274">
@@ -16464,13 +16464,13 @@
         <v>-0.5</v>
       </c>
       <c r="U275" t="n">
-        <v>181400</v>
+        <v>183100</v>
       </c>
       <c r="V275" t="n">
         <v>182100</v>
       </c>
       <c r="W275" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="276">
@@ -16536,13 +16536,13 @@
         <v>0</v>
       </c>
       <c r="U276" t="n">
-        <v>17980</v>
+        <v>18120</v>
       </c>
       <c r="V276" t="n">
         <v>18730</v>
       </c>
       <c r="W276" t="n">
-        <v>-4</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="277">
@@ -16608,13 +16608,13 @@
         <v>0</v>
       </c>
       <c r="U277" t="n">
-        <v>46600</v>
+        <v>46100</v>
       </c>
       <c r="V277" t="n">
         <v>47350</v>
       </c>
       <c r="W277" t="n">
-        <v>-1.6</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="278">
@@ -16653,13 +16653,13 @@
         <v>0</v>
       </c>
       <c r="U278" t="n">
-        <v>30550</v>
+        <v>29700</v>
       </c>
       <c r="V278" t="n">
         <v>29950</v>
       </c>
       <c r="W278" t="n">
-        <v>2</v>
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-02 · 전주 2026-09-28</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-03 · 전주 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -642,13 +642,13 @@
         <v>0.1</v>
       </c>
       <c r="U3" t="n">
-        <v>14740</v>
+        <v>14810</v>
       </c>
       <c r="V3" t="n">
         <v>15110</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="4">
@@ -714,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>74100</v>
+        <v>74200</v>
       </c>
       <c r="V4" t="n">
         <v>74400</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="5">
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>70600</v>
+        <v>70700</v>
       </c>
       <c r="V5" t="n">
         <v>70400</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -858,13 +858,13 @@
         <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1335000</v>
+        <v>1338000</v>
       </c>
       <c r="V6" t="n">
         <v>1415000</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="7">
@@ -930,13 +930,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>48650</v>
+        <v>48700</v>
       </c>
       <c r="V7" t="n">
         <v>51900</v>
       </c>
       <c r="W7" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="8">
@@ -1002,13 +1002,13 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>25350</v>
+        <v>25450</v>
       </c>
       <c r="V8" t="n">
         <v>25150</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -1074,13 +1074,13 @@
         <v>-0.8</v>
       </c>
       <c r="U9" t="n">
-        <v>112700</v>
+        <v>113200</v>
       </c>
       <c r="V9" t="n">
         <v>117100</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.8</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="10">
@@ -1146,13 +1146,13 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>94700</v>
+        <v>94500</v>
       </c>
       <c r="V10" t="n">
         <v>93700</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -1218,13 +1218,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1838000</v>
+        <v>1842000</v>
       </c>
       <c r="V11" t="n">
         <v>1761000</v>
       </c>
       <c r="W11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="12">
@@ -1290,13 +1290,13 @@
         <v>0.3</v>
       </c>
       <c r="U12" t="n">
-        <v>114500</v>
+        <v>114700</v>
       </c>
       <c r="V12" t="n">
         <v>123200</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.1</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="13">
@@ -1362,13 +1362,13 @@
         <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>626000</v>
+        <v>629000</v>
       </c>
       <c r="V13" t="n">
         <v>658000</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.9</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="14">
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>141000</v>
+        <v>141300</v>
       </c>
       <c r="V15" t="n">
         <v>125600</v>
       </c>
       <c r="W15" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="16">
@@ -1578,13 +1578,13 @@
         <v>-0.8</v>
       </c>
       <c r="U16" t="n">
-        <v>131200</v>
+        <v>131000</v>
       </c>
       <c r="V16" t="n">
         <v>133300</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="17">
@@ -1650,13 +1650,13 @@
         <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>46750</v>
+        <v>46900</v>
       </c>
       <c r="V17" t="n">
         <v>44750</v>
       </c>
       <c r="W17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="18">
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>31400</v>
+        <v>31500</v>
       </c>
       <c r="V18" t="n">
         <v>29850</v>
       </c>
       <c r="W18" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="19">
@@ -1785,13 +1785,13 @@
         <v>-0.7</v>
       </c>
       <c r="U19" t="n">
-        <v>47350</v>
+        <v>47650</v>
       </c>
       <c r="V19" t="n">
         <v>48600</v>
       </c>
       <c r="W19" t="n">
-        <v>-2.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
@@ -1839,13 +1839,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>17740</v>
+        <v>17810</v>
       </c>
       <c r="V20" t="n">
         <v>18290</v>
       </c>
       <c r="W20" t="n">
-        <v>-3</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="21">
@@ -1911,13 +1911,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>22900</v>
+        <v>23100</v>
       </c>
       <c r="V21" t="n">
         <v>24000</v>
       </c>
       <c r="W21" t="n">
-        <v>-4.6</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="22">
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5790</v>
+        <v>5800</v>
       </c>
       <c r="V22" t="n">
         <v>5730</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="23">
@@ -2055,13 +2055,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>470000</v>
+        <v>472000</v>
       </c>
       <c r="V23" t="n">
         <v>477500</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="24">
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>12210</v>
+        <v>12250</v>
       </c>
       <c r="V24" t="n">
         <v>12950</v>
       </c>
       <c r="W24" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="25">
@@ -2199,13 +2199,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>114500</v>
+        <v>115400</v>
       </c>
       <c r="V25" t="n">
         <v>107800</v>
       </c>
       <c r="W25" t="n">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="26">
@@ -2271,13 +2271,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>9110</v>
+        <v>9140</v>
       </c>
       <c r="V26" t="n">
         <v>9200</v>
       </c>
       <c r="W26" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="27">
@@ -2343,13 +2343,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>7880</v>
+        <v>7890</v>
       </c>
       <c r="V27" t="n">
         <v>7910</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="28">
@@ -2388,40 +2388,40 @@
         <v>-0.1</v>
       </c>
       <c r="L28" t="n">
-        <v>7328.4</v>
+        <v>7316.4</v>
       </c>
       <c r="M28" t="n">
         <v>7337.9</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="O28" t="n">
-        <v>8969.6</v>
+        <v>8955.1</v>
       </c>
       <c r="P28" t="n">
         <v>8947.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="R28" t="n">
-        <v>10600.1</v>
+        <v>10577.1</v>
       </c>
       <c r="S28" t="n">
         <v>10510.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1212000</v>
+        <v>1215000</v>
       </c>
       <c r="V28" t="n">
         <v>1218000</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="29">
@@ -2451,49 +2451,49 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3046</v>
+        <v>3053</v>
       </c>
       <c r="G29" t="n">
         <v>3131</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="L29" t="n">
-        <v>9657.299999999999</v>
+        <v>8421.9</v>
       </c>
       <c r="M29" t="n">
         <v>9909.1</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.5</v>
+        <v>-15</v>
       </c>
       <c r="O29" t="n">
-        <v>22842.6</v>
+        <v>21914.2</v>
       </c>
       <c r="P29" t="n">
         <v>22587.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.1</v>
+        <v>-3</v>
       </c>
       <c r="R29" t="n">
-        <v>25880.1</v>
+        <v>24935.9</v>
       </c>
       <c r="S29" t="n">
         <v>26015.5</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.5</v>
+        <v>-4.1</v>
       </c>
       <c r="U29" t="n">
-        <v>30600</v>
+        <v>30850</v>
       </c>
       <c r="V29" t="n">
         <v>31450</v>
       </c>
       <c r="W29" t="n">
-        <v>-2.7</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="30">
@@ -2559,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>110600</v>
+        <v>111400</v>
       </c>
       <c r="V30" t="n">
         <v>113200</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.3</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="31">
@@ -2631,13 +2631,13 @@
         <v>-0.5</v>
       </c>
       <c r="U31" t="n">
-        <v>186300</v>
+        <v>186800</v>
       </c>
       <c r="V31" t="n">
         <v>182600</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="32">
@@ -2703,13 +2703,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>42700</v>
+        <v>42850</v>
       </c>
       <c r="V32" t="n">
         <v>44000</v>
       </c>
       <c r="W32" t="n">
-        <v>-3</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="33">
@@ -2775,13 +2775,13 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>30000</v>
+        <v>30100</v>
       </c>
       <c r="V33" t="n">
         <v>31000</v>
       </c>
       <c r="W33" t="n">
-        <v>-3.2</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="34">
@@ -2847,13 +2847,13 @@
         <v>0.6</v>
       </c>
       <c r="U34" t="n">
-        <v>330000</v>
+        <v>332000</v>
       </c>
       <c r="V34" t="n">
         <v>343000</v>
       </c>
       <c r="W34" t="n">
-        <v>-3.8</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="35">
@@ -2955,49 +2955,49 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1920</v>
+        <v>1740</v>
       </c>
       <c r="G36" t="n">
         <v>1920</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-9.4</v>
       </c>
       <c r="L36" t="n">
-        <v>3503</v>
+        <v>3218</v>
       </c>
       <c r="M36" t="n">
         <v>3503</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-8.1</v>
       </c>
       <c r="O36" t="n">
-        <v>4694</v>
+        <v>4064</v>
       </c>
       <c r="P36" t="n">
         <v>4694</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>-13.4</v>
       </c>
       <c r="R36" t="n">
-        <v>5355</v>
+        <v>4920</v>
       </c>
       <c r="S36" t="n">
         <v>5355</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>-8.1</v>
       </c>
       <c r="U36" t="n">
-        <v>23800</v>
+        <v>23900</v>
       </c>
       <c r="V36" t="n">
         <v>24650</v>
       </c>
       <c r="W36" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="37">
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>95700</v>
+        <v>95500</v>
       </c>
       <c r="V37" t="n">
         <v>96000</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="38">
@@ -3135,13 +3135,13 @@
         <v>-0.2</v>
       </c>
       <c r="U38" t="n">
-        <v>346500</v>
+        <v>347000</v>
       </c>
       <c r="V38" t="n">
         <v>354000</v>
       </c>
       <c r="W38" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="39">
@@ -3207,13 +3207,13 @@
         <v>-1.8</v>
       </c>
       <c r="U39" t="n">
-        <v>310500</v>
+        <v>311500</v>
       </c>
       <c r="V39" t="n">
         <v>313500</v>
       </c>
       <c r="W39" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="40">
@@ -3270,13 +3270,13 @@
         <v>0.7</v>
       </c>
       <c r="U40" t="n">
-        <v>181900</v>
+        <v>182500</v>
       </c>
       <c r="V40" t="n">
         <v>190300</v>
       </c>
       <c r="W40" t="n">
-        <v>-4.4</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="41">
@@ -3342,13 +3342,13 @@
         <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>52300</v>
+        <v>52500</v>
       </c>
       <c r="V41" t="n">
         <v>50300</v>
       </c>
       <c r="W41" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="42">
@@ -3378,49 +3378,49 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1081312</v>
+        <v>1069435</v>
       </c>
       <c r="G42" t="n">
         <v>1105736</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.2</v>
+        <v>-3.3</v>
       </c>
       <c r="L42" t="n">
-        <v>3835979.6</v>
+        <v>3812250.1</v>
       </c>
       <c r="M42" t="n">
         <v>3876961.8</v>
       </c>
       <c r="N42" t="n">
-        <v>-1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="O42" t="n">
-        <v>5489912.8</v>
+        <v>5467664.2</v>
       </c>
       <c r="P42" t="n">
         <v>5626926.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>-2.4</v>
+        <v>-2.8</v>
       </c>
       <c r="R42" t="n">
-        <v>5892061.8</v>
+        <v>5868337.4</v>
       </c>
       <c r="S42" t="n">
         <v>5747157.9</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U42" t="n">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="V42" t="n">
         <v>270000</v>
       </c>
       <c r="W42" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="43">
@@ -3459,40 +3459,40 @@
         <v>-0.7</v>
       </c>
       <c r="L43" t="n">
-        <v>23107.4</v>
+        <v>23056.8</v>
       </c>
       <c r="M43" t="n">
         <v>23130.9</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="O43" t="n">
-        <v>20156.2</v>
+        <v>20113.3</v>
       </c>
       <c r="P43" t="n">
         <v>20109.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>20626.3</v>
+        <v>20595.7</v>
       </c>
       <c r="S43" t="n">
         <v>20493.2</v>
       </c>
       <c r="T43" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="U43" t="n">
-        <v>26800</v>
+        <v>26850</v>
       </c>
       <c r="V43" t="n">
         <v>25950</v>
       </c>
       <c r="W43" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="44">
@@ -3630,13 +3630,13 @@
         <v>1.3</v>
       </c>
       <c r="U45" t="n">
-        <v>35200</v>
+        <v>35450</v>
       </c>
       <c r="V45" t="n">
         <v>36000</v>
       </c>
       <c r="W45" t="n">
-        <v>-2.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="46">
@@ -3702,13 +3702,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>298500</v>
+        <v>299000</v>
       </c>
       <c r="V46" t="n">
         <v>312000</v>
       </c>
       <c r="W46" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="47">
@@ -3774,13 +3774,13 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>126400</v>
+        <v>126600</v>
       </c>
       <c r="V47" t="n">
         <v>122900</v>
       </c>
       <c r="W47" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3918,13 +3918,13 @@
         <v>2.2</v>
       </c>
       <c r="U49" t="n">
-        <v>527000</v>
+        <v>529000</v>
       </c>
       <c r="V49" t="n">
         <v>528000</v>
       </c>
       <c r="W49" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="50">
@@ -3954,49 +3954,49 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="G50" t="n">
         <v>362</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="L50" t="n">
-        <v>1533</v>
+        <v>1199</v>
       </c>
       <c r="M50" t="n">
         <v>1533</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>-21.8</v>
       </c>
       <c r="O50" t="n">
-        <v>2101.4</v>
+        <v>1995.4</v>
       </c>
       <c r="P50" t="n">
         <v>2101.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R50" t="n">
-        <v>2380.2</v>
+        <v>2342.2</v>
       </c>
       <c r="S50" t="n">
         <v>2380.2</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="U50" t="n">
-        <v>91200</v>
+        <v>91600</v>
       </c>
       <c r="V50" t="n">
         <v>91800</v>
       </c>
       <c r="W50" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="51">
@@ -4035,40 +4035,40 @@
         <v>-14.3</v>
       </c>
       <c r="L51" t="n">
-        <v>47152.6</v>
+        <v>47083.2</v>
       </c>
       <c r="M51" t="n">
         <v>47488.7</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="O51" t="n">
-        <v>26034.9</v>
+        <v>25932.4</v>
       </c>
       <c r="P51" t="n">
         <v>25854.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="R51" t="n">
-        <v>27914.1</v>
+        <v>27851.6</v>
       </c>
       <c r="S51" t="n">
         <v>27610.4</v>
       </c>
       <c r="T51" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="U51" t="n">
-        <v>31550</v>
+        <v>31600</v>
       </c>
       <c r="V51" t="n">
         <v>31650</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="52">
@@ -4098,49 +4098,49 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="G52" t="n">
         <v>1242</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L52" t="n">
-        <v>3619.9</v>
+        <v>3617.9</v>
       </c>
       <c r="M52" t="n">
         <v>3619.9</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O52" t="n">
-        <v>3908.4</v>
+        <v>3907.1</v>
       </c>
       <c r="P52" t="n">
         <v>3908.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R52" t="n">
-        <v>4117.4</v>
+        <v>4115.2</v>
       </c>
       <c r="S52" t="n">
         <v>4117.4</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="U52" t="n">
-        <v>22100</v>
+        <v>22200</v>
       </c>
       <c r="V52" t="n">
         <v>23050</v>
       </c>
       <c r="W52" t="n">
-        <v>-4.1</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="53">
@@ -4206,13 +4206,13 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>49900</v>
+        <v>50500</v>
       </c>
       <c r="V53" t="n">
         <v>50400</v>
       </c>
       <c r="W53" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
@@ -4278,13 +4278,13 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>121300</v>
+        <v>122000</v>
       </c>
       <c r="V54" t="n">
         <v>112000</v>
       </c>
       <c r="W54" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="55">
@@ -4350,13 +4350,13 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>82600</v>
+        <v>82900</v>
       </c>
       <c r="V55" t="n">
         <v>69600</v>
       </c>
       <c r="W55" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="56">
@@ -4422,13 +4422,13 @@
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>39350</v>
+        <v>39400</v>
       </c>
       <c r="V56" t="n">
         <v>40300</v>
       </c>
       <c r="W56" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="57">
@@ -4461,13 +4461,13 @@
         <v>1783</v>
       </c>
       <c r="U57" t="n">
-        <v>55300</v>
+        <v>55000</v>
       </c>
       <c r="V57" t="n">
         <v>52000</v>
       </c>
       <c r="W57" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="58">
@@ -4533,13 +4533,13 @@
         <v>3.1</v>
       </c>
       <c r="U58" t="n">
-        <v>1573000</v>
+        <v>1577000</v>
       </c>
       <c r="V58" t="n">
         <v>1491000</v>
       </c>
       <c r="W58" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="59">
@@ -4605,13 +4605,13 @@
         <v>-2.6</v>
       </c>
       <c r="U59" t="n">
-        <v>39300</v>
+        <v>39550</v>
       </c>
       <c r="V59" t="n">
         <v>40400</v>
       </c>
       <c r="W59" t="n">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="60">
@@ -4677,13 +4677,13 @@
         <v>0.1</v>
       </c>
       <c r="U60" t="n">
-        <v>325000</v>
+        <v>326500</v>
       </c>
       <c r="V60" t="n">
         <v>332500</v>
       </c>
       <c r="W60" t="n">
-        <v>-2.3</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="61">
@@ -4749,13 +4749,13 @@
         <v>-0.3</v>
       </c>
       <c r="U61" t="n">
-        <v>36050</v>
+        <v>36100</v>
       </c>
       <c r="V61" t="n">
         <v>34250</v>
       </c>
       <c r="W61" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="62">
@@ -4821,13 +4821,13 @@
         <v>-1.1</v>
       </c>
       <c r="U62" t="n">
-        <v>235500</v>
+        <v>236000</v>
       </c>
       <c r="V62" t="n">
         <v>232000</v>
       </c>
       <c r="W62" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="63">
@@ -4893,13 +4893,13 @@
         <v>0.5</v>
       </c>
       <c r="U63" t="n">
-        <v>208500</v>
+        <v>209000</v>
       </c>
       <c r="V63" t="n">
         <v>203000</v>
       </c>
       <c r="W63" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4965,13 +4965,13 @@
         <v>-1.5</v>
       </c>
       <c r="U64" t="n">
-        <v>1080000</v>
+        <v>1083000</v>
       </c>
       <c r="V64" t="n">
         <v>1094000</v>
       </c>
       <c r="W64" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
@@ -5037,13 +5037,13 @@
         <v>-0.3</v>
       </c>
       <c r="U65" t="n">
-        <v>19910</v>
+        <v>19920</v>
       </c>
       <c r="V65" t="n">
         <v>20150</v>
       </c>
       <c r="W65" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="66">
@@ -5082,13 +5082,13 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>17770</v>
+        <v>17860</v>
       </c>
       <c r="V66" t="n">
         <v>17260</v>
       </c>
       <c r="W66" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="67">
@@ -5154,13 +5154,13 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>14600</v>
+        <v>14660</v>
       </c>
       <c r="V67" t="n">
         <v>14970</v>
       </c>
       <c r="W67" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="68">
@@ -5226,13 +5226,13 @@
         <v>2.3</v>
       </c>
       <c r="U68" t="n">
-        <v>164700</v>
+        <v>164900</v>
       </c>
       <c r="V68" t="n">
         <v>164000</v>
       </c>
       <c r="W68" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69">
@@ -5298,13 +5298,13 @@
         <v>-0.8</v>
       </c>
       <c r="U69" t="n">
-        <v>571000</v>
+        <v>574000</v>
       </c>
       <c r="V69" t="n">
         <v>574000</v>
       </c>
       <c r="W69" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5334,49 +5334,49 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-1425</v>
+        <v>-1632</v>
       </c>
       <c r="G70" t="n">
         <v>-1425</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>-14.5</v>
       </c>
       <c r="L70" t="n">
-        <v>-589.5</v>
+        <v>-791.4</v>
       </c>
       <c r="M70" t="n">
         <v>-589.5</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>-34.2</v>
       </c>
       <c r="O70" t="n">
-        <v>503.9</v>
+        <v>643</v>
       </c>
       <c r="P70" t="n">
         <v>503.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="R70" t="n">
-        <v>3593.9</v>
+        <v>3616.6</v>
       </c>
       <c r="S70" t="n">
         <v>3593.9</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U70" t="n">
-        <v>60800</v>
+        <v>60900</v>
       </c>
       <c r="V70" t="n">
         <v>62400</v>
       </c>
       <c r="W70" t="n">
-        <v>-2.6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="71">
@@ -5406,40 +5406,40 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6628</v>
+        <v>6856</v>
       </c>
       <c r="G71" t="n">
         <v>6036</v>
       </c>
       <c r="H71" t="n">
-        <v>9.800000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="L71" t="n">
-        <v>17399.5</v>
+        <v>17719.5</v>
       </c>
       <c r="M71" t="n">
         <v>16185.7</v>
       </c>
       <c r="N71" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="O71" t="n">
-        <v>11219.5</v>
+        <v>11795.6</v>
       </c>
       <c r="P71" t="n">
         <v>10474.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>7.1</v>
+        <v>12.6</v>
       </c>
       <c r="R71" t="n">
-        <v>9473.5</v>
+        <v>9489.6</v>
       </c>
       <c r="S71" t="n">
         <v>8921.9</v>
       </c>
       <c r="T71" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="U71" t="n">
         <v>21400</v>
@@ -5514,13 +5514,13 @@
         <v>-0.2</v>
       </c>
       <c r="U72" t="n">
-        <v>53000</v>
+        <v>53300</v>
       </c>
       <c r="V72" t="n">
         <v>53500</v>
       </c>
       <c r="W72" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="73">
@@ -5586,13 +5586,13 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>116800</v>
+        <v>117500</v>
       </c>
       <c r="V73" t="n">
         <v>117500</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -5658,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>106700</v>
+        <v>106800</v>
       </c>
       <c r="V74" t="n">
         <v>90200</v>
       </c>
       <c r="W74" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="75">
@@ -5730,13 +5730,13 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>19830</v>
+        <v>19940</v>
       </c>
       <c r="V75" t="n">
         <v>17700</v>
       </c>
       <c r="W75" t="n">
-        <v>12</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="76">
@@ -5802,13 +5802,13 @@
         <v>-0.6</v>
       </c>
       <c r="U76" t="n">
-        <v>383500</v>
+        <v>385500</v>
       </c>
       <c r="V76" t="n">
         <v>371500</v>
       </c>
       <c r="W76" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="77">
@@ -5874,13 +5874,13 @@
         <v>0.2</v>
       </c>
       <c r="U77" t="n">
-        <v>1067000</v>
+        <v>1069000</v>
       </c>
       <c r="V77" t="n">
         <v>1034000</v>
       </c>
       <c r="W77" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="78">
@@ -5946,13 +5946,13 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>367000</v>
+        <v>367500</v>
       </c>
       <c r="V78" t="n">
         <v>332000</v>
       </c>
       <c r="W78" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="79">
@@ -6018,13 +6018,13 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>82800</v>
+        <v>84100</v>
       </c>
       <c r="V79" t="n">
         <v>82900</v>
       </c>
       <c r="W79" t="n">
-        <v>-0.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="80">
@@ -6090,13 +6090,13 @@
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>30500</v>
+        <v>30650</v>
       </c>
       <c r="V80" t="n">
         <v>31150</v>
       </c>
       <c r="W80" t="n">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="81">
@@ -6162,13 +6162,13 @@
         <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>273500</v>
+        <v>277500</v>
       </c>
       <c r="V81" t="n">
         <v>239500</v>
       </c>
       <c r="W81" t="n">
-        <v>14.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="82">
@@ -6234,13 +6234,13 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>2520</v>
+        <v>2510</v>
       </c>
       <c r="V82" t="n">
         <v>2590</v>
       </c>
       <c r="W82" t="n">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="83">
@@ -6306,13 +6306,13 @@
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>30050</v>
+        <v>30100</v>
       </c>
       <c r="V83" t="n">
         <v>30600</v>
       </c>
       <c r="W83" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="84">
@@ -6351,40 +6351,40 @@
         <v>-3.8</v>
       </c>
       <c r="L84" t="n">
-        <v>22908.1</v>
+        <v>22869.8</v>
       </c>
       <c r="M84" t="n">
         <v>23030.4</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="O84" t="n">
-        <v>21159.6</v>
+        <v>21087.2</v>
       </c>
       <c r="P84" t="n">
         <v>20903.7</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="R84" t="n">
-        <v>21977.1</v>
+        <v>21884.6</v>
       </c>
       <c r="S84" t="n">
         <v>21395.8</v>
       </c>
       <c r="T84" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="U84" t="n">
-        <v>90100</v>
+        <v>90300</v>
       </c>
       <c r="V84" t="n">
         <v>88800</v>
       </c>
       <c r="W84" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="85">
@@ -6450,13 +6450,13 @@
         <v>0.8</v>
       </c>
       <c r="U85" t="n">
-        <v>88100</v>
+        <v>88600</v>
       </c>
       <c r="V85" t="n">
         <v>87700</v>
       </c>
       <c r="W85" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -6522,13 +6522,13 @@
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>72700</v>
+        <v>73100</v>
       </c>
       <c r="V86" t="n">
         <v>73700</v>
       </c>
       <c r="W86" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="87">
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>20550</v>
+        <v>20650</v>
       </c>
       <c r="V87" t="n">
         <v>20450</v>
       </c>
       <c r="W87" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -6738,13 +6738,13 @@
         <v>0.1</v>
       </c>
       <c r="U89" t="n">
-        <v>3845</v>
+        <v>3840</v>
       </c>
       <c r="V89" t="n">
         <v>3280</v>
       </c>
       <c r="W89" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="90">
@@ -6810,13 +6810,13 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>101100</v>
+        <v>102400</v>
       </c>
       <c r="V90" t="n">
         <v>100700</v>
       </c>
       <c r="W90" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="91">
@@ -6882,13 +6882,13 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>20850</v>
+        <v>20950</v>
       </c>
       <c r="V91" t="n">
         <v>20150</v>
       </c>
       <c r="W91" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -6954,13 +6954,13 @@
         <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>27900</v>
+        <v>28100</v>
       </c>
       <c r="V92" t="n">
         <v>27650</v>
       </c>
       <c r="W92" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="93">
@@ -7026,13 +7026,13 @@
         <v>-0.1</v>
       </c>
       <c r="U93" t="n">
-        <v>101400</v>
+        <v>101800</v>
       </c>
       <c r="V93" t="n">
         <v>102200</v>
       </c>
       <c r="W93" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="94">
@@ -7062,49 +7062,49 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>10282</v>
+        <v>10370</v>
       </c>
       <c r="G94" t="n">
         <v>10232</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="L94" t="n">
-        <v>37259.7</v>
+        <v>37309.7</v>
       </c>
       <c r="M94" t="n">
         <v>37151.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O94" t="n">
-        <v>40176.5</v>
+        <v>40066.8</v>
       </c>
       <c r="P94" t="n">
         <v>40117.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="R94" t="n">
-        <v>42258.8</v>
+        <v>42082.2</v>
       </c>
       <c r="S94" t="n">
         <v>42377.2</v>
       </c>
       <c r="T94" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="U94" t="n">
-        <v>20200</v>
+        <v>20300</v>
       </c>
       <c r="V94" t="n">
         <v>20800</v>
       </c>
       <c r="W94" t="n">
-        <v>-2.9</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="95">
@@ -7134,49 +7134,49 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2481</v>
+        <v>2471</v>
       </c>
       <c r="G95" t="n">
         <v>2479</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="L95" t="n">
-        <v>9807.5</v>
+        <v>9796.5</v>
       </c>
       <c r="M95" t="n">
         <v>9821.6</v>
       </c>
       <c r="N95" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="O95" t="n">
-        <v>11915.5</v>
+        <v>11892.2</v>
       </c>
       <c r="P95" t="n">
         <v>11913.2</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="R95" t="n">
-        <v>13237</v>
+        <v>13174</v>
       </c>
       <c r="S95" t="n">
         <v>13226.6</v>
       </c>
       <c r="T95" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="U95" t="n">
-        <v>47650</v>
+        <v>47850</v>
       </c>
       <c r="V95" t="n">
         <v>49900</v>
       </c>
       <c r="W95" t="n">
-        <v>-4.5</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="96">
@@ -7242,13 +7242,13 @@
         <v>-0.4</v>
       </c>
       <c r="U96" t="n">
-        <v>345000</v>
+        <v>347000</v>
       </c>
       <c r="V96" t="n">
         <v>345500</v>
       </c>
       <c r="W96" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="97">
@@ -7314,13 +7314,13 @@
         <v>1.9</v>
       </c>
       <c r="U97" t="n">
-        <v>6210</v>
+        <v>6250</v>
       </c>
       <c r="V97" t="n">
         <v>5690</v>
       </c>
       <c r="W97" t="n">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -7386,13 +7386,13 @@
         <v>-0.7</v>
       </c>
       <c r="U98" t="n">
-        <v>42000</v>
+        <v>42200</v>
       </c>
       <c r="V98" t="n">
         <v>43150</v>
       </c>
       <c r="W98" t="n">
-        <v>-2.7</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="99">
@@ -7458,13 +7458,13 @@
         <v>-1.7</v>
       </c>
       <c r="U99" t="n">
-        <v>18710</v>
+        <v>18770</v>
       </c>
       <c r="V99" t="n">
         <v>17810</v>
       </c>
       <c r="W99" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="100">
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>14530</v>
+        <v>14570</v>
       </c>
       <c r="V103" t="n">
         <v>14780</v>
       </c>
       <c r="W103" t="n">
-        <v>-1.7</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="104">
@@ -7791,13 +7791,13 @@
         <v>13.5</v>
       </c>
       <c r="U104" t="n">
-        <v>287000</v>
+        <v>288000</v>
       </c>
       <c r="V104" t="n">
         <v>293000</v>
       </c>
       <c r="W104" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="105">
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="U105" t="n">
-        <v>16350</v>
+        <v>16380</v>
       </c>
       <c r="V105" t="n">
         <v>16000</v>
       </c>
       <c r="W105" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="106">
@@ -7935,13 +7935,13 @@
         <v>0.1</v>
       </c>
       <c r="U106" t="n">
-        <v>176000</v>
+        <v>176800</v>
       </c>
       <c r="V106" t="n">
         <v>174600</v>
       </c>
       <c r="W106" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="107">
@@ -7971,49 +7971,49 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2482</v>
+        <v>2492</v>
       </c>
       <c r="G107" t="n">
         <v>2482</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L107" t="n">
-        <v>11307.5</v>
+        <v>11291.2</v>
       </c>
       <c r="M107" t="n">
         <v>11307.5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O107" t="n">
-        <v>16256.4</v>
+        <v>16367.7</v>
       </c>
       <c r="P107" t="n">
         <v>16256.4</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="R107" t="n">
-        <v>20657.3</v>
+        <v>20768.6</v>
       </c>
       <c r="S107" t="n">
         <v>20657.3</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U107" t="n">
-        <v>81300</v>
+        <v>81400</v>
       </c>
       <c r="V107" t="n">
         <v>81100</v>
       </c>
       <c r="W107" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="108">
@@ -8079,13 +8079,13 @@
         <v>0</v>
       </c>
       <c r="U108" t="n">
-        <v>8550</v>
+        <v>8570</v>
       </c>
       <c r="V108" t="n">
         <v>8440</v>
       </c>
       <c r="W108" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="109">
@@ -8151,13 +8151,13 @@
         <v>0.4</v>
       </c>
       <c r="U109" t="n">
-        <v>9340</v>
+        <v>9390</v>
       </c>
       <c r="V109" t="n">
         <v>9670</v>
       </c>
       <c r="W109" t="n">
-        <v>-3.4</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="110">
@@ -8223,13 +8223,13 @@
         <v>-0.7</v>
       </c>
       <c r="U110" t="n">
-        <v>575000</v>
+        <v>578000</v>
       </c>
       <c r="V110" t="n">
         <v>576000</v>
       </c>
       <c r="W110" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="111">
@@ -8295,13 +8295,13 @@
         <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>14320</v>
+        <v>14330</v>
       </c>
       <c r="V111" t="n">
         <v>14430</v>
       </c>
       <c r="W111" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="112">
@@ -8331,49 +8331,49 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5465</v>
+        <v>5334</v>
       </c>
       <c r="G112" t="n">
         <v>5545</v>
       </c>
       <c r="H112" t="n">
-        <v>-1.4</v>
+        <v>-3.8</v>
       </c>
       <c r="L112" t="n">
-        <v>21795.9</v>
+        <v>21637.8</v>
       </c>
       <c r="M112" t="n">
         <v>21960.1</v>
       </c>
       <c r="N112" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="O112" t="n">
-        <v>25803.2</v>
+        <v>25681</v>
       </c>
       <c r="P112" t="n">
         <v>25760.5</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="R112" t="n">
-        <v>31156.8</v>
+        <v>31140.7</v>
       </c>
       <c r="S112" t="n">
         <v>30497</v>
       </c>
       <c r="T112" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U112" t="n">
-        <v>191800</v>
+        <v>192200</v>
       </c>
       <c r="V112" t="n">
         <v>196300</v>
       </c>
       <c r="W112" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="113">
@@ -8583,13 +8583,13 @@
         <v>-0</v>
       </c>
       <c r="U115" t="n">
-        <v>37350</v>
+        <v>37500</v>
       </c>
       <c r="V115" t="n">
         <v>38000</v>
       </c>
       <c r="W115" t="n">
-        <v>-1.7</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="116">
@@ -8655,13 +8655,13 @@
         <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>10880</v>
+        <v>10900</v>
       </c>
       <c r="V116" t="n">
         <v>9300</v>
       </c>
       <c r="W116" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="117">
@@ -8763,49 +8763,49 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>891</v>
+        <v>927</v>
       </c>
       <c r="G118" t="n">
         <v>891</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L118" t="n">
-        <v>5227.9</v>
+        <v>5291.8</v>
       </c>
       <c r="M118" t="n">
         <v>5227.9</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O118" t="n">
-        <v>5901.3</v>
+        <v>5979.8</v>
       </c>
       <c r="P118" t="n">
         <v>5901.3</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R118" t="n">
-        <v>6046.4</v>
+        <v>6114.2</v>
       </c>
       <c r="S118" t="n">
         <v>6046.4</v>
       </c>
       <c r="T118" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="U118" t="n">
-        <v>240500</v>
+        <v>244500</v>
       </c>
       <c r="V118" t="n">
         <v>213500</v>
       </c>
       <c r="W118" t="n">
-        <v>12.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="119">
@@ -8862,13 +8862,13 @@
         <v>28</v>
       </c>
       <c r="U119" t="n">
-        <v>238000</v>
+        <v>239500</v>
       </c>
       <c r="V119" t="n">
         <v>208000</v>
       </c>
       <c r="W119" t="n">
-        <v>14.4</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="120">
@@ -8934,13 +8934,13 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>536000</v>
+        <v>537000</v>
       </c>
       <c r="V120" t="n">
         <v>467500</v>
       </c>
       <c r="W120" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="121">
@@ -9006,13 +9006,13 @@
         <v>-2</v>
       </c>
       <c r="U121" t="n">
-        <v>30050</v>
+        <v>30100</v>
       </c>
       <c r="V121" t="n">
         <v>30350</v>
       </c>
       <c r="W121" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="122">
@@ -9051,7 +9051,7 @@
         <v>-3</v>
       </c>
       <c r="L122" t="n">
-        <v>22695.2</v>
+        <v>22692.4</v>
       </c>
       <c r="M122" t="n">
         <v>22785.2</v>
@@ -9060,16 +9060,16 @@
         <v>-0.4</v>
       </c>
       <c r="O122" t="n">
-        <v>18854.8</v>
+        <v>18836.5</v>
       </c>
       <c r="P122" t="n">
         <v>18805.9</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="R122" t="n">
-        <v>19914.9</v>
+        <v>19903.8</v>
       </c>
       <c r="S122" t="n">
         <v>19670.8</v>
@@ -9078,13 +9078,13 @@
         <v>1.2</v>
       </c>
       <c r="U122" t="n">
-        <v>258000</v>
+        <v>259000</v>
       </c>
       <c r="V122" t="n">
         <v>256500</v>
       </c>
       <c r="W122" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -9150,13 +9150,13 @@
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>10060</v>
+        <v>10090</v>
       </c>
       <c r="V123" t="n">
         <v>9430</v>
       </c>
       <c r="W123" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -9222,13 +9222,13 @@
         <v>-0.1</v>
       </c>
       <c r="U124" t="n">
-        <v>78700</v>
+        <v>78800</v>
       </c>
       <c r="V124" t="n">
         <v>82300</v>
       </c>
       <c r="W124" t="n">
-        <v>-4.4</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="125">
@@ -9294,13 +9294,13 @@
         <v>-0.7</v>
       </c>
       <c r="U125" t="n">
-        <v>78500</v>
+        <v>78700</v>
       </c>
       <c r="V125" t="n">
         <v>80500</v>
       </c>
       <c r="W125" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="126">
@@ -9366,13 +9366,13 @@
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>271500</v>
+        <v>272000</v>
       </c>
       <c r="V126" t="n">
         <v>233000</v>
       </c>
       <c r="W126" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="127">
@@ -9429,13 +9429,13 @@
         <v>4.4</v>
       </c>
       <c r="U127" t="n">
-        <v>31350</v>
+        <v>31400</v>
       </c>
       <c r="V127" t="n">
         <v>24700</v>
       </c>
       <c r="W127" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="128">
@@ -9501,13 +9501,13 @@
         <v>0.3</v>
       </c>
       <c r="U128" t="n">
-        <v>17640</v>
+        <v>17690</v>
       </c>
       <c r="V128" t="n">
         <v>18620</v>
       </c>
       <c r="W128" t="n">
-        <v>-5.3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="129">
@@ -9573,13 +9573,13 @@
         <v>1</v>
       </c>
       <c r="U129" t="n">
-        <v>56500</v>
+        <v>56600</v>
       </c>
       <c r="V129" t="n">
         <v>56900</v>
       </c>
       <c r="W129" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="130">
@@ -9645,13 +9645,13 @@
         <v>0.5</v>
       </c>
       <c r="U130" t="n">
-        <v>132500</v>
+        <v>133300</v>
       </c>
       <c r="V130" t="n">
         <v>128600</v>
       </c>
       <c r="W130" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="131">
@@ -9717,13 +9717,13 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>21800</v>
+        <v>21700</v>
       </c>
       <c r="V131" t="n">
         <v>21850</v>
       </c>
       <c r="W131" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="132">
@@ -9861,13 +9861,13 @@
         <v>-0.8</v>
       </c>
       <c r="U133" t="n">
-        <v>270000</v>
+        <v>271500</v>
       </c>
       <c r="V133" t="n">
         <v>291500</v>
       </c>
       <c r="W133" t="n">
-        <v>-7.4</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="134">
@@ -9933,13 +9933,13 @@
         <v>-0.2</v>
       </c>
       <c r="U134" t="n">
-        <v>261500</v>
+        <v>262000</v>
       </c>
       <c r="V134" t="n">
         <v>262000</v>
       </c>
       <c r="W134" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -9969,40 +9969,40 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G135" t="n">
         <v>152</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L135" t="n">
-        <v>634.9</v>
+        <v>628.7</v>
       </c>
       <c r="M135" t="n">
         <v>634.9</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O135" t="n">
-        <v>952.8</v>
+        <v>959.6</v>
       </c>
       <c r="P135" t="n">
         <v>952.8</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="R135" t="n">
-        <v>1507.4</v>
+        <v>1514.9</v>
       </c>
       <c r="S135" t="n">
         <v>1507.4</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U135" t="n">
         <v>126700</v>
@@ -10041,13 +10041,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>21966</v>
+        <v>22040</v>
       </c>
       <c r="G136" t="n">
         <v>22251</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="L136" t="n">
         <v>80578.5</v>
@@ -10077,13 +10077,13 @@
         <v>1.2</v>
       </c>
       <c r="U136" t="n">
-        <v>105200</v>
+        <v>105900</v>
       </c>
       <c r="V136" t="n">
         <v>110800</v>
       </c>
       <c r="W136" t="n">
-        <v>-5.1</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="137">
@@ -10149,13 +10149,13 @@
         <v>-0.3</v>
       </c>
       <c r="U137" t="n">
-        <v>84900</v>
+        <v>85100</v>
       </c>
       <c r="V137" t="n">
         <v>71000</v>
       </c>
       <c r="W137" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="138">
@@ -10221,13 +10221,13 @@
         <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>103200</v>
+        <v>103400</v>
       </c>
       <c r="V138" t="n">
         <v>96800</v>
       </c>
       <c r="W138" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="139">
@@ -10356,13 +10356,13 @@
         <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>226000</v>
+        <v>227000</v>
       </c>
       <c r="V140" t="n">
         <v>199900</v>
       </c>
       <c r="W140" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="141">
@@ -10392,49 +10392,49 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2875</v>
+        <v>2841</v>
       </c>
       <c r="G141" t="n">
         <v>2894</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.7</v>
+        <v>-1.8</v>
       </c>
       <c r="L141" t="n">
-        <v>10700.3</v>
+        <v>10542.6</v>
       </c>
       <c r="M141" t="n">
         <v>10808.2</v>
       </c>
       <c r="N141" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="O141" t="n">
-        <v>13114.8</v>
+        <v>12908.5</v>
       </c>
       <c r="P141" t="n">
         <v>13191.1</v>
       </c>
       <c r="Q141" t="n">
-        <v>-0.6</v>
+        <v>-2.1</v>
       </c>
       <c r="R141" t="n">
-        <v>16242.3</v>
+        <v>15909.4</v>
       </c>
       <c r="S141" t="n">
         <v>16463.6</v>
       </c>
       <c r="T141" t="n">
-        <v>-1.3</v>
+        <v>-3.4</v>
       </c>
       <c r="U141" t="n">
-        <v>116000</v>
+        <v>115800</v>
       </c>
       <c r="V141" t="n">
         <v>116200</v>
       </c>
       <c r="W141" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="142">
@@ -10500,13 +10500,13 @@
         <v>-0.1</v>
       </c>
       <c r="U142" t="n">
-        <v>71700</v>
+        <v>72000</v>
       </c>
       <c r="V142" t="n">
         <v>69700</v>
       </c>
       <c r="W142" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="143">
@@ -10572,13 +10572,13 @@
         <v>0.4</v>
       </c>
       <c r="U143" t="n">
-        <v>295500</v>
+        <v>298000</v>
       </c>
       <c r="V143" t="n">
         <v>277500</v>
       </c>
       <c r="W143" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="144">
@@ -10644,13 +10644,13 @@
         <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>27050</v>
+        <v>26950</v>
       </c>
       <c r="V144" t="n">
         <v>27250</v>
       </c>
       <c r="W144" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="145">
@@ -10680,49 +10680,49 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>10479</v>
+        <v>10401</v>
       </c>
       <c r="G145" t="n">
         <v>10586</v>
       </c>
       <c r="H145" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="L145" t="n">
-        <v>46246.3</v>
+        <v>46586.2</v>
       </c>
       <c r="M145" t="n">
         <v>46394.5</v>
       </c>
       <c r="N145" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O145" t="n">
-        <v>49317.3</v>
+        <v>49797.3</v>
       </c>
       <c r="P145" t="n">
         <v>49360.8</v>
       </c>
       <c r="Q145" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="R145" t="n">
-        <v>60188.5</v>
+        <v>61119.7</v>
       </c>
       <c r="S145" t="n">
         <v>60193.1</v>
       </c>
       <c r="T145" t="n">
-        <v>-0</v>
+        <v>1.5</v>
       </c>
       <c r="U145" t="n">
-        <v>215000</v>
+        <v>215500</v>
       </c>
       <c r="V145" t="n">
         <v>214500</v>
       </c>
       <c r="W145" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
@@ -10788,13 +10788,13 @@
         <v>0.1</v>
       </c>
       <c r="U146" t="n">
-        <v>113700</v>
+        <v>114100</v>
       </c>
       <c r="V146" t="n">
         <v>114500</v>
       </c>
       <c r="W146" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="147">
@@ -10860,13 +10860,13 @@
         <v>-5.4</v>
       </c>
       <c r="U147" t="n">
-        <v>36400</v>
+        <v>36300</v>
       </c>
       <c r="V147" t="n">
         <v>37000</v>
       </c>
       <c r="W147" t="n">
-        <v>-1.6</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="148">
@@ -10932,13 +10932,13 @@
         <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>51900</v>
+        <v>52200</v>
       </c>
       <c r="V148" t="n">
         <v>45000</v>
       </c>
       <c r="W148" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149">
@@ -11004,13 +11004,13 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>182300</v>
+        <v>182600</v>
       </c>
       <c r="V149" t="n">
         <v>177900</v>
       </c>
       <c r="W149" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="150">
@@ -11076,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>15890</v>
+        <v>15990</v>
       </c>
       <c r="V150" t="n">
         <v>16360</v>
       </c>
       <c r="W150" t="n">
-        <v>-2.9</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="151">
@@ -11148,13 +11148,13 @@
         <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>109000</v>
+        <v>109300</v>
       </c>
       <c r="V151" t="n">
         <v>107900</v>
       </c>
       <c r="W151" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="152">
@@ -11220,13 +11220,13 @@
         <v>-1</v>
       </c>
       <c r="U152" t="n">
-        <v>88700</v>
+        <v>88800</v>
       </c>
       <c r="V152" t="n">
         <v>91200</v>
       </c>
       <c r="W152" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="153">
@@ -11265,31 +11265,31 @@
         <v>-4.5</v>
       </c>
       <c r="L153" t="n">
-        <v>39668.1</v>
+        <v>39419.3</v>
       </c>
       <c r="M153" t="n">
         <v>40083.7</v>
       </c>
       <c r="N153" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="O153" t="n">
-        <v>31824.9</v>
+        <v>31638.1</v>
       </c>
       <c r="P153" t="n">
         <v>32203.7</v>
       </c>
       <c r="Q153" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="R153" t="n">
-        <v>32975.2</v>
+        <v>32889.2</v>
       </c>
       <c r="S153" t="n">
         <v>33383.2</v>
       </c>
       <c r="T153" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="U153" t="n">
         <v>180400</v>
@@ -11364,13 +11364,13 @@
         <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>79100</v>
+        <v>79500</v>
       </c>
       <c r="V154" t="n">
         <v>78800</v>
       </c>
       <c r="W154" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="155">
@@ -11436,13 +11436,13 @@
         <v>-1.6</v>
       </c>
       <c r="U155" t="n">
-        <v>48850</v>
+        <v>49050</v>
       </c>
       <c r="V155" t="n">
         <v>48950</v>
       </c>
       <c r="W155" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="156">
@@ -11553,13 +11553,13 @@
         <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>10000</v>
+        <v>10010</v>
       </c>
       <c r="V157" t="n">
         <v>9990</v>
       </c>
       <c r="W157" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="158">
@@ -11598,13 +11598,13 @@
         <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>14050</v>
+        <v>14110</v>
       </c>
       <c r="V158" t="n">
         <v>12700</v>
       </c>
       <c r="W158" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="159">
@@ -11670,13 +11670,13 @@
         <v>0</v>
       </c>
       <c r="U159" t="n">
-        <v>22600</v>
+        <v>22750</v>
       </c>
       <c r="V159" t="n">
         <v>22100</v>
       </c>
       <c r="W159" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="160">
@@ -11742,13 +11742,13 @@
         <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>105300</v>
+        <v>105100</v>
       </c>
       <c r="V160" t="n">
         <v>114300</v>
       </c>
       <c r="W160" t="n">
-        <v>-7.9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="161">
@@ -11814,13 +11814,13 @@
         <v>0.2</v>
       </c>
       <c r="U161" t="n">
-        <v>756000</v>
+        <v>759000</v>
       </c>
       <c r="V161" t="n">
         <v>690000</v>
       </c>
       <c r="W161" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
@@ -11859,13 +11859,13 @@
         <v>-400</v>
       </c>
       <c r="U162" t="n">
-        <v>8200</v>
+        <v>8250</v>
       </c>
       <c r="V162" t="n">
         <v>8470</v>
       </c>
       <c r="W162" t="n">
-        <v>-3.2</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="163">
@@ -11931,13 +11931,13 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>38900</v>
+        <v>39050</v>
       </c>
       <c r="V163" t="n">
         <v>38200</v>
       </c>
       <c r="W163" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="164">
@@ -12075,13 +12075,13 @@
         <v>0</v>
       </c>
       <c r="U165" t="n">
-        <v>178200</v>
+        <v>179400</v>
       </c>
       <c r="V165" t="n">
         <v>154100</v>
       </c>
       <c r="W165" t="n">
-        <v>15.6</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="166">
@@ -12147,13 +12147,13 @@
         <v>1.1</v>
       </c>
       <c r="U166" t="n">
-        <v>200500</v>
+        <v>201000</v>
       </c>
       <c r="V166" t="n">
         <v>198100</v>
       </c>
       <c r="W166" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="167">
@@ -12183,7 +12183,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>16494</v>
+        <v>16489</v>
       </c>
       <c r="G167" t="n">
         <v>16662</v>
@@ -12192,40 +12192,40 @@
         <v>-1</v>
       </c>
       <c r="L167" t="n">
-        <v>59602.8</v>
+        <v>59536.9</v>
       </c>
       <c r="M167" t="n">
         <v>59870.5</v>
       </c>
       <c r="N167" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="O167" t="n">
-        <v>62134.8</v>
+        <v>61927.2</v>
       </c>
       <c r="P167" t="n">
         <v>62471.9</v>
       </c>
       <c r="Q167" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="R167" t="n">
-        <v>65052.4</v>
+        <v>64861.1</v>
       </c>
       <c r="S167" t="n">
         <v>65090.5</v>
       </c>
       <c r="T167" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="U167" t="n">
-        <v>129100</v>
+        <v>129600</v>
       </c>
       <c r="V167" t="n">
         <v>134400</v>
       </c>
       <c r="W167" t="n">
-        <v>-3.9</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="168">
@@ -12291,13 +12291,13 @@
         <v>1.5</v>
       </c>
       <c r="U168" t="n">
-        <v>5300</v>
+        <v>5320</v>
       </c>
       <c r="V168" t="n">
         <v>5820</v>
       </c>
       <c r="W168" t="n">
-        <v>-8.9</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="169">
@@ -12435,13 +12435,13 @@
         <v>0</v>
       </c>
       <c r="U170" t="n">
-        <v>66800</v>
+        <v>67400</v>
       </c>
       <c r="V170" t="n">
         <v>59800</v>
       </c>
       <c r="W170" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="171">
@@ -12507,13 +12507,13 @@
         <v>-0.4</v>
       </c>
       <c r="U171" t="n">
-        <v>132100</v>
+        <v>132500</v>
       </c>
       <c r="V171" t="n">
         <v>141900</v>
       </c>
       <c r="W171" t="n">
-        <v>-6.9</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="172">
@@ -12552,13 +12552,13 @@
         <v>0</v>
       </c>
       <c r="U172" t="n">
-        <v>16310</v>
+        <v>16400</v>
       </c>
       <c r="V172" t="n">
         <v>13980</v>
       </c>
       <c r="W172" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="173">
@@ -12624,13 +12624,13 @@
         <v>0</v>
       </c>
       <c r="U173" t="n">
-        <v>208500</v>
+        <v>210000</v>
       </c>
       <c r="V173" t="n">
         <v>203500</v>
       </c>
       <c r="W173" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="174">
@@ -12696,13 +12696,13 @@
         <v>1.1</v>
       </c>
       <c r="U174" t="n">
-        <v>178500</v>
+        <v>178400</v>
       </c>
       <c r="V174" t="n">
         <v>161900</v>
       </c>
       <c r="W174" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="175">
@@ -12768,13 +12768,13 @@
         <v>1.6</v>
       </c>
       <c r="U175" t="n">
-        <v>18060</v>
+        <v>18090</v>
       </c>
       <c r="V175" t="n">
         <v>17840</v>
       </c>
       <c r="W175" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="176">
@@ -12912,13 +12912,13 @@
         <v>0</v>
       </c>
       <c r="U177" t="n">
-        <v>152200</v>
+        <v>151300</v>
       </c>
       <c r="V177" t="n">
         <v>158900</v>
       </c>
       <c r="W177" t="n">
-        <v>-4.2</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="178">
@@ -12948,31 +12948,31 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3469</v>
+        <v>3379</v>
       </c>
       <c r="G178" t="n">
         <v>3469</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="L178" t="n">
-        <v>12077.8</v>
+        <v>11990.4</v>
       </c>
       <c r="M178" t="n">
         <v>12077.8</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O178" t="n">
-        <v>13978.5</v>
+        <v>13997.8</v>
       </c>
       <c r="P178" t="n">
         <v>13978.5</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R178" t="n">
         <v>15265.1</v>
@@ -12984,13 +12984,13 @@
         <v>0</v>
       </c>
       <c r="U178" t="n">
-        <v>178800</v>
+        <v>179600</v>
       </c>
       <c r="V178" t="n">
         <v>178800</v>
       </c>
       <c r="W178" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="179">
@@ -13029,13 +13029,13 @@
         <v>0</v>
       </c>
       <c r="U179" t="n">
-        <v>34150</v>
+        <v>34450</v>
       </c>
       <c r="V179" t="n">
         <v>28850</v>
       </c>
       <c r="W179" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="180">
@@ -13101,13 +13101,13 @@
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>16790</v>
+        <v>16900</v>
       </c>
       <c r="V180" t="n">
         <v>15950</v>
       </c>
       <c r="W180" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181">
@@ -13173,13 +13173,13 @@
         <v>0</v>
       </c>
       <c r="U181" t="n">
-        <v>82000</v>
+        <v>82500</v>
       </c>
       <c r="V181" t="n">
         <v>80300</v>
       </c>
       <c r="W181" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="182">
@@ -13281,49 +13281,49 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>25262</v>
+        <v>25503</v>
       </c>
       <c r="G183" t="n">
         <v>25401</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L183" t="n">
-        <v>94142.60000000001</v>
+        <v>94216.3</v>
       </c>
       <c r="M183" t="n">
         <v>94482.60000000001</v>
       </c>
       <c r="N183" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="O183" t="n">
-        <v>96129.60000000001</v>
+        <v>96055.89999999999</v>
       </c>
       <c r="P183" t="n">
         <v>95887.8</v>
       </c>
       <c r="Q183" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="R183" t="n">
-        <v>99372.60000000001</v>
+        <v>99323.89999999999</v>
       </c>
       <c r="S183" t="n">
         <v>98431.89999999999</v>
       </c>
       <c r="T183" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U183" t="n">
-        <v>167600</v>
+        <v>168400</v>
       </c>
       <c r="V183" t="n">
         <v>173800</v>
       </c>
       <c r="W183" t="n">
-        <v>-3.6</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="184">
@@ -13389,13 +13389,13 @@
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>310500</v>
+        <v>312000</v>
       </c>
       <c r="V184" t="n">
         <v>283500</v>
       </c>
       <c r="W184" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="185">
@@ -13461,13 +13461,13 @@
         <v>-0.6</v>
       </c>
       <c r="U185" t="n">
-        <v>67000</v>
+        <v>67300</v>
       </c>
       <c r="V185" t="n">
         <v>71100</v>
       </c>
       <c r="W185" t="n">
-        <v>-5.8</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="186">
@@ -13533,13 +13533,13 @@
         <v>0</v>
       </c>
       <c r="U186" t="n">
-        <v>55200</v>
+        <v>55300</v>
       </c>
       <c r="V186" t="n">
         <v>52800</v>
       </c>
       <c r="W186" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="187">
@@ -13578,13 +13578,13 @@
         <v>-2.7</v>
       </c>
       <c r="U187" t="n">
-        <v>8530</v>
+        <v>8560</v>
       </c>
       <c r="V187" t="n">
         <v>8900</v>
       </c>
       <c r="W187" t="n">
-        <v>-4.2</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="188">
@@ -13650,13 +13650,13 @@
         <v>0</v>
       </c>
       <c r="U188" t="n">
-        <v>56000</v>
+        <v>56400</v>
       </c>
       <c r="V188" t="n">
         <v>55700</v>
       </c>
       <c r="W188" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="189">
@@ -13686,40 +13686,40 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G189" t="n">
         <v>219</v>
       </c>
       <c r="H189" t="n">
-        <v>-6.4</v>
+        <v>-5.9</v>
       </c>
       <c r="L189" t="n">
-        <v>764.3</v>
+        <v>761</v>
       </c>
       <c r="M189" t="n">
         <v>781.6</v>
       </c>
       <c r="N189" t="n">
-        <v>-2.2</v>
+        <v>-2.6</v>
       </c>
       <c r="O189" t="n">
-        <v>717.8</v>
+        <v>724.9</v>
       </c>
       <c r="P189" t="n">
         <v>708.6</v>
       </c>
       <c r="Q189" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="R189" t="n">
-        <v>803.5</v>
+        <v>819.3</v>
       </c>
       <c r="S189" t="n">
         <v>833.1</v>
       </c>
       <c r="T189" t="n">
-        <v>-3.6</v>
+        <v>-1.7</v>
       </c>
       <c r="U189" t="n">
         <v>40700</v>
@@ -13794,13 +13794,13 @@
         <v>0</v>
       </c>
       <c r="U190" t="n">
-        <v>503000</v>
+        <v>504000</v>
       </c>
       <c r="V190" t="n">
         <v>503000</v>
       </c>
       <c r="W190" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="191">
@@ -13830,31 +13830,31 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="G191" t="n">
         <v>506</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="L191" t="n">
-        <v>1876.2</v>
+        <v>1918.3</v>
       </c>
       <c r="M191" t="n">
         <v>1876.2</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O191" t="n">
-        <v>2419.8</v>
+        <v>2469.7</v>
       </c>
       <c r="P191" t="n">
         <v>2419.8</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R191" t="n">
         <v>3054</v>
@@ -13866,13 +13866,13 @@
         <v>0</v>
       </c>
       <c r="U191" t="n">
-        <v>291000</v>
+        <v>292500</v>
       </c>
       <c r="V191" t="n">
         <v>293000</v>
       </c>
       <c r="W191" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="192">
@@ -13914,7 +13914,7 @@
         <v>1359.3</v>
       </c>
       <c r="U192" t="n">
-        <v>108100</v>
+        <v>109000</v>
       </c>
     </row>
     <row r="193">
@@ -13980,13 +13980,13 @@
         <v>-2.1</v>
       </c>
       <c r="U193" t="n">
-        <v>128200</v>
+        <v>128800</v>
       </c>
       <c r="V193" t="n">
         <v>132500</v>
       </c>
       <c r="W193" t="n">
-        <v>-3.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="194">
@@ -14052,13 +14052,13 @@
         <v>0.8</v>
       </c>
       <c r="U194" t="n">
-        <v>15980</v>
+        <v>16020</v>
       </c>
       <c r="V194" t="n">
         <v>16470</v>
       </c>
       <c r="W194" t="n">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="195">
@@ -14088,49 +14088,49 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>2080</v>
+        <v>2040</v>
       </c>
       <c r="G195" t="n">
         <v>2084</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
       <c r="L195" t="n">
-        <v>6308.3</v>
+        <v>6290.6</v>
       </c>
       <c r="M195" t="n">
         <v>6314.5</v>
       </c>
       <c r="N195" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="O195" t="n">
-        <v>6903.2</v>
+        <v>6876.2</v>
       </c>
       <c r="P195" t="n">
         <v>6889.3</v>
       </c>
       <c r="Q195" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="R195" t="n">
-        <v>7326.1</v>
+        <v>7280.2</v>
       </c>
       <c r="S195" t="n">
         <v>7286.1</v>
       </c>
       <c r="T195" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U195" t="n">
-        <v>18540</v>
+        <v>18680</v>
       </c>
       <c r="V195" t="n">
         <v>18700</v>
       </c>
       <c r="W195" t="n">
-        <v>-0.9</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="196">
@@ -14196,13 +14196,13 @@
         <v>1.1</v>
       </c>
       <c r="U196" t="n">
-        <v>71900</v>
+        <v>72000</v>
       </c>
       <c r="V196" t="n">
         <v>72000</v>
       </c>
       <c r="W196" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -14268,13 +14268,13 @@
         <v>1.9</v>
       </c>
       <c r="U197" t="n">
-        <v>297000</v>
+        <v>299000</v>
       </c>
       <c r="V197" t="n">
         <v>263500</v>
       </c>
       <c r="W197" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="198">
@@ -14331,13 +14331,13 @@
         <v>0</v>
       </c>
       <c r="U198" t="n">
-        <v>82600</v>
+        <v>83000</v>
       </c>
       <c r="V198" t="n">
         <v>79400</v>
       </c>
       <c r="W198" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="199">
@@ -14403,13 +14403,13 @@
         <v>-0.4</v>
       </c>
       <c r="U199" t="n">
-        <v>180200</v>
+        <v>180400</v>
       </c>
       <c r="V199" t="n">
         <v>185700</v>
       </c>
       <c r="W199" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="200">
@@ -14475,13 +14475,13 @@
         <v>-3.8</v>
       </c>
       <c r="U200" t="n">
-        <v>38700</v>
+        <v>38650</v>
       </c>
       <c r="V200" t="n">
         <v>37100</v>
       </c>
       <c r="W200" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="201">
@@ -14520,13 +14520,13 @@
         <v>0</v>
       </c>
       <c r="U201" t="n">
-        <v>11200</v>
+        <v>11330</v>
       </c>
       <c r="V201" t="n">
         <v>10400</v>
       </c>
       <c r="W201" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="202">
@@ -14592,13 +14592,13 @@
         <v>0</v>
       </c>
       <c r="U202" t="n">
-        <v>59600</v>
+        <v>60000</v>
       </c>
       <c r="V202" t="n">
         <v>59300</v>
       </c>
       <c r="W202" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="203">
@@ -14664,13 +14664,13 @@
         <v>0.2</v>
       </c>
       <c r="U203" t="n">
-        <v>136700</v>
+        <v>137100</v>
       </c>
       <c r="V203" t="n">
         <v>148000</v>
       </c>
       <c r="W203" t="n">
-        <v>-7.6</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="204">
@@ -14772,34 +14772,34 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3057</v>
+        <v>3040</v>
       </c>
       <c r="G205" t="n">
         <v>3043</v>
       </c>
       <c r="H205" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="L205" t="n">
-        <v>10304.8</v>
+        <v>10328.9</v>
       </c>
       <c r="M205" t="n">
         <v>10267.5</v>
       </c>
       <c r="N205" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="O205" t="n">
-        <v>10995.2</v>
+        <v>11019.4</v>
       </c>
       <c r="P205" t="n">
         <v>10949.5</v>
       </c>
       <c r="Q205" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R205" t="n">
-        <v>11616.2</v>
+        <v>11613.8</v>
       </c>
       <c r="S205" t="n">
         <v>11569</v>
@@ -14808,13 +14808,13 @@
         <v>0.4</v>
       </c>
       <c r="U205" t="n">
-        <v>28900</v>
+        <v>29000</v>
       </c>
       <c r="V205" t="n">
         <v>31150</v>
       </c>
       <c r="W205" t="n">
-        <v>-7.2</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="206">
@@ -14880,13 +14880,13 @@
         <v>0</v>
       </c>
       <c r="U206" t="n">
-        <v>41700</v>
+        <v>41850</v>
       </c>
       <c r="V206" t="n">
         <v>36300</v>
       </c>
       <c r="W206" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="207">
@@ -14952,13 +14952,13 @@
         <v>0</v>
       </c>
       <c r="U207" t="n">
-        <v>65200</v>
+        <v>65300</v>
       </c>
       <c r="V207" t="n">
         <v>65200</v>
       </c>
       <c r="W207" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="208">
@@ -15024,13 +15024,13 @@
         <v>0</v>
       </c>
       <c r="U208" t="n">
-        <v>72800</v>
+        <v>73600</v>
       </c>
       <c r="V208" t="n">
         <v>67200</v>
       </c>
       <c r="W208" t="n">
-        <v>8.300000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="209">
@@ -15060,31 +15060,31 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="G209" t="n">
         <v>716</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="L209" t="n">
-        <v>2832.9</v>
+        <v>2826.2</v>
       </c>
       <c r="M209" t="n">
         <v>2832.9</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O209" t="n">
-        <v>3078.7</v>
+        <v>3065.6</v>
       </c>
       <c r="P209" t="n">
         <v>3078.7</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="R209" t="n">
         <v>3251.8</v>
@@ -15096,13 +15096,13 @@
         <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>58400</v>
+        <v>57800</v>
       </c>
       <c r="V209" t="n">
         <v>58600</v>
       </c>
       <c r="W209" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="210">
@@ -15168,13 +15168,13 @@
         <v>-0.1</v>
       </c>
       <c r="U210" t="n">
-        <v>270000</v>
+        <v>271000</v>
       </c>
       <c r="V210" t="n">
         <v>269500</v>
       </c>
       <c r="W210" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="211">
@@ -15240,13 +15240,13 @@
         <v>0</v>
       </c>
       <c r="U211" t="n">
-        <v>40150</v>
+        <v>40300</v>
       </c>
       <c r="V211" t="n">
         <v>39150</v>
       </c>
       <c r="W211" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="212">
@@ -15312,13 +15312,13 @@
         <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>258000</v>
+        <v>259500</v>
       </c>
       <c r="V212" t="n">
         <v>251000</v>
       </c>
       <c r="W212" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="213">
@@ -15348,49 +15348,49 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="G213" t="n">
         <v>1023</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L213" t="n">
-        <v>4116</v>
+        <v>4123.4</v>
       </c>
       <c r="M213" t="n">
         <v>4116</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O213" t="n">
-        <v>4713.2</v>
+        <v>4715.8</v>
       </c>
       <c r="P213" t="n">
         <v>4713.2</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R213" t="n">
-        <v>5334.9</v>
+        <v>5353.4</v>
       </c>
       <c r="S213" t="n">
         <v>5334.9</v>
       </c>
       <c r="T213" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U213" t="n">
-        <v>47100</v>
+        <v>47300</v>
       </c>
       <c r="V213" t="n">
         <v>46250</v>
       </c>
       <c r="W213" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="214">
@@ -15429,16 +15429,16 @@
         <v>0.4</v>
       </c>
       <c r="L214" t="n">
-        <v>24120.1</v>
+        <v>24090.1</v>
       </c>
       <c r="M214" t="n">
         <v>24162.2</v>
       </c>
       <c r="N214" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="O214" t="n">
-        <v>28068.1</v>
+        <v>28062.9</v>
       </c>
       <c r="P214" t="n">
         <v>28197.6</v>
@@ -15447,22 +15447,22 @@
         <v>-0.5</v>
       </c>
       <c r="R214" t="n">
-        <v>30980.9</v>
+        <v>30916.6</v>
       </c>
       <c r="S214" t="n">
         <v>30980.9</v>
       </c>
       <c r="T214" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="U214" t="n">
-        <v>1363000</v>
+        <v>1366000</v>
       </c>
       <c r="V214" t="n">
         <v>1390000</v>
       </c>
       <c r="W214" t="n">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="215">
@@ -15528,13 +15528,13 @@
         <v>0</v>
       </c>
       <c r="U215" t="n">
-        <v>30800</v>
+        <v>30850</v>
       </c>
       <c r="V215" t="n">
         <v>30850</v>
       </c>
       <c r="W215" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -15600,13 +15600,13 @@
         <v>0</v>
       </c>
       <c r="U216" t="n">
-        <v>306000</v>
+        <v>307000</v>
       </c>
       <c r="V216" t="n">
         <v>319000</v>
       </c>
       <c r="W216" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="217">
@@ -15672,13 +15672,13 @@
         <v>0</v>
       </c>
       <c r="U217" t="n">
-        <v>62000</v>
+        <v>62200</v>
       </c>
       <c r="V217" t="n">
         <v>56400</v>
       </c>
       <c r="W217" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="218">
@@ -15744,13 +15744,13 @@
         <v>0</v>
       </c>
       <c r="U218" t="n">
-        <v>168100</v>
+        <v>170200</v>
       </c>
       <c r="V218" t="n">
         <v>145100</v>
       </c>
       <c r="W218" t="n">
-        <v>15.9</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="219">
@@ -15816,13 +15816,13 @@
         <v>0</v>
       </c>
       <c r="U219" t="n">
-        <v>93200</v>
+        <v>93300</v>
       </c>
       <c r="V219" t="n">
         <v>92800</v>
       </c>
       <c r="W219" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="220">
@@ -15888,13 +15888,13 @@
         <v>0.2</v>
       </c>
       <c r="U220" t="n">
-        <v>138700</v>
+        <v>139400</v>
       </c>
       <c r="V220" t="n">
         <v>123700</v>
       </c>
       <c r="W220" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="221">
@@ -15960,13 +15960,13 @@
         <v>-4.1</v>
       </c>
       <c r="U221" t="n">
-        <v>55200</v>
+        <v>55500</v>
       </c>
       <c r="V221" t="n">
         <v>58300</v>
       </c>
       <c r="W221" t="n">
-        <v>-5.3</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="222">
@@ -15996,49 +15996,49 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G222" t="n">
         <v>331</v>
       </c>
       <c r="H222" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="L222" t="n">
-        <v>1145.7</v>
+        <v>1144.5</v>
       </c>
       <c r="M222" t="n">
         <v>1145</v>
       </c>
       <c r="N222" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="O222" t="n">
-        <v>1376.7</v>
+        <v>1383.1</v>
       </c>
       <c r="P222" t="n">
         <v>1368.3</v>
       </c>
       <c r="Q222" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="R222" t="n">
-        <v>1604.7</v>
+        <v>1613.7</v>
       </c>
       <c r="S222" t="n">
         <v>1592.8</v>
       </c>
       <c r="T222" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="U222" t="n">
-        <v>110200</v>
+        <v>110700</v>
       </c>
       <c r="V222" t="n">
         <v>125000</v>
       </c>
       <c r="W222" t="n">
-        <v>-11.8</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="223">
@@ -16104,13 +16104,13 @@
         <v>-2.3</v>
       </c>
       <c r="U223" t="n">
-        <v>115200</v>
+        <v>115600</v>
       </c>
       <c r="V223" t="n">
         <v>110500</v>
       </c>
       <c r="W223" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="224">
@@ -16140,31 +16140,31 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>964</v>
+        <v>947</v>
       </c>
       <c r="G224" t="n">
         <v>967</v>
       </c>
       <c r="H224" t="n">
-        <v>-0.3</v>
+        <v>-2.1</v>
       </c>
       <c r="L224" t="n">
-        <v>3273.8</v>
+        <v>3243.8</v>
       </c>
       <c r="M224" t="n">
         <v>3272.2</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="O224" t="n">
-        <v>3711.9</v>
+        <v>3738.2</v>
       </c>
       <c r="P224" t="n">
         <v>3717.2</v>
       </c>
       <c r="Q224" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="R224" t="n">
         <v>3980.5</v>
@@ -16176,13 +16176,13 @@
         <v>-0.1</v>
       </c>
       <c r="U224" t="n">
-        <v>35200</v>
+        <v>35250</v>
       </c>
       <c r="V224" t="n">
         <v>35300</v>
       </c>
       <c r="W224" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="225">
@@ -16248,13 +16248,13 @@
         <v>0.2</v>
       </c>
       <c r="U225" t="n">
-        <v>60500</v>
+        <v>60900</v>
       </c>
       <c r="V225" t="n">
         <v>62100</v>
       </c>
       <c r="W225" t="n">
-        <v>-2.6</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="226">
@@ -16284,31 +16284,31 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G226" t="n">
         <v>136</v>
       </c>
       <c r="H226" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L226" t="n">
-        <v>474.2</v>
+        <v>474.8</v>
       </c>
       <c r="M226" t="n">
         <v>474.2</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O226" t="n">
-        <v>589.8</v>
+        <v>589.4</v>
       </c>
       <c r="P226" t="n">
         <v>589.8</v>
       </c>
       <c r="Q226" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R226" t="n">
         <v>686.1</v>
@@ -16320,13 +16320,13 @@
         <v>0</v>
       </c>
       <c r="U226" t="n">
-        <v>20450</v>
+        <v>20600</v>
       </c>
       <c r="V226" t="n">
         <v>20650</v>
       </c>
       <c r="W226" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="227">
@@ -16392,13 +16392,13 @@
         <v>0.3</v>
       </c>
       <c r="U227" t="n">
-        <v>37150</v>
+        <v>37200</v>
       </c>
       <c r="V227" t="n">
         <v>38700</v>
       </c>
       <c r="W227" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="228">
@@ -16428,31 +16428,31 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3341</v>
+        <v>3278</v>
       </c>
       <c r="G228" t="n">
         <v>3345</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.1</v>
+        <v>-2</v>
       </c>
       <c r="L228" t="n">
-        <v>14540.4</v>
+        <v>14492.6</v>
       </c>
       <c r="M228" t="n">
         <v>14507.7</v>
       </c>
       <c r="N228" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="O228" t="n">
-        <v>15566.1</v>
+        <v>15475.9</v>
       </c>
       <c r="P228" t="n">
         <v>15637.9</v>
       </c>
       <c r="Q228" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="R228" t="n">
         <v>16596.7</v>
@@ -16464,13 +16464,13 @@
         <v>-1.1</v>
       </c>
       <c r="U228" t="n">
-        <v>197900</v>
+        <v>199500</v>
       </c>
       <c r="V228" t="n">
         <v>200500</v>
       </c>
       <c r="W228" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="229">
@@ -16536,13 +16536,13 @@
         <v>-1.6</v>
       </c>
       <c r="U229" t="n">
-        <v>33350</v>
+        <v>33450</v>
       </c>
       <c r="V229" t="n">
         <v>33100</v>
       </c>
       <c r="W229" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="230">
@@ -16608,13 +16608,13 @@
         <v>1.6</v>
       </c>
       <c r="U230" t="n">
-        <v>200000</v>
+        <v>200500</v>
       </c>
       <c r="V230" t="n">
         <v>210000</v>
       </c>
       <c r="W230" t="n">
-        <v>-4.8</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="231">
@@ -16680,13 +16680,13 @@
         <v>-0.4</v>
       </c>
       <c r="U231" t="n">
-        <v>675000</v>
+        <v>678000</v>
       </c>
       <c r="V231" t="n">
         <v>693000</v>
       </c>
       <c r="W231" t="n">
-        <v>-2.6</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="232">
@@ -16752,13 +16752,13 @@
         <v>1.6</v>
       </c>
       <c r="U232" t="n">
-        <v>118100</v>
+        <v>118000</v>
       </c>
       <c r="V232" t="n">
         <v>128400</v>
       </c>
       <c r="W232" t="n">
-        <v>-8</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="233">
@@ -16824,13 +16824,13 @@
         <v>-0.1</v>
       </c>
       <c r="U233" t="n">
-        <v>105100</v>
+        <v>105700</v>
       </c>
       <c r="V233" t="n">
         <v>111600</v>
       </c>
       <c r="W233" t="n">
-        <v>-5.8</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="234">
@@ -16896,13 +16896,13 @@
         <v>-0.4</v>
       </c>
       <c r="U234" t="n">
-        <v>82200</v>
+        <v>82000</v>
       </c>
       <c r="V234" t="n">
         <v>72600</v>
       </c>
       <c r="W234" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="235">
@@ -16968,13 +16968,13 @@
         <v>6.3</v>
       </c>
       <c r="U235" t="n">
-        <v>5850</v>
+        <v>5910</v>
       </c>
       <c r="V235" t="n">
         <v>5960</v>
       </c>
       <c r="W235" t="n">
-        <v>-1.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="236">
@@ -17103,13 +17103,13 @@
         <v>-0.6</v>
       </c>
       <c r="U237" t="n">
-        <v>366000</v>
+        <v>367000</v>
       </c>
       <c r="V237" t="n">
         <v>367000</v>
       </c>
       <c r="W237" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -17175,13 +17175,13 @@
         <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>119100</v>
+        <v>120100</v>
       </c>
       <c r="V238" t="n">
         <v>125900</v>
       </c>
       <c r="W238" t="n">
-        <v>-5.4</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="239">
@@ -17247,13 +17247,13 @@
         <v>0.2</v>
       </c>
       <c r="U239" t="n">
-        <v>127600</v>
+        <v>128000</v>
       </c>
       <c r="V239" t="n">
         <v>133500</v>
       </c>
       <c r="W239" t="n">
-        <v>-4.4</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="240">
@@ -17319,13 +17319,13 @@
         <v>0</v>
       </c>
       <c r="U240" t="n">
-        <v>51400</v>
+        <v>51900</v>
       </c>
       <c r="V240" t="n">
         <v>51700</v>
       </c>
       <c r="W240" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="241">
@@ -17391,13 +17391,13 @@
         <v>0.2</v>
       </c>
       <c r="U241" t="n">
-        <v>22450</v>
+        <v>22350</v>
       </c>
       <c r="V241" t="n">
         <v>23450</v>
       </c>
       <c r="W241" t="n">
-        <v>-4.3</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="242">
@@ -17463,13 +17463,13 @@
         <v>-0.5</v>
       </c>
       <c r="U242" t="n">
-        <v>272500</v>
+        <v>274500</v>
       </c>
       <c r="V242" t="n">
         <v>311000</v>
       </c>
       <c r="W242" t="n">
-        <v>-12.4</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="243">
@@ -17535,13 +17535,13 @@
         <v>1.1</v>
       </c>
       <c r="U243" t="n">
-        <v>2785000</v>
+        <v>2790000</v>
       </c>
       <c r="V243" t="n">
         <v>2784000</v>
       </c>
       <c r="W243" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="244">
@@ -17607,13 +17607,13 @@
         <v>-0.9</v>
       </c>
       <c r="U244" t="n">
-        <v>162500</v>
+        <v>163200</v>
       </c>
       <c r="V244" t="n">
         <v>165900</v>
       </c>
       <c r="W244" t="n">
-        <v>-2</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="245">
@@ -17679,13 +17679,13 @@
         <v>0</v>
       </c>
       <c r="U245" t="n">
-        <v>16060</v>
+        <v>16100</v>
       </c>
       <c r="V245" t="n">
         <v>16280</v>
       </c>
       <c r="W245" t="n">
-        <v>-1.4</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="246">
@@ -17742,13 +17742,13 @@
         <v>0</v>
       </c>
       <c r="U246" t="n">
-        <v>36300</v>
+        <v>36500</v>
       </c>
       <c r="V246" t="n">
         <v>36100</v>
       </c>
       <c r="W246" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="247">
@@ -17814,13 +17814,13 @@
         <v>0</v>
       </c>
       <c r="U247" t="n">
-        <v>154400</v>
+        <v>153700</v>
       </c>
       <c r="V247" t="n">
         <v>146200</v>
       </c>
       <c r="W247" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="248">
@@ -17859,7 +17859,7 @@
         <v>-0.1</v>
       </c>
       <c r="L248" t="n">
-        <v>2836.5</v>
+        <v>2836.6</v>
       </c>
       <c r="M248" t="n">
         <v>2830.4</v>
@@ -17868,31 +17868,31 @@
         <v>0.2</v>
       </c>
       <c r="O248" t="n">
-        <v>3539.1</v>
+        <v>3534.2</v>
       </c>
       <c r="P248" t="n">
         <v>3545.5</v>
       </c>
       <c r="Q248" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="R248" t="n">
-        <v>4520.9</v>
+        <v>4510.9</v>
       </c>
       <c r="S248" t="n">
         <v>4543.1</v>
       </c>
       <c r="T248" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="U248" t="n">
-        <v>382000</v>
+        <v>383500</v>
       </c>
       <c r="V248" t="n">
         <v>374500</v>
       </c>
       <c r="W248" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="249">
@@ -17958,13 +17958,13 @@
         <v>0.2</v>
       </c>
       <c r="U249" t="n">
-        <v>33550</v>
+        <v>33750</v>
       </c>
       <c r="V249" t="n">
         <v>36200</v>
       </c>
       <c r="W249" t="n">
-        <v>-7.3</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="250">
@@ -18030,13 +18030,13 @@
         <v>22.1</v>
       </c>
       <c r="U250" t="n">
-        <v>9980</v>
+        <v>9990</v>
       </c>
       <c r="V250" t="n">
         <v>9680</v>
       </c>
       <c r="W250" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="251">
@@ -18174,7 +18174,7 @@
         <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>19720</v>
+        <v>19730</v>
       </c>
       <c r="V252" t="n">
         <v>20400</v>
@@ -18246,13 +18246,13 @@
         <v>0</v>
       </c>
       <c r="U253" t="n">
-        <v>75800</v>
+        <v>76400</v>
       </c>
       <c r="V253" t="n">
         <v>76000</v>
       </c>
       <c r="W253" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="254">
@@ -18318,13 +18318,13 @@
         <v>0.4</v>
       </c>
       <c r="U254" t="n">
-        <v>425500</v>
+        <v>426000</v>
       </c>
       <c r="V254" t="n">
         <v>439000</v>
       </c>
       <c r="W254" t="n">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="255">
@@ -18390,13 +18390,13 @@
         <v>-1.1</v>
       </c>
       <c r="U255" t="n">
-        <v>155100</v>
+        <v>155400</v>
       </c>
       <c r="V255" t="n">
         <v>161900</v>
       </c>
       <c r="W255" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="256">
@@ -18462,13 +18462,13 @@
         <v>0.2</v>
       </c>
       <c r="U256" t="n">
-        <v>147900</v>
+        <v>149200</v>
       </c>
       <c r="V256" t="n">
         <v>121700</v>
       </c>
       <c r="W256" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="257">
@@ -18534,13 +18534,13 @@
         <v>0</v>
       </c>
       <c r="U257" t="n">
-        <v>422500</v>
+        <v>426500</v>
       </c>
       <c r="V257" t="n">
         <v>364500</v>
       </c>
       <c r="W257" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="258">
@@ -18606,13 +18606,13 @@
         <v>0</v>
       </c>
       <c r="U258" t="n">
-        <v>17620</v>
+        <v>17760</v>
       </c>
       <c r="V258" t="n">
         <v>18280</v>
       </c>
       <c r="W258" t="n">
-        <v>-3.6</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="259">
@@ -18678,13 +18678,13 @@
         <v>-1.5</v>
       </c>
       <c r="U259" t="n">
-        <v>368000</v>
+        <v>369000</v>
       </c>
       <c r="V259" t="n">
         <v>360500</v>
       </c>
       <c r="W259" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="260">
@@ -18750,13 +18750,13 @@
         <v>0.2</v>
       </c>
       <c r="U260" t="n">
-        <v>75000</v>
+        <v>75700</v>
       </c>
       <c r="V260" t="n">
         <v>81300</v>
       </c>
       <c r="W260" t="n">
-        <v>-7.7</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="261">
@@ -18822,13 +18822,13 @@
         <v>0</v>
       </c>
       <c r="U261" t="n">
-        <v>18730</v>
+        <v>18790</v>
       </c>
       <c r="V261" t="n">
         <v>17060</v>
       </c>
       <c r="W261" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="262">
@@ -18894,13 +18894,13 @@
         <v>0</v>
       </c>
       <c r="U262" t="n">
-        <v>40050</v>
+        <v>40150</v>
       </c>
       <c r="V262" t="n">
         <v>40900</v>
       </c>
       <c r="W262" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="263">
@@ -19011,13 +19011,13 @@
         <v>-30.8</v>
       </c>
       <c r="U264" t="n">
-        <v>44200</v>
+        <v>44650</v>
       </c>
       <c r="V264" t="n">
         <v>41850</v>
       </c>
       <c r="W264" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="265">
@@ -19056,13 +19056,13 @@
         <v>0</v>
       </c>
       <c r="U265" t="n">
-        <v>32000</v>
+        <v>31900</v>
       </c>
       <c r="V265" t="n">
         <v>31450</v>
       </c>
       <c r="W265" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="266">
@@ -19173,13 +19173,13 @@
         <v>-4.7</v>
       </c>
       <c r="U267" t="n">
-        <v>65800</v>
+        <v>66200</v>
       </c>
       <c r="V267" t="n">
         <v>55400</v>
       </c>
       <c r="W267" t="n">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="268">
@@ -19317,13 +19317,13 @@
         <v>0.9</v>
       </c>
       <c r="U269" t="n">
-        <v>46200</v>
+        <v>46050</v>
       </c>
       <c r="V269" t="n">
         <v>45550</v>
       </c>
       <c r="W269" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="270">
@@ -19389,13 +19389,13 @@
         <v>0</v>
       </c>
       <c r="U270" t="n">
-        <v>86300</v>
+        <v>86900</v>
       </c>
       <c r="V270" t="n">
         <v>80000</v>
       </c>
       <c r="W270" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="271">
@@ -19461,13 +19461,13 @@
         <v>0.2</v>
       </c>
       <c r="U271" t="n">
-        <v>233000</v>
+        <v>234500</v>
       </c>
       <c r="V271" t="n">
         <v>242500</v>
       </c>
       <c r="W271" t="n">
-        <v>-3.9</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="272">
@@ -19533,13 +19533,13 @@
         <v>-6.6</v>
       </c>
       <c r="U272" t="n">
-        <v>73700</v>
+        <v>74100</v>
       </c>
       <c r="V272" t="n">
         <v>79600</v>
       </c>
       <c r="W272" t="n">
-        <v>-7.4</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="273">
@@ -19578,13 +19578,13 @@
         <v>0</v>
       </c>
       <c r="U273" t="n">
-        <v>81000</v>
+        <v>81900</v>
       </c>
       <c r="V273" t="n">
         <v>64400</v>
       </c>
       <c r="W273" t="n">
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="274">
@@ -19650,13 +19650,13 @@
         <v>0</v>
       </c>
       <c r="U274" t="n">
-        <v>9880</v>
+        <v>9910</v>
       </c>
       <c r="V274" t="n">
         <v>9400</v>
       </c>
       <c r="W274" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="275">
@@ -19686,13 +19686,13 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G275" t="n">
         <v>263</v>
       </c>
       <c r="H275" t="n">
-        <v>-5.3</v>
+        <v>-4.2</v>
       </c>
       <c r="L275" t="n">
         <v>1065.1</v>
@@ -19704,31 +19704,31 @@
         <v>-1.4</v>
       </c>
       <c r="O275" t="n">
-        <v>1007.1</v>
+        <v>1001</v>
       </c>
       <c r="P275" t="n">
         <v>1037.8</v>
       </c>
       <c r="Q275" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="R275" t="n">
-        <v>2221.4</v>
+        <v>2005.3</v>
       </c>
       <c r="S275" t="n">
         <v>2317.5</v>
       </c>
       <c r="T275" t="n">
-        <v>-4.1</v>
+        <v>-13.5</v>
       </c>
       <c r="U275" t="n">
-        <v>31050</v>
+        <v>31000</v>
       </c>
       <c r="V275" t="n">
         <v>31550</v>
       </c>
       <c r="W275" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="276">
@@ -19794,13 +19794,13 @@
         <v>-0.1</v>
       </c>
       <c r="U276" t="n">
-        <v>183100</v>
+        <v>183400</v>
       </c>
       <c r="V276" t="n">
         <v>183100</v>
       </c>
       <c r="W276" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="277">
@@ -19866,13 +19866,13 @@
         <v>0</v>
       </c>
       <c r="U277" t="n">
-        <v>18470</v>
+        <v>18520</v>
       </c>
       <c r="V277" t="n">
         <v>18120</v>
       </c>
       <c r="W277" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="278">
@@ -19938,13 +19938,13 @@
         <v>0</v>
       </c>
       <c r="U278" t="n">
-        <v>51500</v>
+        <v>51400</v>
       </c>
       <c r="V278" t="n">
         <v>46100</v>
       </c>
       <c r="W278" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="279">
@@ -19983,13 +19983,13 @@
         <v>0</v>
       </c>
       <c r="U279" t="n">
-        <v>36050</v>
+        <v>36200</v>
       </c>
       <c r="V279" t="n">
         <v>29700</v>
       </c>
       <c r="W279" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-09 · 전주 2026-10-03</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-10 · 전주 2026-10-03</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -465,7 +465,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-16 · 전주 2026-10-10</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-17 · 전주 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -710,13 +710,13 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>15670</v>
+        <v>15600</v>
       </c>
       <c r="AC3" t="n">
         <v>14750</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="4">
@@ -746,73 +746,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>325.3</v>
+        <v>325.8</v>
       </c>
       <c r="G4" t="n">
-        <v>-51.4</v>
+        <v>-51.3</v>
       </c>
       <c r="H4" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="I4" t="n">
         <v>300</v>
       </c>
       <c r="J4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="K4" t="n">
-        <v>235.9</v>
+        <v>241.9</v>
       </c>
       <c r="L4" t="n">
-        <v>-27.5</v>
+        <v>-25.8</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.5</v>
+        <v>-7.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1318</v>
+        <v>1323.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.3</v>
+        <v>26.8</v>
       </c>
       <c r="R4" t="n">
         <v>1291.1</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2035.6</v>
+        <v>2042.4</v>
       </c>
       <c r="U4" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="V4" t="n">
         <v>2032.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3032</v>
+        <v>3020.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>48.9</v>
+        <v>47.9</v>
       </c>
       <c r="Z4" t="n">
         <v>3020.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>80400</v>
+        <v>80600</v>
       </c>
       <c r="AC4" t="n">
         <v>73300</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -938,28 +938,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4774.5</v>
+        <v>4797</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="H6" t="n">
-        <v>106.4</v>
+        <v>107.4</v>
       </c>
       <c r="I6" t="n">
         <v>4749</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>5284.5</v>
+        <v>5390</v>
       </c>
       <c r="L6" t="n">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="M6" t="n">
-        <v>92</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="P6" t="n">
         <v>18121.5</v>
@@ -998,13 +998,13 @@
         <v>2.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1020000</v>
+        <v>1017000</v>
       </c>
       <c r="AC6" t="n">
         <v>1331000</v>
       </c>
       <c r="AD6" t="n">
-        <v>-23.4</v>
+        <v>-23.6</v>
       </c>
     </row>
     <row r="7">
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>44150</v>
+        <v>44250</v>
       </c>
       <c r="AC7" t="n">
         <v>48200</v>
       </c>
       <c r="AD7" t="n">
-        <v>-8.4</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1190,13 +1190,13 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>26200</v>
+        <v>26100</v>
       </c>
       <c r="AC8" t="n">
         <v>26200</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9">
@@ -1286,13 +1286,13 @@
         <v>-2.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>110300</v>
+        <v>110900</v>
       </c>
       <c r="AC9" t="n">
         <v>107000</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
@@ -1478,13 +1478,13 @@
         <v>1.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1273000</v>
+        <v>1265000</v>
       </c>
       <c r="AC11" t="n">
         <v>1686000</v>
       </c>
       <c r="AD11" t="n">
-        <v>-24.5</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="12">
@@ -1514,73 +1514,73 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2120.2</v>
+        <v>2121.9</v>
       </c>
       <c r="G12" t="n">
         <v>-19</v>
       </c>
       <c r="H12" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
       <c r="I12" t="n">
         <v>2143</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="K12" t="n">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="M12" t="n">
-        <v>76.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="P12" t="n">
-        <v>8636.700000000001</v>
+        <v>8634.299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="R12" t="n">
         <v>8691</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="T12" t="n">
-        <v>11409</v>
+        <v>11387.4</v>
       </c>
       <c r="U12" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="V12" t="n">
         <v>11399.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="X12" t="n">
-        <v>13712.8</v>
+        <v>13552.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>20.2</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
         <v>13734.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>93200</v>
+        <v>93300</v>
       </c>
       <c r="AC12" t="n">
         <v>106300</v>
       </c>
       <c r="AD12" t="n">
-        <v>-12.3</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="13">
@@ -1610,64 +1610,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7684.9</v>
+        <v>7769.4</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.2</v>
+        <v>-12.2</v>
       </c>
       <c r="H13" t="n">
-        <v>15.7</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
         <v>8056</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.6</v>
+        <v>-3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>6712.3</v>
+        <v>7188.2</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.7</v>
+        <v>-7.5</v>
       </c>
       <c r="M13" t="n">
-        <v>71.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="P13" t="n">
-        <v>32941.3</v>
+        <v>32996.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="R13" t="n">
         <v>32565.4</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>40036.2</v>
+        <v>39889.6</v>
       </c>
       <c r="U13" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
         <v>39419.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>38337.7</v>
+        <v>38638.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>-4.2</v>
+        <v>-3.1</v>
       </c>
       <c r="Z13" t="n">
         <v>38107.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB13" t="n">
         <v>585000</v>
@@ -1766,13 +1766,13 @@
         <v>-3.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>106600</v>
+        <v>106200</v>
       </c>
       <c r="AC14" t="n">
         <v>110400</v>
       </c>
       <c r="AD14" t="n">
-        <v>-3.4</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="15">
@@ -1862,13 +1862,13 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>107600</v>
+        <v>106500</v>
       </c>
       <c r="AC15" t="n">
         <v>136500</v>
       </c>
       <c r="AD15" t="n">
-        <v>-21.2</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="16">
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>124800</v>
+        <v>125000</v>
       </c>
       <c r="AC16" t="n">
         <v>129700</v>
       </c>
       <c r="AD16" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1994,73 +1994,73 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>341.1</v>
+        <v>331.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-43</v>
+        <v>-44.6</v>
       </c>
       <c r="H17" t="n">
-        <v>26.5</v>
+        <v>23.1</v>
       </c>
       <c r="I17" t="n">
         <v>398</v>
       </c>
       <c r="J17" t="n">
-        <v>-14.3</v>
+        <v>-16.6</v>
       </c>
       <c r="K17" t="n">
-        <v>289.7</v>
+        <v>288.4</v>
       </c>
       <c r="L17" t="n">
-        <v>-15.1</v>
+        <v>-13.1</v>
       </c>
       <c r="M17" t="n">
-        <v>227</v>
+        <v>225.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1542.9</v>
+        <v>1531.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>56.8</v>
+        <v>55.7</v>
       </c>
       <c r="R17" t="n">
         <v>1677.8</v>
       </c>
       <c r="S17" t="n">
-        <v>-8</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>2063.7</v>
+        <v>2072.2</v>
       </c>
       <c r="U17" t="n">
-        <v>33.8</v>
+        <v>35.3</v>
       </c>
       <c r="V17" t="n">
         <v>2298.3</v>
       </c>
       <c r="W17" t="n">
-        <v>-10.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>2469.7</v>
+        <v>2474.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="Z17" t="n">
         <v>2683.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>-8</v>
+        <v>-7.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>35500</v>
+        <v>35650</v>
       </c>
       <c r="AC17" t="n">
         <v>46600</v>
       </c>
       <c r="AD17" t="n">
-        <v>-23.8</v>
+        <v>-23.5</v>
       </c>
     </row>
     <row r="18">
@@ -2090,73 +2090,73 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>506.8</v>
+        <v>482.8</v>
       </c>
       <c r="G18" t="n">
-        <v>-16.7</v>
+        <v>-20.6</v>
       </c>
       <c r="H18" t="n">
-        <v>71.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="I18" t="n">
         <v>512</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>-5.7</v>
       </c>
       <c r="K18" t="n">
-        <v>593.4</v>
+        <v>563.8</v>
       </c>
       <c r="L18" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="M18" t="n">
-        <v>36.7</v>
+        <v>29.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2309.3</v>
+        <v>2267.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>79.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="R18" t="n">
         <v>2293.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2686.6</v>
+        <v>2625.1</v>
       </c>
       <c r="U18" t="n">
-        <v>16.3</v>
+        <v>15.8</v>
       </c>
       <c r="V18" t="n">
         <v>2609.1</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="X18" t="n">
-        <v>3500.3</v>
+        <v>3461.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.3</v>
+        <v>31.9</v>
       </c>
       <c r="Z18" t="n">
         <v>3375.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>23650</v>
+        <v>23800</v>
       </c>
       <c r="AC18" t="n">
         <v>28350</v>
       </c>
       <c r="AD18" t="n">
-        <v>-16.6</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="19">
@@ -2186,19 +2186,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3209.4</v>
+        <v>3000.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-39.3</v>
+        <v>-43.2</v>
       </c>
       <c r="H19" t="n">
-        <v>-54.6</v>
+        <v>-57.6</v>
       </c>
       <c r="K19" t="n">
-        <v>1812</v>
+        <v>1564.2</v>
       </c>
       <c r="L19" t="n">
-        <v>-43.5</v>
+        <v>-47.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13305.3</v>
+        <v>13013.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
         <v>13421.9</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9</v>
+        <v>-3</v>
       </c>
       <c r="T19" t="n">
-        <v>14401</v>
+        <v>14465.3</v>
       </c>
       <c r="U19" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="V19" t="n">
         <v>14395.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X19" t="n">
-        <v>15882.7</v>
+        <v>15983.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
         <v>15881.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>43000</v>
+        <v>43050</v>
       </c>
       <c r="AC19" t="n">
         <v>46900</v>
       </c>
       <c r="AD19" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2302,13 +2302,13 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>18000</v>
+        <v>17930</v>
       </c>
       <c r="AC20" t="n">
         <v>17560</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>22650</v>
+        <v>22800</v>
       </c>
       <c r="AC21" t="n">
         <v>22550</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="22">
@@ -2530,64 +2530,64 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1225</v>
+        <v>1132</v>
       </c>
       <c r="G23" t="n">
-        <v>-5</v>
+        <v>-12.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="I23" t="n">
         <v>1225</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-7.6</v>
       </c>
       <c r="K23" t="n">
-        <v>1174.2</v>
+        <v>1093.4</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.1</v>
+        <v>-3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>76.5</v>
+        <v>64.3</v>
       </c>
       <c r="P23" t="n">
-        <v>4585</v>
+        <v>4495</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="R23" t="n">
         <v>4585</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T23" t="n">
-        <v>5192.2</v>
+        <v>5180.5</v>
       </c>
       <c r="U23" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="V23" t="n">
         <v>5192.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="X23" t="n">
-        <v>5566</v>
+        <v>5544.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
         <v>5566</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AB23" t="n">
         <v>430000</v>
@@ -2641,13 +2641,13 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>10220</v>
+        <v>10270</v>
       </c>
       <c r="AC24" t="n">
         <v>11030</v>
       </c>
       <c r="AD24" t="n">
-        <v>-7.3</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="25">
@@ -2739,13 +2739,13 @@
         <v>-2.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>101100</v>
+        <v>100200</v>
       </c>
       <c r="AC25" t="n">
         <v>103000</v>
       </c>
       <c r="AD25" t="n">
-        <v>-1.8</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="26">
@@ -2837,13 +2837,13 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>8720</v>
+        <v>8800</v>
       </c>
       <c r="AC26" t="n">
         <v>8990</v>
       </c>
       <c r="AD26" t="n">
-        <v>-3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="27">
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>7810</v>
+        <v>7840</v>
       </c>
       <c r="AC27" t="n">
         <v>8100</v>
       </c>
       <c r="AD27" t="n">
-        <v>-3.6</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="28">
@@ -2973,34 +2973,34 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1870.9</v>
+        <v>1868.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="I28" t="n">
         <v>1871</v>
       </c>
       <c r="J28" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="K28" t="n">
         <v>1892.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
         <v>36</v>
       </c>
       <c r="P28" t="n">
-        <v>7295.8</v>
+        <v>7293.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="R28" t="n">
         <v>7302.1</v>
@@ -3009,7 +3009,7 @@
         <v>-0.1</v>
       </c>
       <c r="T28" t="n">
-        <v>8942.4</v>
+        <v>8941.799999999999</v>
       </c>
       <c r="U28" t="n">
         <v>22.6</v>
@@ -3021,7 +3021,7 @@
         <v>-0.2</v>
       </c>
       <c r="X28" t="n">
-        <v>10594.1</v>
+        <v>10594.4</v>
       </c>
       <c r="Y28" t="n">
         <v>18.5</v>
@@ -3033,13 +3033,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1218000</v>
+        <v>1228000</v>
       </c>
       <c r="AC28" t="n">
         <v>1165000</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="29">
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3085.2</v>
+        <v>2851.8</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3077,67 +3077,67 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>95.8</v>
+        <v>81</v>
       </c>
       <c r="I29" t="n">
         <v>3054</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>-6.6</v>
       </c>
       <c r="K29" t="n">
-        <v>2296.4</v>
+        <v>2006.2</v>
       </c>
       <c r="L29" t="n">
-        <v>-25.6</v>
+        <v>-29.7</v>
       </c>
       <c r="M29" t="n">
-        <v>48.2</v>
+        <v>29.5</v>
       </c>
       <c r="P29" t="n">
-        <v>8355.4</v>
+        <v>7624.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>-25</v>
+        <v>-31.5</v>
       </c>
       <c r="R29" t="n">
         <v>8264.9</v>
       </c>
       <c r="S29" t="n">
-        <v>1.1</v>
+        <v>-7.7</v>
       </c>
       <c r="T29" t="n">
-        <v>22094.7</v>
+        <v>21778.1</v>
       </c>
       <c r="U29" t="n">
-        <v>164.4</v>
+        <v>185.6</v>
       </c>
       <c r="V29" t="n">
         <v>21965.2</v>
       </c>
       <c r="W29" t="n">
-        <v>0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="X29" t="n">
-        <v>24899.9</v>
+        <v>26036.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>12.7</v>
+        <v>19.6</v>
       </c>
       <c r="Z29" t="n">
         <v>24899.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>26400</v>
+        <v>26500</v>
       </c>
       <c r="AC29" t="n">
         <v>30500</v>
       </c>
       <c r="AD29" t="n">
-        <v>-13.4</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="30">
@@ -3229,13 +3229,13 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>102700</v>
+        <v>102600</v>
       </c>
       <c r="AC30" t="n">
         <v>108400</v>
       </c>
       <c r="AD30" t="n">
-        <v>-5.3</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="31">
@@ -3423,13 +3423,13 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>40600</v>
+        <v>40550</v>
       </c>
       <c r="AC32" t="n">
         <v>42050</v>
       </c>
       <c r="AD32" t="n">
-        <v>-3.4</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="33">
@@ -3519,13 +3519,13 @@
         <v>-5.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>28300</v>
+        <v>28250</v>
       </c>
       <c r="AC33" t="n">
         <v>28050</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="34">
@@ -3555,73 +3555,73 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1754.5</v>
+        <v>1737.6</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>75.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="I34" t="n">
         <v>1789</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.9</v>
+        <v>-2.9</v>
       </c>
       <c r="K34" t="n">
-        <v>2437.1</v>
+        <v>2422.7</v>
       </c>
       <c r="L34" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="M34" t="n">
-        <v>41.2</v>
+        <v>40.4</v>
       </c>
       <c r="P34" t="n">
-        <v>7824.7</v>
+        <v>7794.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>63</v>
+        <v>62.4</v>
       </c>
       <c r="R34" t="n">
         <v>7876.5</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="T34" t="n">
-        <v>8583.299999999999</v>
+        <v>8512.1</v>
       </c>
       <c r="U34" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V34" t="n">
         <v>8671.299999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>-1</v>
+        <v>-1.8</v>
       </c>
       <c r="X34" t="n">
-        <v>9215.5</v>
+        <v>9110.200000000001</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Z34" t="n">
         <v>9357.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>-1.5</v>
+        <v>-2.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>275000</v>
+        <v>276000</v>
       </c>
       <c r="AC34" t="n">
         <v>305500</v>
       </c>
       <c r="AD34" t="n">
-        <v>-10</v>
+        <v>-9.699999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3711,13 +3711,13 @@
         <v>0.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>409500</v>
+        <v>410500</v>
       </c>
       <c r="AC35" t="n">
         <v>394500</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="36">
@@ -3909,13 +3909,13 @@
         <v>-0.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>98300</v>
+        <v>97900</v>
       </c>
       <c r="AC37" t="n">
         <v>94800</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="38">
@@ -3945,43 +3945,43 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>25546</v>
+        <v>25266</v>
       </c>
       <c r="G38" t="n">
-        <v>-10.4</v>
+        <v>-11.4</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="I38" t="n">
         <v>27894</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.4</v>
+        <v>-9.4</v>
       </c>
       <c r="K38" t="n">
-        <v>26051.3</v>
+        <v>26040.5</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="M38" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="P38" t="n">
-        <v>105425.3</v>
+        <v>105134.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>-8.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="R38" t="n">
         <v>110121.3</v>
       </c>
       <c r="S38" t="n">
-        <v>-4.3</v>
+        <v>-4.5</v>
       </c>
       <c r="T38" t="n">
-        <v>117115</v>
+        <v>116788.2</v>
       </c>
       <c r="U38" t="n">
         <v>11.1</v>
@@ -3990,10 +3990,10 @@
         <v>125334.8</v>
       </c>
       <c r="W38" t="n">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="X38" t="n">
-        <v>127919.7</v>
+        <v>127535</v>
       </c>
       <c r="Y38" t="n">
         <v>9.199999999999999</v>
@@ -4002,16 +4002,16 @@
         <v>136955</v>
       </c>
       <c r="AA38" t="n">
-        <v>-6.6</v>
+        <v>-6.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>312500</v>
+        <v>314000</v>
       </c>
       <c r="AC38" t="n">
         <v>324500</v>
       </c>
       <c r="AD38" t="n">
-        <v>-3.7</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="39">
@@ -4101,13 +4101,13 @@
         <v>2.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>296500</v>
+        <v>297000</v>
       </c>
       <c r="AC39" t="n">
         <v>305500</v>
       </c>
       <c r="AD39" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="40">
@@ -4137,67 +4137,67 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>5297</v>
+        <v>5148.1</v>
       </c>
       <c r="G40" t="n">
-        <v>-54.9</v>
+        <v>-56.1</v>
       </c>
       <c r="H40" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="K40" t="n">
-        <v>4620.1</v>
+        <v>4666.4</v>
       </c>
       <c r="L40" t="n">
-        <v>-12.8</v>
+        <v>-9.4</v>
       </c>
       <c r="M40" t="n">
-        <v>-11.9</v>
+        <v>-11</v>
       </c>
       <c r="P40" t="n">
-        <v>24256.7</v>
+        <v>24151.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="R40" t="n">
         <v>24249.9</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="T40" t="n">
-        <v>24504.1</v>
+        <v>24625.4</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>24347.9</v>
       </c>
       <c r="W40" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>25818.9</v>
+        <v>25935.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z40" t="n">
         <v>25650.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>181700</v>
+        <v>182300</v>
       </c>
       <c r="AC40" t="n">
         <v>186100</v>
       </c>
       <c r="AD40" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="41">
@@ -4287,13 +4287,13 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>48650</v>
+        <v>48450</v>
       </c>
       <c r="AC41" t="n">
         <v>50000</v>
       </c>
       <c r="AD41" t="n">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="42">
@@ -4419,58 +4419,58 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5110.2</v>
+        <v>5184.6</v>
       </c>
       <c r="G43" t="n">
-        <v>-25</v>
+        <v>-23.9</v>
       </c>
       <c r="H43" t="n">
-        <v>30.6</v>
+        <v>32.5</v>
       </c>
       <c r="I43" t="n">
         <v>5175</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.3</v>
+        <v>0.2</v>
       </c>
       <c r="K43" t="n">
-        <v>4492</v>
+        <v>4495.3</v>
       </c>
       <c r="L43" t="n">
-        <v>-12.1</v>
+        <v>-13.3</v>
       </c>
       <c r="M43" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="P43" t="n">
-        <v>22797.8</v>
+        <v>22848.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="R43" t="n">
         <v>22910.5</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="T43" t="n">
-        <v>19947.9</v>
+        <v>19932.3</v>
       </c>
       <c r="U43" t="n">
-        <v>-12.5</v>
+        <v>-12.8</v>
       </c>
       <c r="V43" t="n">
         <v>20113.9</v>
       </c>
       <c r="W43" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="X43" t="n">
         <v>20820.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z43" t="n">
         <v>20934.2</v>
@@ -4479,13 +4479,13 @@
         <v>-0.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>24400</v>
+        <v>24500</v>
       </c>
       <c r="AC43" t="n">
         <v>25050</v>
       </c>
       <c r="AD43" t="n">
-        <v>-2.6</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="44">
@@ -4575,13 +4575,13 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>8000</v>
+        <v>7930</v>
       </c>
       <c r="AC44" t="n">
         <v>8360</v>
       </c>
       <c r="AD44" t="n">
-        <v>-4.3</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="45">
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>36200</v>
+        <v>36150</v>
       </c>
       <c r="AC45" t="n">
         <v>35050</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="46">
@@ -4707,73 +4707,73 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4924.1</v>
+        <v>4898.1</v>
       </c>
       <c r="G46" t="n">
-        <v>-17.3</v>
+        <v>-17.8</v>
       </c>
       <c r="H46" t="n">
-        <v>91.5</v>
+        <v>90.5</v>
       </c>
       <c r="I46" t="n">
         <v>4932</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="K46" t="n">
-        <v>5051.5</v>
+        <v>5126</v>
       </c>
       <c r="L46" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="M46" t="n">
-        <v>97.90000000000001</v>
+        <v>100.8</v>
       </c>
       <c r="P46" t="n">
-        <v>20532.4</v>
+        <v>20592.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>95.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R46" t="n">
         <v>20508.8</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="T46" t="n">
-        <v>23039.2</v>
+        <v>23089.5</v>
       </c>
       <c r="U46" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="V46" t="n">
         <v>23029.8</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="X46" t="n">
-        <v>26689.5</v>
+        <v>27085.7</v>
       </c>
       <c r="Y46" t="n">
-        <v>15.8</v>
+        <v>17.3</v>
       </c>
       <c r="Z46" t="n">
         <v>26635.8</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>226500</v>
+        <v>228500</v>
       </c>
       <c r="AC46" t="n">
         <v>268500</v>
       </c>
       <c r="AD46" t="n">
-        <v>-15.6</v>
+        <v>-14.9</v>
       </c>
     </row>
     <row r="47">
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>128800</v>
+        <v>128200</v>
       </c>
       <c r="AC47" t="n">
         <v>128000</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -4899,58 +4899,58 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1195.1</v>
+        <v>1192.2</v>
       </c>
       <c r="G48" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-19.5</v>
+        <v>-19.7</v>
       </c>
       <c r="I48" t="n">
         <v>1184</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K48" t="n">
-        <v>1232.5</v>
+        <v>1239.4</v>
       </c>
       <c r="L48" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>116.6</v>
+        <v>117.8</v>
       </c>
       <c r="P48" t="n">
-        <v>4081.1</v>
+        <v>4085.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="R48" t="n">
         <v>4115.1</v>
       </c>
       <c r="S48" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="T48" t="n">
-        <v>5912.3</v>
+        <v>5900.4</v>
       </c>
       <c r="U48" t="n">
-        <v>44.9</v>
+        <v>44.4</v>
       </c>
       <c r="V48" t="n">
         <v>5935.9</v>
       </c>
       <c r="W48" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="X48" t="n">
-        <v>6930.3</v>
+        <v>6930.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="Z48" t="n">
         <v>6957.4</v>
@@ -4959,13 +4959,13 @@
         <v>-0.4</v>
       </c>
       <c r="AB48" t="n">
-        <v>28600</v>
+        <v>28550</v>
       </c>
       <c r="AC48" t="n">
         <v>31800</v>
       </c>
       <c r="AD48" t="n">
-        <v>-10.1</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="49">
@@ -5159,13 +5159,13 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>84200</v>
+        <v>84500</v>
       </c>
       <c r="AC50" t="n">
         <v>89000</v>
       </c>
       <c r="AD50" t="n">
-        <v>-5.4</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="51">
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-1638.3</v>
+        <v>-2291.5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -5211,10 +5211,10 @@
         <v>917</v>
       </c>
       <c r="J51" t="n">
-        <v>-278.7</v>
+        <v>-349.9</v>
       </c>
       <c r="K51" t="n">
-        <v>5652.9</v>
+        <v>5774</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -5222,37 +5222,37 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-33.2</v>
+        <v>-31.7</v>
       </c>
       <c r="P51" t="n">
-        <v>44471.1</v>
+        <v>44075.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>132.2</v>
+        <v>130.1</v>
       </c>
       <c r="R51" t="n">
         <v>46449.9</v>
       </c>
       <c r="S51" t="n">
-        <v>-4.3</v>
+        <v>-5.1</v>
       </c>
       <c r="T51" t="n">
-        <v>25148.8</v>
+        <v>25237</v>
       </c>
       <c r="U51" t="n">
-        <v>-43.4</v>
+        <v>-42.7</v>
       </c>
       <c r="V51" t="n">
         <v>25735.7</v>
       </c>
       <c r="W51" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="X51" t="n">
         <v>27467.7</v>
       </c>
       <c r="Y51" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z51" t="n">
         <v>27993.1</v>
@@ -5261,13 +5261,13 @@
         <v>-1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>25500</v>
+        <v>25400</v>
       </c>
       <c r="AC51" t="n">
         <v>29400</v>
       </c>
       <c r="AD51" t="n">
-        <v>-13.3</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="52">
@@ -5357,13 +5357,13 @@
         <v>-0</v>
       </c>
       <c r="AB52" t="n">
-        <v>20600</v>
+        <v>20700</v>
       </c>
       <c r="AC52" t="n">
         <v>21550</v>
       </c>
       <c r="AD52" t="n">
-        <v>-4.4</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="53">
@@ -5453,13 +5453,13 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>39900</v>
+        <v>40250</v>
       </c>
       <c r="AC53" t="n">
         <v>48450</v>
       </c>
       <c r="AD53" t="n">
-        <v>-17.6</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="54">
@@ -5549,13 +5549,13 @@
         <v>0.8</v>
       </c>
       <c r="AB54" t="n">
-        <v>99700</v>
+        <v>99000</v>
       </c>
       <c r="AC54" t="n">
         <v>125000</v>
       </c>
       <c r="AD54" t="n">
-        <v>-20.2</v>
+        <v>-20.8</v>
       </c>
     </row>
     <row r="55">
@@ -5645,13 +5645,13 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>64200</v>
+        <v>64100</v>
       </c>
       <c r="AC55" t="n">
         <v>87100</v>
       </c>
       <c r="AD55" t="n">
-        <v>-26.3</v>
+        <v>-26.4</v>
       </c>
     </row>
     <row r="56">
@@ -5743,13 +5743,13 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>37550</v>
+        <v>37700</v>
       </c>
       <c r="AC56" t="n">
         <v>38800</v>
       </c>
       <c r="AD56" t="n">
-        <v>-3.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="57">
@@ -5791,13 +5791,13 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>47550</v>
+        <v>46900</v>
       </c>
       <c r="AC57" t="n">
         <v>52000</v>
       </c>
       <c r="AD57" t="n">
-        <v>-8.6</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -5887,13 +5887,13 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1187000</v>
+        <v>1184000</v>
       </c>
       <c r="AC58" t="n">
         <v>1559000</v>
       </c>
       <c r="AD58" t="n">
-        <v>-23.9</v>
+        <v>-24.1</v>
       </c>
     </row>
     <row r="59">
@@ -5983,13 +5983,13 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>39550</v>
+        <v>39400</v>
       </c>
       <c r="AC59" t="n">
         <v>40500</v>
       </c>
       <c r="AD59" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="60">
@@ -6079,13 +6079,13 @@
         <v>0.8</v>
       </c>
       <c r="AB60" t="n">
-        <v>263500</v>
+        <v>264500</v>
       </c>
       <c r="AC60" t="n">
         <v>291500</v>
       </c>
       <c r="AD60" t="n">
-        <v>-9.6</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -6181,13 +6181,13 @@
         <v>-1</v>
       </c>
       <c r="AB61" t="n">
-        <v>31100</v>
+        <v>31400</v>
       </c>
       <c r="AC61" t="n">
         <v>35700</v>
       </c>
       <c r="AD61" t="n">
-        <v>-12.9</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="62">
@@ -6281,13 +6281,13 @@
         <v>-1.5</v>
       </c>
       <c r="AB62" t="n">
-        <v>199000</v>
+        <v>198700</v>
       </c>
       <c r="AC62" t="n">
         <v>234000</v>
       </c>
       <c r="AD62" t="n">
-        <v>-15</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="63">
@@ -6377,13 +6377,13 @@
         <v>1.1</v>
       </c>
       <c r="AB63" t="n">
-        <v>158500</v>
+        <v>159000</v>
       </c>
       <c r="AC63" t="n">
         <v>197200</v>
       </c>
       <c r="AD63" t="n">
-        <v>-19.6</v>
+        <v>-19.4</v>
       </c>
     </row>
     <row r="64">
@@ -6569,13 +6569,13 @@
         <v>0.8</v>
       </c>
       <c r="AB65" t="n">
-        <v>18440</v>
+        <v>18430</v>
       </c>
       <c r="AC65" t="n">
         <v>18900</v>
       </c>
       <c r="AD65" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="66">
@@ -6622,13 +6622,13 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>13450</v>
+        <v>13540</v>
       </c>
       <c r="AC66" t="n">
         <v>16970</v>
       </c>
       <c r="AD66" t="n">
-        <v>-20.7</v>
+        <v>-20.2</v>
       </c>
     </row>
     <row r="67">
@@ -6720,13 +6720,13 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>14400</v>
+        <v>14530</v>
       </c>
       <c r="AC67" t="n">
         <v>14670</v>
       </c>
       <c r="AD67" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68">
@@ -6816,13 +6816,13 @@
         <v>3.8</v>
       </c>
       <c r="AB68" t="n">
-        <v>153700</v>
+        <v>154100</v>
       </c>
       <c r="AC68" t="n">
         <v>169000</v>
       </c>
       <c r="AD68" t="n">
-        <v>-9.1</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>407000</v>
+        <v>405500</v>
       </c>
       <c r="AC69" t="n">
         <v>572000</v>
       </c>
       <c r="AD69" t="n">
-        <v>-28.8</v>
+        <v>-29.1</v>
       </c>
     </row>
     <row r="70">
@@ -7020,13 +7020,13 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>54600</v>
+        <v>54800</v>
       </c>
       <c r="AC70" t="n">
         <v>59100</v>
       </c>
       <c r="AD70" t="n">
-        <v>-7.6</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="71">
@@ -7116,13 +7116,13 @@
         <v>5.3</v>
       </c>
       <c r="AB71" t="n">
-        <v>23450</v>
+        <v>23600</v>
       </c>
       <c r="AC71" t="n">
         <v>20850</v>
       </c>
       <c r="AD71" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="72">
@@ -7212,13 +7212,13 @@
         <v>-2.1</v>
       </c>
       <c r="AB72" t="n">
-        <v>48500</v>
+        <v>48300</v>
       </c>
       <c r="AC72" t="n">
         <v>51000</v>
       </c>
       <c r="AD72" t="n">
-        <v>-4.9</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="73">
@@ -7308,13 +7308,13 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>113700</v>
+        <v>113600</v>
       </c>
       <c r="AC73" t="n">
         <v>114700</v>
       </c>
       <c r="AD73" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="74">
@@ -7416,13 +7416,13 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>92900</v>
+        <v>92700</v>
       </c>
       <c r="AC74" t="n">
         <v>107500</v>
       </c>
       <c r="AD74" t="n">
-        <v>-13.6</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="75">
@@ -7512,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>15960</v>
+        <v>15970</v>
       </c>
       <c r="AC75" t="n">
         <v>19690</v>
@@ -7608,13 +7608,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB76" t="n">
-        <v>352500</v>
+        <v>353500</v>
       </c>
       <c r="AC76" t="n">
         <v>360000</v>
       </c>
       <c r="AD76" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="77">
@@ -7644,73 +7644,73 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>12128.6</v>
+        <v>11896.1</v>
       </c>
       <c r="G77" t="n">
-        <v>-11.2</v>
+        <v>-12.9</v>
       </c>
       <c r="H77" t="n">
-        <v>41.6</v>
+        <v>38.9</v>
       </c>
       <c r="I77" t="n">
         <v>12291</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="K77" t="n">
-        <v>14366.2</v>
+        <v>14325.1</v>
       </c>
       <c r="L77" t="n">
-        <v>18.4</v>
+        <v>20.4</v>
       </c>
       <c r="M77" t="n">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="P77" t="n">
-        <v>46381.8</v>
+        <v>46308.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
       <c r="R77" t="n">
         <v>46483.1</v>
       </c>
       <c r="S77" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="T77" t="n">
-        <v>57062.2</v>
+        <v>56827.9</v>
       </c>
       <c r="U77" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="V77" t="n">
         <v>57035</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="X77" t="n">
-        <v>64024</v>
+        <v>63868.3</v>
       </c>
       <c r="Y77" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="Z77" t="n">
         <v>63616.2</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>887000</v>
+        <v>900000</v>
       </c>
       <c r="AC77" t="n">
         <v>904000</v>
       </c>
       <c r="AD77" t="n">
-        <v>-1.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="78">
@@ -7801,13 +7801,13 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>330000</v>
+        <v>332500</v>
       </c>
       <c r="AC78" t="n">
         <v>343000</v>
       </c>
       <c r="AD78" t="n">
-        <v>-3.8</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="79">
@@ -7852,49 +7852,49 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>576.3</v>
+        <v>557.5</v>
       </c>
       <c r="L79" t="n">
-        <v>-8.1</v>
+        <v>-11.1</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>-0.1</v>
       </c>
       <c r="P79" t="n">
-        <v>2060.8</v>
+        <v>2063.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>-12.1</v>
+        <v>-12</v>
       </c>
       <c r="R79" t="n">
         <v>2060.8</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T79" t="n">
-        <v>2536.8</v>
+        <v>2511</v>
       </c>
       <c r="U79" t="n">
-        <v>23.1</v>
+        <v>21.7</v>
       </c>
       <c r="V79" t="n">
         <v>2536.8</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>2694</v>
+        <v>2669.8</v>
       </c>
       <c r="Y79" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z79" t="n">
         <v>2694</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="AB79" t="n">
         <v>97300</v>
@@ -7969,13 +7969,13 @@
         <v>10.5</v>
       </c>
       <c r="AB80" t="n">
-        <v>21600</v>
+        <v>21800</v>
       </c>
       <c r="AC80" t="n">
         <v>21100</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="81">
@@ -8065,13 +8065,13 @@
         <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>27200</v>
+        <v>27100</v>
       </c>
       <c r="AC81" t="n">
         <v>28850</v>
       </c>
       <c r="AD81" t="n">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="82">
@@ -8293,64 +8293,64 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>23346.5</v>
+        <v>23175</v>
       </c>
       <c r="G84" t="n">
-        <v>106.9</v>
+        <v>105.4</v>
       </c>
       <c r="H84" t="n">
-        <v>-58.7</v>
+        <v>-59</v>
       </c>
       <c r="I84" t="n">
         <v>23527</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="K84" t="n">
-        <v>3231.2</v>
+        <v>3735.8</v>
       </c>
       <c r="L84" t="n">
-        <v>-86.2</v>
+        <v>-83.90000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>-83.40000000000001</v>
+        <v>-80.8</v>
       </c>
       <c r="P84" t="n">
-        <v>76079.10000000001</v>
+        <v>76388.3</v>
       </c>
       <c r="Q84" t="n">
-        <v>-43.6</v>
+        <v>-43.4</v>
       </c>
       <c r="R84" t="n">
         <v>77650.8</v>
       </c>
       <c r="S84" t="n">
-        <v>-2</v>
+        <v>-1.6</v>
       </c>
       <c r="T84" t="n">
-        <v>105024.6</v>
+        <v>104568.4</v>
       </c>
       <c r="U84" t="n">
-        <v>38</v>
+        <v>36.9</v>
       </c>
       <c r="V84" t="n">
         <v>111501.1</v>
       </c>
       <c r="W84" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="X84" t="n">
-        <v>130434.6</v>
+        <v>129928.1</v>
       </c>
       <c r="Y84" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Z84" t="n">
         <v>133061.2</v>
       </c>
       <c r="AA84" t="n">
-        <v>-2</v>
+        <v>-2.4</v>
       </c>
       <c r="AB84" t="n">
         <v>28600</v>
@@ -8389,58 +8389,58 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4985.9</v>
+        <v>5016.5</v>
       </c>
       <c r="G85" t="n">
-        <v>-26.2</v>
+        <v>-25.8</v>
       </c>
       <c r="H85" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="I85" t="n">
         <v>5201</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.1</v>
+        <v>-3.5</v>
       </c>
       <c r="K85" t="n">
         <v>4383</v>
       </c>
       <c r="L85" t="n">
-        <v>-12.1</v>
+        <v>-12.6</v>
       </c>
       <c r="M85" t="n">
         <v>32.6</v>
       </c>
       <c r="P85" t="n">
-        <v>22446.1</v>
+        <v>22466.5</v>
       </c>
       <c r="Q85" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="R85" t="n">
         <v>22701.3</v>
       </c>
       <c r="S85" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="T85" t="n">
-        <v>20682.9</v>
+        <v>20553</v>
       </c>
       <c r="U85" t="n">
-        <v>-7.9</v>
+        <v>-8.5</v>
       </c>
       <c r="V85" t="n">
         <v>20843.1</v>
       </c>
       <c r="W85" t="n">
-        <v>-0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="X85" t="n">
         <v>21820.9</v>
       </c>
       <c r="Y85" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z85" t="n">
         <v>21848.3</v>
@@ -8449,13 +8449,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB85" t="n">
-        <v>78800</v>
+        <v>79000</v>
       </c>
       <c r="AC85" t="n">
         <v>85900</v>
       </c>
       <c r="AD85" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="86">
@@ -8485,31 +8485,31 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5288.6</v>
+        <v>5281.2</v>
       </c>
       <c r="G86" t="n">
-        <v>-6.6</v>
+        <v>-6.7</v>
       </c>
       <c r="H86" t="n">
-        <v>991.8</v>
+        <v>990.3</v>
       </c>
       <c r="I86" t="n">
         <v>5239</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K86" t="n">
-        <v>3307.6</v>
+        <v>3287.1</v>
       </c>
       <c r="L86" t="n">
-        <v>-37.5</v>
+        <v>-37.8</v>
       </c>
       <c r="M86" t="n">
-        <v>177.6</v>
+        <v>175.9</v>
       </c>
       <c r="P86" t="n">
-        <v>19576.7</v>
+        <v>19580.1</v>
       </c>
       <c r="Q86" t="n">
         <v>82.40000000000001</v>
@@ -8521,7 +8521,7 @@
         <v>-0.4</v>
       </c>
       <c r="T86" t="n">
-        <v>20856.9</v>
+        <v>20854.6</v>
       </c>
       <c r="U86" t="n">
         <v>6.5</v>
@@ -8533,10 +8533,10 @@
         <v>0.1</v>
       </c>
       <c r="X86" t="n">
-        <v>22199.3</v>
+        <v>22206.7</v>
       </c>
       <c r="Y86" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z86" t="n">
         <v>22293.8</v>
@@ -8545,13 +8545,13 @@
         <v>-0.4</v>
       </c>
       <c r="AB86" t="n">
-        <v>78400</v>
+        <v>78500</v>
       </c>
       <c r="AC86" t="n">
         <v>84200</v>
       </c>
       <c r="AD86" t="n">
-        <v>-6.9</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="87">
@@ -8641,13 +8641,13 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>71200</v>
+        <v>71000</v>
       </c>
       <c r="AC87" t="n">
         <v>70200</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="88">
@@ -8737,13 +8737,13 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>17840</v>
+        <v>17850</v>
       </c>
       <c r="AC88" t="n">
         <v>19260</v>
       </c>
       <c r="AD88" t="n">
-        <v>-7.4</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="89">
@@ -8833,13 +8833,13 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>199100</v>
+        <v>198700</v>
       </c>
       <c r="AC89" t="n">
         <v>196100</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="90">
@@ -8929,13 +8929,13 @@
         <v>-0.2</v>
       </c>
       <c r="AB90" t="n">
-        <v>3855</v>
+        <v>3850</v>
       </c>
       <c r="AC90" t="n">
         <v>4020</v>
       </c>
       <c r="AD90" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="91">
@@ -8965,58 +8965,58 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2652.7</v>
+        <v>2636.3</v>
       </c>
       <c r="G91" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="H91" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="I91" t="n">
         <v>2649</v>
       </c>
       <c r="J91" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="K91" t="n">
-        <v>2365</v>
+        <v>2325.7</v>
       </c>
       <c r="L91" t="n">
-        <v>-10.8</v>
+        <v>-11.8</v>
       </c>
       <c r="M91" t="n">
-        <v>30.2</v>
+        <v>28</v>
       </c>
       <c r="P91" t="n">
-        <v>10059</v>
+        <v>10003.3</v>
       </c>
       <c r="Q91" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="R91" t="n">
         <v>10133</v>
       </c>
       <c r="S91" t="n">
-        <v>-0.7</v>
+        <v>-1.3</v>
       </c>
       <c r="T91" t="n">
-        <v>11834.7</v>
+        <v>11658.3</v>
       </c>
       <c r="U91" t="n">
-        <v>17.7</v>
+        <v>16.5</v>
       </c>
       <c r="V91" t="n">
         <v>11836</v>
       </c>
       <c r="W91" t="n">
-        <v>-0</v>
+        <v>-1.5</v>
       </c>
       <c r="X91" t="n">
         <v>12775.5</v>
       </c>
       <c r="Y91" t="n">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="Z91" t="n">
         <v>12775.5</v>
@@ -9172,13 +9172,13 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>26700</v>
+        <v>26500</v>
       </c>
       <c r="AC93" t="n">
         <v>26200</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="94">
@@ -9268,13 +9268,13 @@
         <v>-0.2</v>
       </c>
       <c r="AB94" t="n">
-        <v>85400</v>
+        <v>85900</v>
       </c>
       <c r="AC94" t="n">
         <v>97400</v>
       </c>
       <c r="AD94" t="n">
-        <v>-12.3</v>
+        <v>-11.8</v>
       </c>
     </row>
     <row r="95">
@@ -9364,7 +9364,7 @@
         <v>-0</v>
       </c>
       <c r="AB95" t="n">
-        <v>19960</v>
+        <v>19950</v>
       </c>
       <c r="AC95" t="n">
         <v>19900</v>
@@ -9400,73 +9400,73 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2474.7</v>
+        <v>2492.6</v>
       </c>
       <c r="G96" t="n">
-        <v>-9.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>40.2</v>
+        <v>41.2</v>
       </c>
       <c r="I96" t="n">
         <v>2467</v>
       </c>
       <c r="J96" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>2762.4</v>
+        <v>2763.3</v>
       </c>
       <c r="L96" t="n">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
       <c r="M96" t="n">
         <v>-0.4</v>
       </c>
       <c r="P96" t="n">
-        <v>9800.9</v>
+        <v>9818.9</v>
       </c>
       <c r="Q96" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="R96" t="n">
         <v>9786.299999999999</v>
       </c>
       <c r="S96" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="T96" t="n">
-        <v>11920</v>
+        <v>11945.8</v>
       </c>
       <c r="U96" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V96" t="n">
         <v>11890.2</v>
       </c>
       <c r="W96" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="X96" t="n">
-        <v>13236.1</v>
+        <v>13290.1</v>
       </c>
       <c r="Y96" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="Z96" t="n">
         <v>13213.9</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AB96" t="n">
-        <v>43650</v>
+        <v>43600</v>
       </c>
       <c r="AC96" t="n">
         <v>47900</v>
       </c>
       <c r="AD96" t="n">
-        <v>-8.9</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="97">
@@ -9556,13 +9556,13 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>284500</v>
+        <v>284000</v>
       </c>
       <c r="AC97" t="n">
         <v>320000</v>
       </c>
       <c r="AD97" t="n">
-        <v>-11.1</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="98">
@@ -9652,13 +9652,13 @@
         <v>1.5</v>
       </c>
       <c r="AB98" t="n">
-        <v>6680</v>
+        <v>6660</v>
       </c>
       <c r="AC98" t="n">
         <v>6090</v>
       </c>
       <c r="AD98" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="99">
@@ -9748,13 +9748,13 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>42600</v>
+        <v>42700</v>
       </c>
       <c r="AC99" t="n">
         <v>41350</v>
       </c>
       <c r="AD99" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="100">
@@ -9844,13 +9844,13 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>19460</v>
+        <v>19520</v>
       </c>
       <c r="AC100" t="n">
         <v>18820</v>
       </c>
       <c r="AD100" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="101">
@@ -9880,73 +9880,73 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>5408.9</v>
+        <v>5347.4</v>
       </c>
       <c r="G101" t="n">
-        <v>-16.6</v>
+        <v>-17.5</v>
       </c>
       <c r="H101" t="n">
-        <v>0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I101" t="n">
         <v>5496</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.6</v>
+        <v>-2.7</v>
       </c>
       <c r="K101" t="n">
-        <v>4153.4</v>
+        <v>4120.8</v>
       </c>
       <c r="L101" t="n">
-        <v>-23.2</v>
+        <v>-22.9</v>
       </c>
       <c r="M101" t="n">
-        <v>82.7</v>
+        <v>81.2</v>
       </c>
       <c r="P101" t="n">
-        <v>20991.7</v>
+        <v>20885.6</v>
       </c>
       <c r="Q101" t="n">
-        <v>-15</v>
+        <v>-15.4</v>
       </c>
       <c r="R101" t="n">
         <v>21200.5</v>
       </c>
       <c r="S101" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="T101" t="n">
-        <v>22445.9</v>
+        <v>22376.1</v>
       </c>
       <c r="U101" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="V101" t="n">
         <v>22636.6</v>
       </c>
       <c r="W101" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="X101" t="n">
-        <v>23488.9</v>
+        <v>23358.9</v>
       </c>
       <c r="Y101" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Z101" t="n">
         <v>23675.9</v>
       </c>
       <c r="AA101" t="n">
-        <v>-0.8</v>
+        <v>-1.3</v>
       </c>
       <c r="AB101" t="n">
-        <v>50500</v>
+        <v>50400</v>
       </c>
       <c r="AC101" t="n">
         <v>51300</v>
       </c>
       <c r="AD101" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="102">
@@ -9976,73 +9976,73 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>354.2</v>
+        <v>341.2</v>
       </c>
       <c r="G102" t="n">
-        <v>156.7</v>
+        <v>147.2</v>
       </c>
       <c r="H102" t="n">
-        <v>-14.1</v>
+        <v>-17.3</v>
       </c>
       <c r="I102" t="n">
         <v>360</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.6</v>
+        <v>-5.2</v>
       </c>
       <c r="K102" t="n">
-        <v>520.6</v>
+        <v>527.4</v>
       </c>
       <c r="L102" t="n">
-        <v>47</v>
+        <v>54.6</v>
       </c>
       <c r="M102" t="n">
-        <v>267.4</v>
+        <v>272.2</v>
       </c>
       <c r="P102" t="n">
-        <v>1103.2</v>
+        <v>1097</v>
       </c>
       <c r="Q102" t="n">
-        <v>50.3</v>
+        <v>49.5</v>
       </c>
       <c r="R102" t="n">
         <v>1101.2</v>
       </c>
       <c r="S102" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="T102" t="n">
-        <v>1760.6</v>
+        <v>1847.6</v>
       </c>
       <c r="U102" t="n">
-        <v>59.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="V102" t="n">
         <v>1657.4</v>
       </c>
       <c r="W102" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="X102" t="n">
-        <v>2207</v>
+        <v>2522</v>
       </c>
       <c r="Y102" t="n">
-        <v>25.4</v>
+        <v>36.5</v>
       </c>
       <c r="Z102" t="n">
         <v>1895.5</v>
       </c>
       <c r="AA102" t="n">
-        <v>16.4</v>
+        <v>33.1</v>
       </c>
       <c r="AB102" t="n">
-        <v>199000</v>
+        <v>199400</v>
       </c>
       <c r="AC102" t="n">
         <v>209500</v>
       </c>
       <c r="AD102" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="103">
@@ -10072,28 +10072,28 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>539</v>
+        <v>494</v>
       </c>
       <c r="G103" t="n">
-        <v>3.9</v>
+        <v>-4.8</v>
       </c>
       <c r="H103" t="n">
-        <v>1.7</v>
+        <v>-6.8</v>
       </c>
       <c r="I103" t="n">
         <v>597</v>
       </c>
       <c r="J103" t="n">
-        <v>-9.699999999999999</v>
+        <v>-17.3</v>
       </c>
       <c r="AB103" t="n">
-        <v>10670</v>
+        <v>10690</v>
       </c>
       <c r="AC103" t="n">
         <v>11070</v>
       </c>
       <c r="AD103" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="104">
@@ -10123,73 +10123,73 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3011.4</v>
+        <v>3005.3</v>
       </c>
       <c r="G104" t="n">
-        <v>-12.6</v>
+        <v>-12.8</v>
       </c>
       <c r="H104" t="n">
-        <v>86.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I104" t="n">
         <v>3001</v>
       </c>
       <c r="J104" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K104" t="n">
-        <v>2285.6</v>
+        <v>2292.4</v>
       </c>
       <c r="L104" t="n">
-        <v>-24.1</v>
+        <v>-23.7</v>
       </c>
       <c r="M104" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="P104" t="n">
-        <v>11515.7</v>
+        <v>11505.6</v>
       </c>
       <c r="Q104" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="R104" t="n">
         <v>11498.3</v>
       </c>
       <c r="S104" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="T104" t="n">
-        <v>12325.4</v>
+        <v>12320.2</v>
       </c>
       <c r="U104" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="V104" t="n">
         <v>12363.6</v>
       </c>
       <c r="W104" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="X104" t="n">
-        <v>13218.1</v>
+        <v>13250.9</v>
       </c>
       <c r="Y104" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z104" t="n">
         <v>13190.7</v>
       </c>
       <c r="AA104" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AB104" t="n">
-        <v>15430</v>
+        <v>15510</v>
       </c>
       <c r="AC104" t="n">
         <v>14430</v>
       </c>
       <c r="AD104" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="105">
@@ -10219,25 +10219,25 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8258.6</v>
+        <v>8044.6</v>
       </c>
       <c r="G105" t="n">
-        <v>32.6</v>
+        <v>29.2</v>
       </c>
       <c r="H105" t="n">
-        <v>1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="I105" t="n">
         <v>8259</v>
       </c>
       <c r="J105" t="n">
-        <v>-0</v>
+        <v>-2.6</v>
       </c>
       <c r="K105" t="n">
         <v>7670.5</v>
       </c>
       <c r="L105" t="n">
-        <v>-7.1</v>
+        <v>-4.7</v>
       </c>
       <c r="M105" t="n">
         <v>705.2</v>
@@ -10279,13 +10279,13 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>237500</v>
+        <v>238000</v>
       </c>
       <c r="AC105" t="n">
         <v>270000</v>
       </c>
       <c r="AD105" t="n">
-        <v>-12</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="106">
@@ -10375,13 +10375,13 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>14390</v>
+        <v>14410</v>
       </c>
       <c r="AC106" t="n">
         <v>15190</v>
       </c>
       <c r="AD106" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="107">
@@ -10471,13 +10471,13 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>189900</v>
+        <v>191400</v>
       </c>
       <c r="AC107" t="n">
         <v>177300</v>
       </c>
       <c r="AD107" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -10507,43 +10507,43 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2483.8</v>
+        <v>2480.3</v>
       </c>
       <c r="G108" t="n">
-        <v>-21</v>
+        <v>-21.1</v>
       </c>
       <c r="H108" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="I108" t="n">
         <v>2484</v>
       </c>
       <c r="J108" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="K108" t="n">
-        <v>3300.2</v>
+        <v>3287.1</v>
       </c>
       <c r="L108" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="M108" t="n">
-        <v>55.6</v>
+        <v>55</v>
       </c>
       <c r="P108" t="n">
-        <v>11291.2</v>
+        <v>11277.5</v>
       </c>
       <c r="Q108" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="R108" t="n">
         <v>11291.2</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="T108" t="n">
-        <v>16367.7</v>
+        <v>16352.7</v>
       </c>
       <c r="U108" t="n">
         <v>45</v>
@@ -10552,10 +10552,10 @@
         <v>16367.7</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="X108" t="n">
-        <v>20768.6</v>
+        <v>20753.3</v>
       </c>
       <c r="Y108" t="n">
         <v>26.9</v>
@@ -10564,16 +10564,16 @@
         <v>20768.6</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AB108" t="n">
-        <v>64800</v>
+        <v>64400</v>
       </c>
       <c r="AC108" t="n">
         <v>76700</v>
       </c>
       <c r="AD108" t="n">
-        <v>-15.5</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="109">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3003.1</v>
+        <v>2705.6</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -10611,58 +10611,58 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>-30.3</v>
+        <v>-37.2</v>
       </c>
       <c r="I109" t="n">
         <v>3229</v>
       </c>
       <c r="J109" t="n">
-        <v>-7</v>
+        <v>-16.2</v>
       </c>
       <c r="K109" t="n">
-        <v>3481.6</v>
+        <v>3181.6</v>
       </c>
       <c r="L109" t="n">
-        <v>15.9</v>
+        <v>17.6</v>
       </c>
       <c r="M109" t="n">
-        <v>106.6</v>
+        <v>88.8</v>
       </c>
       <c r="P109" t="n">
-        <v>6877.9</v>
+        <v>6280.9</v>
       </c>
       <c r="Q109" t="n">
-        <v>33</v>
+        <v>21.5</v>
       </c>
       <c r="R109" t="n">
         <v>7369.3</v>
       </c>
       <c r="S109" t="n">
-        <v>-6.7</v>
+        <v>-14.8</v>
       </c>
       <c r="T109" t="n">
-        <v>11262.9</v>
+        <v>10410.3</v>
       </c>
       <c r="U109" t="n">
-        <v>63.8</v>
+        <v>65.7</v>
       </c>
       <c r="V109" t="n">
         <v>11865.7</v>
       </c>
       <c r="W109" t="n">
-        <v>-5.1</v>
+        <v>-12.3</v>
       </c>
       <c r="X109" t="n">
-        <v>14238.1</v>
+        <v>13102.4</v>
       </c>
       <c r="Y109" t="n">
-        <v>26.4</v>
+        <v>25.9</v>
       </c>
       <c r="Z109" t="n">
         <v>14419.6</v>
       </c>
       <c r="AA109" t="n">
-        <v>-1.3</v>
+        <v>-9.1</v>
       </c>
       <c r="AB109" t="n">
         <v>7500</v>
@@ -10701,31 +10701,31 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>518.9</v>
+        <v>523.4</v>
       </c>
       <c r="G110" t="n">
-        <v>46</v>
+        <v>47.2</v>
       </c>
       <c r="H110" t="n">
-        <v>31.3</v>
+        <v>32.5</v>
       </c>
       <c r="I110" t="n">
         <v>508</v>
       </c>
       <c r="J110" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="K110" t="n">
-        <v>333</v>
+        <v>334.6</v>
       </c>
       <c r="L110" t="n">
-        <v>-35.8</v>
+        <v>-36.1</v>
       </c>
       <c r="M110" t="n">
-        <v>105.8</v>
+        <v>106.8</v>
       </c>
       <c r="P110" t="n">
-        <v>1661.6</v>
+        <v>1660.7</v>
       </c>
       <c r="Q110" t="n">
         <v>6.6</v>
@@ -10737,28 +10737,28 @@
         <v>-0.1</v>
       </c>
       <c r="T110" t="n">
-        <v>2028.8</v>
+        <v>2011.6</v>
       </c>
       <c r="U110" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="V110" t="n">
         <v>2036.8</v>
       </c>
       <c r="W110" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="X110" t="n">
-        <v>2386.5</v>
+        <v>2334</v>
       </c>
       <c r="Y110" t="n">
-        <v>17.6</v>
+        <v>16</v>
       </c>
       <c r="Z110" t="n">
         <v>2396.9</v>
       </c>
       <c r="AA110" t="n">
-        <v>-0.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AB110" t="n">
         <v>9880</v>
@@ -10857,13 +10857,13 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>452000</v>
+        <v>450500</v>
       </c>
       <c r="AC111" t="n">
         <v>561000</v>
       </c>
       <c r="AD111" t="n">
-        <v>-19.4</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="112">
@@ -10941,25 +10941,25 @@
         <v>0.9</v>
       </c>
       <c r="X112" t="n">
-        <v>2673</v>
+        <v>2640.3</v>
       </c>
       <c r="Y112" t="n">
-        <v>30.5</v>
+        <v>28.9</v>
       </c>
       <c r="Z112" t="n">
         <v>2653.1</v>
       </c>
       <c r="AA112" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="AB112" t="n">
-        <v>14250</v>
+        <v>14270</v>
       </c>
       <c r="AC112" t="n">
         <v>14220</v>
       </c>
       <c r="AD112" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="113">
@@ -11049,13 +11049,13 @@
         <v>-0.5</v>
       </c>
       <c r="AB113" t="n">
-        <v>180100</v>
+        <v>180300</v>
       </c>
       <c r="AC113" t="n">
         <v>183200</v>
       </c>
       <c r="AD113" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="114">
@@ -11085,46 +11085,46 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2543.6</v>
+        <v>2526.9</v>
       </c>
       <c r="G114" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>22.3</v>
+        <v>21.5</v>
       </c>
       <c r="I114" t="n">
         <v>2623</v>
       </c>
       <c r="J114" t="n">
-        <v>-3</v>
+        <v>-3.7</v>
       </c>
       <c r="K114" t="n">
-        <v>2773.1</v>
+        <v>2755.3</v>
       </c>
       <c r="L114" t="n">
         <v>9</v>
       </c>
       <c r="M114" t="n">
-        <v>19.2</v>
+        <v>18.4</v>
       </c>
       <c r="P114" t="n">
-        <v>10200</v>
+        <v>10165.2</v>
       </c>
       <c r="Q114" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="R114" t="n">
         <v>10291.2</v>
       </c>
       <c r="S114" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="T114" t="n">
-        <v>11723.5</v>
+        <v>11723.2</v>
       </c>
       <c r="U114" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="V114" t="n">
         <v>11766.3</v>
@@ -11133,25 +11133,25 @@
         <v>-0.4</v>
       </c>
       <c r="X114" t="n">
-        <v>13407.1</v>
+        <v>13450.4</v>
       </c>
       <c r="Y114" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="Z114" t="n">
         <v>13451.6</v>
       </c>
       <c r="AA114" t="n">
-        <v>-0.3</v>
+        <v>-0</v>
       </c>
       <c r="AB114" t="n">
-        <v>31850</v>
+        <v>31700</v>
       </c>
       <c r="AC114" t="n">
         <v>32400</v>
       </c>
       <c r="AD114" t="n">
-        <v>-1.7</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="115">
@@ -11241,13 +11241,13 @@
         <v>-2.4</v>
       </c>
       <c r="AB115" t="n">
-        <v>40300</v>
+        <v>40750</v>
       </c>
       <c r="AC115" t="n">
         <v>35400</v>
       </c>
       <c r="AD115" t="n">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="116">
@@ -11277,43 +11277,43 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>440.7</v>
+        <v>435.9</v>
       </c>
       <c r="G116" t="n">
-        <v>42.2</v>
+        <v>40.6</v>
       </c>
       <c r="H116" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="I116" t="n">
         <v>442</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="K116" t="n">
-        <v>393.1</v>
+        <v>384.2</v>
       </c>
       <c r="L116" t="n">
-        <v>-10.8</v>
+        <v>-11.9</v>
       </c>
       <c r="M116" t="n">
-        <v>-6.2</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P116" t="n">
-        <v>1479.3</v>
+        <v>1466.1</v>
       </c>
       <c r="Q116" t="n">
-        <v>-4.7</v>
+        <v>-5.6</v>
       </c>
       <c r="R116" t="n">
         <v>1489.4</v>
       </c>
       <c r="S116" t="n">
-        <v>-0.7</v>
+        <v>-1.6</v>
       </c>
       <c r="T116" t="n">
-        <v>1636.2</v>
+        <v>1621.5</v>
       </c>
       <c r="U116" t="n">
         <v>10.6</v>
@@ -11322,28 +11322,28 @@
         <v>1655.8</v>
       </c>
       <c r="W116" t="n">
-        <v>-1.2</v>
+        <v>-2.1</v>
       </c>
       <c r="X116" t="n">
-        <v>1663.3</v>
+        <v>1654.5</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z116" t="n">
         <v>1672.1</v>
       </c>
       <c r="AA116" t="n">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="AB116" t="n">
-        <v>39100</v>
+        <v>39000</v>
       </c>
       <c r="AC116" t="n">
         <v>38900</v>
       </c>
       <c r="AD116" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="117">
@@ -11388,13 +11388,13 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>8900</v>
+        <v>8890</v>
       </c>
       <c r="AC117" t="n">
         <v>10780</v>
       </c>
       <c r="AD117" t="n">
-        <v>-17.4</v>
+        <v>-17.5</v>
       </c>
     </row>
     <row r="118">
@@ -11484,13 +11484,13 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>36200</v>
+        <v>36350</v>
       </c>
       <c r="AC118" t="n">
         <v>35700</v>
       </c>
       <c r="AD118" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="119">
@@ -11582,13 +11582,13 @@
         <v>-0.6</v>
       </c>
       <c r="AB119" t="n">
-        <v>207500</v>
+        <v>208500</v>
       </c>
       <c r="AC119" t="n">
         <v>223000</v>
       </c>
       <c r="AD119" t="n">
-        <v>-7</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="120">
@@ -11654,13 +11654,13 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>210500</v>
+        <v>211500</v>
       </c>
       <c r="AC120" t="n">
         <v>263500</v>
       </c>
       <c r="AD120" t="n">
-        <v>-20.1</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="121">
@@ -11750,13 +11750,13 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>446500</v>
+        <v>445500</v>
       </c>
       <c r="AC121" t="n">
         <v>519000</v>
       </c>
       <c r="AD121" t="n">
-        <v>-14</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="122">
@@ -11846,13 +11846,13 @@
         <v>-1.9</v>
       </c>
       <c r="AB122" t="n">
-        <v>29000</v>
+        <v>29200</v>
       </c>
       <c r="AC122" t="n">
         <v>29750</v>
       </c>
       <c r="AD122" t="n">
-        <v>-2.5</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="123">
@@ -11918,7 +11918,7 @@
         <v>-0.5</v>
       </c>
       <c r="T123" t="n">
-        <v>18627.4</v>
+        <v>18618.9</v>
       </c>
       <c r="U123" t="n">
         <v>-17.3</v>
@@ -11933,7 +11933,7 @@
         <v>19804</v>
       </c>
       <c r="Y123" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z123" t="n">
         <v>19820.9</v>
@@ -11942,13 +11942,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB123" t="n">
-        <v>222000</v>
+        <v>223000</v>
       </c>
       <c r="AC123" t="n">
         <v>242000</v>
       </c>
       <c r="AD123" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="124">
@@ -12038,13 +12038,13 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>9310</v>
+        <v>9300</v>
       </c>
       <c r="AC124" t="n">
         <v>9650</v>
       </c>
       <c r="AD124" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="125">
@@ -12134,13 +12134,13 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>85000</v>
+        <v>85100</v>
       </c>
       <c r="AC125" t="n">
         <v>77900</v>
       </c>
       <c r="AD125" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -12170,55 +12170,55 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>5491.5</v>
+        <v>5426.7</v>
       </c>
       <c r="G126" t="n">
-        <v>-25.4</v>
+        <v>-26.3</v>
       </c>
       <c r="H126" t="n">
-        <v>89.5</v>
+        <v>87.3</v>
       </c>
       <c r="I126" t="n">
         <v>5695</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.6</v>
+        <v>-4.7</v>
       </c>
       <c r="K126" t="n">
-        <v>5034.6</v>
+        <v>5004.1</v>
       </c>
       <c r="L126" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.8</v>
       </c>
       <c r="M126" t="n">
-        <v>103.4</v>
+        <v>102.2</v>
       </c>
       <c r="P126" t="n">
-        <v>22239.2</v>
+        <v>22149.7</v>
       </c>
       <c r="Q126" t="n">
-        <v>90.5</v>
+        <v>89.7</v>
       </c>
       <c r="R126" t="n">
         <v>22551.3</v>
       </c>
       <c r="S126" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="T126" t="n">
-        <v>24426.5</v>
+        <v>24370.1</v>
       </c>
       <c r="U126" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="V126" t="n">
         <v>24841.7</v>
       </c>
       <c r="W126" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="X126" t="n">
-        <v>27874.4</v>
+        <v>27813</v>
       </c>
       <c r="Y126" t="n">
         <v>14.1</v>
@@ -12227,7 +12227,7 @@
         <v>28243.2</v>
       </c>
       <c r="AA126" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AB126" t="n">
         <v>64600</v>
@@ -12266,25 +12266,25 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1657.7</v>
+        <v>1651.7</v>
       </c>
       <c r="G127" t="n">
-        <v>-28.6</v>
+        <v>-28.9</v>
       </c>
       <c r="H127" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I127" t="n">
         <v>1636</v>
       </c>
       <c r="J127" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K127" t="n">
-        <v>1831.8</v>
+        <v>1839</v>
       </c>
       <c r="L127" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>8357.799999999999</v>
+        <v>8358.9</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="T127" t="n">
-        <v>8284.799999999999</v>
+        <v>8285</v>
       </c>
       <c r="U127" t="n">
         <v>-0.9</v>
@@ -12318,25 +12318,25 @@
         <v>0.9</v>
       </c>
       <c r="X127" t="n">
-        <v>9257.299999999999</v>
+        <v>9235.6</v>
       </c>
       <c r="Y127" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="Z127" t="n">
         <v>9204.700000000001</v>
       </c>
       <c r="AA127" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="AB127" t="n">
-        <v>14750</v>
+        <v>14800</v>
       </c>
       <c r="AC127" t="n">
         <v>16610</v>
       </c>
       <c r="AD127" t="n">
-        <v>-11.2</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="128">
@@ -12426,13 +12426,13 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>56300</v>
+        <v>56500</v>
       </c>
       <c r="AC128" t="n">
         <v>56800</v>
       </c>
       <c r="AD128" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="129">
@@ -12462,55 +12462,55 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>816.5</v>
+        <v>829.5</v>
       </c>
       <c r="G129" t="n">
-        <v>68.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="H129" t="n">
-        <v>35.7</v>
+        <v>37.8</v>
       </c>
       <c r="I129" t="n">
         <v>816</v>
       </c>
       <c r="J129" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="K129" t="n">
-        <v>1411</v>
+        <v>1389.2</v>
       </c>
       <c r="L129" t="n">
-        <v>72.8</v>
+        <v>67.5</v>
       </c>
       <c r="M129" t="n">
-        <v>83.3</v>
+        <v>80.5</v>
       </c>
       <c r="P129" t="n">
-        <v>3425.5</v>
+        <v>3417.6</v>
       </c>
       <c r="Q129" t="n">
-        <v>27.3</v>
+        <v>27</v>
       </c>
       <c r="R129" t="n">
         <v>3454.7</v>
       </c>
       <c r="S129" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="T129" t="n">
-        <v>5783.4</v>
+        <v>5808.7</v>
       </c>
       <c r="U129" t="n">
-        <v>68.8</v>
+        <v>70</v>
       </c>
       <c r="V129" t="n">
         <v>5810.7</v>
       </c>
       <c r="W129" t="n">
-        <v>-0.5</v>
+        <v>-0</v>
       </c>
       <c r="X129" t="n">
-        <v>7438.9</v>
+        <v>7469.9</v>
       </c>
       <c r="Y129" t="n">
         <v>28.6</v>
@@ -12519,16 +12519,16 @@
         <v>7423.7</v>
       </c>
       <c r="AA129" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AB129" t="n">
-        <v>107500</v>
+        <v>107700</v>
       </c>
       <c r="AC129" t="n">
         <v>121600</v>
       </c>
       <c r="AD129" t="n">
-        <v>-11.6</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="130">
@@ -12618,13 +12618,13 @@
         <v>-1.1</v>
       </c>
       <c r="AB130" t="n">
-        <v>22100</v>
+        <v>22250</v>
       </c>
       <c r="AC130" t="n">
         <v>21900</v>
       </c>
       <c r="AD130" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="131">
@@ -12714,13 +12714,13 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>41950</v>
+        <v>42000</v>
       </c>
       <c r="AC131" t="n">
         <v>43750</v>
       </c>
       <c r="AD131" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="132">
@@ -12812,13 +12812,13 @@
         <v>-2.6</v>
       </c>
       <c r="AB132" t="n">
-        <v>274000</v>
+        <v>275500</v>
       </c>
       <c r="AC132" t="n">
         <v>266000</v>
       </c>
       <c r="AD132" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="133">
@@ -12910,13 +12910,13 @@
         <v>-0.3</v>
       </c>
       <c r="AB133" t="n">
-        <v>253000</v>
+        <v>254500</v>
       </c>
       <c r="AC133" t="n">
         <v>281500</v>
       </c>
       <c r="AD133" t="n">
-        <v>-10.1</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="134">
@@ -13006,13 +13006,13 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>101000</v>
+        <v>100700</v>
       </c>
       <c r="AC134" t="n">
         <v>120600</v>
       </c>
       <c r="AD134" t="n">
-        <v>-16.3</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="135">
@@ -13198,13 +13198,13 @@
         <v>-1.5</v>
       </c>
       <c r="AB136" t="n">
-        <v>70800</v>
+        <v>70900</v>
       </c>
       <c r="AC136" t="n">
         <v>87800</v>
       </c>
       <c r="AD136" t="n">
-        <v>-19.4</v>
+        <v>-19.2</v>
       </c>
     </row>
     <row r="137">
@@ -13294,13 +13294,13 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>79200</v>
+        <v>79100</v>
       </c>
       <c r="AC137" t="n">
         <v>97300</v>
       </c>
       <c r="AD137" t="n">
-        <v>-18.6</v>
+        <v>-18.7</v>
       </c>
     </row>
     <row r="138">
@@ -13462,13 +13462,13 @@
         <v>0.4</v>
       </c>
       <c r="AB139" t="n">
-        <v>181100</v>
+        <v>181700</v>
       </c>
       <c r="AC139" t="n">
         <v>222000</v>
       </c>
       <c r="AD139" t="n">
-        <v>-18.4</v>
+        <v>-18.2</v>
       </c>
     </row>
     <row r="140">
@@ -13498,73 +13498,73 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2763.8</v>
+        <v>2759.7</v>
       </c>
       <c r="G140" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I140" t="n">
         <v>2821</v>
       </c>
       <c r="J140" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="K140" t="n">
-        <v>2924.9</v>
+        <v>2912.4</v>
       </c>
       <c r="L140" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="M140" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="P140" t="n">
-        <v>10346.9</v>
+        <v>10326.1</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R140" t="n">
         <v>10510.2</v>
       </c>
       <c r="S140" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="T140" t="n">
-        <v>12220.6</v>
+        <v>12108.5</v>
       </c>
       <c r="U140" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="V140" t="n">
         <v>12800.4</v>
       </c>
       <c r="W140" t="n">
-        <v>-4.5</v>
+        <v>-5.4</v>
       </c>
       <c r="X140" t="n">
-        <v>14777.1</v>
+        <v>14991.7</v>
       </c>
       <c r="Y140" t="n">
-        <v>20.9</v>
+        <v>23.8</v>
       </c>
       <c r="Z140" t="n">
         <v>15744.6</v>
       </c>
       <c r="AA140" t="n">
-        <v>-6.1</v>
+        <v>-4.8</v>
       </c>
       <c r="AB140" t="n">
-        <v>96600</v>
+        <v>97500</v>
       </c>
       <c r="AC140" t="n">
         <v>104800</v>
       </c>
       <c r="AD140" t="n">
-        <v>-7.8</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="141">
@@ -13594,34 +13594,34 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1357.7</v>
+        <v>1354.3</v>
       </c>
       <c r="G141" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H141" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="I141" t="n">
         <v>1355</v>
       </c>
       <c r="J141" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="K141" t="n">
         <v>2279.7</v>
       </c>
       <c r="L141" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="M141" t="n">
         <v>7.5</v>
       </c>
       <c r="P141" t="n">
-        <v>5860.7</v>
+        <v>5857.3</v>
       </c>
       <c r="Q141" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="R141" t="n">
         <v>5829.8</v>
@@ -13630,37 +13630,37 @@
         <v>0.5</v>
       </c>
       <c r="T141" t="n">
-        <v>6701.2</v>
+        <v>6677.1</v>
       </c>
       <c r="U141" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="V141" t="n">
         <v>6677.1</v>
       </c>
       <c r="W141" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>7424.5</v>
+        <v>7438.2</v>
       </c>
       <c r="Y141" t="n">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="Z141" t="n">
         <v>7368.2</v>
       </c>
       <c r="AA141" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB141" t="n">
-        <v>65000</v>
+        <v>65200</v>
       </c>
       <c r="AC141" t="n">
         <v>67700</v>
       </c>
       <c r="AD141" t="n">
-        <v>-4</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="142">
@@ -13750,13 +13750,13 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>240500</v>
+        <v>238000</v>
       </c>
       <c r="AC142" t="n">
         <v>293000</v>
       </c>
       <c r="AD142" t="n">
-        <v>-17.9</v>
+        <v>-18.8</v>
       </c>
     </row>
     <row r="143">
@@ -13846,13 +13846,13 @@
         <v>-0.3</v>
       </c>
       <c r="AB143" t="n">
-        <v>25000</v>
+        <v>25100</v>
       </c>
       <c r="AC143" t="n">
         <v>26250</v>
       </c>
       <c r="AD143" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="144">
@@ -13944,13 +13944,13 @@
         <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>170100</v>
+        <v>170700</v>
       </c>
       <c r="AC144" t="n">
         <v>201000</v>
       </c>
       <c r="AD144" t="n">
-        <v>-15.4</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="145">
@@ -13980,31 +13980,31 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>99.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G145" t="n">
-        <v>-52.4</v>
+        <v>-62.4</v>
       </c>
       <c r="H145" t="n">
-        <v>-55.2</v>
+        <v>-64.59999999999999</v>
       </c>
       <c r="I145" t="n">
         <v>178</v>
       </c>
       <c r="J145" t="n">
-        <v>-44.3</v>
+        <v>-56</v>
       </c>
       <c r="K145" t="n">
-        <v>305.3</v>
+        <v>292.8</v>
       </c>
       <c r="L145" t="n">
-        <v>208.1</v>
+        <v>273.5</v>
       </c>
       <c r="M145" t="n">
-        <v>-63</v>
+        <v>-64.5</v>
       </c>
       <c r="P145" t="n">
-        <v>1795.6</v>
+        <v>1751.8</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -14015,40 +14015,40 @@
         <v>1937.4</v>
       </c>
       <c r="S145" t="n">
-        <v>-7.3</v>
+        <v>-9.6</v>
       </c>
       <c r="T145" t="n">
-        <v>2190</v>
+        <v>2144.7</v>
       </c>
       <c r="U145" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="V145" t="n">
         <v>2345</v>
       </c>
       <c r="W145" t="n">
-        <v>-6.6</v>
+        <v>-8.5</v>
       </c>
       <c r="X145" t="n">
-        <v>3098.8</v>
+        <v>3006.4</v>
       </c>
       <c r="Y145" t="n">
-        <v>41.5</v>
+        <v>40.2</v>
       </c>
       <c r="Z145" t="n">
         <v>3178.9</v>
       </c>
       <c r="AA145" t="n">
-        <v>-2.5</v>
+        <v>-5.4</v>
       </c>
       <c r="AB145" t="n">
-        <v>94300</v>
+        <v>94400</v>
       </c>
       <c r="AC145" t="n">
         <v>115600</v>
       </c>
       <c r="AD145" t="n">
-        <v>-18.4</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="146">
@@ -14138,13 +14138,13 @@
         <v>-10.7</v>
       </c>
       <c r="AB146" t="n">
-        <v>39400</v>
+        <v>38550</v>
       </c>
       <c r="AC146" t="n">
         <v>37300</v>
       </c>
       <c r="AD146" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="147">
@@ -14189,13 +14189,13 @@
         <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>40950</v>
+        <v>40800</v>
       </c>
       <c r="AC147" t="n">
         <v>50200</v>
       </c>
       <c r="AD147" t="n">
-        <v>-18.4</v>
+        <v>-18.7</v>
       </c>
     </row>
     <row r="148">
@@ -14285,13 +14285,13 @@
         <v>-0.3</v>
       </c>
       <c r="AB148" t="n">
-        <v>193600</v>
+        <v>193900</v>
       </c>
       <c r="AC148" t="n">
         <v>179000</v>
       </c>
       <c r="AD148" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -14381,13 +14381,13 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>15430</v>
+        <v>15460</v>
       </c>
       <c r="AC149" t="n">
         <v>15700</v>
       </c>
       <c r="AD149" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="150">
@@ -14417,43 +14417,43 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>871.3</v>
+        <v>842</v>
       </c>
       <c r="G150" t="n">
-        <v>28</v>
+        <v>23.7</v>
       </c>
       <c r="H150" t="n">
-        <v>53.2</v>
+        <v>48</v>
       </c>
       <c r="I150" t="n">
         <v>871</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="K150" t="n">
-        <v>422.8</v>
+        <v>402.8</v>
       </c>
       <c r="L150" t="n">
-        <v>-51.5</v>
+        <v>-52.2</v>
       </c>
       <c r="M150" t="n">
-        <v>-2.4</v>
+        <v>-7.1</v>
       </c>
       <c r="P150" t="n">
-        <v>2311</v>
+        <v>2261.4</v>
       </c>
       <c r="Q150" t="n">
-        <v>17.4</v>
+        <v>14.9</v>
       </c>
       <c r="R150" t="n">
         <v>2311</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="T150" t="n">
-        <v>2420.3</v>
+        <v>2368</v>
       </c>
       <c r="U150" t="n">
         <v>4.7</v>
@@ -14462,28 +14462,28 @@
         <v>2420.3</v>
       </c>
       <c r="W150" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="X150" t="n">
-        <v>2825.8</v>
+        <v>2747.9</v>
       </c>
       <c r="Y150" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="Z150" t="n">
         <v>2825.8</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="AB150" t="n">
-        <v>105300</v>
+        <v>105200</v>
       </c>
       <c r="AC150" t="n">
         <v>108600</v>
       </c>
       <c r="AD150" t="n">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="151">
@@ -14573,13 +14573,13 @@
         <v>0.4</v>
       </c>
       <c r="AB151" t="n">
-        <v>79000</v>
+        <v>80000</v>
       </c>
       <c r="AC151" t="n">
         <v>85500</v>
       </c>
       <c r="AD151" t="n">
-        <v>-7.6</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="152">
@@ -14645,22 +14645,22 @@
         <v>-1.8</v>
       </c>
       <c r="T152" t="n">
-        <v>30623.8</v>
+        <v>30561.7</v>
       </c>
       <c r="U152" t="n">
-        <v>-21.2</v>
+        <v>-21.3</v>
       </c>
       <c r="V152" t="n">
         <v>31564.6</v>
       </c>
       <c r="W152" t="n">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
       <c r="X152" t="n">
         <v>32719.1</v>
       </c>
       <c r="Y152" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="Z152" t="n">
         <v>33081.3</v>
@@ -14669,13 +14669,13 @@
         <v>-1.1</v>
       </c>
       <c r="AB152" t="n">
-        <v>151100</v>
+        <v>152100</v>
       </c>
       <c r="AC152" t="n">
         <v>169000</v>
       </c>
       <c r="AD152" t="n">
-        <v>-10.6</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="153">
@@ -14765,13 +14765,13 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>76000</v>
+        <v>75900</v>
       </c>
       <c r="AC153" t="n">
         <v>77100</v>
       </c>
       <c r="AD153" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="154">
@@ -14861,13 +14861,13 @@
         <v>-0.4</v>
       </c>
       <c r="AB154" t="n">
-        <v>41200</v>
+        <v>41150</v>
       </c>
       <c r="AC154" t="n">
         <v>42800</v>
       </c>
       <c r="AD154" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="155">
@@ -14897,73 +14897,73 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1445</v>
+        <v>1448.1</v>
       </c>
       <c r="G155" t="n">
-        <v>-20.7</v>
+        <v>-20.5</v>
       </c>
       <c r="H155" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="I155" t="n">
         <v>1447</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="K155" t="n">
-        <v>1518.6</v>
+        <v>1525.9</v>
       </c>
       <c r="L155" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="M155" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P155" t="n">
-        <v>6210.7</v>
+        <v>6266</v>
       </c>
       <c r="Q155" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R155" t="n">
         <v>6186.9</v>
       </c>
       <c r="S155" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="T155" t="n">
-        <v>6469.7</v>
+        <v>6496.6</v>
       </c>
       <c r="U155" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="V155" t="n">
         <v>6481.5</v>
       </c>
       <c r="W155" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="X155" t="n">
-        <v>7361</v>
+        <v>7568.5</v>
       </c>
       <c r="Y155" t="n">
-        <v>13.8</v>
+        <v>16.5</v>
       </c>
       <c r="Z155" t="n">
         <v>7343.8</v>
       </c>
       <c r="AA155" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB155" t="n">
-        <v>6090</v>
+        <v>6080</v>
       </c>
       <c r="AC155" t="n">
         <v>6640</v>
       </c>
       <c r="AD155" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="156">
@@ -15008,13 +15008,13 @@
         <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>8290</v>
+        <v>8370</v>
       </c>
       <c r="AC156" t="n">
         <v>9310</v>
       </c>
       <c r="AD156" t="n">
-        <v>-11</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="157">
@@ -15059,13 +15059,13 @@
         <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>12080</v>
+        <v>12120</v>
       </c>
       <c r="AC157" t="n">
         <v>14110</v>
       </c>
       <c r="AD157" t="n">
-        <v>-14.4</v>
+        <v>-14.1</v>
       </c>
     </row>
     <row r="158">
@@ -15155,7 +15155,7 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>18460</v>
+        <v>18480</v>
       </c>
       <c r="AC158" t="n">
         <v>20800</v>
@@ -15287,73 +15287,73 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1072.2</v>
+        <v>1055.2</v>
       </c>
       <c r="G160" t="n">
-        <v>1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="H160" t="n">
-        <v>19.7</v>
+        <v>17.8</v>
       </c>
       <c r="I160" t="n">
         <v>1072</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="K160" t="n">
-        <v>622.1</v>
+        <v>633.9</v>
       </c>
       <c r="L160" t="n">
-        <v>-42</v>
+        <v>-39.9</v>
       </c>
       <c r="M160" t="n">
-        <v>60.8</v>
+        <v>63.9</v>
       </c>
       <c r="P160" t="n">
-        <v>4476.7</v>
+        <v>4471.2</v>
       </c>
       <c r="Q160" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="R160" t="n">
         <v>4485.9</v>
       </c>
       <c r="S160" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="T160" t="n">
-        <v>6243.8</v>
+        <v>6249.9</v>
       </c>
       <c r="U160" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="V160" t="n">
         <v>6237.4</v>
       </c>
       <c r="W160" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="X160" t="n">
-        <v>8373.4</v>
+        <v>8387.9</v>
       </c>
       <c r="Y160" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="Z160" t="n">
         <v>8373</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AB160" t="n">
-        <v>572000</v>
+        <v>580000</v>
       </c>
       <c r="AC160" t="n">
         <v>619000</v>
       </c>
       <c r="AD160" t="n">
-        <v>-7.6</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="161">
@@ -15402,13 +15402,13 @@
         <v>43.3</v>
       </c>
       <c r="AB161" t="n">
-        <v>7360</v>
+        <v>7180</v>
       </c>
       <c r="AC161" t="n">
         <v>7860</v>
       </c>
       <c r="AD161" t="n">
-        <v>-6.4</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="162">
@@ -15538,28 +15538,28 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="G163" t="n">
-        <v>52</v>
+        <v>50.4</v>
       </c>
       <c r="H163" t="n">
-        <v>116.5</v>
+        <v>114.3</v>
       </c>
       <c r="I163" t="n">
         <v>595</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.2</v>
+        <v>-4.2</v>
       </c>
       <c r="AB163" t="n">
-        <v>37500</v>
+        <v>37700</v>
       </c>
       <c r="AC163" t="n">
         <v>41150</v>
       </c>
       <c r="AD163" t="n">
-        <v>-8.9</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="164">
@@ -15649,13 +15649,13 @@
         <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>128900</v>
+        <v>127600</v>
       </c>
       <c r="AC164" t="n">
         <v>171700</v>
       </c>
       <c r="AD164" t="n">
-        <v>-24.9</v>
+        <v>-25.7</v>
       </c>
     </row>
     <row r="165">
@@ -15745,13 +15745,13 @@
         <v>-0.4</v>
       </c>
       <c r="AB165" t="n">
-        <v>186000</v>
+        <v>186400</v>
       </c>
       <c r="AC165" t="n">
         <v>183200</v>
       </c>
       <c r="AD165" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="166">
@@ -15841,13 +15841,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB166" t="n">
-        <v>123200</v>
+        <v>122700</v>
       </c>
       <c r="AC166" t="n">
         <v>124500</v>
       </c>
       <c r="AD166" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="167">
@@ -15877,73 +15877,73 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1908.5</v>
+        <v>1615.2</v>
       </c>
       <c r="G167" t="n">
-        <v>-69.59999999999999</v>
+        <v>-74.2</v>
       </c>
       <c r="H167" t="n">
-        <v>-46.2</v>
+        <v>-54.5</v>
       </c>
       <c r="I167" t="n">
         <v>4601</v>
       </c>
       <c r="J167" t="n">
-        <v>-58.5</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="K167" t="n">
         <v>1263.8</v>
       </c>
       <c r="L167" t="n">
-        <v>-33.8</v>
+        <v>-21.8</v>
       </c>
       <c r="M167" t="n">
         <v>-29.9</v>
       </c>
       <c r="P167" t="n">
-        <v>9656.9</v>
+        <v>9436.9</v>
       </c>
       <c r="Q167" t="n">
-        <v>-15.8</v>
+        <v>-17.7</v>
       </c>
       <c r="R167" t="n">
         <v>9525.200000000001</v>
       </c>
       <c r="S167" t="n">
-        <v>1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="T167" t="n">
-        <v>10129.8</v>
+        <v>10008.7</v>
       </c>
       <c r="U167" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="V167" t="n">
         <v>9971.799999999999</v>
       </c>
       <c r="W167" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="X167" t="n">
-        <v>10873.3</v>
+        <v>10693.3</v>
       </c>
       <c r="Y167" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="Z167" t="n">
         <v>10873.3</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="AB167" t="n">
-        <v>4725</v>
+        <v>4740</v>
       </c>
       <c r="AC167" t="n">
         <v>5180</v>
       </c>
       <c r="AD167" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="168">
@@ -16033,13 +16033,13 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>50000</v>
+        <v>50100</v>
       </c>
       <c r="AC168" t="n">
         <v>51200</v>
       </c>
       <c r="AD168" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="169">
@@ -16084,13 +16084,13 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>49100</v>
+        <v>49350</v>
       </c>
       <c r="AC169" t="n">
         <v>66800</v>
       </c>
       <c r="AD169" t="n">
-        <v>-26.5</v>
+        <v>-26.1</v>
       </c>
     </row>
     <row r="170">
@@ -16180,13 +16180,13 @@
         <v>-0.6</v>
       </c>
       <c r="AB170" t="n">
-        <v>138100</v>
+        <v>138200</v>
       </c>
       <c r="AC170" t="n">
         <v>133900</v>
       </c>
       <c r="AD170" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="171">
@@ -16231,13 +16231,13 @@
         <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>12010</v>
+        <v>11930</v>
       </c>
       <c r="AC171" t="n">
         <v>15030</v>
       </c>
       <c r="AD171" t="n">
-        <v>-20.1</v>
+        <v>-20.6</v>
       </c>
     </row>
     <row r="172">
@@ -16423,13 +16423,13 @@
         <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>127100</v>
+        <v>126800</v>
       </c>
       <c r="AC173" t="n">
         <v>163300</v>
       </c>
       <c r="AD173" t="n">
-        <v>-22.2</v>
+        <v>-22.4</v>
       </c>
     </row>
     <row r="174">
@@ -16519,13 +16519,13 @@
         <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>18170</v>
+        <v>18100</v>
       </c>
       <c r="AC174" t="n">
         <v>17570</v>
       </c>
       <c r="AD174" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -16615,13 +16615,13 @@
         <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>37900</v>
+        <v>37850</v>
       </c>
       <c r="AC175" t="n">
         <v>37950</v>
       </c>
       <c r="AD175" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="176">
@@ -16711,13 +16711,13 @@
         <v>9.4</v>
       </c>
       <c r="AB176" t="n">
-        <v>152100</v>
+        <v>151800</v>
       </c>
       <c r="AC176" t="n">
         <v>161500</v>
       </c>
       <c r="AD176" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="177">
@@ -16807,13 +16807,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB177" t="n">
-        <v>186200</v>
+        <v>186500</v>
       </c>
       <c r="AC177" t="n">
         <v>182600</v>
       </c>
       <c r="AD177" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="178">
@@ -16858,13 +16858,13 @@
         <v>5.8</v>
       </c>
       <c r="AB178" t="n">
-        <v>33100</v>
+        <v>32500</v>
       </c>
       <c r="AC178" t="n">
         <v>37350</v>
       </c>
       <c r="AD178" t="n">
-        <v>-11.4</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="179">
@@ -16954,13 +16954,13 @@
         <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>16280</v>
+        <v>16250</v>
       </c>
       <c r="AC179" t="n">
         <v>16620</v>
       </c>
       <c r="AD179" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="180">
@@ -17050,13 +17050,13 @@
         <v>-36.1</v>
       </c>
       <c r="AB180" t="n">
-        <v>57300</v>
+        <v>57400</v>
       </c>
       <c r="AC180" t="n">
         <v>69200</v>
       </c>
       <c r="AD180" t="n">
-        <v>-17.2</v>
+        <v>-17.1</v>
       </c>
     </row>
     <row r="181">
@@ -17086,73 +17086,73 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1064</v>
+        <v>1038.9</v>
       </c>
       <c r="G181" t="n">
-        <v>-15</v>
+        <v>-17</v>
       </c>
       <c r="H181" t="n">
-        <v>149.9</v>
+        <v>144</v>
       </c>
       <c r="I181" t="n">
         <v>1086</v>
       </c>
       <c r="J181" t="n">
-        <v>-2</v>
+        <v>-4.3</v>
       </c>
       <c r="K181" t="n">
-        <v>1060.3</v>
+        <v>1058.9</v>
       </c>
       <c r="L181" t="n">
-        <v>-0.3</v>
+        <v>1.9</v>
       </c>
       <c r="M181" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P181" t="n">
-        <v>4277.7</v>
+        <v>4251.2</v>
       </c>
       <c r="Q181" t="n">
-        <v>43.8</v>
+        <v>42.9</v>
       </c>
       <c r="R181" t="n">
         <v>4298.5</v>
       </c>
       <c r="S181" t="n">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="T181" t="n">
-        <v>3969.2</v>
+        <v>3938.9</v>
       </c>
       <c r="U181" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
       <c r="V181" t="n">
         <v>3933.1</v>
       </c>
       <c r="W181" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="X181" t="n">
-        <v>4370.1</v>
+        <v>4394.4</v>
       </c>
       <c r="Y181" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="Z181" t="n">
         <v>4306.3</v>
       </c>
       <c r="AA181" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB181" t="n">
-        <v>62500</v>
+        <v>62600</v>
       </c>
       <c r="AC181" t="n">
         <v>65900</v>
       </c>
       <c r="AD181" t="n">
-        <v>-5.2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="182">
@@ -17342,13 +17342,13 @@
         <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>232500</v>
+        <v>234000</v>
       </c>
       <c r="AC183" t="n">
         <v>298000</v>
       </c>
       <c r="AD183" t="n">
-        <v>-22</v>
+        <v>-21.5</v>
       </c>
     </row>
     <row r="184">
@@ -17378,73 +17378,73 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2078.6</v>
+        <v>2072.9</v>
       </c>
       <c r="G184" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="H184" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="I184" t="n">
         <v>2097</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="K184" t="n">
-        <v>1247.3</v>
+        <v>1240.1</v>
       </c>
       <c r="L184" t="n">
-        <v>-40</v>
+        <v>-40.2</v>
       </c>
       <c r="M184" t="n">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
       <c r="P184" t="n">
-        <v>6341.7</v>
+        <v>6330.3</v>
       </c>
       <c r="Q184" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="R184" t="n">
         <v>6369</v>
       </c>
       <c r="S184" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="T184" t="n">
-        <v>6984.4</v>
+        <v>6940.1</v>
       </c>
       <c r="U184" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="V184" t="n">
         <v>7059.1</v>
       </c>
       <c r="W184" t="n">
-        <v>-1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="X184" t="n">
-        <v>7810.2</v>
+        <v>7645.2</v>
       </c>
       <c r="Y184" t="n">
-        <v>11.8</v>
+        <v>10.2</v>
       </c>
       <c r="Z184" t="n">
         <v>7903.5</v>
       </c>
       <c r="AA184" t="n">
-        <v>-1.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AB184" t="n">
-        <v>74900</v>
+        <v>74400</v>
       </c>
       <c r="AC184" t="n">
         <v>70800</v>
       </c>
       <c r="AD184" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="185">
@@ -17534,13 +17534,13 @@
         <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>51000</v>
+        <v>51200</v>
       </c>
       <c r="AC185" t="n">
         <v>55400</v>
       </c>
       <c r="AD185" t="n">
-        <v>-7.9</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="186">
@@ -17570,28 +17570,28 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G186" t="n">
-        <v>-23.1</v>
+        <v>-26.4</v>
       </c>
       <c r="H186" t="n">
-        <v>-7.5</v>
+        <v>-11.6</v>
       </c>
       <c r="I186" t="n">
         <v>175</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.6</v>
+        <v>-12.6</v>
       </c>
       <c r="AB186" t="n">
-        <v>8590</v>
+        <v>8580</v>
       </c>
       <c r="AC186" t="n">
         <v>8640</v>
       </c>
       <c r="AD186" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="187">
@@ -17681,13 +17681,13 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>48550</v>
+        <v>48750</v>
       </c>
       <c r="AC187" t="n">
         <v>55700</v>
       </c>
       <c r="AD187" t="n">
-        <v>-12.8</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="188">
@@ -17777,13 +17777,13 @@
         <v>-1.4</v>
       </c>
       <c r="AB188" t="n">
-        <v>42100</v>
+        <v>42200</v>
       </c>
       <c r="AC188" t="n">
         <v>40500</v>
       </c>
       <c r="AD188" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="189">
@@ -17813,55 +17813,55 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>802.7</v>
+        <v>810.6</v>
       </c>
       <c r="G189" t="n">
-        <v>-38.8</v>
+        <v>-38.2</v>
       </c>
       <c r="H189" t="n">
-        <v>45.8</v>
+        <v>47.2</v>
       </c>
       <c r="I189" t="n">
         <v>1062</v>
       </c>
       <c r="J189" t="n">
-        <v>-24.4</v>
+        <v>-23.7</v>
       </c>
       <c r="K189" t="n">
-        <v>1596.8</v>
+        <v>1635.5</v>
       </c>
       <c r="L189" t="n">
-        <v>98.90000000000001</v>
+        <v>101.8</v>
       </c>
       <c r="M189" t="n">
-        <v>91.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P189" t="n">
-        <v>4213.1</v>
+        <v>4313.4</v>
       </c>
       <c r="Q189" t="n">
-        <v>63.4</v>
+        <v>67.3</v>
       </c>
       <c r="R189" t="n">
         <v>3812.4</v>
       </c>
       <c r="S189" t="n">
-        <v>10.5</v>
+        <v>13.1</v>
       </c>
       <c r="T189" t="n">
-        <v>2969</v>
+        <v>2974.1</v>
       </c>
       <c r="U189" t="n">
-        <v>-29.5</v>
+        <v>-31</v>
       </c>
       <c r="V189" t="n">
         <v>3142.5</v>
       </c>
       <c r="W189" t="n">
-        <v>-5.5</v>
+        <v>-5.4</v>
       </c>
       <c r="X189" t="n">
-        <v>2985.8</v>
+        <v>2991.2</v>
       </c>
       <c r="Y189" t="n">
         <v>0.6</v>
@@ -17870,7 +17870,7 @@
         <v>3113.4</v>
       </c>
       <c r="AA189" t="n">
-        <v>-4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="AB189" t="n">
         <v>397000</v>
@@ -17969,13 +17969,13 @@
         <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>295500</v>
+        <v>294000</v>
       </c>
       <c r="AC190" t="n">
         <v>309000</v>
       </c>
       <c r="AD190" t="n">
-        <v>-4.4</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="191">
@@ -18067,13 +18067,13 @@
         <v>0.9</v>
       </c>
       <c r="AB191" t="n">
-        <v>114600</v>
+        <v>113800</v>
       </c>
       <c r="AC191" t="n">
         <v>123300</v>
       </c>
       <c r="AD191" t="n">
-        <v>-7.1</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="192">
@@ -18163,13 +18163,13 @@
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>130300</v>
+        <v>129700</v>
       </c>
       <c r="AC192" t="n">
         <v>126700</v>
       </c>
       <c r="AD192" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="193">
@@ -18259,13 +18259,13 @@
         <v>-1.8</v>
       </c>
       <c r="AB193" t="n">
-        <v>14640</v>
+        <v>14680</v>
       </c>
       <c r="AC193" t="n">
         <v>15270</v>
       </c>
       <c r="AD193" t="n">
-        <v>-4.1</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="194">
@@ -18355,13 +18355,13 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>16910</v>
+        <v>16950</v>
       </c>
       <c r="AC194" t="n">
         <v>17600</v>
       </c>
       <c r="AD194" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="195">
@@ -18455,13 +18455,13 @@
         <v>-0.3</v>
       </c>
       <c r="AB195" t="n">
-        <v>73200</v>
+        <v>73100</v>
       </c>
       <c r="AC195" t="n">
         <v>70400</v>
       </c>
       <c r="AD195" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="196">
@@ -18665,73 +18665,73 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>335.5</v>
+        <v>291.5</v>
       </c>
       <c r="G198" t="n">
-        <v>-40.1</v>
+        <v>-48</v>
       </c>
       <c r="H198" t="n">
-        <v>-29.2</v>
+        <v>-38.5</v>
       </c>
       <c r="I198" t="n">
         <v>416</v>
       </c>
       <c r="J198" t="n">
-        <v>-19.4</v>
+        <v>-29.9</v>
       </c>
       <c r="K198" t="n">
-        <v>522.6</v>
+        <v>510.4</v>
       </c>
       <c r="L198" t="n">
-        <v>55.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="M198" t="n">
-        <v>-9.6</v>
+        <v>-11.7</v>
       </c>
       <c r="P198" t="n">
-        <v>1915.1</v>
+        <v>1862.9</v>
       </c>
       <c r="Q198" t="n">
-        <v>-4.7</v>
+        <v>-7.2</v>
       </c>
       <c r="R198" t="n">
         <v>2002.6</v>
       </c>
       <c r="S198" t="n">
-        <v>-4.4</v>
+        <v>-7</v>
       </c>
       <c r="T198" t="n">
-        <v>2611.1</v>
+        <v>2566</v>
       </c>
       <c r="U198" t="n">
-        <v>36.3</v>
+        <v>37.7</v>
       </c>
       <c r="V198" t="n">
         <v>2694</v>
       </c>
       <c r="W198" t="n">
-        <v>-3.1</v>
+        <v>-4.8</v>
       </c>
       <c r="X198" t="n">
-        <v>3521.6</v>
+        <v>3464.5</v>
       </c>
       <c r="Y198" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="Z198" t="n">
         <v>3534.6</v>
       </c>
       <c r="AA198" t="n">
-        <v>-0.4</v>
+        <v>-2</v>
       </c>
       <c r="AB198" t="n">
-        <v>180000</v>
+        <v>176700</v>
       </c>
       <c r="AC198" t="n">
         <v>181300</v>
       </c>
       <c r="AD198" t="n">
-        <v>-0.7</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="199">
@@ -18821,13 +18821,13 @@
         <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>40150</v>
+        <v>39300</v>
       </c>
       <c r="AC199" t="n">
         <v>40150</v>
       </c>
       <c r="AD199" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="200">
@@ -18917,13 +18917,13 @@
         <v>0.6</v>
       </c>
       <c r="AB200" t="n">
-        <v>62600</v>
+        <v>63000</v>
       </c>
       <c r="AC200" t="n">
         <v>61700</v>
       </c>
       <c r="AD200" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="201">
@@ -19013,13 +19013,13 @@
         <v>0.7</v>
       </c>
       <c r="AB201" t="n">
-        <v>129200</v>
+        <v>130000</v>
       </c>
       <c r="AC201" t="n">
         <v>137500</v>
       </c>
       <c r="AD201" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="202">
@@ -19111,13 +19111,13 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>34800</v>
+        <v>34700</v>
       </c>
       <c r="AC202" t="n">
         <v>34950</v>
       </c>
       <c r="AD202" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="203">
@@ -19307,13 +19307,13 @@
         <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>39750</v>
+        <v>39350</v>
       </c>
       <c r="AC204" t="n">
         <v>41150</v>
       </c>
       <c r="AD204" t="n">
-        <v>-3.4</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="205">
@@ -19367,7 +19367,7 @@
         <v>-5.2</v>
       </c>
       <c r="P205" t="n">
-        <v>797</v>
+        <v>797.2</v>
       </c>
       <c r="Q205" t="n">
         <v>-1.1</v>
@@ -19379,37 +19379,37 @@
         <v>1.4</v>
       </c>
       <c r="T205" t="n">
-        <v>858.8</v>
+        <v>850.2</v>
       </c>
       <c r="U205" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="V205" t="n">
         <v>840</v>
       </c>
       <c r="W205" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="X205" t="n">
-        <v>991.6</v>
+        <v>997</v>
       </c>
       <c r="Y205" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="Z205" t="n">
         <v>958</v>
       </c>
       <c r="AA205" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB205" t="n">
-        <v>66300</v>
+        <v>66400</v>
       </c>
       <c r="AC205" t="n">
         <v>65400</v>
       </c>
       <c r="AD205" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="206">
@@ -19499,13 +19499,13 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>56600</v>
+        <v>57000</v>
       </c>
       <c r="AC206" t="n">
         <v>63800</v>
       </c>
       <c r="AD206" t="n">
-        <v>-11.3</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="207">
@@ -19691,13 +19691,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB208" t="n">
-        <v>293000</v>
+        <v>296500</v>
       </c>
       <c r="AC208" t="n">
         <v>303500</v>
       </c>
       <c r="AD208" t="n">
-        <v>-3.5</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="209">
@@ -19751,49 +19751,49 @@
         <v>-3</v>
       </c>
       <c r="P209" t="n">
-        <v>1302.1</v>
+        <v>1294.9</v>
       </c>
       <c r="Q209" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="R209" t="n">
         <v>1307.2</v>
       </c>
       <c r="S209" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="T209" t="n">
-        <v>1474.5</v>
+        <v>1453.6</v>
       </c>
       <c r="U209" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="V209" t="n">
         <v>1480.5</v>
       </c>
       <c r="W209" t="n">
-        <v>-0.4</v>
+        <v>-1.8</v>
       </c>
       <c r="X209" t="n">
-        <v>1673.1</v>
+        <v>1652.3</v>
       </c>
       <c r="Y209" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="Z209" t="n">
         <v>1688.6</v>
       </c>
       <c r="AA209" t="n">
-        <v>-0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AB209" t="n">
-        <v>35950</v>
+        <v>36050</v>
       </c>
       <c r="AC209" t="n">
         <v>40300</v>
       </c>
       <c r="AD209" t="n">
-        <v>-10.8</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="210">
@@ -19979,13 +19979,13 @@
         <v>1</v>
       </c>
       <c r="AB211" t="n">
-        <v>40800</v>
+        <v>41150</v>
       </c>
       <c r="AC211" t="n">
         <v>44350</v>
       </c>
       <c r="AD211" t="n">
-        <v>-8</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="212">
@@ -20075,13 +20075,13 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1282000</v>
+        <v>1291000</v>
       </c>
       <c r="AC212" t="n">
         <v>1220000</v>
       </c>
       <c r="AD212" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="213">
@@ -20162,58 +20162,58 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>733.3</v>
+        <v>729.4</v>
       </c>
       <c r="G214" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H214" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="I214" t="n">
         <v>735</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="K214" t="n">
-        <v>752.7</v>
+        <v>747</v>
       </c>
       <c r="L214" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M214" t="n">
-        <v>45</v>
+        <v>43.9</v>
       </c>
       <c r="P214" t="n">
-        <v>2724.3</v>
+        <v>2714.8</v>
       </c>
       <c r="Q214" t="n">
-        <v>27.1</v>
+        <v>26.6</v>
       </c>
       <c r="R214" t="n">
         <v>2726.9</v>
       </c>
       <c r="S214" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="T214" t="n">
-        <v>3407.7</v>
+        <v>3390.6</v>
       </c>
       <c r="U214" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="V214" t="n">
         <v>3411</v>
       </c>
       <c r="W214" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="X214" t="n">
         <v>4098.7</v>
       </c>
       <c r="Y214" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="Z214" t="n">
         <v>4102.9</v>
@@ -20222,13 +20222,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB214" t="n">
-        <v>278000</v>
+        <v>279000</v>
       </c>
       <c r="AC214" t="n">
         <v>299000</v>
       </c>
       <c r="AD214" t="n">
-        <v>-7</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="215">
@@ -20318,13 +20318,13 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>50400</v>
+        <v>50100</v>
       </c>
       <c r="AC215" t="n">
         <v>58000</v>
       </c>
       <c r="AD215" t="n">
-        <v>-13.1</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="216">
@@ -20414,13 +20414,13 @@
         <v>0.5</v>
       </c>
       <c r="AB216" t="n">
-        <v>126300</v>
+        <v>126500</v>
       </c>
       <c r="AC216" t="n">
         <v>170700</v>
       </c>
       <c r="AD216" t="n">
-        <v>-26</v>
+        <v>-25.9</v>
       </c>
     </row>
     <row r="217">
@@ -20510,13 +20510,13 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>90800</v>
+        <v>90900</v>
       </c>
       <c r="AC217" t="n">
         <v>92100</v>
       </c>
       <c r="AD217" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="218">
@@ -20606,13 +20606,13 @@
         <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>108400</v>
+        <v>108600</v>
       </c>
       <c r="AC218" t="n">
         <v>134200</v>
       </c>
       <c r="AD218" t="n">
-        <v>-19.2</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="219">
@@ -20702,13 +20702,13 @@
         <v>-0</v>
       </c>
       <c r="AB219" t="n">
-        <v>51000</v>
+        <v>51100</v>
       </c>
       <c r="AC219" t="n">
         <v>53700</v>
       </c>
       <c r="AD219" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="220">
@@ -20798,13 +20798,13 @@
         <v>0.3</v>
       </c>
       <c r="AB220" t="n">
-        <v>115000</v>
+        <v>114900</v>
       </c>
       <c r="AC220" t="n">
         <v>112100</v>
       </c>
       <c r="AD220" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="221">
@@ -20894,13 +20894,13 @@
         <v>2.3</v>
       </c>
       <c r="AB221" t="n">
-        <v>106300</v>
+        <v>106500</v>
       </c>
       <c r="AC221" t="n">
         <v>126500</v>
       </c>
       <c r="AD221" t="n">
-        <v>-16</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="222">
@@ -20930,73 +20930,73 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>890.3</v>
+        <v>866.8</v>
       </c>
       <c r="G222" t="n">
-        <v>11.1</v>
+        <v>8.1</v>
       </c>
       <c r="H222" t="n">
-        <v>-2</v>
+        <v>-4.6</v>
       </c>
       <c r="I222" t="n">
         <v>942</v>
       </c>
       <c r="J222" t="n">
-        <v>-5.5</v>
+        <v>-8</v>
       </c>
       <c r="K222" t="n">
-        <v>911.5</v>
+        <v>889.8</v>
       </c>
       <c r="L222" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M222" t="n">
-        <v>-17.7</v>
+        <v>-19.7</v>
       </c>
       <c r="P222" t="n">
-        <v>3146.5</v>
+        <v>3103.9</v>
       </c>
       <c r="Q222" t="n">
-        <v>-10.7</v>
+        <v>-11.9</v>
       </c>
       <c r="R222" t="n">
         <v>3228.6</v>
       </c>
       <c r="S222" t="n">
-        <v>-2.5</v>
+        <v>-3.9</v>
       </c>
       <c r="T222" t="n">
-        <v>3628.9</v>
+        <v>3508</v>
       </c>
       <c r="U222" t="n">
-        <v>15.3</v>
+        <v>13</v>
       </c>
       <c r="V222" t="n">
         <v>3695.9</v>
       </c>
       <c r="W222" t="n">
-        <v>-1.8</v>
+        <v>-5.1</v>
       </c>
       <c r="X222" t="n">
-        <v>3670.3</v>
+        <v>3578.9</v>
       </c>
       <c r="Y222" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="Z222" t="n">
         <v>3980.5</v>
       </c>
       <c r="AA222" t="n">
-        <v>-7.8</v>
+        <v>-10.1</v>
       </c>
       <c r="AB222" t="n">
-        <v>34600</v>
+        <v>34900</v>
       </c>
       <c r="AC222" t="n">
         <v>33700</v>
       </c>
       <c r="AD222" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="223">
@@ -21086,13 +21086,13 @@
         <v>2.5</v>
       </c>
       <c r="AB223" t="n">
-        <v>71700</v>
+        <v>73000</v>
       </c>
       <c r="AC223" t="n">
         <v>65800</v>
       </c>
       <c r="AD223" t="n">
-        <v>9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="224">
@@ -21182,13 +21182,13 @@
         <v>0.8</v>
       </c>
       <c r="AB224" t="n">
-        <v>23400</v>
+        <v>23650</v>
       </c>
       <c r="AC224" t="n">
         <v>20950</v>
       </c>
       <c r="AD224" t="n">
-        <v>11.7</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="225">
@@ -21278,13 +21278,13 @@
         <v>-0.4</v>
       </c>
       <c r="AB225" t="n">
-        <v>34800</v>
+        <v>34750</v>
       </c>
       <c r="AC225" t="n">
         <v>35700</v>
       </c>
       <c r="AD225" t="n">
-        <v>-2.5</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="226">
@@ -21314,73 +21314,73 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2791.3</v>
+        <v>2801.5</v>
       </c>
       <c r="G226" t="n">
-        <v>-32.1</v>
+        <v>-31.8</v>
       </c>
       <c r="H226" t="n">
-        <v>-19.9</v>
+        <v>-19.6</v>
       </c>
       <c r="I226" t="n">
         <v>3024</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.7</v>
+        <v>-7.4</v>
       </c>
       <c r="K226" t="n">
-        <v>1332.1</v>
+        <v>1347.4</v>
       </c>
       <c r="L226" t="n">
-        <v>-52.3</v>
+        <v>-51.9</v>
       </c>
       <c r="M226" t="n">
-        <v>5381.9</v>
+        <v>5444.9</v>
       </c>
       <c r="P226" t="n">
-        <v>13970.4</v>
+        <v>13993.9</v>
       </c>
       <c r="Q226" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="R226" t="n">
         <v>14280.1</v>
       </c>
       <c r="S226" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="T226" t="n">
-        <v>14778.6</v>
+        <v>14836.1</v>
       </c>
       <c r="U226" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="V226" t="n">
         <v>15420.5</v>
       </c>
       <c r="W226" t="n">
-        <v>-4.2</v>
+        <v>-3.8</v>
       </c>
       <c r="X226" t="n">
-        <v>15708.5</v>
+        <v>15780.6</v>
       </c>
       <c r="Y226" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z226" t="n">
         <v>16544.9</v>
       </c>
       <c r="AA226" t="n">
-        <v>-5.1</v>
+        <v>-4.6</v>
       </c>
       <c r="AB226" t="n">
-        <v>193700</v>
+        <v>194400</v>
       </c>
       <c r="AC226" t="n">
         <v>186600</v>
       </c>
       <c r="AD226" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="227">
@@ -21474,13 +21474,13 @@
         <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>33600</v>
+        <v>33500</v>
       </c>
       <c r="AC227" t="n">
         <v>32700</v>
       </c>
       <c r="AD227" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="228">
@@ -21570,13 +21570,13 @@
         <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>158400</v>
+        <v>158600</v>
       </c>
       <c r="AC228" t="n">
         <v>180800</v>
       </c>
       <c r="AD228" t="n">
-        <v>-12.4</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="229">
@@ -21666,13 +21666,13 @@
         <v>-1.4</v>
       </c>
       <c r="AB229" t="n">
-        <v>515000</v>
+        <v>513000</v>
       </c>
       <c r="AC229" t="n">
         <v>607000</v>
       </c>
       <c r="AD229" t="n">
-        <v>-15.2</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="230">
@@ -21762,13 +21762,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB230" t="n">
-        <v>92200</v>
+        <v>92300</v>
       </c>
       <c r="AC230" t="n">
         <v>107100</v>
       </c>
       <c r="AD230" t="n">
-        <v>-13.9</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="231">
@@ -21858,13 +21858,13 @@
         <v>1</v>
       </c>
       <c r="AB231" t="n">
-        <v>109000</v>
+        <v>108700</v>
       </c>
       <c r="AC231" t="n">
         <v>104100</v>
       </c>
       <c r="AD231" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="232">
@@ -21894,73 +21894,73 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>605.9</v>
+        <v>604</v>
       </c>
       <c r="G232" t="n">
-        <v>-41.5</v>
+        <v>-41.7</v>
       </c>
       <c r="H232" t="n">
-        <v>169</v>
+        <v>168.2</v>
       </c>
       <c r="I232" t="n">
         <v>606</v>
       </c>
       <c r="J232" t="n">
-        <v>-0</v>
+        <v>-0.3</v>
       </c>
       <c r="K232" t="n">
-        <v>600.5</v>
+        <v>592.7</v>
       </c>
       <c r="L232" t="n">
-        <v>-0.9</v>
+        <v>-1.9</v>
       </c>
       <c r="M232" t="n">
-        <v>942.5</v>
+        <v>929</v>
       </c>
       <c r="P232" t="n">
-        <v>2541.7</v>
+        <v>2550.9</v>
       </c>
       <c r="Q232" t="n">
-        <v>112</v>
+        <v>112.8</v>
       </c>
       <c r="R232" t="n">
         <v>2541.7</v>
       </c>
       <c r="S232" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T232" t="n">
-        <v>4536.1</v>
+        <v>4565</v>
       </c>
       <c r="U232" t="n">
-        <v>78.5</v>
+        <v>79</v>
       </c>
       <c r="V232" t="n">
         <v>4536.1</v>
       </c>
       <c r="W232" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X232" t="n">
-        <v>5742.1</v>
+        <v>5721.2</v>
       </c>
       <c r="Y232" t="n">
-        <v>26.6</v>
+        <v>25.3</v>
       </c>
       <c r="Z232" t="n">
         <v>5742.1</v>
       </c>
       <c r="AA232" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AB232" t="n">
-        <v>79400</v>
+        <v>80500</v>
       </c>
       <c r="AC232" t="n">
         <v>76700</v>
       </c>
       <c r="AD232" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233">
@@ -22009,13 +22009,13 @@
         <v>-118.8</v>
       </c>
       <c r="AB233" t="n">
-        <v>5940</v>
+        <v>5960</v>
       </c>
       <c r="AC233" t="n">
         <v>5770</v>
       </c>
       <c r="AD233" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="234">
@@ -22083,13 +22083,13 @@
         <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>352500</v>
+        <v>355500</v>
       </c>
       <c r="AC234" t="n">
         <v>431500</v>
       </c>
       <c r="AD234" t="n">
-        <v>-18.3</v>
+        <v>-17.6</v>
       </c>
     </row>
     <row r="235">
@@ -22179,13 +22179,13 @@
         <v>-1.9</v>
       </c>
       <c r="AB235" t="n">
-        <v>326000</v>
+        <v>326500</v>
       </c>
       <c r="AC235" t="n">
         <v>369000</v>
       </c>
       <c r="AD235" t="n">
-        <v>-11.7</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="236">
@@ -22215,25 +22215,25 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>861.7</v>
+        <v>864.6</v>
       </c>
       <c r="G236" t="n">
-        <v>33.2</v>
+        <v>33.6</v>
       </c>
       <c r="H236" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="I236" t="n">
         <v>866</v>
       </c>
       <c r="J236" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="K236" t="n">
-        <v>276.1</v>
+        <v>280.4</v>
       </c>
       <c r="L236" t="n">
-        <v>-68</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -22241,43 +22241,43 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>2142.7</v>
+        <v>2149.1</v>
       </c>
       <c r="Q236" t="n">
-        <v>95.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="R236" t="n">
         <v>2145.4</v>
       </c>
       <c r="S236" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="T236" t="n">
-        <v>2405.1</v>
+        <v>2409.4</v>
       </c>
       <c r="U236" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="V236" t="n">
         <v>2407.9</v>
       </c>
       <c r="W236" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="X236" t="n">
-        <v>2654.5</v>
+        <v>2667.2</v>
       </c>
       <c r="Y236" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="Z236" t="n">
         <v>2657.1</v>
       </c>
       <c r="AA236" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AB236" t="n">
-        <v>121100</v>
+        <v>121200</v>
       </c>
       <c r="AC236" t="n">
         <v>121400</v>
@@ -22373,13 +22373,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB237" t="n">
-        <v>135700</v>
+        <v>136000</v>
       </c>
       <c r="AC237" t="n">
         <v>125600</v>
       </c>
       <c r="AD237" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -22545,7 +22545,7 @@
         <v>36.6</v>
       </c>
       <c r="AB239" t="n">
-        <v>71000</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="240">
@@ -22635,13 +22635,13 @@
         <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>21400</v>
+        <v>21250</v>
       </c>
       <c r="AC240" t="n">
         <v>21850</v>
       </c>
       <c r="AD240" t="n">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="241">
@@ -22731,13 +22731,13 @@
         <v>0</v>
       </c>
       <c r="AB241" t="n">
-        <v>271500</v>
+        <v>270500</v>
       </c>
       <c r="AC241" t="n">
         <v>277000</v>
       </c>
       <c r="AD241" t="n">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="242">
@@ -22827,13 +22827,13 @@
         <v>-0.7</v>
       </c>
       <c r="AB242" t="n">
-        <v>1940000</v>
+        <v>1944000</v>
       </c>
       <c r="AC242" t="n">
         <v>2514000</v>
       </c>
       <c r="AD242" t="n">
-        <v>-22.8</v>
+        <v>-22.7</v>
       </c>
     </row>
     <row r="243">
@@ -22923,13 +22923,13 @@
         <v>0</v>
       </c>
       <c r="AB243" t="n">
-        <v>153900</v>
+        <v>152400</v>
       </c>
       <c r="AC243" t="n">
         <v>162100</v>
       </c>
       <c r="AD243" t="n">
-        <v>-5.1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="244">
@@ -23019,13 +23019,13 @@
         <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>16980</v>
+        <v>16950</v>
       </c>
       <c r="AC244" t="n">
         <v>16150</v>
       </c>
       <c r="AD244" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245">
@@ -23097,13 +23097,13 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>36200</v>
+        <v>36100</v>
       </c>
       <c r="AC245" t="n">
         <v>36850</v>
       </c>
       <c r="AD245" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="246">
@@ -23195,13 +23195,13 @@
         <v>-0.8</v>
       </c>
       <c r="AB246" t="n">
-        <v>138600</v>
+        <v>138100</v>
       </c>
       <c r="AC246" t="n">
         <v>143100</v>
       </c>
       <c r="AD246" t="n">
-        <v>-3.1</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="247">
@@ -23291,13 +23291,13 @@
         <v>0.2</v>
       </c>
       <c r="AB247" t="n">
-        <v>324500</v>
+        <v>329000</v>
       </c>
       <c r="AC247" t="n">
         <v>363000</v>
       </c>
       <c r="AD247" t="n">
-        <v>-10.6</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="248">
@@ -23387,13 +23387,13 @@
         <v>-0.5</v>
       </c>
       <c r="AB248" t="n">
-        <v>31500</v>
+        <v>31600</v>
       </c>
       <c r="AC248" t="n">
         <v>32400</v>
       </c>
       <c r="AD248" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="249">
@@ -23485,13 +23485,13 @@
         <v>0</v>
       </c>
       <c r="AB249" t="n">
-        <v>8170</v>
+        <v>8140</v>
       </c>
       <c r="AC249" t="n">
         <v>9880</v>
       </c>
       <c r="AD249" t="n">
-        <v>-17.3</v>
+        <v>-17.6</v>
       </c>
     </row>
     <row r="250">
@@ -23581,13 +23581,13 @@
         <v>2.1</v>
       </c>
       <c r="AB250" t="n">
-        <v>129900</v>
+        <v>129400</v>
       </c>
       <c r="AC250" t="n">
         <v>145100</v>
       </c>
       <c r="AD250" t="n">
-        <v>-10.5</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="251">
@@ -23677,13 +23677,13 @@
         <v>-0.1</v>
       </c>
       <c r="AB251" t="n">
-        <v>20300</v>
+        <v>20350</v>
       </c>
       <c r="AC251" t="n">
         <v>19520</v>
       </c>
       <c r="AD251" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="252">
@@ -23869,13 +23869,13 @@
         <v>-0.7</v>
       </c>
       <c r="AB253" t="n">
-        <v>352000</v>
+        <v>351500</v>
       </c>
       <c r="AC253" t="n">
         <v>384500</v>
       </c>
       <c r="AD253" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="254">
@@ -23905,10 +23905,10 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1642.4</v>
+        <v>1641</v>
       </c>
       <c r="G254" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23922,58 +23922,58 @@
         <v>-0.5</v>
       </c>
       <c r="K254" t="n">
-        <v>1432.6</v>
+        <v>1432.1</v>
       </c>
       <c r="L254" t="n">
-        <v>-12.8</v>
+        <v>-12.7</v>
       </c>
       <c r="M254" t="n">
-        <v>3508.6</v>
+        <v>3507.3</v>
       </c>
       <c r="P254" t="n">
-        <v>2826.4</v>
+        <v>2824.5</v>
       </c>
       <c r="Q254" t="n">
-        <v>473.1</v>
+        <v>472.7</v>
       </c>
       <c r="R254" t="n">
         <v>2840.9</v>
       </c>
       <c r="S254" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="T254" t="n">
-        <v>4834</v>
+        <v>4832.1</v>
       </c>
       <c r="U254" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="V254" t="n">
         <v>4860</v>
       </c>
       <c r="W254" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="X254" t="n">
-        <v>5342.6</v>
+        <v>5354.7</v>
       </c>
       <c r="Y254" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="Z254" t="n">
         <v>5358.4</v>
       </c>
       <c r="AA254" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AB254" t="n">
-        <v>177000</v>
+        <v>177500</v>
       </c>
       <c r="AC254" t="n">
         <v>164000</v>
       </c>
       <c r="AD254" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="255">
@@ -24063,13 +24063,13 @@
         <v>0.1</v>
       </c>
       <c r="AB255" t="n">
-        <v>130800</v>
+        <v>128300</v>
       </c>
       <c r="AC255" t="n">
         <v>157600</v>
       </c>
       <c r="AD255" t="n">
-        <v>-17</v>
+        <v>-18.6</v>
       </c>
     </row>
     <row r="256">
@@ -24159,13 +24159,13 @@
         <v>-2.1</v>
       </c>
       <c r="AB256" t="n">
-        <v>339500</v>
+        <v>335000</v>
       </c>
       <c r="AC256" t="n">
         <v>413000</v>
       </c>
       <c r="AD256" t="n">
-        <v>-17.8</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="257">
@@ -24269,13 +24269,13 @@
         <v>0</v>
       </c>
       <c r="AB257" t="n">
-        <v>17460</v>
+        <v>17480</v>
       </c>
       <c r="AC257" t="n">
         <v>18420</v>
       </c>
       <c r="AD257" t="n">
-        <v>-5.2</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="258">
@@ -24367,13 +24367,13 @@
         <v>2.2</v>
       </c>
       <c r="AB258" t="n">
-        <v>402500</v>
+        <v>403500</v>
       </c>
       <c r="AC258" t="n">
         <v>403000</v>
       </c>
       <c r="AD258" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="259">
@@ -24403,43 +24403,43 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>1169.2</v>
+        <v>1144.8</v>
       </c>
       <c r="G259" t="n">
-        <v>-26.7</v>
+        <v>-28.2</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="I259" t="n">
         <v>1208</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.2</v>
+        <v>-5.2</v>
       </c>
       <c r="K259" t="n">
-        <v>1279.7</v>
+        <v>1263.6</v>
       </c>
       <c r="L259" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="M259" t="n">
-        <v>103.1</v>
+        <v>100.5</v>
       </c>
       <c r="P259" t="n">
-        <v>5584.8</v>
+        <v>5559.9</v>
       </c>
       <c r="Q259" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
       <c r="R259" t="n">
         <v>5643.7</v>
       </c>
       <c r="S259" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="T259" t="n">
-        <v>5765.2</v>
+        <v>5738.1</v>
       </c>
       <c r="U259" t="n">
         <v>3.2</v>
@@ -24448,28 +24448,28 @@
         <v>5742.8</v>
       </c>
       <c r="W259" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="X259" t="n">
-        <v>6533.2</v>
+        <v>6528.6</v>
       </c>
       <c r="Y259" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="Z259" t="n">
         <v>6468.1</v>
       </c>
       <c r="AA259" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB259" t="n">
-        <v>59700</v>
+        <v>59900</v>
       </c>
       <c r="AC259" t="n">
         <v>68000</v>
       </c>
       <c r="AD259" t="n">
-        <v>-12.2</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="260">
@@ -24559,13 +24559,13 @@
         <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>20150</v>
+        <v>20400</v>
       </c>
       <c r="AC260" t="n">
         <v>19480</v>
       </c>
       <c r="AD260" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="261">
@@ -24655,13 +24655,13 @@
         <v>-0.9</v>
       </c>
       <c r="AB261" t="n">
-        <v>35700</v>
+        <v>35750</v>
       </c>
       <c r="AC261" t="n">
         <v>38100</v>
       </c>
       <c r="AD261" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="262">
@@ -24751,13 +24751,13 @@
         <v>-1.3</v>
       </c>
       <c r="AB262" t="n">
-        <v>72800</v>
+        <v>72600</v>
       </c>
       <c r="AC262" t="n">
         <v>72900</v>
       </c>
       <c r="AD262" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="263">
@@ -24806,13 +24806,13 @@
         <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>32600</v>
+        <v>33000</v>
       </c>
       <c r="AC263" t="n">
         <v>41250</v>
       </c>
       <c r="AD263" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="264">
@@ -24861,13 +24861,13 @@
         <v>0</v>
       </c>
       <c r="AB264" t="n">
-        <v>26500</v>
+        <v>26350</v>
       </c>
       <c r="AC264" t="n">
         <v>29700</v>
       </c>
       <c r="AD264" t="n">
-        <v>-10.8</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="265">
@@ -24957,13 +24957,13 @@
         <v>-11.4</v>
       </c>
       <c r="AB265" t="n">
-        <v>784000</v>
+        <v>782000</v>
       </c>
       <c r="AC265" t="n">
         <v>1059000</v>
       </c>
       <c r="AD265" t="n">
-        <v>-26</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="266">
@@ -25008,13 +25008,13 @@
         <v>0</v>
       </c>
       <c r="AB266" t="n">
-        <v>54000</v>
+        <v>53900</v>
       </c>
       <c r="AC266" t="n">
         <v>64000</v>
       </c>
       <c r="AD266" t="n">
-        <v>-15.6</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="267">
@@ -25104,13 +25104,13 @@
         <v>0</v>
       </c>
       <c r="AB267" t="n">
-        <v>118100</v>
+        <v>117300</v>
       </c>
       <c r="AC267" t="n">
         <v>137500</v>
       </c>
       <c r="AD267" t="n">
-        <v>-14.1</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="268">
@@ -25200,13 +25200,13 @@
         <v>0.7</v>
       </c>
       <c r="AB268" t="n">
-        <v>40700</v>
+        <v>40900</v>
       </c>
       <c r="AC268" t="n">
         <v>44800</v>
       </c>
       <c r="AD268" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="269">
@@ -25236,10 +25236,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G269" t="n">
-        <v>108</v>
+        <v>107.4</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -25250,16 +25250,16 @@
         <v>337</v>
       </c>
       <c r="J269" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AB269" t="n">
-        <v>57500</v>
+        <v>57300</v>
       </c>
       <c r="AC269" t="n">
         <v>83000</v>
       </c>
       <c r="AD269" t="n">
-        <v>-30.7</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="270">
@@ -25447,13 +25447,13 @@
         <v>-3.4</v>
       </c>
       <c r="AB271" t="n">
-        <v>66000</v>
+        <v>65900</v>
       </c>
       <c r="AC271" t="n">
         <v>71100</v>
       </c>
       <c r="AD271" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="272">
@@ -25500,13 +25500,13 @@
         <v>0</v>
       </c>
       <c r="AB272" t="n">
-        <v>86800</v>
+        <v>86900</v>
       </c>
       <c r="AC272" t="n">
         <v>80500</v>
       </c>
       <c r="AD272" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273">
@@ -25596,13 +25596,13 @@
         <v>6.7</v>
       </c>
       <c r="AB273" t="n">
-        <v>9700</v>
+        <v>9740</v>
       </c>
       <c r="AC273" t="n">
         <v>9380</v>
       </c>
       <c r="AD273" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="274">
@@ -25692,13 +25692,13 @@
         <v>-2.6</v>
       </c>
       <c r="AB274" t="n">
-        <v>31500</v>
+        <v>31600</v>
       </c>
       <c r="AC274" t="n">
         <v>30550</v>
       </c>
       <c r="AD274" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="275">
@@ -25728,43 +25728,43 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>327.1</v>
+        <v>327.5</v>
       </c>
       <c r="G275" t="n">
-        <v>-30.8</v>
+        <v>-30.7</v>
       </c>
       <c r="H275" t="n">
-        <v>96.5</v>
+        <v>96.7</v>
       </c>
       <c r="I275" t="n">
         <v>325</v>
       </c>
       <c r="J275" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K275" t="n">
-        <v>412.1</v>
+        <v>409.9</v>
       </c>
       <c r="L275" t="n">
-        <v>26</v>
+        <v>25.2</v>
       </c>
       <c r="M275" t="n">
-        <v>61.4</v>
+        <v>60.5</v>
       </c>
       <c r="P275" t="n">
-        <v>1669.4</v>
+        <v>1667.7</v>
       </c>
       <c r="Q275" t="n">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R275" t="n">
         <v>1664.8</v>
       </c>
       <c r="S275" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="T275" t="n">
-        <v>2225.6</v>
+        <v>2222.8</v>
       </c>
       <c r="U275" t="n">
         <v>33.3</v>
@@ -25773,10 +25773,10 @@
         <v>2214.2</v>
       </c>
       <c r="W275" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="X275" t="n">
-        <v>2796.2</v>
+        <v>2792.2</v>
       </c>
       <c r="Y275" t="n">
         <v>25.6</v>
@@ -25785,16 +25785,16 @@
         <v>2773.1</v>
       </c>
       <c r="AA275" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AB275" t="n">
-        <v>173200</v>
+        <v>174000</v>
       </c>
       <c r="AC275" t="n">
         <v>173000</v>
       </c>
       <c r="AD275" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="276">
@@ -25839,13 +25839,13 @@
         <v>0</v>
       </c>
       <c r="AB276" t="n">
-        <v>17140</v>
+        <v>17110</v>
       </c>
       <c r="AC276" t="n">
         <v>18630</v>
       </c>
       <c r="AD276" t="n">
-        <v>-8</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -25990,13 +25990,13 @@
         <v>0</v>
       </c>
       <c r="AB278" t="n">
-        <v>44050</v>
+        <v>44200</v>
       </c>
       <c r="AC278" t="n">
         <v>37450</v>
       </c>
       <c r="AD278" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -465,7 +465,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-23 · 전주 2026-10-17</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-10-24 · 전주 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -1058,70 +1058,70 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1904</v>
+        <v>1928</v>
       </c>
       <c r="G7" t="n">
-        <v>-25.8</v>
+        <v>-24.8</v>
       </c>
       <c r="H7" t="n">
-        <v>74.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="I7" t="n">
         <v>1904</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
-        <v>1175</v>
+        <v>1330</v>
       </c>
       <c r="L7" t="n">
-        <v>-38.3</v>
+        <v>-31</v>
       </c>
       <c r="M7" t="n">
-        <v>897.5</v>
+        <v>1029</v>
       </c>
       <c r="N7" t="n">
         <v>1175</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="P7" t="n">
-        <v>6496</v>
+        <v>6952</v>
       </c>
       <c r="Q7" t="n">
-        <v>117.6</v>
+        <v>132.9</v>
       </c>
       <c r="R7" t="n">
         <v>6496</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>6105</v>
+        <v>5610</v>
       </c>
       <c r="U7" t="n">
-        <v>-6</v>
+        <v>-19.3</v>
       </c>
       <c r="V7" t="n">
         <v>6105</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-8.1</v>
       </c>
       <c r="X7" t="n">
-        <v>6170</v>
+        <v>5480</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>-2.3</v>
       </c>
       <c r="Z7" t="n">
         <v>6170</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-11.2</v>
       </c>
       <c r="AB7" t="n">
         <v>42150</v>
@@ -1670,70 +1670,70 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7627.1</v>
+        <v>7242.4</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="H13" t="n">
-        <v>14.9</v>
+        <v>9.1</v>
       </c>
       <c r="I13" t="n">
         <v>7769.4</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8</v>
+        <v>-6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>7450.9</v>
+        <v>7867</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.3</v>
+        <v>8.6</v>
       </c>
       <c r="M13" t="n">
-        <v>90.40000000000001</v>
+        <v>101.1</v>
       </c>
       <c r="N13" t="n">
         <v>7188.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="P13" t="n">
-        <v>32887.4</v>
+        <v>32937.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="R13" t="n">
         <v>32996.1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="T13" t="n">
-        <v>40481.2</v>
+        <v>39448.2</v>
       </c>
       <c r="U13" t="n">
-        <v>23.1</v>
+        <v>19.8</v>
       </c>
       <c r="V13" t="n">
         <v>39889.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>-1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>39144</v>
+        <v>38291.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>-3.3</v>
+        <v>-2.9</v>
       </c>
       <c r="Z13" t="n">
         <v>38638.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="AB13" t="n">
         <v>602000</v>
@@ -3135,25 +3135,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1852.8</v>
+        <v>1846.6</v>
       </c>
       <c r="G28" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H28" t="n">
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="I28" t="n">
         <v>1868.1</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="K28" t="n">
         <v>1889.8</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
         <v>35.8</v>
@@ -3165,40 +3165,40 @@
         <v>-0.1</v>
       </c>
       <c r="P28" t="n">
-        <v>7275.4</v>
+        <v>7269.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="R28" t="n">
         <v>7293.4</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="T28" t="n">
-        <v>8922.6</v>
+        <v>8941.799999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="V28" t="n">
         <v>8941.799999999999</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>10608.5</v>
+        <v>10639.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="n">
         <v>10594.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="AB28" t="n">
         <v>1225000</v>
@@ -3855,64 +3855,64 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>614.2</v>
+        <v>611.7</v>
       </c>
       <c r="G35" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="H35" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="I35" t="n">
         <v>622.4</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="K35" t="n">
-        <v>439.8</v>
+        <v>435.7</v>
       </c>
       <c r="L35" t="n">
-        <v>-28.4</v>
+        <v>-28.8</v>
       </c>
       <c r="M35" t="n">
-        <v>31.9</v>
+        <v>30.6</v>
       </c>
       <c r="N35" t="n">
         <v>439.9</v>
       </c>
       <c r="O35" t="n">
-        <v>-0</v>
+        <v>-1</v>
       </c>
       <c r="P35" t="n">
-        <v>2321.2</v>
+        <v>2314.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="R35" t="n">
         <v>2329.5</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2477.2</v>
+        <v>2474.2</v>
       </c>
       <c r="U35" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="V35" t="n">
         <v>2484</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="X35" t="n">
         <v>2636.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z35" t="n">
         <v>2648</v>
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>834.5</v>
+        <v>828</v>
       </c>
       <c r="G37" t="n">
-        <v>49.4</v>
+        <v>48.3</v>
       </c>
       <c r="H37" t="n">
-        <v>-9.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>841.2</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8</v>
+        <v>-1.6</v>
       </c>
       <c r="K37" t="n">
-        <v>91.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-89</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -4092,37 +4092,37 @@
         <v>92.8</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.3</v>
+        <v>-2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>1968.9</v>
+        <v>1961</v>
       </c>
       <c r="Q37" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="R37" t="n">
         <v>1976.6</v>
       </c>
       <c r="S37" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2212.4</v>
+        <v>2203</v>
       </c>
       <c r="U37" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="V37" t="n">
         <v>2222.8</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="X37" t="n">
         <v>2381.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="Z37" t="n">
         <v>2388.1</v>
@@ -4221,16 +4221,16 @@
         <v>-0.7</v>
       </c>
       <c r="X38" t="n">
-        <v>125630.7</v>
+        <v>125691.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z38" t="n">
         <v>127535</v>
       </c>
       <c r="AA38" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AB38" t="n">
         <v>293000</v>
@@ -4677,25 +4677,25 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5109.6</v>
+        <v>5092.6</v>
       </c>
       <c r="G43" t="n">
-        <v>-25</v>
+        <v>-25.2</v>
       </c>
       <c r="H43" t="n">
-        <v>30.6</v>
+        <v>30.1</v>
       </c>
       <c r="I43" t="n">
         <v>5184.6</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="K43" t="n">
         <v>4370.3</v>
       </c>
       <c r="L43" t="n">
-        <v>-14.5</v>
+        <v>-14.2</v>
       </c>
       <c r="M43" t="n">
         <v>4.5</v>
@@ -6173,13 +6173,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6453.9</v>
+        <v>6453.3</v>
       </c>
       <c r="G58" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="H58" t="n">
-        <v>148</v>
+        <v>147.9</v>
       </c>
       <c r="I58" t="n">
         <v>6422.7</v>
@@ -6188,55 +6188,55 @@
         <v>0.5</v>
       </c>
       <c r="K58" t="n">
-        <v>6974.6</v>
+        <v>7023.4</v>
       </c>
       <c r="L58" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>191.2</v>
+        <v>193.3</v>
       </c>
       <c r="N58" t="n">
         <v>6829.6</v>
       </c>
       <c r="O58" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="P58" t="n">
-        <v>20637.5</v>
+        <v>20685.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>126</v>
+        <v>126.5</v>
       </c>
       <c r="R58" t="n">
         <v>20461.4</v>
       </c>
       <c r="S58" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="T58" t="n">
-        <v>41087.1</v>
+        <v>41627.4</v>
       </c>
       <c r="U58" t="n">
-        <v>99.09999999999999</v>
+        <v>101.2</v>
       </c>
       <c r="V58" t="n">
         <v>40214.8</v>
       </c>
       <c r="W58" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="X58" t="n">
-        <v>64033.9</v>
+        <v>64992.1</v>
       </c>
       <c r="Y58" t="n">
-        <v>55.8</v>
+        <v>56.1</v>
       </c>
       <c r="Z58" t="n">
         <v>62301</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="AB58" t="n">
         <v>1111000</v>
@@ -6708,55 +6708,55 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>2410.4</v>
+        <v>2414.5</v>
       </c>
       <c r="L63" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="M63" t="n">
-        <v>85.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N63" t="n">
         <v>2208.8</v>
       </c>
       <c r="O63" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P63" t="n">
-        <v>7668.6</v>
+        <v>7693.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>79.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R63" t="n">
         <v>7217</v>
       </c>
       <c r="S63" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="T63" t="n">
-        <v>11238.2</v>
+        <v>11248.2</v>
       </c>
       <c r="U63" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
       <c r="V63" t="n">
         <v>10444.5</v>
       </c>
       <c r="W63" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X63" t="n">
-        <v>14699.9</v>
+        <v>14718.4</v>
       </c>
       <c r="Y63" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="Z63" t="n">
         <v>13854.9</v>
       </c>
       <c r="AA63" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="AB63" t="n">
         <v>154600</v>
@@ -7258,70 +7258,70 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2028.9</v>
+        <v>1972.8</v>
       </c>
       <c r="G69" t="n">
-        <v>-17.4</v>
+        <v>-19.7</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4</v>
+        <v>-3.2</v>
       </c>
       <c r="I69" t="n">
         <v>2028.9</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="K69" t="n">
-        <v>3867.2</v>
+        <v>3825.4</v>
       </c>
       <c r="L69" t="n">
-        <v>90.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="N69" t="n">
         <v>3867.2</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="P69" t="n">
-        <v>11250.8</v>
+        <v>11155.8</v>
       </c>
       <c r="Q69" t="n">
-        <v>69.2</v>
+        <v>67.8</v>
       </c>
       <c r="R69" t="n">
         <v>11250.8</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="T69" t="n">
-        <v>13798.7</v>
+        <v>13706.8</v>
       </c>
       <c r="U69" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="V69" t="n">
         <v>13798.7</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="X69" t="n">
-        <v>16417.9</v>
+        <v>16345.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="Z69" t="n">
         <v>16417.9</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AB69" t="n">
         <v>376000</v>
@@ -7474,70 +7474,70 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>7792.3</v>
+        <v>7975.3</v>
       </c>
       <c r="G71" t="n">
-        <v>120</v>
+        <v>125.2</v>
       </c>
       <c r="H71" t="n">
-        <v>162.5</v>
+        <v>168.7</v>
       </c>
       <c r="I71" t="n">
         <v>7442.9</v>
       </c>
       <c r="J71" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="K71" t="n">
-        <v>5997.8</v>
+        <v>6091.3</v>
       </c>
       <c r="L71" t="n">
-        <v>-23</v>
+        <v>-23.6</v>
       </c>
       <c r="M71" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N71" t="n">
         <v>5493.4</v>
       </c>
       <c r="O71" t="n">
-        <v>9.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="P71" t="n">
-        <v>20059.7</v>
+        <v>20301.2</v>
       </c>
       <c r="Q71" t="n">
-        <v>37.3</v>
+        <v>38.9</v>
       </c>
       <c r="R71" t="n">
         <v>19208.9</v>
       </c>
       <c r="S71" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="T71" t="n">
-        <v>13318.2</v>
+        <v>13306.5</v>
       </c>
       <c r="U71" t="n">
-        <v>-33.6</v>
+        <v>-34.5</v>
       </c>
       <c r="V71" t="n">
         <v>12894.5</v>
       </c>
       <c r="W71" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="X71" t="n">
-        <v>9981.9</v>
+        <v>9830.9</v>
       </c>
       <c r="Y71" t="n">
-        <v>-25.1</v>
+        <v>-26.1</v>
       </c>
       <c r="Z71" t="n">
         <v>9921</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="AB71" t="n">
         <v>22500</v>
@@ -8507,34 +8507,34 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G81" t="n">
-        <v>41.9</v>
+        <v>23.9</v>
       </c>
       <c r="H81" t="n">
-        <v>21.1</v>
+        <v>5.7</v>
       </c>
       <c r="I81" t="n">
         <v>142</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="K81" t="n">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="L81" t="n">
-        <v>14.8</v>
+        <v>17.7</v>
       </c>
       <c r="M81" t="n">
-        <v>87.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N81" t="n">
         <v>163</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>-10.4</v>
       </c>
       <c r="P81" t="n">
         <v>488</v>
@@ -8609,70 +8609,70 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>513.5</v>
+        <v>507</v>
       </c>
       <c r="G82" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="H82" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="I82" t="n">
         <v>513.5</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="K82" t="n">
-        <v>331</v>
+        <v>329.5</v>
       </c>
       <c r="L82" t="n">
-        <v>-35.5</v>
+        <v>-35</v>
       </c>
       <c r="M82" t="n">
-        <v>96.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="N82" t="n">
         <v>331</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="P82" t="n">
-        <v>1789.3</v>
+        <v>1781.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="R82" t="n">
         <v>1789.3</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="T82" t="n">
-        <v>2256.7</v>
+        <v>2248.2</v>
       </c>
       <c r="U82" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="V82" t="n">
         <v>2256.7</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="X82" t="n">
-        <v>2968.2</v>
+        <v>2848.5</v>
       </c>
       <c r="Y82" t="n">
-        <v>31.5</v>
+        <v>26.7</v>
       </c>
       <c r="Z82" t="n">
         <v>2968.2</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AB82" t="n">
         <v>210500</v>
@@ -9047,19 +9047,19 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>19580.1</v>
+        <v>19568.9</v>
       </c>
       <c r="Q86" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="R86" t="n">
         <v>19580.1</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="T86" t="n">
-        <v>20854.6</v>
+        <v>20845.9</v>
       </c>
       <c r="U86" t="n">
         <v>6.5</v>
@@ -9068,19 +9068,19 @@
         <v>20854.6</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="X86" t="n">
-        <v>22206.7</v>
+        <v>22188.2</v>
       </c>
       <c r="Y86" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z86" t="n">
         <v>22206.7</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AB86" t="n">
         <v>74200</v>
@@ -9323,70 +9323,70 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1113.4</v>
+        <v>1107.7</v>
       </c>
       <c r="G89" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H89" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="I89" t="n">
         <v>1108.9</v>
       </c>
       <c r="J89" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="K89" t="n">
-        <v>1185.7</v>
+        <v>1192.3</v>
       </c>
       <c r="L89" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="M89" t="n">
-        <v>32.2</v>
+        <v>32.9</v>
       </c>
       <c r="N89" t="n">
         <v>1184.7</v>
       </c>
       <c r="O89" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="P89" t="n">
-        <v>4324</v>
+        <v>4307.8</v>
       </c>
       <c r="Q89" t="n">
-        <v>59.9</v>
+        <v>59.3</v>
       </c>
       <c r="R89" t="n">
         <v>4318.2</v>
       </c>
       <c r="S89" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="T89" t="n">
-        <v>4984.4</v>
+        <v>4936.2</v>
       </c>
       <c r="U89" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="V89" t="n">
         <v>4982.1</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="X89" t="n">
-        <v>5543.8</v>
+        <v>5509.4</v>
       </c>
       <c r="Y89" t="n">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="Z89" t="n">
         <v>5541.6</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AB89" t="n">
         <v>3690</v>
@@ -9578,34 +9578,34 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="G92" t="n">
-        <v>16.5</v>
+        <v>63.7</v>
       </c>
       <c r="H92" t="n">
-        <v>-27.4</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
         <v>84</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="K92" t="n">
-        <v>165.5</v>
+        <v>141</v>
       </c>
       <c r="L92" t="n">
-        <v>97</v>
+        <v>19.5</v>
       </c>
       <c r="M92" t="n">
-        <v>36.7</v>
+        <v>16.4</v>
       </c>
       <c r="N92" t="n">
         <v>165.5</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>-14.8</v>
       </c>
       <c r="P92" t="n">
         <v>452.5</v>
@@ -9899,55 +9899,55 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>2786</v>
+        <v>4172.8</v>
       </c>
       <c r="L95" t="n">
-        <v>11.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="M95" t="n">
-        <v>0.4</v>
+        <v>50.4</v>
       </c>
       <c r="N95" t="n">
         <v>2763.3</v>
       </c>
       <c r="O95" t="n">
-        <v>0.8</v>
+        <v>51</v>
       </c>
       <c r="P95" t="n">
-        <v>9893.1</v>
+        <v>13535.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>24.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="R95" t="n">
         <v>9818.9</v>
       </c>
       <c r="S95" t="n">
-        <v>0.8</v>
+        <v>37.9</v>
       </c>
       <c r="T95" t="n">
-        <v>12058.4</v>
+        <v>14373.8</v>
       </c>
       <c r="U95" t="n">
-        <v>21.9</v>
+        <v>6.2</v>
       </c>
       <c r="V95" t="n">
         <v>11945.8</v>
       </c>
       <c r="W95" t="n">
-        <v>0.9</v>
+        <v>20.3</v>
       </c>
       <c r="X95" t="n">
-        <v>13525.4</v>
+        <v>15696.5</v>
       </c>
       <c r="Y95" t="n">
-        <v>12.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z95" t="n">
         <v>13290.1</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="AB95" t="n">
         <v>59100</v>
@@ -9986,37 +9986,37 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>9945.799999999999</v>
+        <v>10033.4</v>
       </c>
       <c r="G96" t="n">
-        <v>-3.6</v>
+        <v>-2.8</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
         <v>9943.1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K96" t="n">
-        <v>10556.6</v>
+        <v>10375.6</v>
       </c>
       <c r="L96" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="M96" t="n">
-        <v>28.4</v>
+        <v>26.2</v>
       </c>
       <c r="N96" t="n">
         <v>10529.9</v>
       </c>
       <c r="O96" t="n">
-        <v>0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="P96" t="n">
-        <v>37919.8</v>
+        <v>37936.5</v>
       </c>
       <c r="Q96" t="n">
         <v>15.2</v>
@@ -10028,28 +10028,28 @@
         <v>0.1</v>
       </c>
       <c r="T96" t="n">
-        <v>43987.6</v>
+        <v>44061.4</v>
       </c>
       <c r="U96" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="V96" t="n">
         <v>44032.6</v>
       </c>
       <c r="W96" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="X96" t="n">
-        <v>47719.1</v>
+        <v>47656.2</v>
       </c>
       <c r="Y96" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z96" t="n">
         <v>47685.8</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AB96" t="n">
         <v>286000</v>
@@ -10088,13 +10088,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1900.4</v>
+        <v>1899.6</v>
       </c>
       <c r="G97" t="n">
         <v>-1.9</v>
       </c>
       <c r="H97" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="I97" t="n">
         <v>1879.6</v>
@@ -10103,22 +10103,22 @@
         <v>1.1</v>
       </c>
       <c r="K97" t="n">
-        <v>1753.8</v>
+        <v>1755.2</v>
       </c>
       <c r="L97" t="n">
-        <v>-7.7</v>
+        <v>-7.6</v>
       </c>
       <c r="M97" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="N97" t="n">
         <v>1721.6</v>
       </c>
       <c r="O97" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="P97" t="n">
-        <v>6999.5</v>
+        <v>7000.2</v>
       </c>
       <c r="Q97" t="n">
         <v>42.3</v>
@@ -10130,28 +10130,28 @@
         <v>0.8</v>
       </c>
       <c r="T97" t="n">
-        <v>7302</v>
+        <v>7320.6</v>
       </c>
       <c r="U97" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="V97" t="n">
         <v>7183.4</v>
       </c>
       <c r="W97" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="X97" t="n">
-        <v>7379.1</v>
+        <v>7419.9</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="Z97" t="n">
         <v>7259.9</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AB97" t="n">
         <v>6190</v>
@@ -10598,19 +10598,19 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="G102" t="n">
-        <v>-11.2</v>
+        <v>-14.1</v>
       </c>
       <c r="H102" t="n">
-        <v>-13</v>
+        <v>-15.8</v>
       </c>
       <c r="I102" t="n">
         <v>494</v>
       </c>
       <c r="J102" t="n">
-        <v>-6.7</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AB102" t="n">
         <v>10660</v>
@@ -10691,19 +10691,19 @@
         <v>-0.1</v>
       </c>
       <c r="T103" t="n">
-        <v>12248</v>
+        <v>12236.9</v>
       </c>
       <c r="U103" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="V103" t="n">
         <v>12320.2</v>
       </c>
       <c r="W103" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="X103" t="n">
-        <v>13178.1</v>
+        <v>13167</v>
       </c>
       <c r="Y103" t="n">
         <v>7.6</v>
@@ -10712,7 +10712,7 @@
         <v>13250.9</v>
       </c>
       <c r="AA103" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AB103" t="n">
         <v>14200</v>
@@ -10955,25 +10955,25 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>5063.1</v>
+        <v>5077.8</v>
       </c>
       <c r="G106" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="H106" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I106" t="n">
         <v>4994.6</v>
       </c>
       <c r="J106" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="K106" t="n">
-        <v>2487.9</v>
+        <v>2486.7</v>
       </c>
       <c r="L106" t="n">
-        <v>-50.9</v>
+        <v>-51</v>
       </c>
       <c r="M106" t="n">
         <v>2.4</v>
@@ -10985,22 +10985,22 @@
         <v>-2.2</v>
       </c>
       <c r="P106" t="n">
-        <v>15340.1</v>
+        <v>15353.6</v>
       </c>
       <c r="Q106" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="R106" t="n">
         <v>15327.6</v>
       </c>
       <c r="S106" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="T106" t="n">
-        <v>16490.3</v>
+        <v>16485.1</v>
       </c>
       <c r="U106" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="V106" t="n">
         <v>16550</v>
@@ -11012,7 +11012,7 @@
         <v>17402.8</v>
       </c>
       <c r="Y106" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z106" t="n">
         <v>17515.4</v>
@@ -11176,55 +11176,55 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>3110.1</v>
+        <v>2967.7</v>
       </c>
       <c r="L108" t="n">
-        <v>15</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M108" t="n">
-        <v>84.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N108" t="n">
         <v>3181.6</v>
       </c>
       <c r="O108" t="n">
-        <v>-2.2</v>
+        <v>-6.7</v>
       </c>
       <c r="P108" t="n">
-        <v>6093.7</v>
+        <v>5808.8</v>
       </c>
       <c r="Q108" t="n">
-        <v>17.9</v>
+        <v>12.4</v>
       </c>
       <c r="R108" t="n">
         <v>6280.9</v>
       </c>
       <c r="S108" t="n">
-        <v>-3</v>
+        <v>-7.5</v>
       </c>
       <c r="T108" t="n">
-        <v>9957.4</v>
+        <v>9510</v>
       </c>
       <c r="U108" t="n">
-        <v>63.4</v>
+        <v>63.7</v>
       </c>
       <c r="V108" t="n">
         <v>10410.3</v>
       </c>
       <c r="W108" t="n">
-        <v>-4.4</v>
+        <v>-8.6</v>
       </c>
       <c r="X108" t="n">
-        <v>12623.9</v>
+        <v>12667.3</v>
       </c>
       <c r="Y108" t="n">
-        <v>26.8</v>
+        <v>33.2</v>
       </c>
       <c r="Z108" t="n">
         <v>13102.4</v>
       </c>
       <c r="AA108" t="n">
-        <v>-3.7</v>
+        <v>-3.3</v>
       </c>
       <c r="AB108" t="n">
         <v>7100</v>
@@ -11263,70 +11263,70 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>531.8</v>
+        <v>540.4</v>
       </c>
       <c r="G109" t="n">
-        <v>49.6</v>
+        <v>52</v>
       </c>
       <c r="H109" t="n">
-        <v>34.6</v>
+        <v>36.8</v>
       </c>
       <c r="I109" t="n">
         <v>523.4</v>
       </c>
       <c r="J109" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="K109" t="n">
-        <v>330.2</v>
+        <v>320.2</v>
       </c>
       <c r="L109" t="n">
-        <v>-37.9</v>
+        <v>-40.7</v>
       </c>
       <c r="M109" t="n">
-        <v>104.1</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="N109" t="n">
         <v>334.6</v>
       </c>
       <c r="O109" t="n">
-        <v>-1.3</v>
+        <v>-4.3</v>
       </c>
       <c r="P109" t="n">
-        <v>1656.6</v>
+        <v>1649.6</v>
       </c>
       <c r="Q109" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="R109" t="n">
         <v>1660.7</v>
       </c>
       <c r="S109" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="T109" t="n">
-        <v>2013.4</v>
+        <v>2011.3</v>
       </c>
       <c r="U109" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="V109" t="n">
         <v>2011.6</v>
       </c>
       <c r="W109" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="X109" t="n">
-        <v>2334</v>
+        <v>2314.7</v>
       </c>
       <c r="Y109" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="Z109" t="n">
         <v>2334</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="AB109" t="n">
         <v>9590</v>
@@ -11467,70 +11467,70 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>636.4</v>
+        <v>636.9</v>
       </c>
       <c r="G111" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="H111" t="n">
-        <v>-12.5</v>
+        <v>-12.4</v>
       </c>
       <c r="I111" t="n">
         <v>636.4</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K111" t="n">
-        <v>313.4</v>
+        <v>309.2</v>
       </c>
       <c r="L111" t="n">
-        <v>-50.8</v>
+        <v>-51.5</v>
       </c>
       <c r="M111" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N111" t="n">
         <v>313.4</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="P111" t="n">
-        <v>2115.2</v>
+        <v>2108</v>
       </c>
       <c r="Q111" t="n">
-        <v>-10.1</v>
+        <v>-10.4</v>
       </c>
       <c r="R111" t="n">
         <v>2115.2</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="T111" t="n">
-        <v>2048.5</v>
+        <v>2026.4</v>
       </c>
       <c r="U111" t="n">
-        <v>-3.2</v>
+        <v>-3.9</v>
       </c>
       <c r="V111" t="n">
         <v>2048.5</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="X111" t="n">
-        <v>2640.3</v>
+        <v>2576</v>
       </c>
       <c r="Y111" t="n">
-        <v>28.9</v>
+        <v>27.1</v>
       </c>
       <c r="Z111" t="n">
         <v>2640.3</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="AB111" t="n">
         <v>14170</v>
@@ -12714,70 +12714,70 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>382.7</v>
+        <v>380.3</v>
       </c>
       <c r="G124" t="n">
-        <v>-27.6</v>
+        <v>-28.1</v>
       </c>
       <c r="H124" t="n">
-        <v>-20.6</v>
+        <v>-21.1</v>
       </c>
       <c r="I124" t="n">
         <v>396.9</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.6</v>
+        <v>-4.2</v>
       </c>
       <c r="K124" t="n">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="L124" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="M124" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="N124" t="n">
         <v>558.1</v>
       </c>
       <c r="O124" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="P124" t="n">
-        <v>1838.9</v>
+        <v>1834.1</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R124" t="n">
         <v>1863.3</v>
       </c>
       <c r="S124" t="n">
-        <v>-1.3</v>
+        <v>-1.6</v>
       </c>
       <c r="T124" t="n">
-        <v>2159.2</v>
+        <v>2165.4</v>
       </c>
       <c r="U124" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="V124" t="n">
         <v>2155.7</v>
       </c>
       <c r="W124" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="X124" t="n">
-        <v>2385.9</v>
+        <v>2388.5</v>
       </c>
       <c r="Y124" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="Z124" t="n">
         <v>2405.8</v>
       </c>
       <c r="AA124" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AB124" t="n">
         <v>82500</v>
@@ -13742,40 +13742,40 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>20650.6</v>
+        <v>20523</v>
       </c>
       <c r="G134" t="n">
-        <v>-16.6</v>
+        <v>-17.1</v>
       </c>
       <c r="H134" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="I134" t="n">
         <v>20703</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="K134" t="n">
-        <v>11546.4</v>
+        <v>11517</v>
       </c>
       <c r="L134" t="n">
-        <v>-44.1</v>
+        <v>-43.9</v>
       </c>
       <c r="M134" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N134" t="n">
         <v>11584</v>
       </c>
       <c r="O134" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="P134" t="n">
-        <v>78789.8</v>
+        <v>78747.2</v>
       </c>
       <c r="Q134" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="R134" t="n">
         <v>78928.60000000001</v>
@@ -13784,28 +13784,28 @@
         <v>-0.2</v>
       </c>
       <c r="T134" t="n">
-        <v>82922.39999999999</v>
+        <v>82960.89999999999</v>
       </c>
       <c r="U134" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="V134" t="n">
         <v>82823.2</v>
       </c>
       <c r="W134" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="X134" t="n">
-        <v>87020.2</v>
+        <v>87303.10000000001</v>
       </c>
       <c r="Y134" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="Z134" t="n">
         <v>86770.8</v>
       </c>
       <c r="AA134" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="AB134" t="n">
         <v>88000</v>
@@ -14120,70 +14120,70 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>643.6</v>
+        <v>635.6</v>
       </c>
       <c r="G138" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="H138" t="n">
-        <v>51.2</v>
+        <v>49.3</v>
       </c>
       <c r="I138" t="n">
         <v>657.7</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.1</v>
+        <v>-3.4</v>
       </c>
       <c r="K138" t="n">
-        <v>704.7</v>
+        <v>709.7</v>
       </c>
       <c r="L138" t="n">
-        <v>9.5</v>
+        <v>11.7</v>
       </c>
       <c r="M138" t="n">
-        <v>34.6</v>
+        <v>35.5</v>
       </c>
       <c r="N138" t="n">
         <v>707.5</v>
       </c>
       <c r="O138" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="P138" t="n">
-        <v>2525.2</v>
+        <v>2522.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="R138" t="n">
         <v>2541.9</v>
       </c>
       <c r="S138" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="T138" t="n">
-        <v>3389</v>
+        <v>3402</v>
       </c>
       <c r="U138" t="n">
-        <v>34.2</v>
+        <v>34.9</v>
       </c>
       <c r="V138" t="n">
         <v>3404.3</v>
       </c>
       <c r="W138" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="X138" t="n">
-        <v>4410.4</v>
+        <v>4412.4</v>
       </c>
       <c r="Y138" t="n">
-        <v>30.1</v>
+        <v>29.7</v>
       </c>
       <c r="Z138" t="n">
         <v>4411.6</v>
       </c>
       <c r="AA138" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
         <v>162700</v>
@@ -15006,55 +15006,55 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>5862.8</v>
+        <v>5902</v>
       </c>
       <c r="L147" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="M147" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="N147" t="n">
         <v>5862.8</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P147" t="n">
-        <v>18617.5</v>
+        <v>18697.7</v>
       </c>
       <c r="Q147" t="n">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="R147" t="n">
         <v>18617.5</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="T147" t="n">
-        <v>22916.2</v>
+        <v>23047.7</v>
       </c>
       <c r="U147" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V147" t="n">
         <v>22916.2</v>
       </c>
       <c r="W147" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X147" t="n">
-        <v>25807.6</v>
+        <v>25964.3</v>
       </c>
       <c r="Y147" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="Z147" t="n">
         <v>25807.6</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AB147" t="n">
         <v>192600</v>
@@ -15924,19 +15924,19 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G157" t="n">
-        <v>11.9</v>
+        <v>5</v>
       </c>
       <c r="H157" t="n">
-        <v>606.2</v>
+        <v>562.5</v>
       </c>
       <c r="I157" t="n">
         <v>117</v>
       </c>
       <c r="J157" t="n">
-        <v>-3.4</v>
+        <v>-9.4</v>
       </c>
       <c r="AB157" t="n">
         <v>11140</v>
@@ -16799,25 +16799,25 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>896.8</v>
+        <v>480.8</v>
       </c>
       <c r="G167" t="n">
-        <v>-85.7</v>
+        <v>-92.3</v>
       </c>
       <c r="H167" t="n">
-        <v>-74.7</v>
+        <v>-86.5</v>
       </c>
       <c r="I167" t="n">
         <v>1615.2</v>
       </c>
       <c r="J167" t="n">
-        <v>-44.5</v>
+        <v>-70.2</v>
       </c>
       <c r="K167" t="n">
         <v>1161.2</v>
       </c>
       <c r="L167" t="n">
-        <v>29.5</v>
+        <v>141.5</v>
       </c>
       <c r="M167" t="n">
         <v>-35.6</v>
@@ -16829,40 +16829,40 @@
         <v>-8.1</v>
       </c>
       <c r="P167" t="n">
-        <v>9091.299999999999</v>
+        <v>8850.200000000001</v>
       </c>
       <c r="Q167" t="n">
-        <v>-20.8</v>
+        <v>-22.9</v>
       </c>
       <c r="R167" t="n">
         <v>9436.9</v>
       </c>
       <c r="S167" t="n">
-        <v>-3.7</v>
+        <v>-6.2</v>
       </c>
       <c r="T167" t="n">
-        <v>10057.6</v>
+        <v>10098.7</v>
       </c>
       <c r="U167" t="n">
-        <v>10.6</v>
+        <v>14.1</v>
       </c>
       <c r="V167" t="n">
         <v>10008.7</v>
       </c>
       <c r="W167" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="X167" t="n">
-        <v>10740</v>
+        <v>10821.1</v>
       </c>
       <c r="Y167" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z167" t="n">
         <v>10693.3</v>
       </c>
       <c r="AA167" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB167" t="n">
         <v>3985</v>
@@ -16901,70 +16901,70 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>918.4</v>
+        <v>918</v>
       </c>
       <c r="G168" t="n">
         <v>8.5</v>
       </c>
       <c r="H168" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I168" t="n">
         <v>924.1</v>
       </c>
       <c r="J168" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="K168" t="n">
-        <v>895</v>
+        <v>888.6</v>
       </c>
       <c r="L168" t="n">
-        <v>-2.5</v>
+        <v>-3.2</v>
       </c>
       <c r="M168" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="N168" t="n">
         <v>895.3</v>
       </c>
       <c r="O168" t="n">
-        <v>-0</v>
+        <v>-0.7</v>
       </c>
       <c r="P168" t="n">
-        <v>3496.6</v>
+        <v>3492.1</v>
       </c>
       <c r="Q168" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="R168" t="n">
         <v>3505.9</v>
       </c>
       <c r="S168" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="T168" t="n">
-        <v>3822.4</v>
+        <v>3799</v>
       </c>
       <c r="U168" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V168" t="n">
         <v>3833</v>
       </c>
       <c r="W168" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="X168" t="n">
-        <v>4171.8</v>
+        <v>4141.6</v>
       </c>
       <c r="Y168" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="Z168" t="n">
         <v>4151.2</v>
       </c>
       <c r="AA168" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="AB168" t="n">
         <v>50300</v>
@@ -18176,37 +18176,37 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>25452.2</v>
+        <v>25429.3</v>
       </c>
       <c r="G182" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="H182" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I182" t="n">
         <v>25528.5</v>
       </c>
       <c r="J182" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="K182" t="n">
-        <v>14423.3</v>
+        <v>14413.6</v>
       </c>
       <c r="L182" t="n">
         <v>-43.3</v>
       </c>
       <c r="M182" t="n">
-        <v>-17.9</v>
+        <v>-18</v>
       </c>
       <c r="N182" t="n">
         <v>14442.7</v>
       </c>
       <c r="O182" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="P182" t="n">
-        <v>94139.5</v>
+        <v>94107.7</v>
       </c>
       <c r="Q182" t="n">
         <v>10.5</v>
@@ -18215,10 +18215,10 @@
         <v>94352.39999999999</v>
       </c>
       <c r="S182" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="T182" t="n">
-        <v>95973</v>
+        <v>95857.3</v>
       </c>
       <c r="U182" t="n">
         <v>1.9</v>
@@ -18227,10 +18227,10 @@
         <v>96183.8</v>
       </c>
       <c r="W182" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="X182" t="n">
-        <v>99679.89999999999</v>
+        <v>99579.3</v>
       </c>
       <c r="Y182" t="n">
         <v>3.9</v>
@@ -18239,7 +18239,7 @@
         <v>99708.7</v>
       </c>
       <c r="AA182" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="AB182" t="n">
         <v>153000</v>
@@ -18384,70 +18384,70 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2072.9</v>
+        <v>2051.7</v>
       </c>
       <c r="G184" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="H184" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="I184" t="n">
         <v>2072.9</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K184" t="n">
-        <v>1240.1</v>
+        <v>1226.8</v>
       </c>
       <c r="L184" t="n">
         <v>-40.2</v>
       </c>
       <c r="M184" t="n">
-        <v>17.9</v>
+        <v>16.6</v>
       </c>
       <c r="N184" t="n">
         <v>1240.1</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="P184" t="n">
-        <v>6330.3</v>
+        <v>6266.7</v>
       </c>
       <c r="Q184" t="n">
-        <v>23.1</v>
+        <v>21.8</v>
       </c>
       <c r="R184" t="n">
         <v>6330.3</v>
       </c>
       <c r="S184" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T184" t="n">
-        <v>6940.1</v>
+        <v>6826.7</v>
       </c>
       <c r="U184" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="V184" t="n">
         <v>6940.1</v>
       </c>
       <c r="W184" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="X184" t="n">
-        <v>7645.2</v>
+        <v>7376</v>
       </c>
       <c r="Y184" t="n">
-        <v>10.2</v>
+        <v>8</v>
       </c>
       <c r="Z184" t="n">
         <v>7645.2</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="AB184" t="n">
         <v>69700</v>
@@ -18486,70 +18486,70 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>826.7</v>
+        <v>815.9</v>
       </c>
       <c r="G185" t="n">
-        <v>-3.9</v>
+        <v>-5.2</v>
       </c>
       <c r="H185" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="I185" t="n">
         <v>826.7</v>
       </c>
       <c r="J185" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="K185" t="n">
-        <v>606.8</v>
+        <v>617.3</v>
       </c>
       <c r="L185" t="n">
-        <v>-26.6</v>
+        <v>-24.3</v>
       </c>
       <c r="M185" t="n">
-        <v>-13.5</v>
+        <v>-12</v>
       </c>
       <c r="N185" t="n">
         <v>606.8</v>
       </c>
       <c r="O185" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P185" t="n">
-        <v>3035.4</v>
+        <v>3034.2</v>
       </c>
       <c r="Q185" t="n">
-        <v>-5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="R185" t="n">
         <v>3035.4</v>
       </c>
       <c r="S185" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T185" t="n">
-        <v>3365.3</v>
+        <v>3330.7</v>
       </c>
       <c r="U185" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V185" t="n">
         <v>3365.3</v>
       </c>
       <c r="W185" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X185" t="n">
-        <v>2642.8</v>
+        <v>2582.5</v>
       </c>
       <c r="Y185" t="n">
-        <v>-21.5</v>
+        <v>-22.5</v>
       </c>
       <c r="Z185" t="n">
         <v>2642.8</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="AB185" t="n">
         <v>43450</v>
@@ -21207,10 +21207,10 @@
         <v>-3.2</v>
       </c>
       <c r="P212" t="n">
-        <v>24577.9</v>
+        <v>24562</v>
       </c>
       <c r="Q212" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="R212" t="n">
         <v>24521.1</v>
@@ -21219,28 +21219,28 @@
         <v>0.2</v>
       </c>
       <c r="T212" t="n">
-        <v>28826.5</v>
+        <v>28728.2</v>
       </c>
       <c r="U212" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="V212" t="n">
         <v>28668.1</v>
       </c>
       <c r="W212" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="X212" t="n">
-        <v>31334.8</v>
+        <v>31258.1</v>
       </c>
       <c r="Y212" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z212" t="n">
         <v>30906.4</v>
       </c>
       <c r="AA212" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AB212" t="n">
         <v>1460000</v>
@@ -21279,19 +21279,19 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="G213" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="H213" t="n">
-        <v>26.1</v>
+        <v>22.3</v>
       </c>
       <c r="I213" t="n">
         <v>492</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.7</v>
+        <v>-6.5</v>
       </c>
       <c r="AB213" t="n">
         <v>27500</v>
@@ -21534,70 +21534,70 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>855.2</v>
+        <v>851.5</v>
       </c>
       <c r="G216" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="H216" t="n">
-        <v>590.2</v>
+        <v>587.2</v>
       </c>
       <c r="I216" t="n">
         <v>862.9</v>
       </c>
       <c r="J216" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="K216" t="n">
-        <v>952.8</v>
+        <v>954.2</v>
       </c>
       <c r="L216" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="M216" t="n">
-        <v>828.7</v>
+        <v>830</v>
       </c>
       <c r="N216" t="n">
         <v>965.4</v>
       </c>
       <c r="O216" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="P216" t="n">
-        <v>2573.1</v>
+        <v>2570.8</v>
       </c>
       <c r="Q216" t="n">
-        <v>2067.7</v>
+        <v>2065.8</v>
       </c>
       <c r="R216" t="n">
         <v>2593.4</v>
       </c>
       <c r="S216" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="T216" t="n">
-        <v>4368.5</v>
+        <v>4397.2</v>
       </c>
       <c r="U216" t="n">
-        <v>69.8</v>
+        <v>71</v>
       </c>
       <c r="V216" t="n">
         <v>4386.8</v>
       </c>
       <c r="W216" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="X216" t="n">
-        <v>5696.2</v>
+        <v>5728.2</v>
       </c>
       <c r="Y216" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="Z216" t="n">
         <v>5684</v>
       </c>
       <c r="AA216" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="AB216" t="n">
         <v>111400</v>
@@ -21840,70 +21840,70 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1672.4</v>
+        <v>1760.5</v>
       </c>
       <c r="G219" t="n">
-        <v>-42.1</v>
+        <v>-39.1</v>
       </c>
       <c r="H219" t="n">
-        <v>21.3</v>
+        <v>27.7</v>
       </c>
       <c r="I219" t="n">
         <v>1672.4</v>
       </c>
       <c r="J219" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="K219" t="n">
-        <v>1605</v>
+        <v>1673.3</v>
       </c>
       <c r="L219" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="M219" t="n">
-        <v>8.199999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="N219" t="n">
         <v>1605</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P219" t="n">
-        <v>8312.5</v>
+        <v>8434.200000000001</v>
       </c>
       <c r="Q219" t="n">
-        <v>21.2</v>
+        <v>22.9</v>
       </c>
       <c r="R219" t="n">
         <v>8312.5</v>
       </c>
       <c r="S219" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T219" t="n">
-        <v>8512.700000000001</v>
+        <v>8459.6</v>
       </c>
       <c r="U219" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="V219" t="n">
         <v>8512.700000000001</v>
       </c>
       <c r="W219" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="X219" t="n">
-        <v>9544.5</v>
+        <v>9649.6</v>
       </c>
       <c r="Y219" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="Z219" t="n">
         <v>9544.5</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB219" t="n">
         <v>49000</v>
@@ -23068,64 +23068,64 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>1542.6</v>
+        <v>1540.5</v>
       </c>
       <c r="G231" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="H231" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="I231" t="n">
         <v>1548.1</v>
       </c>
       <c r="J231" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="K231" t="n">
-        <v>1840.6</v>
+        <v>1838.8</v>
       </c>
       <c r="L231" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="M231" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N231" t="n">
         <v>1839.4</v>
       </c>
       <c r="O231" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="P231" t="n">
-        <v>6365.1</v>
+        <v>6361.1</v>
       </c>
       <c r="Q231" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="R231" t="n">
         <v>6372.8</v>
       </c>
       <c r="S231" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="T231" t="n">
-        <v>6910.3</v>
+        <v>6895.9</v>
       </c>
       <c r="U231" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="V231" t="n">
         <v>6937.7</v>
       </c>
       <c r="W231" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="X231" t="n">
         <v>7433</v>
       </c>
       <c r="Y231" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z231" t="n">
         <v>7503.3</v>
@@ -23503,7 +23503,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>863.1</v>
+        <v>863.3</v>
       </c>
       <c r="G236" t="n">
         <v>33.4</v>
@@ -23518,10 +23518,10 @@
         <v>-0.2</v>
       </c>
       <c r="K236" t="n">
-        <v>281.1</v>
+        <v>281</v>
       </c>
       <c r="L236" t="n">
-        <v>-67.40000000000001</v>
+        <v>-67.5</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>0.2</v>
       </c>
       <c r="P236" t="n">
-        <v>2149.1</v>
+        <v>2149.2</v>
       </c>
       <c r="Q236" t="n">
         <v>96.2</v>
@@ -23547,22 +23547,22 @@
         <v>0</v>
       </c>
       <c r="T236" t="n">
-        <v>2410.9</v>
+        <v>2408.5</v>
       </c>
       <c r="U236" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="V236" t="n">
         <v>2409.4</v>
       </c>
       <c r="W236" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="X236" t="n">
         <v>2673.3</v>
       </c>
       <c r="Y236" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="Z236" t="n">
         <v>2667.2</v>
@@ -24403,10 +24403,10 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>237.2</v>
+        <v>229.3</v>
       </c>
       <c r="G245" t="n">
-        <v>-32.1</v>
+        <v>-34.4</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -24417,52 +24417,52 @@
         <v>232.7</v>
       </c>
       <c r="J245" t="n">
-        <v>1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="K245" t="n">
-        <v>302</v>
+        <v>293.3</v>
       </c>
       <c r="L245" t="n">
-        <v>27.3</v>
+        <v>27.9</v>
       </c>
       <c r="M245" t="n">
-        <v>264.7</v>
+        <v>254.2</v>
       </c>
       <c r="N245" t="n">
         <v>285</v>
       </c>
       <c r="O245" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="P245" t="n">
-        <v>1130.4</v>
+        <v>1113.7</v>
       </c>
       <c r="Q245" t="n">
-        <v>127.9</v>
+        <v>124.5</v>
       </c>
       <c r="R245" t="n">
         <v>1098.8</v>
       </c>
       <c r="S245" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="T245" t="n">
-        <v>1374.2</v>
+        <v>1325.2</v>
       </c>
       <c r="U245" t="n">
-        <v>21.6</v>
+        <v>19</v>
       </c>
       <c r="V245" t="n">
         <v>1316.8</v>
       </c>
       <c r="W245" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="X245" t="n">
         <v>1468.2</v>
       </c>
       <c r="Y245" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="Z245" t="n">
         <v>1468.2</v>
@@ -24815,70 +24815,70 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>551.5</v>
+        <v>553.2</v>
       </c>
       <c r="G249" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="H249" t="n">
-        <v>135.7</v>
+        <v>136.4</v>
       </c>
       <c r="I249" t="n">
         <v>536.8</v>
       </c>
       <c r="J249" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="K249" t="n">
-        <v>424.5</v>
+        <v>437.6</v>
       </c>
       <c r="L249" t="n">
-        <v>-23</v>
+        <v>-20.9</v>
       </c>
       <c r="M249" t="n">
-        <v>93.8</v>
+        <v>99.8</v>
       </c>
       <c r="N249" t="n">
         <v>403.5</v>
       </c>
       <c r="O249" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="P249" t="n">
-        <v>1951</v>
+        <v>1966.8</v>
       </c>
       <c r="Q249" t="n">
-        <v>120.5</v>
+        <v>122.3</v>
       </c>
       <c r="R249" t="n">
         <v>1915</v>
       </c>
       <c r="S249" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="T249" t="n">
-        <v>2384</v>
+        <v>2393.2</v>
       </c>
       <c r="U249" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="V249" t="n">
         <v>2353.2</v>
       </c>
       <c r="W249" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="X249" t="n">
-        <v>2465.8</v>
+        <v>2568.6</v>
       </c>
       <c r="Y249" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="Z249" t="n">
         <v>2443.2</v>
       </c>
       <c r="AA249" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="AB249" t="n">
         <v>115900</v>
@@ -25342,25 +25342,25 @@
         <v>0.5</v>
       </c>
       <c r="K254" t="n">
-        <v>800.4</v>
+        <v>800.8</v>
       </c>
       <c r="L254" t="n">
         <v>4.3</v>
       </c>
       <c r="M254" t="n">
-        <v>176.5</v>
+        <v>176.6</v>
       </c>
       <c r="N254" t="n">
         <v>794.6</v>
       </c>
       <c r="O254" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="P254" t="n">
-        <v>2783.5</v>
+        <v>2784</v>
       </c>
       <c r="Q254" t="n">
-        <v>467.4</v>
+        <v>467.5</v>
       </c>
       <c r="R254" t="n">
         <v>2775</v>
@@ -25369,28 +25369,28 @@
         <v>0.3</v>
       </c>
       <c r="T254" t="n">
-        <v>4150.5</v>
+        <v>4174.2</v>
       </c>
       <c r="U254" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="V254" t="n">
         <v>4106.6</v>
       </c>
       <c r="W254" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="X254" t="n">
-        <v>5164.4</v>
+        <v>5186.1</v>
       </c>
       <c r="Y254" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="Z254" t="n">
         <v>5127.8</v>
       </c>
       <c r="AA254" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="AB254" t="n">
         <v>122700</v>
@@ -26057,70 +26057,70 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>1310.8</v>
+        <v>1286.1</v>
       </c>
       <c r="G261" t="n">
-        <v>51.5</v>
+        <v>48.7</v>
       </c>
       <c r="H261" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="I261" t="n">
         <v>1335.8</v>
       </c>
       <c r="J261" t="n">
-        <v>-1.9</v>
+        <v>-3.7</v>
       </c>
       <c r="K261" t="n">
-        <v>1477.2</v>
+        <v>1468</v>
       </c>
       <c r="L261" t="n">
-        <v>12.7</v>
+        <v>14.1</v>
       </c>
       <c r="M261" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="N261" t="n">
         <v>1491</v>
       </c>
       <c r="O261" t="n">
-        <v>-0.9</v>
+        <v>-1.5</v>
       </c>
       <c r="P261" t="n">
-        <v>5205</v>
+        <v>5152.7</v>
       </c>
       <c r="Q261" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="R261" t="n">
         <v>5266.2</v>
       </c>
       <c r="S261" t="n">
-        <v>-1.2</v>
+        <v>-2.2</v>
       </c>
       <c r="T261" t="n">
-        <v>5622</v>
+        <v>5549.7</v>
       </c>
       <c r="U261" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="V261" t="n">
         <v>5678.2</v>
       </c>
       <c r="W261" t="n">
-        <v>-1</v>
+        <v>-2.3</v>
       </c>
       <c r="X261" t="n">
-        <v>6128.6</v>
+        <v>5988.3</v>
       </c>
       <c r="Y261" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="Z261" t="n">
         <v>6195.7</v>
       </c>
       <c r="AA261" t="n">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="AB261" t="n">
         <v>63100</v>
@@ -26781,10 +26781,10 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>433</v>
+        <v>326</v>
       </c>
       <c r="G270" t="n">
-        <v>0.1</v>
+        <v>-24.6</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -26795,58 +26795,58 @@
         <v>433</v>
       </c>
       <c r="J270" t="n">
-        <v>0</v>
+        <v>-24.7</v>
       </c>
       <c r="K270" t="n">
-        <v>392.5</v>
+        <v>285</v>
       </c>
       <c r="L270" t="n">
-        <v>-9.4</v>
+        <v>-12.6</v>
       </c>
       <c r="M270" t="n">
-        <v>1296.8</v>
+        <v>914.2</v>
       </c>
       <c r="N270" t="n">
         <v>392.5</v>
       </c>
       <c r="O270" t="n">
-        <v>0</v>
+        <v>-27.4</v>
       </c>
       <c r="P270" t="n">
-        <v>1440.7</v>
+        <v>1286</v>
       </c>
       <c r="Q270" t="n">
-        <v>32643.2</v>
+        <v>29127.3</v>
       </c>
       <c r="R270" t="n">
         <v>1536</v>
       </c>
       <c r="S270" t="n">
-        <v>-6.2</v>
+        <v>-16.3</v>
       </c>
       <c r="T270" t="n">
-        <v>1692.3</v>
+        <v>1478.5</v>
       </c>
       <c r="U270" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="V270" t="n">
         <v>1758.5</v>
       </c>
       <c r="W270" t="n">
-        <v>-3.8</v>
+        <v>-15.9</v>
       </c>
       <c r="X270" t="n">
-        <v>1726.7</v>
+        <v>1505</v>
       </c>
       <c r="Y270" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Z270" t="n">
         <v>1775</v>
       </c>
       <c r="AA270" t="n">
-        <v>-2.7</v>
+        <v>-15.2</v>
       </c>
       <c r="AB270" t="n">
         <v>59500</v>
@@ -27040,49 +27040,49 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>257.7</v>
+        <v>255.4</v>
       </c>
       <c r="G273" t="n">
-        <v>-8.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H273" t="n">
-        <v>-48</v>
+        <v>-48.5</v>
       </c>
       <c r="I273" t="n">
         <v>254</v>
       </c>
       <c r="J273" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="K273" t="n">
-        <v>307.6</v>
+        <v>306.4</v>
       </c>
       <c r="L273" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="M273" t="n">
-        <v>-17.8</v>
+        <v>-18.1</v>
       </c>
       <c r="N273" t="n">
         <v>310.7</v>
       </c>
       <c r="O273" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="P273" t="n">
-        <v>1064.9</v>
+        <v>1061.6</v>
       </c>
       <c r="Q273" t="n">
-        <v>-41.3</v>
+        <v>-41.5</v>
       </c>
       <c r="R273" t="n">
         <v>1064.2</v>
       </c>
       <c r="S273" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="T273" t="n">
-        <v>989.8</v>
+        <v>986.4</v>
       </c>
       <c r="U273" t="n">
         <v>-7.1</v>
@@ -27091,13 +27091,13 @@
         <v>995.7</v>
       </c>
       <c r="W273" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="X273" t="n">
         <v>1873.4</v>
       </c>
       <c r="Y273" t="n">
-        <v>89.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Z273" t="n">
         <v>2003.7</v>
